--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="126">
   <si>
     <r>
       <t>描述</t>
@@ -660,6 +660,14 @@
   </si>
   <si>
     <t>特性编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-61 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-40 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -990,28 +998,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -1030,48 +1017,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2540,7 +2485,9 @@
         <v>102</v>
       </c>
       <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
+      <c r="D44" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="E44" s="2" t="s">
         <v>46</v>
       </c>
@@ -2598,7 +2545,9 @@
         <v>95</v>
       </c>
       <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
+      <c r="D46" s="8" t="s">
+        <v>125</v>
+      </c>
       <c r="E46" s="8" t="s">
         <v>89</v>
       </c>
@@ -3278,16 +3227,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L200">
-    <cfRule type="expression" dxfId="6" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="129">
   <si>
     <r>
       <t>描述</t>
@@ -527,18 +527,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sdb工具中的createRG/getRG/startRG等所有RG相关的接口隐藏，并添加相应的Shard接口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>mth match优化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>mth</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -547,37 +539,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>离线全量同步</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新增加的catalog信息如何刷到配置文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>路径支持通佩符（%H,%S,%G…）
---暂时只适用于备份路径</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Coord需要针对“通讯失败”、“无主节点”、“全量同步”、“离线备份”、“故障无应答”、“节点数不足”等错误抽象出一套重试机制和流程
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>PMD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdbdpsdump工具和sdbinspt工具加强，合入发版本发布包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>清除所有节点的缓存信息(db.invalid)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>驱动中增加Interrupt和isConnect接口</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -668,6 +635,59 @@
   </si>
   <si>
     <t xml:space="preserve">SEQUOIADBMAINSTREAM-40 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谭钊波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-80 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">驱动中增加Interrupt和isConnect接口
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">清除所有节点的缓存信息(db.invalid)
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">新增加的catalog信息如何刷到配置文件
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">离线全量同步
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">mth match优化
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">sdb工具中的createRG/getRG/startRG等所有RG相关的接口隐藏，并添加相应的Shard接口
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">sdbdpsdump工具和sdbinspt工具加强，合入发版本发布包
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">路径支持通佩符（%H,%S,%G…）
+--暂时只适用于备份路径
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-29 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -897,7 +917,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -993,6 +1013,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1345,10 +1368,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -1404,7 +1427,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -2061,7 +2084,9 @@
         <v>61</v>
       </c>
       <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
+      <c r="D28" s="28" t="s">
+        <v>128</v>
+      </c>
       <c r="E28" s="29" t="s">
         <v>56</v>
       </c>
@@ -2477,16 +2502,16 @@
       <c r="K43" s="2"/>
       <c r="L43" s="3"/>
     </row>
-    <row r="44" spans="1:12" ht="27">
+    <row r="44" spans="1:12" ht="40.5">
       <c r="A44" s="1">
         <v>46</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>46</v>
@@ -2513,12 +2538,12 @@
         <v>41679</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="27">
+    <row r="45" spans="1:12" ht="40.5">
       <c r="A45" s="1">
         <v>48</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
@@ -2537,16 +2562,16 @@
       <c r="K45" s="2"/>
       <c r="L45" s="3"/>
     </row>
-    <row r="46" spans="1:12" ht="27">
+    <row r="46" spans="1:12" ht="40.5">
       <c r="A46" s="13">
         <v>51</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>89</v>
@@ -2569,12 +2594,12 @@
       <c r="K46" s="8"/>
       <c r="L46" s="14"/>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:12" ht="27">
       <c r="A47" s="13">
         <v>52</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
@@ -2585,7 +2610,7 @@
         <v>12</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H47" s="8">
         <v>2</v>
@@ -2595,12 +2620,12 @@
       <c r="K47" s="8"/>
       <c r="L47" s="14"/>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" ht="27">
       <c r="A48" s="13">
         <v>53</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
@@ -2619,12 +2644,12 @@
       <c r="K48" s="8"/>
       <c r="L48" s="14"/>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" ht="27">
       <c r="A49" s="13">
         <v>54</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
@@ -2635,7 +2660,7 @@
         <v>24</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
@@ -2643,12 +2668,12 @@
       <c r="K49" s="8"/>
       <c r="L49" s="14"/>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" ht="27">
       <c r="A50" s="13">
         <v>56</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
@@ -2665,15 +2690,17 @@
       <c r="K50" s="8"/>
       <c r="L50" s="14"/>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" ht="27">
       <c r="A51" s="13">
         <v>57</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
+      <c r="D51" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="E51" s="8" t="s">
         <v>76</v>
       </c>
@@ -2682,9 +2709,15 @@
       </c>
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
+      <c r="I51" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="K51" s="32">
+        <v>41688</v>
+      </c>
       <c r="L51" s="14"/>
     </row>
     <row r="52" spans="1:12">
@@ -3283,10 +3316,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -3318,11 +3351,11 @@
         <v>55</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>89</v>
@@ -3354,11 +3387,11 @@
         <v>49</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>76</v>
@@ -3390,11 +3423,11 @@
         <v>50</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="10" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>74</v>
@@ -3409,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>93</v>
@@ -3426,11 +3459,11 @@
         <v>47</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="26" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>89</v>
@@ -3451,10 +3484,10 @@
         <v>93</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="40.5">
@@ -3462,11 +3495,11 @@
         <v>42</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="12" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>76</v>
@@ -3481,7 +3514,7 @@
         <v>4</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>93</v>
@@ -3502,7 +3535,7 @@
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>14</v>
@@ -3538,7 +3571,7 @@
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>11</v>
@@ -3553,7 +3586,7 @@
         <v>4</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>93</v>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$L$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$L$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">已完成任务!$A$1:$L$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="130">
   <si>
     <r>
       <t>描述</t>
@@ -646,11 +646,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">驱动中增加Interrupt和isConnect接口
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">清除所有节点的缓存信息(db.invalid)
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -688,6 +683,14 @@
   </si>
   <si>
     <t xml:space="preserve">SEQUOIADBMAINSTREAM-29 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CANCEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">驱动中增加closeAllCursor和isClosed接口
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1021,7 +1024,63 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1343,7 +1402,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -2084,9 +2143,7 @@
         <v>61</v>
       </c>
       <c r="C28" s="28"/>
-      <c r="D28" s="28" t="s">
-        <v>128</v>
-      </c>
+      <c r="D28" s="28"/>
       <c r="E28" s="29" t="s">
         <v>56</v>
       </c>
@@ -2116,7 +2173,9 @@
         <v>63</v>
       </c>
       <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
+      <c r="D29" s="28" t="s">
+        <v>127</v>
+      </c>
       <c r="E29" s="29" t="s">
         <v>56</v>
       </c>
@@ -2507,7 +2566,7 @@
         <v>46</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8" t="s">
@@ -2543,7 +2602,7 @@
         <v>48</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
@@ -2562,59 +2621,51 @@
       <c r="K45" s="2"/>
       <c r="L45" s="3"/>
     </row>
-    <row r="46" spans="1:12" ht="40.5">
+    <row r="46" spans="1:12" ht="27">
       <c r="A46" s="13">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C46" s="8"/>
-      <c r="D46" s="8" t="s">
-        <v>117</v>
-      </c>
+      <c r="D46" s="8"/>
       <c r="E46" s="8" t="s">
         <v>89</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="H46" s="8">
-        <v>1</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>66</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
       <c r="K46" s="8"/>
       <c r="L46" s="14"/>
     </row>
     <row r="47" spans="1:12" ht="27">
       <c r="A47" s="13">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>12</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="H47" s="8">
-        <v>2</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H47" s="8"/>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
       <c r="K47" s="8"/>
@@ -2622,21 +2673,21 @@
     </row>
     <row r="48" spans="1:12" ht="27">
       <c r="A48" s="13">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="8" t="s">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
@@ -2646,22 +2697,20 @@
     </row>
     <row r="49" spans="1:12" ht="27">
       <c r="A49" s="13">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G49" s="8" t="s">
-        <v>99</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
@@ -2670,13 +2719,15 @@
     </row>
     <row r="50" spans="1:12" ht="27">
       <c r="A50" s="13">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
+      <c r="D50" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="E50" s="8" t="s">
         <v>76</v>
       </c>
@@ -2685,39 +2736,29 @@
       </c>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
-      <c r="I50" s="8"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="8"/>
+      <c r="I50" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="K50" s="32">
+        <v>41688</v>
+      </c>
       <c r="L50" s="14"/>
     </row>
-    <row r="51" spans="1:12" ht="27">
-      <c r="A51" s="13">
-        <v>57</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>120</v>
-      </c>
+    <row r="51" spans="1:12">
+      <c r="A51" s="13"/>
+      <c r="B51" s="8"/>
       <c r="C51" s="8"/>
-      <c r="D51" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>12</v>
-      </c>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
-      <c r="I51" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="J51" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="K51" s="32">
-        <v>41688</v>
-      </c>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
       <c r="L51" s="14"/>
     </row>
     <row r="52" spans="1:12">
@@ -3224,63 +3265,49 @@
       <c r="K87" s="8"/>
       <c r="L87" s="14"/>
     </row>
-    <row r="88" spans="1:12">
-      <c r="A88" s="13"/>
-      <c r="B88" s="8"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="8"/>
-      <c r="G88" s="8"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="8"/>
-      <c r="J88" s="8"/>
-      <c r="K88" s="8"/>
-      <c r="L88" s="14"/>
-    </row>
-    <row r="89" spans="1:12" ht="14.25" thickBot="1">
-      <c r="A89" s="15"/>
-      <c r="B89" s="16"/>
-      <c r="C89" s="16"/>
-      <c r="D89" s="16"/>
-      <c r="E89" s="16"/>
-      <c r="F89" s="16"/>
-      <c r="G89" s="16"/>
-      <c r="H89" s="16"/>
-      <c r="I89" s="16"/>
-      <c r="J89" s="16"/>
-      <c r="K89" s="16"/>
-      <c r="L89" s="17"/>
+    <row r="88" spans="1:12" ht="14.25" thickBot="1">
+      <c r="A88" s="15"/>
+      <c r="B88" s="16"/>
+      <c r="C88" s="16"/>
+      <c r="D88" s="16"/>
+      <c r="E88" s="16"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="16"/>
+      <c r="H88" s="16"/>
+      <c r="I88" s="16"/>
+      <c r="J88" s="16"/>
+      <c r="K88" s="16"/>
+      <c r="L88" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L49">
+  <autoFilter ref="A1:L50">
     <filterColumn colId="2"/>
     <filterColumn colId="3"/>
     <filterColumn colId="5"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:L200">
-    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
-      <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
+  <conditionalFormatting sqref="A2:L199">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+      <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+      <formula>$J2="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
-      <formula>$J2="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
-      <formula>$J2="HANG-UP"</formula>
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+      <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E89">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E88">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F89">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F88">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J89">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J88">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3598,19 +3625,37 @@
         <v>41683</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="1"/>
-      <c r="B9" s="8"/>
+    <row r="9" spans="1:12" ht="40.5">
+      <c r="A9" s="13">
+        <v>51</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="3"/>
+      <c r="D9" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="14"/>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1"/>
@@ -4528,6 +4573,20 @@
     <filterColumn colId="3"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A9:L9">
+    <cfRule type="expression" dxfId="8" priority="1" stopIfTrue="1">
+      <formula>$J9="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="2" stopIfTrue="1">
+      <formula>$J9="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="3" stopIfTrue="1">
+      <formula>$J9="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="4" stopIfTrue="1">
+      <formula>OR($J9="CLOSED",$J9="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J74">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -4,23 +4,23 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="11010"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="11010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="2014年1季度" sheetId="1" r:id="rId1"/>
-    <sheet name="已完成任务" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="2014年2季度" sheetId="3" r:id="rId2"/>
+    <sheet name="已完成任务" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$L$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">已完成任务!$A$1:$L$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$L$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已完成任务!$A$1:$L$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="141">
   <si>
     <r>
       <t>描述</t>
@@ -180,11 +180,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">节点启动时，服务端口被临时端口占用，导致启动失败
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>低</t>
   </si>
   <si>
@@ -197,325 +192,306 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">主备节点数据同步时，但主节点过快备跟不上，需要根据配置“流程主”节点，以防止全量同步发生
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REPL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">全系统断电，系统能自动恢复，数据能自动恢复
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>DATA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">数据同步大压力时，会出现节点间sharing-break
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">批量Insert过程中，Split完成，导致数据Insert到错误的节点
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHARD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">索引排序、非索引排序针对数组时，需要把数组相同的内容放在一起，以保证聚集的正确性
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">按索引分布并发查询时，不能对数组类型字段的索引进行记录踢重
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">并发创建CS会出现文件已存在错误，某些会话失败，如果是并发insert时根据Catalog创建的，则会出现insert失败；同样，删除CS也存在并发问题
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">事务机制的死锁检测
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRANS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebuild DB性能优化（依赖Rebuild Index）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>性能</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebuild Index性能优化
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">数组踢重优化
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">索引压缩（相同key保存一份）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">驱动性能优化
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRIVER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove({})优化
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">DMS over flow优化
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>易用性</t>
+  </si>
+  <si>
+    <t>SDB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Sdb/Web集成详细的帮助信息
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">自动化部署
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Coord启动机制
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">完善管理界面易用性和管控功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提升文档质量（正确性、全面性）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DOC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">动态参数修改和查看
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可维护性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS load/unload/load all/unload all
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RTN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">查询进行Memory总量，以及Dump内存信息
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OSS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">数据收集工具（自动收集log/core）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOOLS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">性能监控工具
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阮亦邦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡晓军</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>何嘉文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Snapshot和list命令完善，能灵活查看系统状态
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Coord节点的监控
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">管理界面增加错误告警（节点故障，重启，操作失败等）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">手动降备命令
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可测试性</t>
+  </si>
+  <si>
+    <t>功能</t>
+  </si>
+  <si>
+    <t>CATA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">创建CS可指定域和组
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">创建CL可指定组
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Alter collection修改collection属性
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Collection增加查询模式，可指定查询是通过主还是备的方式（依赖 可以向指定主、备节点查询）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">增加OM管理服务（集“策略”，“信息采集”，“告警”等模块）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">模块解耦合
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLATFORM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLATFORM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Insert/Update/Delete等所有外部操作都可以返回详细信息（包含访问计划，详细错误描述）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>PMD</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">主备节点数据同步时，但主节点过快备跟不上，需要根据配置“流程主”节点，以防止全量同步发生
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>REPL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">全系统断电，系统能自动恢复，数据能自动恢复
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高</t>
-  </si>
-  <si>
-    <t>DATA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">数据同步大压力时，会出现节点间sharing-break
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">批量Insert过程中，Split完成，导致数据Insert到错误的节点
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHARD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">索引排序、非索引排序针对数组时，需要把数组相同的内容放在一起，以保证聚集的正确性
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DMS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">按索引分布并发查询时，不能对数组类型字段的索引进行记录踢重
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DMS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">并发创建CS会出现文件已存在错误，某些会话失败，如果是并发insert时根据Catalog创建的，则会出现insert失败；同样，删除CS也存在并发问题
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">事务机制的死锁检测
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TRANS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebuild DB性能优化（依赖Rebuild Index）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>性能</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebuild Index性能优化
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DMS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">数组踢重优化
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">索引压缩（相同key保存一份）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">驱动性能优化
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DRIVER</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Remove({})优化
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">DMS over flow优化
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>易用性</t>
+    <t>优化</t>
+  </si>
+  <si>
+    <t>IXM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>SDB</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Sdb/Web集成详细的帮助信息
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">自动化部署
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Coord启动机制
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">完善管理界面易用性和管控功能
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">提升文档质量（正确性、全面性）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DOC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">动态参数修改和查看
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可维护性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS load/unload/load all/unload all
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RTN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">查询进行Memory总量，以及Dump内存信息
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OSS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">数据收集工具（自动收集log/core）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TOOLS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">性能监控工具
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阮亦邦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>胡晓军</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>何嘉文</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Snapshot和list命令完善，能灵活查看系统状态
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Coord节点的监控
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">管理界面增加错误告警（节点故障，重启，操作失败等）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Force EDU/Interrupt EDU命令，停止或中断EDU操作
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">手动降备命令
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可测试性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">创建\删除域，域中增加、删除组
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>功能</t>
-  </si>
-  <si>
-    <t>CATA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">创建CS可指定域和组
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">创建CL可指定组
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Alter collection修改collection属性
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Collection增加查询模式，可指定查询是通过主还是备的方式（依赖 可以向指定主、备节点查询）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Truncate collection
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">增加OM管理服务（集“策略”，“信息采集”，“告警”等模块）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">模块解耦合
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PLATFORM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PLATFORM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Insert/Update/Delete等所有外部操作都可以返回详细信息（包含访问计划，详细错误描述）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PMD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>优化</t>
-  </si>
-  <si>
-    <t>IXM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SDB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>许建辉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -528,10 +504,6 @@
   </si>
   <si>
     <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mth</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -661,11 +633,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">mth match优化
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">sdb工具中的createRG/getRG/startRG等所有RG相关的接口隐藏，并添加相应的Shard接口
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -690,6 +657,95 @@
   </si>
   <si>
     <t xml:space="preserve">驱动中增加closeAllCursor和isClosed接口
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">诊断日志分文件存储，按时间归档，按个数清除
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">增加流程跟踪动态日志，只在出错时打印
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">日志关联：Data/Catalog/Coord等节点的日志能够通过会话的操作ID进行关联
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">日志拉取：能够在SDB客户端远程拉取会话最后操作的关联日志
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">监控信息按会话关联，对外展现为关联信息
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">抽象出统一的监控框架，按级别精细化Watch点的监控和输出
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">支持动态开/关Watch点
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">能够返回操作的具体节点的错误信息
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">能够返回操作的具体节点的统计信息
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Truncate collection功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">PMD启动重构，启动分两个阶段，第一阶段Init，用于建立端口，初始化资源；第二阶段启动定时器，开始业务
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Interrupt/Disconnect EDU命令，中断EDU操作
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">创建删除Domain，Domain中增加删除RG
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">mth match、ixm优化和去mongo影子
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内置SQL dirty join</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ShardingKey需要加上0,1…的Field信息以方便外部显示
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">定时刷mmap保持性能平稳
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">加载文件由于元数据损坏的文件如何rebuild
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1024,7 +1080,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="56">
     <dxf>
       <fill>
         <patternFill>
@@ -1084,7 +1140,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF0070C0"/>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1098,6 +1161,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -1105,7 +1182,294 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1402,7 +1766,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -1427,10 +1791,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -1486,7 +1850,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -1535,89 +1899,89 @@
     </row>
     <row r="5" spans="1:12" ht="40.5">
       <c r="A5" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="H5" s="2">
+        <v>4</v>
+      </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="3"/>
     </row>
     <row r="6" spans="1:12" ht="40.5">
-      <c r="A6" s="1">
-        <v>7</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="A6" s="27">
+        <v>8</v>
+      </c>
+      <c r="B6" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="29">
+        <v>1</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" s="30">
+        <v>41679</v>
+      </c>
+      <c r="L6" s="31"/>
+    </row>
+    <row r="7" spans="1:12" ht="40.5">
+      <c r="A7" s="1">
+        <v>9</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="2">
-        <v>4</v>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" ht="40.5">
-      <c r="A7" s="27">
-        <v>8</v>
-      </c>
-      <c r="B7" s="28" t="s">
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="29">
-        <v>1</v>
-      </c>
-      <c r="I7" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="J7" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="K7" s="30">
-        <v>41679</v>
-      </c>
-      <c r="L7" s="31"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:12" ht="40.5">
       <c r="A8" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>27</v>
@@ -1625,15 +1989,17 @@
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="H8" s="2">
+        <v>3</v>
+      </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -1641,7 +2007,7 @@
     </row>
     <row r="9" spans="1:12" ht="40.5">
       <c r="A9" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>29</v>
@@ -1649,25 +2015,23 @@
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="2">
-        <v>3</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="1:12" ht="40.5">
+    <row r="10" spans="1:12" ht="67.5">
       <c r="A10" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>31</v>
@@ -1678,10 +2042,10 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -1689,25 +2053,27 @@
       <c r="K10" s="2"/>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="1:12" ht="67.5">
+    <row r="11" spans="1:12" ht="27">
       <c r="A11" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="H11" s="2">
+        <v>15</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -1715,7 +2081,7 @@
     </row>
     <row r="12" spans="1:12" ht="27">
       <c r="A12" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>34</v>
@@ -1723,16 +2089,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="2" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -1741,7 +2107,7 @@
     </row>
     <row r="13" spans="1:12" ht="27">
       <c r="A13" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>36</v>
@@ -1749,16 +2115,16 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -1767,7 +2133,7 @@
     </row>
     <row r="14" spans="1:12" ht="27">
       <c r="A14" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>38</v>
@@ -1775,17 +2141,15 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="2">
-        <v>8</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -1793,23 +2157,25 @@
     </row>
     <row r="15" spans="1:12" ht="27">
       <c r="A15" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H15" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="H15" s="2">
+        <v>5</v>
+      </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -1817,33 +2183,37 @@
     </row>
     <row r="16" spans="1:12" ht="27">
       <c r="A16" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="H16" s="2">
-        <v>5</v>
-      </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="K16" s="2"/>
       <c r="L16" s="3"/>
     </row>
     <row r="17" spans="1:12" ht="27">
       <c r="A17" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>42</v>
@@ -1851,43 +2221,39 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="H17" s="2">
-        <v>13</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>66</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="1:12" ht="27">
       <c r="A18" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H18" s="2">
         <v>4</v>
@@ -1899,24 +2265,24 @@
     </row>
     <row r="19" spans="1:12" ht="27">
       <c r="A19" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H19" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -1924,81 +2290,81 @@
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="1:12" ht="27">
-      <c r="A20" s="1">
-        <v>21</v>
-      </c>
-      <c r="B20" s="8" t="s">
+      <c r="A20" s="27">
+        <v>22</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H20" s="2">
-        <v>15</v>
-      </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="3"/>
+      <c r="H20" s="29">
+        <v>8</v>
+      </c>
+      <c r="I20" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="J20" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="K20" s="29"/>
+      <c r="L20" s="31"/>
     </row>
     <row r="21" spans="1:12" ht="27">
-      <c r="A21" s="27">
-        <v>22</v>
-      </c>
-      <c r="B21" s="28" t="s">
+      <c r="A21" s="1">
+        <v>23</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="G21" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="H21" s="29">
-        <v>8</v>
-      </c>
-      <c r="I21" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="J21" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="K21" s="29"/>
-      <c r="L21" s="31"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H21" s="2">
+        <v>5</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="3"/>
     </row>
     <row r="22" spans="1:12" ht="27">
       <c r="A22" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H22" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
@@ -2007,24 +2373,24 @@
     </row>
     <row r="23" spans="1:12" ht="27">
       <c r="A23" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H23" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -2033,7 +2399,7 @@
     </row>
     <row r="24" spans="1:12" ht="27">
       <c r="A24" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>53</v>
@@ -2041,16 +2407,16 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="H24" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
@@ -2059,7 +2425,7 @@
     </row>
     <row r="25" spans="1:12" ht="27">
       <c r="A25" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>55</v>
@@ -2067,13 +2433,13 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="H25" s="2">
         <v>4</v>
@@ -2085,7 +2451,7 @@
     </row>
     <row r="26" spans="1:12" ht="27">
       <c r="A26" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>57</v>
@@ -2093,7 +2459,7 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>12</v>
@@ -2102,7 +2468,7 @@
         <v>58</v>
       </c>
       <c r="H26" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
@@ -2110,122 +2476,122 @@
       <c r="L26" s="3"/>
     </row>
     <row r="27" spans="1:12" ht="27">
-      <c r="A27" s="1">
-        <v>28</v>
-      </c>
-      <c r="B27" s="8" t="s">
+      <c r="A27" s="27">
+        <v>29</v>
+      </c>
+      <c r="B27" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="H27" s="2">
-        <v>8</v>
-      </c>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="3"/>
+      <c r="H27" s="29">
+        <v>20</v>
+      </c>
+      <c r="I27" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="J27" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="K27" s="29"/>
+      <c r="L27" s="31"/>
     </row>
     <row r="28" spans="1:12" ht="27">
       <c r="A28" s="27">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28" s="28" t="s">
         <v>61</v>
       </c>
       <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
+      <c r="D28" s="28" t="s">
+        <v>120</v>
+      </c>
       <c r="E28" s="29" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F28" s="29" t="s">
         <v>12</v>
       </c>
       <c r="G28" s="29" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H28" s="29">
         <v>20</v>
       </c>
       <c r="I28" s="29" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="J28" s="29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K28" s="29"/>
       <c r="L28" s="31"/>
     </row>
-    <row r="29" spans="1:12" ht="27">
-      <c r="A29" s="27">
-        <v>30</v>
-      </c>
-      <c r="B29" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="E29" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="F29" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="H29" s="29">
-        <v>20</v>
-      </c>
-      <c r="I29" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="J29" s="29" t="s">
+    <row r="29" spans="1:12" ht="40.5">
+      <c r="A29" s="1">
+        <v>31</v>
+      </c>
+      <c r="B29" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="K29" s="29"/>
-      <c r="L29" s="31"/>
-    </row>
-    <row r="30" spans="1:12" ht="40.5">
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H29" s="2">
+        <v>8</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="1:12" ht="27">
       <c r="A30" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="H30" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="3"/>
     </row>
-    <row r="31" spans="1:12" ht="27">
+    <row r="31" spans="1:12" ht="40.5">
       <c r="A31" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>69</v>
@@ -2233,39 +2599,39 @@
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H31" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" s="3"/>
     </row>
-    <row r="32" spans="1:12" ht="40.5">
+    <row r="32" spans="1:12" ht="54">
       <c r="A32" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H32" s="2">
         <v>8</v>
@@ -2275,78 +2641,78 @@
       <c r="K32" s="2"/>
       <c r="L32" s="3"/>
     </row>
-    <row r="33" spans="1:12" ht="54">
+    <row r="33" spans="1:12" ht="27">
       <c r="A33" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="H33" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="3"/>
     </row>
-    <row r="34" spans="1:12" ht="40.5">
+    <row r="34" spans="1:12" ht="54">
       <c r="A34" s="1">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="2" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H34" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
+      <c r="K34" s="21"/>
       <c r="L34" s="3"/>
     </row>
-    <row r="35" spans="1:12" ht="27">
+    <row r="35" spans="1:12" ht="40.5">
       <c r="A35" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
       <c r="E35" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="H35" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
@@ -2355,361 +2721,273 @@
     </row>
     <row r="36" spans="1:12" ht="27">
       <c r="A36" s="1">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H36" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
       <c r="L36" s="3"/>
     </row>
-    <row r="37" spans="1:12" ht="27">
+    <row r="37" spans="1:12" ht="40.5">
       <c r="A37" s="1">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
+      <c r="D37" s="8" t="s">
+        <v>110</v>
+      </c>
       <c r="E37" s="2" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H37" s="2">
         <v>3</v>
       </c>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="3"/>
-    </row>
-    <row r="38" spans="1:12" ht="27">
+      <c r="I37" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K37" s="21">
+        <v>41679</v>
+      </c>
+      <c r="L37" s="22">
+        <v>41679</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="40.5">
       <c r="A38" s="1">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
       <c r="E38" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H38" s="2">
-        <v>3</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="3"/>
     </row>
     <row r="39" spans="1:12" ht="27">
-      <c r="A39" s="1">
-        <v>40</v>
+      <c r="A39" s="13">
+        <v>53</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
-      <c r="E39" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H39" s="2">
-        <v>4</v>
-      </c>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="1:12" ht="54">
-      <c r="A40" s="1">
-        <v>41</v>
+      <c r="E39" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="14"/>
+    </row>
+    <row r="40" spans="1:12" ht="27">
+      <c r="A40" s="13">
+        <v>54</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
-      <c r="E40" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F40" s="2" t="s">
+      <c r="E40" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="14"/>
+    </row>
+    <row r="41" spans="1:12" ht="27">
+      <c r="A41" s="13">
+        <v>57</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F41" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H40" s="2">
-        <v>2</v>
-      </c>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="1:12" ht="27">
-      <c r="A41" s="1">
-        <v>43</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H41" s="2">
-        <v>3</v>
-      </c>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="1:12" ht="40.5">
-      <c r="A42" s="1">
-        <v>44</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>83</v>
-      </c>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K41" s="32">
+        <v>41688</v>
+      </c>
+      <c r="L41" s="14"/>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="13"/>
+      <c r="B42" s="8"/>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
-      <c r="E42" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H42" s="2">
-        <v>15</v>
-      </c>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="1:12" ht="27">
-      <c r="A43" s="1">
-        <v>45</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>84</v>
-      </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="14"/>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="13"/>
+      <c r="B43" s="8"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
-      <c r="E43" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H43" s="2">
-        <v>15</v>
-      </c>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="1:12" ht="40.5">
-      <c r="A44" s="1">
-        <v>46</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>126</v>
-      </c>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="14"/>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="13"/>
+      <c r="B44" s="8"/>
       <c r="C44" s="8"/>
-      <c r="D44" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H44" s="2">
-        <v>3</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K44" s="21">
-        <v>41679</v>
-      </c>
-      <c r="L44" s="22">
-        <v>41679</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="40.5">
-      <c r="A45" s="1">
-        <v>48</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>125</v>
-      </c>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="14"/>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="13"/>
+      <c r="B45" s="8"/>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
-      <c r="E45" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="1:12" ht="27">
-      <c r="A46" s="13">
-        <v>52</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>123</v>
-      </c>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="14"/>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="13"/>
+      <c r="B46" s="8"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
-      <c r="E46" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="H46" s="8">
-        <v>2</v>
-      </c>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
       <c r="I46" s="8"/>
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
       <c r="L46" s="14"/>
     </row>
-    <row r="47" spans="1:12" ht="27">
-      <c r="A47" s="13">
-        <v>53</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>122</v>
-      </c>
+    <row r="47" spans="1:12">
+      <c r="A47" s="13"/>
+      <c r="B47" s="8"/>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
-      <c r="E47" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>22</v>
-      </c>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
       <c r="K47" s="8"/>
       <c r="L47" s="14"/>
     </row>
-    <row r="48" spans="1:12" ht="27">
-      <c r="A48" s="13">
-        <v>54</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>121</v>
-      </c>
+    <row r="48" spans="1:12">
+      <c r="A48" s="13"/>
+      <c r="B48" s="8"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
-      <c r="E48" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G48" s="8" t="s">
-        <v>99</v>
-      </c>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
       <c r="K48" s="8"/>
       <c r="L48" s="14"/>
     </row>
-    <row r="49" spans="1:12" ht="27">
-      <c r="A49" s="13">
-        <v>56</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>120</v>
-      </c>
+    <row r="49" spans="1:12">
+      <c r="A49" s="13"/>
+      <c r="B49" s="8"/>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
-      <c r="E49" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>12</v>
-      </c>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
@@ -2717,34 +2995,18 @@
       <c r="K49" s="8"/>
       <c r="L49" s="14"/>
     </row>
-    <row r="50" spans="1:12" ht="27">
-      <c r="A50" s="13">
-        <v>57</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>129</v>
-      </c>
+    <row r="50" spans="1:12">
+      <c r="A50" s="13"/>
+      <c r="B50" s="8"/>
       <c r="C50" s="8"/>
-      <c r="D50" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>12</v>
-      </c>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
-      <c r="I50" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="J50" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="K50" s="32">
-        <v>41688</v>
-      </c>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
       <c r="L50" s="14"/>
     </row>
     <row r="51" spans="1:12">
@@ -3139,154 +3401,28 @@
       <c r="K78" s="8"/>
       <c r="L78" s="14"/>
     </row>
-    <row r="79" spans="1:12">
-      <c r="A79" s="13"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8"/>
-      <c r="J79" s="8"/>
-      <c r="K79" s="8"/>
-      <c r="L79" s="14"/>
-    </row>
-    <row r="80" spans="1:12">
-      <c r="A80" s="13"/>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
-      <c r="I80" s="8"/>
-      <c r="J80" s="8"/>
-      <c r="K80" s="8"/>
-      <c r="L80" s="14"/>
-    </row>
-    <row r="81" spans="1:12">
-      <c r="A81" s="13"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="8"/>
-      <c r="J81" s="8"/>
-      <c r="K81" s="8"/>
-      <c r="L81" s="14"/>
-    </row>
-    <row r="82" spans="1:12">
-      <c r="A82" s="13"/>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="8"/>
-      <c r="J82" s="8"/>
-      <c r="K82" s="8"/>
-      <c r="L82" s="14"/>
-    </row>
-    <row r="83" spans="1:12">
-      <c r="A83" s="13"/>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="8"/>
-      <c r="I83" s="8"/>
-      <c r="J83" s="8"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="14"/>
-    </row>
-    <row r="84" spans="1:12">
-      <c r="A84" s="13"/>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="8"/>
-      <c r="I84" s="8"/>
-      <c r="J84" s="8"/>
-      <c r="K84" s="8"/>
-      <c r="L84" s="14"/>
-    </row>
-    <row r="85" spans="1:12">
-      <c r="A85" s="13"/>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="8"/>
-      <c r="K85" s="8"/>
-      <c r="L85" s="14"/>
-    </row>
-    <row r="86" spans="1:12">
-      <c r="A86" s="13"/>
-      <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
-      <c r="G86" s="8"/>
-      <c r="H86" s="8"/>
-      <c r="I86" s="8"/>
-      <c r="J86" s="8"/>
-      <c r="K86" s="8"/>
-      <c r="L86" s="14"/>
-    </row>
-    <row r="87" spans="1:12">
-      <c r="A87" s="13"/>
-      <c r="B87" s="8"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
-      <c r="G87" s="8"/>
-      <c r="H87" s="8"/>
-      <c r="I87" s="8"/>
-      <c r="J87" s="8"/>
-      <c r="K87" s="8"/>
-      <c r="L87" s="14"/>
-    </row>
-    <row r="88" spans="1:12" ht="14.25" thickBot="1">
-      <c r="A88" s="15"/>
-      <c r="B88" s="16"/>
-      <c r="C88" s="16"/>
-      <c r="D88" s="16"/>
-      <c r="E88" s="16"/>
-      <c r="F88" s="16"/>
-      <c r="G88" s="16"/>
-      <c r="H88" s="16"/>
-      <c r="I88" s="16"/>
-      <c r="J88" s="16"/>
-      <c r="K88" s="16"/>
-      <c r="L88" s="17"/>
+    <row r="79" spans="1:12" ht="14.25" thickBot="1">
+      <c r="A79" s="15"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16"/>
+      <c r="H79" s="16"/>
+      <c r="I79" s="16"/>
+      <c r="J79" s="16"/>
+      <c r="K79" s="16"/>
+      <c r="L79" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L50">
+  <autoFilter ref="A1:L41">
     <filterColumn colId="2"/>
     <filterColumn colId="3"/>
     <filterColumn colId="5"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:L199">
+  <conditionalFormatting sqref="A2:L190">
     <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
@@ -3301,13 +3437,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E88">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E79">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F88">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F79">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J88">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J79">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3317,6 +3453,1494 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1:L87"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="39.75" customWidth="1"/>
+    <col min="3" max="3" width="20.125" customWidth="1"/>
+    <col min="4" max="4" width="24.75" customWidth="1"/>
+    <col min="5" max="5" width="9.375" customWidth="1"/>
+    <col min="6" max="6" width="9.75" customWidth="1"/>
+    <col min="7" max="7" width="9.875" customWidth="1"/>
+    <col min="8" max="8" width="14.125" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="15.875" customWidth="1"/>
+    <col min="12" max="12" width="17.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="29.45" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="40.5">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" spans="1:12" ht="27">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12" ht="40.5">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" ht="40.5">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="1:12" ht="27">
+      <c r="A6" s="27">
+        <v>5</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="31"/>
+    </row>
+    <row r="7" spans="1:12" ht="40.5">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="3"/>
+    </row>
+    <row r="8" spans="1:12" ht="27">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" ht="27">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" ht="27">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" ht="54">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" ht="27">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" ht="40.5">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="2">
+        <v>5</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" ht="27">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" ht="27">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" s="2">
+        <v>3</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" ht="27">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="1:12" ht="27">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="1:12" ht="27">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="1:12" ht="27">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="27">
+        <v>19</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="31"/>
+    </row>
+    <row r="21" spans="1:12" ht="40.5">
+      <c r="A21" s="1">
+        <v>27</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="1:12" ht="27">
+      <c r="A22" s="1">
+        <v>28</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="1:12" ht="27">
+      <c r="A23" s="1">
+        <v>29</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="1"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="1"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="1"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="27"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="31"/>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="27"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="31"/>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="1"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="1"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="1"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="1"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="1"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="1"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="1"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="3"/>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="1"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="3"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="1"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="3"/>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="1"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="3"/>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="1"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="1"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="1"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="1"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="1"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="22"/>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="1"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="13"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="14"/>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="13"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="14"/>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="13"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="14"/>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" s="13"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="14"/>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="13"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="14"/>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="13"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="14"/>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="13"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="14"/>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="13"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="14"/>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="13"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="14"/>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="13"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="14"/>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="13"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="14"/>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" s="13"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="8"/>
+      <c r="J56" s="8"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="14"/>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" s="13"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="14"/>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" s="13"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="14"/>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="13"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="14"/>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" s="13"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="14"/>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" s="13"/>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="8"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="14"/>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" s="13"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="14"/>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" s="13"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="8"/>
+      <c r="J63" s="8"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="14"/>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" s="13"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
+      <c r="I64" s="8"/>
+      <c r="J64" s="8"/>
+      <c r="K64" s="8"/>
+      <c r="L64" s="14"/>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" s="13"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+      <c r="I65" s="8"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="14"/>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66" s="13"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="8"/>
+      <c r="J66" s="8"/>
+      <c r="K66" s="8"/>
+      <c r="L66" s="14"/>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="A67" s="13"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="8"/>
+      <c r="J67" s="8"/>
+      <c r="K67" s="8"/>
+      <c r="L67" s="14"/>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="A68" s="13"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="8"/>
+      <c r="J68" s="8"/>
+      <c r="K68" s="8"/>
+      <c r="L68" s="14"/>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="A69" s="13"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="8"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="8"/>
+      <c r="J69" s="8"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="14"/>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70" s="13"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="14"/>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="A71" s="13"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="8"/>
+      <c r="J71" s="8"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="14"/>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" s="13"/>
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="8"/>
+      <c r="K72" s="8"/>
+      <c r="L72" s="14"/>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" s="13"/>
+      <c r="B73" s="8"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="8"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
+      <c r="I73" s="8"/>
+      <c r="J73" s="8"/>
+      <c r="K73" s="8"/>
+      <c r="L73" s="14"/>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74" s="13"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="14"/>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" s="13"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="14"/>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="A76" s="13"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="14"/>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77" s="13"/>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="14"/>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78" s="13"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="14"/>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79" s="13"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="14"/>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" s="13"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="8"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="8"/>
+      <c r="I80" s="8"/>
+      <c r="J80" s="8"/>
+      <c r="K80" s="8"/>
+      <c r="L80" s="14"/>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" s="13"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="8"/>
+      <c r="J81" s="8"/>
+      <c r="K81" s="8"/>
+      <c r="L81" s="14"/>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" s="13"/>
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8"/>
+      <c r="I82" s="8"/>
+      <c r="J82" s="8"/>
+      <c r="K82" s="8"/>
+      <c r="L82" s="14"/>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" s="13"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="8"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="14"/>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" s="13"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="8"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="14"/>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" s="13"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="8"/>
+      <c r="K85" s="8"/>
+      <c r="L85" s="14"/>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" s="13"/>
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="8"/>
+      <c r="J86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="14"/>
+    </row>
+    <row r="87" spans="1:12" ht="14.25" thickBot="1">
+      <c r="A87" s="15"/>
+      <c r="B87" s="16"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="16"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="16"/>
+      <c r="H87" s="16"/>
+      <c r="I87" s="16"/>
+      <c r="J87" s="16"/>
+      <c r="K87" s="16"/>
+      <c r="L87" s="17"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A2:L198">
+    <cfRule type="expression" dxfId="47" priority="21" stopIfTrue="1">
+      <formula>$J2="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="46" priority="22" stopIfTrue="1">
+      <formula>$J2="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="23" stopIfTrue="1">
+      <formula>$J2="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="24" stopIfTrue="1">
+      <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13:L13">
+    <cfRule type="expression" dxfId="43" priority="17" stopIfTrue="1">
+      <formula>$J13="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="18" stopIfTrue="1">
+      <formula>$J13="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="41" priority="19" stopIfTrue="1">
+      <formula>$J13="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="20" stopIfTrue="1">
+      <formula>OR($J13="CLOSED",$J13="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15:H15">
+    <cfRule type="expression" dxfId="35" priority="13" stopIfTrue="1">
+      <formula>$J15="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="14" stopIfTrue="1">
+      <formula>$J15="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="15" stopIfTrue="1">
+      <formula>$J15="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="16" stopIfTrue="1">
+      <formula>OR($J15="CLOSED",$J15="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="expression" dxfId="27" priority="9" stopIfTrue="1">
+      <formula>$J16="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="10" stopIfTrue="1">
+      <formula>$J16="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="11" stopIfTrue="1">
+      <formula>$J16="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="12" stopIfTrue="1">
+      <formula>OR($J16="CLOSED",$J16="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="expression" dxfId="19" priority="5" stopIfTrue="1">
+      <formula>$J17="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="6" stopIfTrue="1">
+      <formula>$J17="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="7" stopIfTrue="1">
+      <formula>$J17="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="8" stopIfTrue="1">
+      <formula>OR($J17="CLOSED",$J17="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19">
+    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
+      <formula>$J19="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
+      <formula>$J19="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
+      <formula>$J19="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
+      <formula>OR($J19="CLOSED",$J19="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J87">
+      <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F87">
+      <formula1>"高,中,低"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E87">
+      <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L74"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -3343,10 +4967,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -3378,29 +5002,29 @@
         <v>55</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H2" s="12">
         <v>1</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K2" s="24">
         <v>41680</v>
@@ -3414,29 +5038,29 @@
         <v>49</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H3" s="10">
         <v>1</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K3" s="11">
         <v>41664</v>
@@ -3450,29 +5074,29 @@
         <v>50</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="10" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H4" s="10">
         <v>1</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K4" s="11">
         <v>41665</v>
@@ -3486,35 +5110,35 @@
         <v>47</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="26" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H5" s="10">
         <v>0</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="40.5">
@@ -3522,14 +5146,14 @@
         <v>42</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="12" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>12</v>
@@ -3541,10 +5165,10 @@
         <v>4</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K6" s="11">
         <v>41662</v>
@@ -3558,11 +5182,11 @@
         <v>6</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>14</v>
@@ -3571,16 +5195,16 @@
         <v>12</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H7" s="10">
         <v>4</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K7" s="11">
         <v>41679</v>
@@ -3594,29 +5218,29 @@
         <v>5</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>18</v>
       </c>
       <c r="H8" s="10">
         <v>4</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K8" s="11">
         <v>41680</v>
@@ -3630,29 +5254,29 @@
         <v>51</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H9" s="8">
         <v>1</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="K9" s="8"/>
       <c r="L9" s="14"/>
@@ -4574,16 +6198,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:L9">
-    <cfRule type="expression" dxfId="8" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="1" stopIfTrue="1">
       <formula>$J9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="2" stopIfTrue="1">
       <formula>$J9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="3" stopIfTrue="1">
       <formula>$J9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="4" stopIfTrue="1">
       <formula>OR($J9="CLOSED",$J9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4601,15 +6225,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
-</worksheet>
 </file>
--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="142">
   <si>
     <r>
       <t>描述</t>
@@ -731,10 +731,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>内置SQL dirty join</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">ShardingKey需要加上0,1…的Field信息以方便外部显示
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -747,6 +743,14 @@
   <si>
     <t xml:space="preserve">加载文件由于元数据损坏的文件如何rebuild
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内置SQL anti-join</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1080,175 +1084,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="56">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="32">
     <dxf>
       <fill>
         <patternFill>
@@ -3423,16 +3259,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L190">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="1" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="2" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="3" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="4" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3527,10 +3363,18 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="3"/>
+      <c r="I2" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" s="21">
+        <v>41754</v>
+      </c>
+      <c r="L2" s="22">
+        <v>41757</v>
+      </c>
     </row>
     <row r="3" spans="1:12" ht="27">
       <c r="A3" s="1">
@@ -3706,7 +3550,9 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
+      <c r="J11" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="K11" s="2"/>
       <c r="L11" s="3"/>
     </row>
@@ -3794,7 +3640,9 @@
         <v>3</v>
       </c>
       <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+      <c r="J15" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="K15" s="2"/>
       <c r="L15" s="3"/>
     </row>
@@ -3812,7 +3660,9 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+      <c r="J16" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="K16" s="2"/>
       <c r="L16" s="3"/>
     </row>
@@ -3848,7 +3698,9 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+      <c r="J18" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="K18" s="2"/>
       <c r="L18" s="3"/>
     </row>
@@ -3875,7 +3727,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C20" s="28"/>
       <c r="D20" s="28"/>
@@ -3893,7 +3745,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -3911,7 +3763,7 @@
         <v>28</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -3920,7 +3772,9 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
+      <c r="J22" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="K22" s="2"/>
       <c r="L22" s="3"/>
     </row>
@@ -3929,7 +3783,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -4841,86 +4695,86 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L198">
-    <cfRule type="expression" dxfId="47" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:L13">
-    <cfRule type="expression" dxfId="43" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="17" stopIfTrue="1">
       <formula>$J13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="18" stopIfTrue="1">
       <formula>$J13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="19" stopIfTrue="1">
       <formula>$J13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="20" stopIfTrue="1">
       <formula>OR($J13="CLOSED",$J13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:H15">
-    <cfRule type="expression" dxfId="35" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="13" stopIfTrue="1">
       <formula>$J15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="14" stopIfTrue="1">
       <formula>$J15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="15" stopIfTrue="1">
       <formula>$J15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="16" stopIfTrue="1">
       <formula>OR($J15="CLOSED",$J15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="expression" dxfId="27" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="9" stopIfTrue="1">
       <formula>$J16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="10" stopIfTrue="1">
       <formula>$J16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="11" stopIfTrue="1">
       <formula>$J16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="12" stopIfTrue="1">
       <formula>OR($J16="CLOSED",$J16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="expression" dxfId="19" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="5" stopIfTrue="1">
       <formula>$J17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="6" stopIfTrue="1">
       <formula>$J17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="7" stopIfTrue="1">
       <formula>$J17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="8" stopIfTrue="1">
       <formula>OR($J17="CLOSED",$J17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
-    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
       <formula>$J19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
       <formula>$J19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
       <formula>$J19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="4" stopIfTrue="1">
       <formula>OR($J19="CLOSED",$J19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6198,16 +6052,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:L9">
-    <cfRule type="expression" dxfId="55" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>$J9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
       <formula>$J9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>$J9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
       <formula>OR($J9="CLOSED",$J9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -12,7 +12,7 @@
     <sheet name="已完成任务" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$L$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$L$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已完成任务!$A$1:$L$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="169">
   <si>
     <r>
       <t>描述</t>
@@ -434,11 +434,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">创建CS可指定域和组
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">创建CL可指定组
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -736,11 +731,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">定时刷mmap保持性能平稳
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">加载文件由于元数据损坏的文件如何rebuild
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -751,6 +741,125 @@
   </si>
   <si>
     <t>内置SQL anti-join</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-238</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CATA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-159 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">定时将DMS中MMAP数据脏页持久化至磁盘，提升性能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PMD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘圳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">所有驱动增加多个连接的IP+端口，如果一个IP连接不成功自动选择下一个
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-120 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRIVER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>导入数据时，能够指定字段类型，并设置默认值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-132</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOOL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何嘉文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbexprt 加入新参数, 可以指定不导出_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-139</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-140 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王涛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加$isnull匹配条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-155</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MTH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉、武赟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉、武赟、谭钊波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武赟、谭钊波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-239</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">创建CS可指定域
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -980,7 +1089,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1080,11 +1189,770 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="140">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1602,7 +2470,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -1627,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -1686,7 +2554,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -1734,82 +2602,82 @@
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:12" ht="40.5">
-      <c r="A5" s="1">
-        <v>7</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="A5" s="27">
+        <v>8</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="2">
-        <v>4</v>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="3"/>
+      <c r="G5" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="29">
+        <v>1</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="K5" s="30">
+        <v>41679</v>
+      </c>
+      <c r="L5" s="31"/>
     </row>
     <row r="6" spans="1:12" ht="40.5">
-      <c r="A6" s="27">
-        <v>8</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="29" t="s">
+      <c r="A6" s="1">
+        <v>9</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="29">
-        <v>1</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="J6" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="K6" s="30">
-        <v>41679</v>
-      </c>
-      <c r="L6" s="31"/>
+      <c r="G6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" ht="40.5">
       <c r="A7" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="H7" s="2">
+        <v>3</v>
+      </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -1817,36 +2685,34 @@
     </row>
     <row r="8" spans="1:12" ht="40.5">
       <c r="A8" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2">
-        <v>3</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="1:12" ht="40.5">
+    <row r="9" spans="1:12" ht="67.5">
       <c r="A9" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -1854,10 +2720,10 @@
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -1865,25 +2731,27 @@
       <c r="K9" s="2"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="1:12" ht="67.5">
+    <row r="10" spans="1:12" ht="27">
       <c r="A10" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="H10" s="2">
+        <v>15</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -1891,24 +2759,24 @@
     </row>
     <row r="11" spans="1:12" ht="27">
       <c r="A11" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="2" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H11" s="2">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -1917,10 +2785,10 @@
     </row>
     <row r="12" spans="1:12" ht="27">
       <c r="A12" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -1928,13 +2796,13 @@
         <v>35</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -1943,10 +2811,10 @@
     </row>
     <row r="13" spans="1:12" ht="27">
       <c r="A13" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -1954,14 +2822,12 @@
         <v>35</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="2">
-        <v>8</v>
-      </c>
+      <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -1969,10 +2835,10 @@
     </row>
     <row r="14" spans="1:12" ht="27">
       <c r="A14" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -1980,12 +2846,14 @@
         <v>35</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="H14" s="2">
+        <v>5</v>
+      </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -1993,10 +2861,10 @@
     </row>
     <row r="15" spans="1:12" ht="27">
       <c r="A15" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -2004,25 +2872,29 @@
         <v>35</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="H15" s="2">
-        <v>5</v>
-      </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="K15" s="2"/>
       <c r="L15" s="3"/>
     </row>
     <row r="16" spans="1:12" ht="27">
       <c r="A16" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -2033,26 +2905,22 @@
         <v>22</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H16" s="2">
-        <v>13</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>64</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="3"/>
     </row>
     <row r="17" spans="1:12" ht="27">
       <c r="A17" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -2060,10 +2928,10 @@
         <v>35</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H17" s="2">
         <v>4</v>
@@ -2075,24 +2943,24 @@
     </row>
     <row r="18" spans="1:12" ht="27">
       <c r="A18" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H18" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -2100,67 +2968,67 @@
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="1:12" ht="27">
-      <c r="A19" s="1">
-        <v>21</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="2" t="s">
+      <c r="A19" s="27">
+        <v>22</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H19" s="2">
-        <v>15</v>
-      </c>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="3"/>
+      <c r="G19" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="29">
+        <v>8</v>
+      </c>
+      <c r="I19" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="J19" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="K19" s="29"/>
+      <c r="L19" s="31"/>
     </row>
     <row r="20" spans="1:12" ht="27">
-      <c r="A20" s="27">
-        <v>22</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="29" t="s">
+      <c r="A20" s="1">
+        <v>23</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="29" t="s">
+      <c r="F20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="29">
-        <v>8</v>
-      </c>
-      <c r="I20" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="J20" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="K20" s="29"/>
-      <c r="L20" s="31"/>
+      <c r="H20" s="2">
+        <v>5</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="3"/>
     </row>
     <row r="21" spans="1:12" ht="27">
       <c r="A21" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -2174,7 +3042,7 @@
         <v>48</v>
       </c>
       <c r="H21" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -2183,10 +3051,10 @@
     </row>
     <row r="22" spans="1:12" ht="27">
       <c r="A22" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -2194,13 +3062,13 @@
         <v>44</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H22" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
@@ -2209,24 +3077,24 @@
     </row>
     <row r="23" spans="1:12" ht="27">
       <c r="A23" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="H23" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -2235,10 +3103,10 @@
     </row>
     <row r="24" spans="1:12" ht="27">
       <c r="A24" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -2246,10 +3114,10 @@
         <v>54</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="H24" s="2">
         <v>4</v>
@@ -2261,10 +3129,10 @@
     </row>
     <row r="25" spans="1:12" ht="27">
       <c r="A25" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -2275,10 +3143,10 @@
         <v>12</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H25" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -2286,40 +3154,46 @@
       <c r="L25" s="3"/>
     </row>
     <row r="26" spans="1:12" ht="27">
-      <c r="A26" s="1">
-        <v>28</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="2" t="s">
+      <c r="A26" s="27">
+        <v>29</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H26" s="2">
-        <v>8</v>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="3"/>
+      <c r="G26" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="H26" s="29">
+        <v>20</v>
+      </c>
+      <c r="I26" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="J26" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="K26" s="29"/>
+      <c r="L26" s="31"/>
     </row>
     <row r="27" spans="1:12" ht="27">
       <c r="A27" s="27">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
+      <c r="D27" s="28" t="s">
+        <v>119</v>
+      </c>
       <c r="E27" s="29" t="s">
         <v>54</v>
       </c>
@@ -2333,7 +3207,7 @@
         <v>20</v>
       </c>
       <c r="I27" s="29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J27" s="29" t="s">
         <v>64</v>
@@ -2341,44 +3215,38 @@
       <c r="K27" s="29"/>
       <c r="L27" s="31"/>
     </row>
-    <row r="28" spans="1:12" ht="27">
-      <c r="A28" s="27">
-        <v>30</v>
-      </c>
-      <c r="B28" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="E28" s="29" t="s">
+    <row r="28" spans="1:12" ht="40.5">
+      <c r="A28" s="1">
+        <v>31</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F28" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="H28" s="29">
-        <v>20</v>
-      </c>
-      <c r="I28" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="J28" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="K28" s="29"/>
-      <c r="L28" s="31"/>
-    </row>
-    <row r="29" spans="1:12" ht="40.5">
+      <c r="F28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H28" s="2">
+        <v>8</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="1:12" ht="27">
       <c r="A29" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -2386,25 +3254,25 @@
         <v>54</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="H29" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="3"/>
     </row>
-    <row r="30" spans="1:12" ht="27">
+    <row r="30" spans="1:12" ht="40.5">
       <c r="A30" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -2412,25 +3280,25 @@
         <v>54</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>48</v>
       </c>
       <c r="H30" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="3"/>
     </row>
-    <row r="31" spans="1:12" ht="40.5">
+    <row r="31" spans="1:12" ht="54">
       <c r="A31" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -2451,61 +3319,61 @@
       <c r="K31" s="2"/>
       <c r="L31" s="3"/>
     </row>
-    <row r="32" spans="1:12" ht="54">
+    <row r="32" spans="1:12" ht="27">
       <c r="A32" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="2" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H32" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="3"/>
     </row>
-    <row r="33" spans="1:12" ht="27">
+    <row r="33" spans="1:12" ht="54">
       <c r="A33" s="1">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="H33" s="2">
         <v>2</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
+      <c r="K33" s="21"/>
       <c r="L33" s="3"/>
     </row>
-    <row r="34" spans="1:12" ht="54">
+    <row r="34" spans="1:12" ht="40.5">
       <c r="A34" s="1">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>77</v>
@@ -2516,22 +3384,22 @@
         <v>72</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="H34" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="21"/>
+      <c r="K34" s="2"/>
       <c r="L34" s="3"/>
     </row>
-    <row r="35" spans="1:12" ht="40.5">
+    <row r="35" spans="1:12" ht="27">
       <c r="A35" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>78</v>
@@ -2542,10 +3410,10 @@
         <v>72</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H35" s="2">
         <v>15</v>
@@ -2555,168 +3423,120 @@
       <c r="K35" s="2"/>
       <c r="L35" s="3"/>
     </row>
-    <row r="36" spans="1:12" ht="27">
+    <row r="36" spans="1:12" ht="40.5">
       <c r="A36" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
+      <c r="D36" s="8" t="s">
+        <v>109</v>
+      </c>
       <c r="E36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H36" s="2">
+        <v>3</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K36" s="21">
+        <v>41679</v>
+      </c>
+      <c r="L36" s="22">
+        <v>41679</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="27">
+      <c r="A37" s="13">
+        <v>53</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F37" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H36" s="2">
-        <v>15</v>
-      </c>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="3"/>
-    </row>
-    <row r="37" spans="1:12" ht="40.5">
-      <c r="A37" s="1">
-        <v>46</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H37" s="2">
-        <v>3</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K37" s="21">
-        <v>41679</v>
-      </c>
-      <c r="L37" s="22">
-        <v>41679</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="40.5">
-      <c r="A38" s="1">
-        <v>48</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>118</v>
-      </c>
+      <c r="G37" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="14"/>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="13"/>
+      <c r="B38" s="8"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
-      <c r="E38" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="3"/>
-    </row>
-    <row r="39" spans="1:12" ht="27">
-      <c r="A39" s="13">
-        <v>53</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>116</v>
-      </c>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="14"/>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="13"/>
+      <c r="B39" s="8"/>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
-      <c r="E39" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>20</v>
-      </c>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" spans="1:12" ht="27">
-      <c r="A40" s="13">
-        <v>54</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>115</v>
-      </c>
+    <row r="40" spans="1:12">
+      <c r="A40" s="13"/>
+      <c r="B40" s="8"/>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
-      <c r="E40" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>93</v>
-      </c>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
       <c r="L40" s="14"/>
     </row>
-    <row r="41" spans="1:12" ht="27">
-      <c r="A41" s="13">
-        <v>57</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>122</v>
-      </c>
+    <row r="41" spans="1:12">
+      <c r="A41" s="13"/>
+      <c r="B41" s="8"/>
       <c r="C41" s="8"/>
-      <c r="D41" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>12</v>
-      </c>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
-      <c r="I41" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="K41" s="32">
-        <v>41688</v>
-      </c>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
       <c r="L41" s="14"/>
     </row>
     <row r="42" spans="1:12">
@@ -3181,105 +4001,49 @@
       <c r="K74" s="8"/>
       <c r="L74" s="14"/>
     </row>
-    <row r="75" spans="1:12">
-      <c r="A75" s="13"/>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="8"/>
-      <c r="I75" s="8"/>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8"/>
-      <c r="L75" s="14"/>
-    </row>
-    <row r="76" spans="1:12">
-      <c r="A76" s="13"/>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="14"/>
-    </row>
-    <row r="77" spans="1:12">
-      <c r="A77" s="13"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="14"/>
-    </row>
-    <row r="78" spans="1:12">
-      <c r="A78" s="13"/>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="8"/>
-      <c r="J78" s="8"/>
-      <c r="K78" s="8"/>
-      <c r="L78" s="14"/>
-    </row>
-    <row r="79" spans="1:12" ht="14.25" thickBot="1">
-      <c r="A79" s="15"/>
-      <c r="B79" s="16"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16"/>
-      <c r="H79" s="16"/>
-      <c r="I79" s="16"/>
-      <c r="J79" s="16"/>
-      <c r="K79" s="16"/>
-      <c r="L79" s="17"/>
+    <row r="75" spans="1:12" ht="14.25" thickBot="1">
+      <c r="A75" s="15"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16"/>
+      <c r="H75" s="16"/>
+      <c r="I75" s="16"/>
+      <c r="J75" s="16"/>
+      <c r="K75" s="16"/>
+      <c r="L75" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L41">
+  <autoFilter ref="A1:L37">
     <filterColumn colId="2"/>
     <filterColumn colId="3"/>
     <filterColumn colId="5"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:L190">
-    <cfRule type="expression" dxfId="31" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:L186">
+    <cfRule type="expression" dxfId="135" priority="1" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="134" priority="2" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="133" priority="3" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="132" priority="4" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E79">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E75">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F79">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F75">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J79">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J75">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3293,7 +4057,7 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -3318,10 +4082,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -3348,9 +4112,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="40.5">
+    <row r="2" spans="1:12" ht="27">
       <c r="A2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>123</v>
@@ -3363,22 +4127,14 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="K2" s="21">
-        <v>41754</v>
-      </c>
-      <c r="L2" s="22">
-        <v>41757</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="27">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" spans="1:12" ht="40.5">
       <c r="A3" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>124</v>
@@ -3398,7 +4154,7 @@
     </row>
     <row r="4" spans="1:12" ht="40.5">
       <c r="A4" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>125</v>
@@ -3416,49 +4172,49 @@
       <c r="K4" s="2"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:12" ht="40.5">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8" t="s">
+    <row r="5" spans="1:12" ht="27">
+      <c r="A5" s="27">
+        <v>5</v>
+      </c>
+      <c r="B5" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="2" t="s">
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:12" ht="27">
-      <c r="A6" s="27">
-        <v>5</v>
-      </c>
-      <c r="B6" s="28" t="s">
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="31"/>
+    </row>
+    <row r="6" spans="1:12" ht="40.5">
+      <c r="A6" s="1">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="29" t="s">
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="31"/>
-    </row>
-    <row r="7" spans="1:12" ht="40.5">
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" ht="27">
       <c r="A7" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>128</v>
@@ -3478,7 +4234,7 @@
     </row>
     <row r="8" spans="1:12" ht="27">
       <c r="A8" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>129</v>
@@ -3498,7 +4254,7 @@
     </row>
     <row r="9" spans="1:12" ht="27">
       <c r="A9" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>130</v>
@@ -3518,16 +4274,14 @@
     </row>
     <row r="10" spans="1:12" ht="27">
       <c r="A10" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
-      <c r="E10" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -3536,32 +4290,38 @@
       <c r="K10" s="2"/>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="1:12" ht="54">
+    <row r="11" spans="1:12" ht="40.5">
       <c r="A11" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>133</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="2">
+        <v>5</v>
+      </c>
       <c r="I11" s="2"/>
-      <c r="J11" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:12" ht="27">
       <c r="A12" s="1">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -3574,38 +4334,30 @@
       <c r="K12" s="2"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="1:12" ht="40.5">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="2">
-        <v>5</v>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" ht="27">
+    <row r="13" spans="1:12">
+      <c r="A13" s="27">
+        <v>19</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="31"/>
+    </row>
+    <row r="14" spans="1:12" ht="40.5">
       <c r="A14" s="1">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -3620,39 +4372,25 @@
     </row>
     <row r="15" spans="1:12" ht="27">
       <c r="A15" s="1">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H15" s="2">
-        <v>3</v>
-      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
       <c r="I15" s="2"/>
-      <c r="J15" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="1:12" ht="27">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>75</v>
-      </c>
+    <row r="16" spans="1:12">
+      <c r="A16" s="1"/>
+      <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="2"/>
@@ -3660,19 +4398,13 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
-      <c r="J16" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="1:12" ht="27">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>76</v>
-      </c>
+    <row r="17" spans="1:12">
+      <c r="A17" s="1"/>
+      <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="2"/>
@@ -3684,69 +4416,51 @@
       <c r="K17" s="2"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" spans="1:12" ht="27">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="K18" s="2"/>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="1:12" ht="27">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="3"/>
+    <row r="18" spans="1:12">
+      <c r="A18" s="27"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="31"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="31"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="27">
-        <v>19</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="31"/>
-    </row>
-    <row r="21" spans="1:12" ht="40.5">
-      <c r="A21" s="1">
-        <v>27</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>137</v>
-      </c>
+      <c r="A20" s="1"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="1"/>
+      <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="2"/>
@@ -3758,13 +4472,9 @@
       <c r="K21" s="2"/>
       <c r="L21" s="3"/>
     </row>
-    <row r="22" spans="1:12" ht="27">
-      <c r="A22" s="1">
-        <v>28</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>138</v>
-      </c>
+    <row r="22" spans="1:12">
+      <c r="A22" s="1"/>
+      <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="2"/>
@@ -3772,19 +4482,13 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="3"/>
     </row>
-    <row r="23" spans="1:12" ht="27">
-      <c r="A23" s="1">
-        <v>29</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>139</v>
-      </c>
+    <row r="23" spans="1:12">
+      <c r="A23" s="1"/>
+      <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="2"/>
@@ -3839,32 +4543,32 @@
       <c r="L26" s="3"/>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="27"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="31"/>
+      <c r="A27" s="1"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="3"/>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="27"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="31"/>
+      <c r="A28" s="1"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="3"/>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="1"/>
@@ -3891,7 +4595,7 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
+      <c r="K30" s="21"/>
       <c r="L30" s="3"/>
     </row>
     <row r="31" spans="1:12">
@@ -3947,8 +4651,8 @@
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="3"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="22"/>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="1"/>
@@ -3965,130 +4669,130 @@
       <c r="L35" s="3"/>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1"/>
+      <c r="A36" s="13"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="3"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="14"/>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1"/>
+      <c r="A37" s="13"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="3"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="14"/>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1"/>
+      <c r="A38" s="13"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="3"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="14"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1"/>
+      <c r="A39" s="13"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="3"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="14"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1"/>
+      <c r="A40" s="13"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="3"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="14"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1"/>
+      <c r="A41" s="13"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="3"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="14"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1"/>
+      <c r="A42" s="13"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-      <c r="L42" s="3"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="14"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1"/>
+      <c r="A43" s="13"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="21"/>
-      <c r="L43" s="22"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="14"/>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1"/>
+      <c r="A44" s="13"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="3"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="14"/>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="13"/>
@@ -4157,7 +4861,7 @@
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
-      <c r="K49" s="32"/>
+      <c r="K49" s="8"/>
       <c r="L49" s="14"/>
     </row>
     <row r="50" spans="1:12">
@@ -4552,240 +5256,58 @@
       <c r="K77" s="8"/>
       <c r="L77" s="14"/>
     </row>
-    <row r="78" spans="1:12">
-      <c r="A78" s="13"/>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="8"/>
-      <c r="J78" s="8"/>
-      <c r="K78" s="8"/>
-      <c r="L78" s="14"/>
-    </row>
-    <row r="79" spans="1:12">
-      <c r="A79" s="13"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8"/>
-      <c r="J79" s="8"/>
-      <c r="K79" s="8"/>
-      <c r="L79" s="14"/>
-    </row>
-    <row r="80" spans="1:12">
-      <c r="A80" s="13"/>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
-      <c r="I80" s="8"/>
-      <c r="J80" s="8"/>
-      <c r="K80" s="8"/>
-      <c r="L80" s="14"/>
-    </row>
-    <row r="81" spans="1:12">
-      <c r="A81" s="13"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="8"/>
-      <c r="J81" s="8"/>
-      <c r="K81" s="8"/>
-      <c r="L81" s="14"/>
-    </row>
-    <row r="82" spans="1:12">
-      <c r="A82" s="13"/>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="8"/>
-      <c r="J82" s="8"/>
-      <c r="K82" s="8"/>
-      <c r="L82" s="14"/>
-    </row>
-    <row r="83" spans="1:12">
-      <c r="A83" s="13"/>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="8"/>
-      <c r="I83" s="8"/>
-      <c r="J83" s="8"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="14"/>
-    </row>
-    <row r="84" spans="1:12">
-      <c r="A84" s="13"/>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="8"/>
-      <c r="I84" s="8"/>
-      <c r="J84" s="8"/>
-      <c r="K84" s="8"/>
-      <c r="L84" s="14"/>
-    </row>
-    <row r="85" spans="1:12">
-      <c r="A85" s="13"/>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="8"/>
-      <c r="K85" s="8"/>
-      <c r="L85" s="14"/>
-    </row>
-    <row r="86" spans="1:12">
-      <c r="A86" s="13"/>
-      <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
-      <c r="G86" s="8"/>
-      <c r="H86" s="8"/>
-      <c r="I86" s="8"/>
-      <c r="J86" s="8"/>
-      <c r="K86" s="8"/>
-      <c r="L86" s="14"/>
-    </row>
-    <row r="87" spans="1:12" ht="14.25" thickBot="1">
-      <c r="A87" s="15"/>
-      <c r="B87" s="16"/>
-      <c r="C87" s="16"/>
-      <c r="D87" s="16"/>
-      <c r="E87" s="16"/>
-      <c r="F87" s="16"/>
-      <c r="G87" s="16"/>
-      <c r="H87" s="16"/>
-      <c r="I87" s="16"/>
-      <c r="J87" s="16"/>
-      <c r="K87" s="16"/>
-      <c r="L87" s="17"/>
+    <row r="78" spans="1:12" ht="14.25" thickBot="1">
+      <c r="A78" s="15"/>
+      <c r="B78" s="16"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16"/>
+      <c r="H78" s="16"/>
+      <c r="I78" s="16"/>
+      <c r="J78" s="16"/>
+      <c r="K78" s="16"/>
+      <c r="L78" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:L198">
-    <cfRule type="expression" dxfId="27" priority="21" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:L189">
+    <cfRule type="expression" dxfId="7" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13:L13">
-    <cfRule type="expression" dxfId="23" priority="17" stopIfTrue="1">
-      <formula>$J13="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="18" stopIfTrue="1">
-      <formula>$J13="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="19" stopIfTrue="1">
-      <formula>$J13="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="20" stopIfTrue="1">
-      <formula>OR($J13="CLOSED",$J13="CANCEL")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B15:H15">
-    <cfRule type="expression" dxfId="19" priority="13" stopIfTrue="1">
-      <formula>$J15="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="14" stopIfTrue="1">
-      <formula>$J15="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="15" stopIfTrue="1">
-      <formula>$J15="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="16" stopIfTrue="1">
-      <formula>OR($J15="CLOSED",$J15="CANCEL")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16">
-    <cfRule type="expression" dxfId="15" priority="9" stopIfTrue="1">
-      <formula>$J16="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="10" stopIfTrue="1">
-      <formula>$J16="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="11" stopIfTrue="1">
-      <formula>$J16="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="12" stopIfTrue="1">
-      <formula>OR($J16="CLOSED",$J16="CANCEL")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
-    <cfRule type="expression" dxfId="11" priority="5" stopIfTrue="1">
-      <formula>$J17="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="6" stopIfTrue="1">
-      <formula>$J17="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="7" stopIfTrue="1">
-      <formula>$J17="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="8" stopIfTrue="1">
-      <formula>OR($J17="CLOSED",$J17="CANCEL")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19">
-    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
-      <formula>$J19="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
-      <formula>$J19="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
-      <formula>$J19="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4" stopIfTrue="1">
-      <formula>OR($J19="CLOSED",$J19="CANCEL")</formula>
+  <conditionalFormatting sqref="A11:L11">
+    <cfRule type="expression" dxfId="3" priority="17" stopIfTrue="1">
+      <formula>$J11="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="18" stopIfTrue="1">
+      <formula>$J11="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="19" stopIfTrue="1">
+      <formula>$J11="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="20" stopIfTrue="1">
+      <formula>OR($J11="CLOSED",$J11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J87">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J78">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F87">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F78">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E87">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E78">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4821,10 +5343,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -4856,14 +5378,14 @@
         <v>55</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>22</v>
@@ -4875,10 +5397,10 @@
         <v>1</v>
       </c>
       <c r="I2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="J2" s="12" t="s">
         <v>87</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>88</v>
       </c>
       <c r="K2" s="24">
         <v>41680</v>
@@ -4892,11 +5414,11 @@
         <v>49</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>72</v>
@@ -4911,10 +5433,10 @@
         <v>1</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K3" s="11">
         <v>41664</v>
@@ -4928,11 +5450,11 @@
         <v>50</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>71</v>
@@ -4947,10 +5469,10 @@
         <v>1</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K4" s="11">
         <v>41665</v>
@@ -4964,35 +5486,35 @@
         <v>47</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" s="10">
         <v>0</v>
       </c>
       <c r="I5" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>88</v>
-      </c>
       <c r="K5" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="40.5">
@@ -5000,11 +5522,11 @@
         <v>42</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>72</v>
@@ -5019,10 +5541,10 @@
         <v>4</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K6" s="11">
         <v>41662</v>
@@ -5040,7 +5562,7 @@
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>14</v>
@@ -5055,10 +5577,10 @@
         <v>4</v>
       </c>
       <c r="I7" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="K7" s="11">
         <v>41679</v>
@@ -5076,7 +5598,7 @@
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>11</v>
@@ -5091,10 +5613,10 @@
         <v>4</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K8" s="11">
         <v>41680</v>
@@ -5108,254 +5630,530 @@
         <v>51</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H9" s="8">
         <v>1</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K9" s="8"/>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="1"/>
-      <c r="B10" s="8"/>
+    <row r="10" spans="1:12" ht="27">
+      <c r="A10" s="13">
+        <v>54</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>114</v>
+      </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="1"/>
-      <c r="B11" s="8"/>
+      <c r="E10" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="8">
+        <v>3</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K10" s="8"/>
+      <c r="L10" s="14"/>
+    </row>
+    <row r="11" spans="1:12" ht="40.5">
+      <c r="A11" s="1">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
+      <c r="D11" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="2">
+        <v>4</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="K11" s="2"/>
       <c r="L11" s="3"/>
     </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="1"/>
-      <c r="B12" s="8"/>
+    <row r="12" spans="1:12" ht="40.5">
+      <c r="A12" s="1">
+        <v>48</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>117</v>
+      </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="2">
+        <v>14</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="K12" s="2"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="1"/>
-      <c r="B13" s="8"/>
+    <row r="13" spans="1:12" ht="27">
+      <c r="A13" s="13">
+        <v>57</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>121</v>
+      </c>
       <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="1"/>
-      <c r="B14" s="8"/>
+      <c r="D13" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8">
+        <v>3</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K13" s="32">
+        <v>41688</v>
+      </c>
+      <c r="L13" s="14"/>
+    </row>
+    <row r="14" spans="1:12" ht="40.5">
+      <c r="A14" s="1">
+        <v>1</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="2"/>
+      <c r="D14" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="1"/>
-      <c r="B15" s="8"/>
+      <c r="H14" s="2">
+        <v>5</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K14" s="21">
+        <v>41754</v>
+      </c>
+      <c r="L14" s="22">
+        <v>41757</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="54">
+      <c r="A15" s="1">
+        <v>10</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>132</v>
+      </c>
       <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+      <c r="D15" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H15" s="2">
+        <v>7</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="K15" s="2"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="1"/>
-      <c r="B16" s="8"/>
+    <row r="16" spans="1:12" ht="40.5">
+      <c r="A16" s="1">
+        <v>30</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>149</v>
+      </c>
       <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+      <c r="D16" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H16" s="2">
+        <v>4</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="K16" s="2"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="1"/>
-      <c r="B17" s="8"/>
+    <row r="17" spans="1:12" ht="27">
+      <c r="A17" s="1">
+        <v>31</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>152</v>
+      </c>
       <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
+      <c r="D17" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H17" s="2">
+        <v>3</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="K17" s="2"/>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1"/>
-      <c r="B18" s="8"/>
+      <c r="A18" s="1">
+        <v>32</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>156</v>
+      </c>
       <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+      <c r="D18" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H18" s="2">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="K18" s="2"/>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="1"/>
-      <c r="B19" s="8"/>
+    <row r="19" spans="1:12" ht="40.5">
+      <c r="A19" s="1">
+        <v>28</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>144</v>
+      </c>
       <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="D19" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H19" s="2">
+        <v>3</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="K19" s="2"/>
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1"/>
-      <c r="B20" s="8"/>
+      <c r="A20" s="1">
+        <v>33</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>160</v>
+      </c>
       <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+      <c r="D20" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H20" s="2">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="K20" s="2"/>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="1"/>
-      <c r="B21" s="8"/>
+    <row r="21" spans="1:12" ht="27">
+      <c r="A21" s="1">
+        <v>17</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>135</v>
+      </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="E21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+      <c r="H21" s="2">
+        <v>5</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="K21" s="2"/>
       <c r="L21" s="3"/>
     </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="1"/>
-      <c r="B22" s="8"/>
+    <row r="22" spans="1:12" ht="27">
+      <c r="A22" s="1">
+        <v>14</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
+      <c r="E22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H22" s="2">
+        <v>5</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="K22" s="2"/>
       <c r="L22" s="3"/>
     </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="1"/>
-      <c r="B23" s="8"/>
+    <row r="23" spans="1:12" ht="27">
+      <c r="A23" s="1">
+        <v>15</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
+      <c r="E23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H23" s="2">
+        <v>5</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="K23" s="2"/>
       <c r="L23" s="3"/>
     </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="1"/>
-      <c r="B24" s="8"/>
+    <row r="24" spans="1:12" ht="27">
+      <c r="A24" s="1">
+        <v>13</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>134</v>
+      </c>
       <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
+      <c r="D24" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" s="2">
+        <v>9</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="K24" s="2"/>
       <c r="L24" s="3"/>
     </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="1"/>
-      <c r="B25" s="8"/>
+    <row r="25" spans="1:12" ht="27">
+      <c r="A25" s="1">
+        <v>16</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
+      <c r="D25" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H25" s="2">
+        <v>5</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="K25" s="2"/>
       <c r="L25" s="3"/>
     </row>
@@ -6052,17 +6850,255 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:L9">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="69" stopIfTrue="1">
       <formula>$J9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="70" stopIfTrue="1">
       <formula>$J9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="71" stopIfTrue="1">
       <formula>$J9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="72" stopIfTrue="1">
       <formula>OR($J9="CLOSED",$J9="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10:L10">
+    <cfRule type="expression" dxfId="75" priority="65" stopIfTrue="1">
+      <formula>$J10="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="66" stopIfTrue="1">
+      <formula>$J10="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="73" priority="67" stopIfTrue="1">
+      <formula>$J10="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="68" stopIfTrue="1">
+      <formula>OR($J10="CLOSED",$J10="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11:L11">
+    <cfRule type="expression" dxfId="71" priority="61" stopIfTrue="1">
+      <formula>$J11="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="62" stopIfTrue="1">
+      <formula>$J11="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="69" priority="63" stopIfTrue="1">
+      <formula>$J11="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="68" priority="64" stopIfTrue="1">
+      <formula>OR($J11="CLOSED",$J11="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:L12">
+    <cfRule type="expression" dxfId="67" priority="57" stopIfTrue="1">
+      <formula>$J12="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="66" priority="58" stopIfTrue="1">
+      <formula>$J12="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="59" stopIfTrue="1">
+      <formula>$J12="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="60" stopIfTrue="1">
+      <formula>OR($J12="CLOSED",$J12="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13:L13">
+    <cfRule type="expression" dxfId="63" priority="53" stopIfTrue="1">
+      <formula>$J13="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="54" stopIfTrue="1">
+      <formula>$J13="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="55" stopIfTrue="1">
+      <formula>$J13="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="60" priority="56" stopIfTrue="1">
+      <formula>OR($J13="CLOSED",$J13="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14:L14">
+    <cfRule type="expression" dxfId="59" priority="49" stopIfTrue="1">
+      <formula>$J14="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="50" stopIfTrue="1">
+      <formula>$J14="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="57" priority="51" stopIfTrue="1">
+      <formula>$J14="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="52" stopIfTrue="1">
+      <formula>OR($J14="CLOSED",$J14="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:L15">
+    <cfRule type="expression" dxfId="55" priority="45" stopIfTrue="1">
+      <formula>$J15="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="46" stopIfTrue="1">
+      <formula>$J15="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="47" stopIfTrue="1">
+      <formula>$J15="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="48" stopIfTrue="1">
+      <formula>OR($J15="CLOSED",$J15="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16:L16">
+    <cfRule type="expression" dxfId="51" priority="41" stopIfTrue="1">
+      <formula>$J16="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="42" stopIfTrue="1">
+      <formula>$J16="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="43" stopIfTrue="1">
+      <formula>$J16="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="44" stopIfTrue="1">
+      <formula>OR($J16="CLOSED",$J16="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A17:L17">
+    <cfRule type="expression" dxfId="47" priority="37" stopIfTrue="1">
+      <formula>$J17="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="46" priority="38" stopIfTrue="1">
+      <formula>$J17="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="39" stopIfTrue="1">
+      <formula>$J17="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="40" stopIfTrue="1">
+      <formula>OR($J17="CLOSED",$J17="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:L18">
+    <cfRule type="expression" dxfId="43" priority="33" stopIfTrue="1">
+      <formula>$J18="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="34" stopIfTrue="1">
+      <formula>$J18="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="41" priority="35" stopIfTrue="1">
+      <formula>$J18="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="36" stopIfTrue="1">
+      <formula>OR($J18="CLOSED",$J18="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19:L19">
+    <cfRule type="expression" dxfId="39" priority="29" stopIfTrue="1">
+      <formula>$J19="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="30" stopIfTrue="1">
+      <formula>$J19="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="31" stopIfTrue="1">
+      <formula>$J19="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="32" stopIfTrue="1">
+      <formula>OR($J19="CLOSED",$J19="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:L20">
+    <cfRule type="expression" dxfId="35" priority="25" stopIfTrue="1">
+      <formula>$J20="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="26" stopIfTrue="1">
+      <formula>$J20="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="27" stopIfTrue="1">
+      <formula>$J20="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="28" stopIfTrue="1">
+      <formula>OR($J20="CLOSED",$J20="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A21:L21">
+    <cfRule type="expression" dxfId="31" priority="21" stopIfTrue="1">
+      <formula>$J21="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="22" stopIfTrue="1">
+      <formula>$J21="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="23" stopIfTrue="1">
+      <formula>$J21="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="24" stopIfTrue="1">
+      <formula>OR($J21="CLOSED",$J21="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22:L23">
+    <cfRule type="expression" dxfId="27" priority="17" stopIfTrue="1">
+      <formula>$J22="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="18" stopIfTrue="1">
+      <formula>$J22="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="19" stopIfTrue="1">
+      <formula>$J22="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="20" stopIfTrue="1">
+      <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22:H22">
+    <cfRule type="expression" dxfId="23" priority="13" stopIfTrue="1">
+      <formula>$J22="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="14" stopIfTrue="1">
+      <formula>$J22="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="15" stopIfTrue="1">
+      <formula>$J22="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="16" stopIfTrue="1">
+      <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="expression" dxfId="19" priority="9" stopIfTrue="1">
+      <formula>$J23="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="10" stopIfTrue="1">
+      <formula>$J23="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="11" stopIfTrue="1">
+      <formula>$J23="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="12" stopIfTrue="1">
+      <formula>OR($J23="CLOSED",$J23="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A24:L25">
+    <cfRule type="expression" dxfId="15" priority="5" stopIfTrue="1">
+      <formula>$J24="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="6" stopIfTrue="1">
+      <formula>$J24="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="7" stopIfTrue="1">
+      <formula>$J24="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="8" stopIfTrue="1">
+      <formula>OR($J24="CLOSED",$J24="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
+      <formula>$J25="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
+      <formula>$J25="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
+      <formula>$J25="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
+      <formula>OR($J25="CLOSED",$J25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="173">
   <si>
     <r>
       <t>描述</t>
@@ -860,6 +860,23 @@
   <si>
     <t xml:space="preserve">创建CS可指定域
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">显示查询的访问计划
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-243</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MTH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武赟</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1196,343 +1213,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="140">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="92">
     <dxf>
       <fill>
         <patternFill>
@@ -4023,16 +3704,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L186">
-    <cfRule type="expression" dxfId="135" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="1" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="2" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="133" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="3" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="4" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4057,7 +3738,7 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -4403,18 +4084,18 @@
       <c r="L16" s="3"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="3"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="31"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="27"/>
@@ -4431,18 +4112,18 @@
       <c r="L18" s="31"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="27"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="31"/>
+      <c r="A19" s="1"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="3"/>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="1"/>
@@ -4581,7 +4262,7 @@
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
+      <c r="K29" s="21"/>
       <c r="L29" s="3"/>
     </row>
     <row r="30" spans="1:12">
@@ -4595,7 +4276,7 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="21"/>
+      <c r="K30" s="2"/>
       <c r="L30" s="3"/>
     </row>
     <row r="31" spans="1:12">
@@ -4637,8 +4318,8 @@
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="3"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="22"/>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="1"/>
@@ -4651,22 +4332,22 @@
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="22"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="3"/>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1"/>
+      <c r="A35" s="13"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="3"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="14"/>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="13"/>
@@ -4721,7 +4402,7 @@
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
+      <c r="K39" s="32"/>
       <c r="L39" s="14"/>
     </row>
     <row r="40" spans="1:12">
@@ -4735,7 +4416,7 @@
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
       <c r="J40" s="8"/>
-      <c r="K40" s="32"/>
+      <c r="K40" s="8"/>
       <c r="L40" s="14"/>
     </row>
     <row r="41" spans="1:12">
@@ -5242,37 +4923,23 @@
       <c r="K76" s="8"/>
       <c r="L76" s="14"/>
     </row>
-    <row r="77" spans="1:12">
-      <c r="A77" s="13"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="14"/>
-    </row>
-    <row r="78" spans="1:12" ht="14.25" thickBot="1">
-      <c r="A78" s="15"/>
-      <c r="B78" s="16"/>
-      <c r="C78" s="16"/>
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="16"/>
-      <c r="H78" s="16"/>
-      <c r="I78" s="16"/>
-      <c r="J78" s="16"/>
-      <c r="K78" s="16"/>
-      <c r="L78" s="17"/>
+    <row r="77" spans="1:12" ht="14.25" thickBot="1">
+      <c r="A77" s="15"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16"/>
+      <c r="H77" s="16"/>
+      <c r="I77" s="16"/>
+      <c r="J77" s="16"/>
+      <c r="K77" s="16"/>
+      <c r="L77" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:L189">
+  <conditionalFormatting sqref="A2:L188">
     <cfRule type="expression" dxfId="7" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
@@ -5301,13 +4968,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J78">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J77">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F78">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F77">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E78">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E77">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6157,17 +5824,35 @@
       <c r="K25" s="2"/>
       <c r="L25" s="3"/>
     </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="1"/>
-      <c r="B26" s="8"/>
+    <row r="26" spans="1:12" ht="27">
+      <c r="A26" s="1">
+        <v>34</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>169</v>
+      </c>
       <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
+      <c r="D26" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="H26" s="2">
+        <v>5</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="K26" s="2"/>
       <c r="L26" s="3"/>
     </row>
@@ -6850,188 +6535,202 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:L9">
-    <cfRule type="expression" dxfId="79" priority="69" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="73" stopIfTrue="1">
       <formula>$J9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="74" stopIfTrue="1">
       <formula>$J9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="71" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="75" stopIfTrue="1">
       <formula>$J9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="76" stopIfTrue="1">
       <formula>OR($J9="CLOSED",$J9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:L10">
-    <cfRule type="expression" dxfId="75" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="69" stopIfTrue="1">
       <formula>$J10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="70" stopIfTrue="1">
       <formula>$J10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="71" stopIfTrue="1">
       <formula>$J10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="72" stopIfTrue="1">
       <formula>OR($J10="CLOSED",$J10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:L11">
-    <cfRule type="expression" dxfId="71" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="65" stopIfTrue="1">
       <formula>$J11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="66" stopIfTrue="1">
       <formula>$J11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="67" stopIfTrue="1">
       <formula>$J11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="68" stopIfTrue="1">
       <formula>OR($J11="CLOSED",$J11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:L12">
-    <cfRule type="expression" dxfId="67" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="61" stopIfTrue="1">
       <formula>$J12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="62" stopIfTrue="1">
       <formula>$J12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="63" stopIfTrue="1">
       <formula>$J12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="64" stopIfTrue="1">
       <formula>OR($J12="CLOSED",$J12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:L13">
-    <cfRule type="expression" dxfId="63" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="57" stopIfTrue="1">
       <formula>$J13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="58" stopIfTrue="1">
       <formula>$J13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="59" stopIfTrue="1">
       <formula>$J13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="60" stopIfTrue="1">
       <formula>OR($J13="CLOSED",$J13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:L14">
-    <cfRule type="expression" dxfId="59" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="53" stopIfTrue="1">
       <formula>$J14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="54" stopIfTrue="1">
       <formula>$J14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="55" stopIfTrue="1">
       <formula>$J14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="56" stopIfTrue="1">
       <formula>OR($J14="CLOSED",$J14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:L15">
-    <cfRule type="expression" dxfId="55" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="49" stopIfTrue="1">
       <formula>$J15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="50" stopIfTrue="1">
       <formula>$J15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="51" stopIfTrue="1">
       <formula>$J15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="52" stopIfTrue="1">
       <formula>OR($J15="CLOSED",$J15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:L16">
-    <cfRule type="expression" dxfId="51" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="45" stopIfTrue="1">
       <formula>$J16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="46" stopIfTrue="1">
       <formula>$J16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="47" stopIfTrue="1">
       <formula>$J16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="48" stopIfTrue="1">
       <formula>OR($J16="CLOSED",$J16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:L17">
-    <cfRule type="expression" dxfId="47" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="41" stopIfTrue="1">
       <formula>$J17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="42" stopIfTrue="1">
       <formula>$J17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="43" stopIfTrue="1">
       <formula>$J17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="44" stopIfTrue="1">
       <formula>OR($J17="CLOSED",$J17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:L18">
-    <cfRule type="expression" dxfId="43" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="37" stopIfTrue="1">
       <formula>$J18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="38" stopIfTrue="1">
       <formula>$J18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="39" stopIfTrue="1">
       <formula>$J18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="40" stopIfTrue="1">
       <formula>OR($J18="CLOSED",$J18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:L19">
-    <cfRule type="expression" dxfId="39" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="33" stopIfTrue="1">
       <formula>$J19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="34" stopIfTrue="1">
       <formula>$J19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="35" stopIfTrue="1">
       <formula>$J19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="36" stopIfTrue="1">
       <formula>OR($J19="CLOSED",$J19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:L20">
-    <cfRule type="expression" dxfId="35" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="29" stopIfTrue="1">
       <formula>$J20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="30" stopIfTrue="1">
       <formula>$J20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="31" stopIfTrue="1">
       <formula>$J20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="32" stopIfTrue="1">
       <formula>OR($J20="CLOSED",$J20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:L21">
-    <cfRule type="expression" dxfId="31" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="25" stopIfTrue="1">
       <formula>$J21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="26" stopIfTrue="1">
       <formula>$J21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="27" stopIfTrue="1">
       <formula>$J21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="28" stopIfTrue="1">
       <formula>OR($J21="CLOSED",$J21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:L23">
+    <cfRule type="expression" dxfId="31" priority="21" stopIfTrue="1">
+      <formula>$J22="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="22" stopIfTrue="1">
+      <formula>$J22="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="23" stopIfTrue="1">
+      <formula>$J22="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="24" stopIfTrue="1">
+      <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22:H22">
     <cfRule type="expression" dxfId="27" priority="17" stopIfTrue="1">
       <formula>$J22="HANG-UP"</formula>
     </cfRule>
@@ -7045,60 +6744,60 @@
       <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B22:H22">
+  <conditionalFormatting sqref="B23">
     <cfRule type="expression" dxfId="23" priority="13" stopIfTrue="1">
-      <formula>$J22="HANG-UP"</formula>
+      <formula>$J23="HANG-UP"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="14" stopIfTrue="1">
-      <formula>$J22="PLAN"</formula>
+      <formula>$J23="PLAN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="21" priority="15" stopIfTrue="1">
-      <formula>$J22="OPEN"</formula>
+      <formula>$J23="OPEN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="16" stopIfTrue="1">
-      <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="19" priority="9" stopIfTrue="1">
-      <formula>$J23="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="10" stopIfTrue="1">
-      <formula>$J23="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="11" stopIfTrue="1">
-      <formula>$J23="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="12" stopIfTrue="1">
       <formula>OR($J23="CLOSED",$J23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:L25">
-    <cfRule type="expression" dxfId="15" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="9" stopIfTrue="1">
       <formula>$J24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="10" stopIfTrue="1">
       <formula>$J24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="11" stopIfTrue="1">
       <formula>$J24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="12" stopIfTrue="1">
       <formula>OR($J24="CLOSED",$J24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
+    <cfRule type="expression" dxfId="15" priority="5" stopIfTrue="1">
+      <formula>$J25="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="6" stopIfTrue="1">
+      <formula>$J25="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="7" stopIfTrue="1">
+      <formula>$J25="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="8" stopIfTrue="1">
+      <formula>OR($J25="CLOSED",$J25="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26:L26">
     <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
-      <formula>$J25="HANG-UP"</formula>
+      <formula>$J26="HANG-UP"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
-      <formula>$J25="PLAN"</formula>
+      <formula>$J26="PLAN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
-      <formula>$J25="OPEN"</formula>
+      <formula>$J26="OPEN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
-      <formula>OR($J25="CLOSED",$J25="CANCEL")</formula>
+      <formula>OR($J26="CLOSED",$J26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="173">
   <si>
     <r>
       <t>描述</t>
@@ -676,11 +676,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">监控信息按会话关联，对外展现为关联信息
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">抽象出统一的监控框架，按级别精细化Watch点的监控和输出
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -877,6 +872,11 @@
   </si>
   <si>
     <t>武赟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">会话关联：监控信息按会话关联，对外展现为关联信息
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1213,35 +1213,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="92">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="88">
     <dxf>
       <fill>
         <patternFill>
@@ -3704,16 +3676,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L186">
-    <cfRule type="expression" dxfId="91" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="1" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="2" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="3" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="4" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3853,12 +3825,12 @@
       <c r="K4" s="2"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:12" ht="27">
+    <row r="5" spans="1:12" ht="40.5">
       <c r="A5" s="27">
         <v>5</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>126</v>
+        <v>172</v>
       </c>
       <c r="C5" s="28"/>
       <c r="D5" s="28"/>
@@ -3878,7 +3850,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -3898,7 +3870,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -3918,7 +3890,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -3938,7 +3910,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -3958,11 +3930,13 @@
         <v>11</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
-      <c r="E10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -3976,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -4006,7 +3980,9 @@
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -4020,11 +3996,13 @@
         <v>19</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C13" s="28"/>
       <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="E13" s="29" t="s">
+        <v>72</v>
+      </c>
       <c r="F13" s="29"/>
       <c r="G13" s="29"/>
       <c r="H13" s="29"/>
@@ -4038,11 +4016,13 @@
         <v>27</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -4056,11 +4036,13 @@
         <v>29</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -4940,30 +4922,30 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L188">
-    <cfRule type="expression" dxfId="7" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:L11">
-    <cfRule type="expression" dxfId="3" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="17" stopIfTrue="1">
       <formula>$J11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="18" stopIfTrue="1">
       <formula>$J11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="19" stopIfTrue="1">
       <formula>$J11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="20" stopIfTrue="1">
       <formula>OR($J11="CLOSED",$J11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5346,7 +5328,7 @@
         <v>3</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>87</v>
@@ -5363,7 +5345,7 @@
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
@@ -5378,7 +5360,7 @@
         <v>4</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>87</v>
@@ -5408,7 +5390,7 @@
         <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>87</v>
@@ -5457,7 +5439,7 @@
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>54</v>
@@ -5468,7 +5450,7 @@
         <v>5</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>87</v>
@@ -5485,11 +5467,11 @@
         <v>10</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="33" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>83</v>
@@ -5498,13 +5480,13 @@
         <v>12</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H15" s="2">
         <v>7</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>87</v>
@@ -5517,11 +5499,11 @@
         <v>30</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>72</v>
@@ -5530,7 +5512,7 @@
         <v>12</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H16" s="2">
         <v>4</v>
@@ -5549,11 +5531,11 @@
         <v>31</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>72</v>
@@ -5562,13 +5544,13 @@
         <v>12</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H17" s="2">
         <v>3</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>87</v>
@@ -5581,11 +5563,11 @@
         <v>32</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>72</v>
@@ -5594,13 +5576,13 @@
         <v>12</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>87</v>
@@ -5613,11 +5595,11 @@
         <v>28</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>72</v>
@@ -5626,13 +5608,13 @@
         <v>12</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H19" s="2">
         <v>3</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>87</v>
@@ -5645,11 +5627,11 @@
         <v>33</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>72</v>
@@ -5658,13 +5640,13 @@
         <v>12</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>87</v>
@@ -5677,7 +5659,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -5692,7 +5674,7 @@
         <v>5</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>87</v>
@@ -5705,7 +5687,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -5722,7 +5704,7 @@
         <v>5</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>87</v>
@@ -5746,13 +5728,13 @@
         <v>12</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H23" s="2">
         <v>5</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>87</v>
@@ -5765,11 +5747,11 @@
         <v>13</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>72</v>
@@ -5784,7 +5766,7 @@
         <v>9</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>87</v>
@@ -5801,7 +5783,7 @@
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>72</v>
@@ -5810,13 +5792,13 @@
         <v>12</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H25" s="2">
         <v>5</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>87</v>
@@ -5829,11 +5811,11 @@
         <v>34</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>72</v>
@@ -5842,13 +5824,13 @@
         <v>12</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H26" s="2">
         <v>5</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>87</v>
@@ -6535,268 +6517,268 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:L9">
-    <cfRule type="expression" dxfId="83" priority="73" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="73" stopIfTrue="1">
       <formula>$J9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="74" stopIfTrue="1">
       <formula>$J9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="75" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="75" stopIfTrue="1">
       <formula>$J9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="76" stopIfTrue="1">
       <formula>OR($J9="CLOSED",$J9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:L10">
-    <cfRule type="expression" dxfId="79" priority="69" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="69" stopIfTrue="1">
       <formula>$J10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="70" stopIfTrue="1">
       <formula>$J10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="71" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="71" stopIfTrue="1">
       <formula>$J10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="72" stopIfTrue="1">
       <formula>OR($J10="CLOSED",$J10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:L11">
-    <cfRule type="expression" dxfId="75" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="65" stopIfTrue="1">
       <formula>$J11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="66" stopIfTrue="1">
       <formula>$J11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="67" stopIfTrue="1">
       <formula>$J11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="68" stopIfTrue="1">
       <formula>OR($J11="CLOSED",$J11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:L12">
-    <cfRule type="expression" dxfId="71" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="61" stopIfTrue="1">
       <formula>$J12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="62" stopIfTrue="1">
       <formula>$J12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="63" stopIfTrue="1">
       <formula>$J12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="64" stopIfTrue="1">
       <formula>OR($J12="CLOSED",$J12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:L13">
-    <cfRule type="expression" dxfId="67" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="57" stopIfTrue="1">
       <formula>$J13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="58" stopIfTrue="1">
       <formula>$J13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="59" stopIfTrue="1">
       <formula>$J13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="60" stopIfTrue="1">
       <formula>OR($J13="CLOSED",$J13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:L14">
-    <cfRule type="expression" dxfId="63" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="53" stopIfTrue="1">
       <formula>$J14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="54" stopIfTrue="1">
       <formula>$J14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="55" stopIfTrue="1">
       <formula>$J14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="56" stopIfTrue="1">
       <formula>OR($J14="CLOSED",$J14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:L15">
-    <cfRule type="expression" dxfId="59" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="49" stopIfTrue="1">
       <formula>$J15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="50" stopIfTrue="1">
       <formula>$J15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="51" stopIfTrue="1">
       <formula>$J15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="52" stopIfTrue="1">
       <formula>OR($J15="CLOSED",$J15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:L16">
-    <cfRule type="expression" dxfId="55" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
       <formula>$J16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
       <formula>$J16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
       <formula>$J16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
       <formula>OR($J16="CLOSED",$J16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:L17">
-    <cfRule type="expression" dxfId="51" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
       <formula>$J17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
       <formula>$J17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="43" stopIfTrue="1">
       <formula>$J17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="44" stopIfTrue="1">
       <formula>OR($J17="CLOSED",$J17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:L18">
-    <cfRule type="expression" dxfId="47" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="37" stopIfTrue="1">
       <formula>$J18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="38" stopIfTrue="1">
       <formula>$J18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="39" stopIfTrue="1">
       <formula>$J18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="40" stopIfTrue="1">
       <formula>OR($J18="CLOSED",$J18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:L19">
-    <cfRule type="expression" dxfId="43" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
       <formula>$J19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
       <formula>$J19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
       <formula>$J19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
       <formula>OR($J19="CLOSED",$J19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:L20">
-    <cfRule type="expression" dxfId="39" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
       <formula>$J20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
       <formula>$J20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="31" stopIfTrue="1">
       <formula>$J20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
       <formula>OR($J20="CLOSED",$J20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:L21">
-    <cfRule type="expression" dxfId="35" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
       <formula>$J21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
       <formula>$J21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="27" stopIfTrue="1">
       <formula>$J21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="28" stopIfTrue="1">
       <formula>OR($J21="CLOSED",$J21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:L23">
-    <cfRule type="expression" dxfId="31" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
       <formula>$J22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
       <formula>$J22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
       <formula>$J22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
       <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:H22">
-    <cfRule type="expression" dxfId="27" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
       <formula>$J22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
       <formula>$J22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
       <formula>$J22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
       <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="23" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
       <formula>$J23="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="14" stopIfTrue="1">
       <formula>$J23="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="15" stopIfTrue="1">
       <formula>$J23="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
       <formula>OR($J23="CLOSED",$J23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:L25">
-    <cfRule type="expression" dxfId="19" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
       <formula>$J24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
       <formula>$J24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
       <formula>$J24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
       <formula>OR($J24="CLOSED",$J24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="15" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
       <formula>$J25="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
       <formula>$J25="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
       <formula>$J25="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
       <formula>OR($J25="CLOSED",$J25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:L26">
-    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>$J26="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
       <formula>$J26="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>$J26="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
       <formula>OR($J26="CLOSED",$J26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -4,23 +4,25 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="11010" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="11010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="2014年1季度" sheetId="1" r:id="rId1"/>
     <sheet name="2014年2季度" sheetId="3" r:id="rId2"/>
-    <sheet name="已完成任务" sheetId="2" r:id="rId3"/>
+    <sheet name="2014年3季度" sheetId="4" r:id="rId3"/>
+    <sheet name="已完成任务" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$L$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">已完成任务!$A$1:$L$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2014年3季度'!$A$1:$M$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$L$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="211">
   <si>
     <r>
       <t>描述</t>
@@ -877,6 +879,188 @@
   <si>
     <t xml:space="preserve">会话关联：监控信息按会话关联，对外展现为关联信息
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>归属</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">支持存储大对象（LOB、文件系统、分布式KV）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2014Q3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Coord加入到系统管理，实现Coord自动负载均衡和监控（catalogaddr参数自动保存）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供sequence、time、count等field自动取值功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">split过程中保持数据不出现重复（split窗口开启范围检测，或split窗口禁止读写）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">本地数据文件损坏的恢复（独立元数据文件）优化
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">集群数据一致性校验功能（对CL中数据反复在一个组中的各节点比对，直至收敛到次数和阀值）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">参数动态生效（getConfig/setConfig，需要区分出能匹量修改的和不能匹量修改的，以前匹量修改时可否用系统变量替换等）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Coord流程重构（1、Coord采用session模式； 2、Coord各种操作抽象出几种模板；3、抽象出各种错误下的重试机制）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">批量insert在split窗口中数据会分发错误（批量insert和split互斥， 或者 数据节点转发）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">去除sharding key不能update的约束（ 数据节点转发 ）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">正则表达式性能优化（1、匹配索引；2、字符串匹配）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SequoiaDB集群支持IP地址方式
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LBS（1、2d索引；2、near操作；3、within）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LBS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">数据库审计，对接全文检索引擎（根据策略调用审计接口，推送数据文日志；提供基本的审计策略）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AUDIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">OM（自动部署）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">OM（数据库监控）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">事务死锁检测
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRANS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">索引压缩优化（相同Key保存引用）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Query性能优化（端对端全程序优化，减少内存拷贝，io和锁延时）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain auto rebanlance
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">对于各种操作能够返回详细的错误信息和统计信息
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">日志关联：Data/Catalog/Coord等节点的日志能够通过会话的操作ID进程关联
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">主子表操作优化（1、主表下直接创建分区；2、只能attach被detach的分区；3、保持分区有效性）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">自动更改节点运行的用户（对于正式安装的版本，检测是否存在sdbadmin，如果存在则用该用户启动）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">disable/enable节点（用于让数据库不同步进行快速操作）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">全索引匹配后不需要再匹配match的优化
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">会话关联：Coord监控信息按会话关联，对外展现为关联信息
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">访问计划优化（1、基于规则优化；2、简单基于开销优化）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">索引or和and
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供以集合的方式访问repllog
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DPS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1213,7 +1397,63 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="88">
+  <dxfs count="96">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3676,16 +3916,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L186">
-    <cfRule type="expression" dxfId="87" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="1" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="2" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="3" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="4" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4922,30 +5162,30 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L188">
-    <cfRule type="expression" dxfId="83" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:L11">
-    <cfRule type="expression" dxfId="79" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="17" stopIfTrue="1">
       <formula>$J11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="18" stopIfTrue="1">
       <formula>$J11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="19" stopIfTrue="1">
       <formula>$J11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="20" stopIfTrue="1">
       <formula>OR($J11="CLOSED",$J11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4966,6 +5206,1697 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1">
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:M77"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="39.75" customWidth="1"/>
+    <col min="3" max="3" width="20.125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="24.75" hidden="1" customWidth="1"/>
+    <col min="5" max="6" width="9.375" customWidth="1"/>
+    <col min="7" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="9" width="14.125" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="15.875" customWidth="1"/>
+    <col min="13" max="13" width="17.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="29.45" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="27">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="2">
+        <v>28</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" spans="1:13" ht="40.5" hidden="1">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" spans="1:13" ht="40.5" hidden="1">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="1:13" ht="40.5" hidden="1">
+      <c r="A5" s="27">
+        <v>4</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I5" s="29">
+        <v>8</v>
+      </c>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="31"/>
+    </row>
+    <row r="6" spans="1:13" ht="40.5">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="2">
+        <v>10</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="3"/>
+    </row>
+    <row r="7" spans="1:13" ht="54">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="3"/>
+    </row>
+    <row r="8" spans="1:13" ht="54">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" ht="54">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="2">
+        <v>18</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" ht="54">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" ht="40.5" hidden="1">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I11" s="2">
+        <v>16</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" ht="40.5" hidden="1">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="I12" s="2">
+        <v>5</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" ht="27" hidden="1">
+      <c r="A13" s="27">
+        <v>12</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I13" s="29">
+        <v>3</v>
+      </c>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="31"/>
+    </row>
+    <row r="14" spans="1:13" ht="27" hidden="1">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I14" s="2">
+        <v>70</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" ht="54" hidden="1">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I15" s="2">
+        <v>30</v>
+      </c>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" ht="27">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" s="2">
+        <v>80</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="1:13" ht="27">
+      <c r="A17" s="27">
+        <v>16</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" s="29">
+        <v>80</v>
+      </c>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="31"/>
+    </row>
+    <row r="18" spans="1:13" ht="27" hidden="1">
+      <c r="A18" s="27">
+        <v>17</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="F18" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="29" t="s">
+        <v>195</v>
+      </c>
+      <c r="I18" s="29">
+        <v>25</v>
+      </c>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="31"/>
+    </row>
+    <row r="19" spans="1:13" ht="27" hidden="1">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I19" s="2">
+        <v>10</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="1:13" ht="40.5">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="1:13" ht="27" hidden="1">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I21" s="2">
+        <v>25</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="1:13" ht="40.5">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I22" s="2">
+        <v>20</v>
+      </c>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="1:13" ht="40.5" hidden="1">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" s="2">
+        <v>8</v>
+      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="1:13" ht="40.5" hidden="1">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I24" s="2">
+        <v>8</v>
+      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="1:13" ht="54" hidden="1">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I25" s="2">
+        <v>18</v>
+      </c>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="1:13" ht="54" hidden="1">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I26" s="2">
+        <v>4</v>
+      </c>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="1:13" ht="40.5" hidden="1">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I27" s="2">
+        <v>10</v>
+      </c>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="1:13" ht="27">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I28" s="2">
+        <v>2</v>
+      </c>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="1:13" ht="40.5">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I29" s="2">
+        <v>10</v>
+      </c>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="1:13" ht="40.5" hidden="1">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="I30" s="2">
+        <v>20</v>
+      </c>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="1:13" ht="27" hidden="1">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I31" s="2">
+        <v>20</v>
+      </c>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="1:13" ht="27" hidden="1">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="I32" s="2">
+        <v>30</v>
+      </c>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="1"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="22"/>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="1"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="13"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="14"/>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="13"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="14"/>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="13"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="14"/>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="13"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="14"/>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="13"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="32"/>
+      <c r="M39" s="14"/>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="13"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="14"/>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="13"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="14"/>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="13"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="14"/>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43" s="13"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="14"/>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="13"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="14"/>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="13"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="14"/>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="13"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="14"/>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="13"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="14"/>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="13"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="14"/>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="13"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="14"/>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="13"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="14"/>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51" s="13"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="14"/>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="A52" s="13"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="14"/>
+    </row>
+    <row r="53" spans="1:13">
+      <c r="A53" s="13"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="14"/>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="A54" s="13"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="14"/>
+    </row>
+    <row r="55" spans="1:13">
+      <c r="A55" s="13"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+      <c r="M55" s="14"/>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="A56" s="13"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="8"/>
+      <c r="J56" s="8"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="8"/>
+      <c r="M56" s="14"/>
+    </row>
+    <row r="57" spans="1:13">
+      <c r="A57" s="13"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8"/>
+      <c r="M57" s="14"/>
+    </row>
+    <row r="58" spans="1:13">
+      <c r="A58" s="13"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="8"/>
+      <c r="M58" s="14"/>
+    </row>
+    <row r="59" spans="1:13">
+      <c r="A59" s="13"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="8"/>
+      <c r="M59" s="14"/>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="A60" s="13"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="8"/>
+      <c r="M60" s="14"/>
+    </row>
+    <row r="61" spans="1:13">
+      <c r="A61" s="13"/>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="8"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="8"/>
+      <c r="M61" s="14"/>
+    </row>
+    <row r="62" spans="1:13">
+      <c r="A62" s="13"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="8"/>
+      <c r="M62" s="14"/>
+    </row>
+    <row r="63" spans="1:13">
+      <c r="A63" s="13"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="8"/>
+      <c r="J63" s="8"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="8"/>
+      <c r="M63" s="14"/>
+    </row>
+    <row r="64" spans="1:13">
+      <c r="A64" s="13"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
+      <c r="I64" s="8"/>
+      <c r="J64" s="8"/>
+      <c r="K64" s="8"/>
+      <c r="L64" s="8"/>
+      <c r="M64" s="14"/>
+    </row>
+    <row r="65" spans="1:13">
+      <c r="A65" s="13"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+      <c r="I65" s="8"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="14"/>
+    </row>
+    <row r="66" spans="1:13">
+      <c r="A66" s="13"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="8"/>
+      <c r="J66" s="8"/>
+      <c r="K66" s="8"/>
+      <c r="L66" s="8"/>
+      <c r="M66" s="14"/>
+    </row>
+    <row r="67" spans="1:13">
+      <c r="A67" s="13"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="8"/>
+      <c r="J67" s="8"/>
+      <c r="K67" s="8"/>
+      <c r="L67" s="8"/>
+      <c r="M67" s="14"/>
+    </row>
+    <row r="68" spans="1:13">
+      <c r="A68" s="13"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="8"/>
+      <c r="J68" s="8"/>
+      <c r="K68" s="8"/>
+      <c r="L68" s="8"/>
+      <c r="M68" s="14"/>
+    </row>
+    <row r="69" spans="1:13">
+      <c r="A69" s="13"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="8"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="8"/>
+      <c r="J69" s="8"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="8"/>
+      <c r="M69" s="14"/>
+    </row>
+    <row r="70" spans="1:13">
+      <c r="A70" s="13"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+      <c r="M70" s="14"/>
+    </row>
+    <row r="71" spans="1:13">
+      <c r="A71" s="13"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="8"/>
+      <c r="J71" s="8"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="8"/>
+      <c r="M71" s="14"/>
+    </row>
+    <row r="72" spans="1:13">
+      <c r="A72" s="13"/>
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="8"/>
+      <c r="K72" s="8"/>
+      <c r="L72" s="8"/>
+      <c r="M72" s="14"/>
+    </row>
+    <row r="73" spans="1:13">
+      <c r="A73" s="13"/>
+      <c r="B73" s="8"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="8"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
+      <c r="I73" s="8"/>
+      <c r="J73" s="8"/>
+      <c r="K73" s="8"/>
+      <c r="L73" s="8"/>
+      <c r="M73" s="14"/>
+    </row>
+    <row r="74" spans="1:13">
+      <c r="A74" s="13"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+      <c r="M74" s="14"/>
+    </row>
+    <row r="75" spans="1:13">
+      <c r="A75" s="13"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="8"/>
+      <c r="M75" s="14"/>
+    </row>
+    <row r="76" spans="1:13">
+      <c r="A76" s="13"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="8"/>
+      <c r="M76" s="14"/>
+    </row>
+    <row r="77" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A77" s="15"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16"/>
+      <c r="H77" s="16"/>
+      <c r="I77" s="16"/>
+      <c r="J77" s="16"/>
+      <c r="K77" s="16"/>
+      <c r="L77" s="16"/>
+      <c r="M77" s="17"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M32">
+    <filterColumn colId="4"/>
+    <filterColumn colId="6">
+      <filters>
+        <filter val="高"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A2:M188">
+    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
+      <formula>$K2="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+      <formula>$K2="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+      <formula>$K2="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+      <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11:M11">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+      <formula>$K11="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+      <formula>$K11="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+      <formula>$K11="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+      <formula>OR($K11="CLOSED",$K11="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F77">
+      <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G77">
+      <formula1>"高,中,低"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K77">
+      <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L74"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -6517,268 +8448,268 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:L9">
-    <cfRule type="expression" dxfId="75" priority="73" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="73" stopIfTrue="1">
       <formula>$J9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="74" stopIfTrue="1">
       <formula>$J9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="75" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="75" stopIfTrue="1">
       <formula>$J9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="76" stopIfTrue="1">
       <formula>OR($J9="CLOSED",$J9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:L10">
-    <cfRule type="expression" dxfId="71" priority="69" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="69" stopIfTrue="1">
       <formula>$J10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="70" stopIfTrue="1">
       <formula>$J10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="71" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="71" stopIfTrue="1">
       <formula>$J10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="72" stopIfTrue="1">
       <formula>OR($J10="CLOSED",$J10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:L11">
-    <cfRule type="expression" dxfId="67" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="65" stopIfTrue="1">
       <formula>$J11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="66" stopIfTrue="1">
       <formula>$J11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="67" stopIfTrue="1">
       <formula>$J11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="68" stopIfTrue="1">
       <formula>OR($J11="CLOSED",$J11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:L12">
-    <cfRule type="expression" dxfId="63" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="61" stopIfTrue="1">
       <formula>$J12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="62" stopIfTrue="1">
       <formula>$J12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="63" stopIfTrue="1">
       <formula>$J12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="64" stopIfTrue="1">
       <formula>OR($J12="CLOSED",$J12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:L13">
-    <cfRule type="expression" dxfId="59" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="57" stopIfTrue="1">
       <formula>$J13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="58" stopIfTrue="1">
       <formula>$J13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="59" stopIfTrue="1">
       <formula>$J13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="60" stopIfTrue="1">
       <formula>OR($J13="CLOSED",$J13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:L14">
-    <cfRule type="expression" dxfId="55" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="53" stopIfTrue="1">
       <formula>$J14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="54" stopIfTrue="1">
       <formula>$J14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="55" stopIfTrue="1">
       <formula>$J14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="56" stopIfTrue="1">
       <formula>OR($J14="CLOSED",$J14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:L15">
-    <cfRule type="expression" dxfId="51" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="49" stopIfTrue="1">
       <formula>$J15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="50" stopIfTrue="1">
       <formula>$J15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="51" stopIfTrue="1">
       <formula>$J15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="52" stopIfTrue="1">
       <formula>OR($J15="CLOSED",$J15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:L16">
-    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="45" stopIfTrue="1">
       <formula>$J16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="46" stopIfTrue="1">
       <formula>$J16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="47" stopIfTrue="1">
       <formula>$J16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="48" stopIfTrue="1">
       <formula>OR($J16="CLOSED",$J16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:L17">
-    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="41" stopIfTrue="1">
       <formula>$J17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="42" stopIfTrue="1">
       <formula>$J17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="43" stopIfTrue="1">
       <formula>$J17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="44" stopIfTrue="1">
       <formula>OR($J17="CLOSED",$J17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:L18">
-    <cfRule type="expression" dxfId="39" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="37" stopIfTrue="1">
       <formula>$J18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="38" stopIfTrue="1">
       <formula>$J18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="39" stopIfTrue="1">
       <formula>$J18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="40" stopIfTrue="1">
       <formula>OR($J18="CLOSED",$J18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:L19">
-    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="33" stopIfTrue="1">
       <formula>$J19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="34" stopIfTrue="1">
       <formula>$J19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="35" stopIfTrue="1">
       <formula>$J19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="36" stopIfTrue="1">
       <formula>OR($J19="CLOSED",$J19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:L20">
-    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="29" stopIfTrue="1">
       <formula>$J20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="30" stopIfTrue="1">
       <formula>$J20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="31" stopIfTrue="1">
       <formula>$J20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="32" stopIfTrue="1">
       <formula>OR($J20="CLOSED",$J20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:L21">
-    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="25" stopIfTrue="1">
       <formula>$J21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="26" stopIfTrue="1">
       <formula>$J21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="27" stopIfTrue="1">
       <formula>$J21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="28" stopIfTrue="1">
       <formula>OR($J21="CLOSED",$J21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:L23">
-    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="21" stopIfTrue="1">
       <formula>$J22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="22" stopIfTrue="1">
       <formula>$J22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="23" stopIfTrue="1">
       <formula>$J22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="24" stopIfTrue="1">
       <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:H22">
-    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="17" stopIfTrue="1">
       <formula>$J22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="18" stopIfTrue="1">
       <formula>$J22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="19" stopIfTrue="1">
       <formula>$J22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="20" stopIfTrue="1">
       <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="13" stopIfTrue="1">
       <formula>$J23="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="14" stopIfTrue="1">
       <formula>$J23="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="15" stopIfTrue="1">
       <formula>$J23="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="16" stopIfTrue="1">
       <formula>OR($J23="CLOSED",$J23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:L25">
-    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="9" stopIfTrue="1">
       <formula>$J24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="10" stopIfTrue="1">
       <formula>$J24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="11" stopIfTrue="1">
       <formula>$J24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="12" stopIfTrue="1">
       <formula>OR($J24="CLOSED",$J24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="5" stopIfTrue="1">
       <formula>$J25="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="6" stopIfTrue="1">
       <formula>$J25="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="7" stopIfTrue="1">
       <formula>$J25="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="8" stopIfTrue="1">
       <formula>OR($J25="CLOSED",$J25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:L26">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
       <formula>$J26="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
       <formula>$J26="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
       <formula>$J26="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
       <formula>OR($J26="CLOSED",$J26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="215">
   <si>
     <r>
       <t>描述</t>
@@ -1061,6 +1061,22 @@
   </si>
   <si>
     <t>DPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武赟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘圳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林友滨、何嘉文、谭钊波</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5292,8 +5308,12 @@
       <c r="I2" s="2">
         <v>28</v>
       </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="L2" s="2"/>
       <c r="M2" s="3"/>
     </row>
@@ -5437,8 +5457,12 @@
       <c r="I7" s="2">
         <v>8</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="3"/>
     </row>
@@ -5524,8 +5548,12 @@
       <c r="I10" s="2">
         <v>8</v>
       </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="J10" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="3"/>
     </row>
@@ -5698,8 +5726,12 @@
       <c r="I16" s="2">
         <v>80</v>
       </c>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
+      <c r="J16" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="L16" s="2"/>
       <c r="M16" s="3"/>
     </row>
@@ -6853,30 +6885,30 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M188">
-    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="5" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="6" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="7" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="8" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:M11">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="1" stopIfTrue="1">
       <formula>$K11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="2" stopIfTrue="1">
       <formula>$K11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="3" stopIfTrue="1">
       <formula>$K11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="4" stopIfTrue="1">
       <formula>OR($K11="CLOSED",$K11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8448,268 +8480,268 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:L9">
-    <cfRule type="expression" dxfId="83" priority="73" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="73" stopIfTrue="1">
       <formula>$J9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="74" stopIfTrue="1">
       <formula>$J9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="75" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="75" stopIfTrue="1">
       <formula>$J9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="76" stopIfTrue="1">
       <formula>OR($J9="CLOSED",$J9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:L10">
-    <cfRule type="expression" dxfId="79" priority="69" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="69" stopIfTrue="1">
       <formula>$J10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="70" stopIfTrue="1">
       <formula>$J10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="71" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="71" stopIfTrue="1">
       <formula>$J10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="72" stopIfTrue="1">
       <formula>OR($J10="CLOSED",$J10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:L11">
-    <cfRule type="expression" dxfId="75" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="65" stopIfTrue="1">
       <formula>$J11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="66" stopIfTrue="1">
       <formula>$J11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="67" stopIfTrue="1">
       <formula>$J11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="68" stopIfTrue="1">
       <formula>OR($J11="CLOSED",$J11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:L12">
-    <cfRule type="expression" dxfId="71" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="61" stopIfTrue="1">
       <formula>$J12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="62" stopIfTrue="1">
       <formula>$J12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="63" stopIfTrue="1">
       <formula>$J12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="64" stopIfTrue="1">
       <formula>OR($J12="CLOSED",$J12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:L13">
-    <cfRule type="expression" dxfId="67" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="57" stopIfTrue="1">
       <formula>$J13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="58" stopIfTrue="1">
       <formula>$J13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="59" stopIfTrue="1">
       <formula>$J13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="60" stopIfTrue="1">
       <formula>OR($J13="CLOSED",$J13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:L14">
-    <cfRule type="expression" dxfId="63" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="53" stopIfTrue="1">
       <formula>$J14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="54" stopIfTrue="1">
       <formula>$J14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="55" stopIfTrue="1">
       <formula>$J14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="56" stopIfTrue="1">
       <formula>OR($J14="CLOSED",$J14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:L15">
-    <cfRule type="expression" dxfId="59" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="49" stopIfTrue="1">
       <formula>$J15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="50" stopIfTrue="1">
       <formula>$J15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="51" stopIfTrue="1">
       <formula>$J15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="52" stopIfTrue="1">
       <formula>OR($J15="CLOSED",$J15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:L16">
-    <cfRule type="expression" dxfId="55" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
       <formula>$J16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
       <formula>$J16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
       <formula>$J16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
       <formula>OR($J16="CLOSED",$J16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:L17">
-    <cfRule type="expression" dxfId="51" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
       <formula>$J17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
       <formula>$J17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="43" stopIfTrue="1">
       <formula>$J17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="44" stopIfTrue="1">
       <formula>OR($J17="CLOSED",$J17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:L18">
-    <cfRule type="expression" dxfId="47" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="37" stopIfTrue="1">
       <formula>$J18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="38" stopIfTrue="1">
       <formula>$J18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="39" stopIfTrue="1">
       <formula>$J18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="40" stopIfTrue="1">
       <formula>OR($J18="CLOSED",$J18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:L19">
-    <cfRule type="expression" dxfId="43" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
       <formula>$J19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
       <formula>$J19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
       <formula>$J19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
       <formula>OR($J19="CLOSED",$J19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:L20">
-    <cfRule type="expression" dxfId="39" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
       <formula>$J20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
       <formula>$J20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="31" stopIfTrue="1">
       <formula>$J20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
       <formula>OR($J20="CLOSED",$J20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:L21">
-    <cfRule type="expression" dxfId="35" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
       <formula>$J21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
       <formula>$J21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="27" stopIfTrue="1">
       <formula>$J21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="28" stopIfTrue="1">
       <formula>OR($J21="CLOSED",$J21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:L23">
-    <cfRule type="expression" dxfId="31" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
       <formula>$J22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
       <formula>$J22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
       <formula>$J22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
       <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:H22">
-    <cfRule type="expression" dxfId="27" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
       <formula>$J22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
       <formula>$J22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
       <formula>$J22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
       <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="23" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
       <formula>$J23="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="14" stopIfTrue="1">
       <formula>$J23="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="15" stopIfTrue="1">
       <formula>$J23="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
       <formula>OR($J23="CLOSED",$J23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:L25">
-    <cfRule type="expression" dxfId="19" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
       <formula>$J24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
       <formula>$J24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
       <formula>$J24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
       <formula>OR($J24="CLOSED",$J24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="15" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
       <formula>$J25="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
       <formula>$J25="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
       <formula>$J25="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
       <formula>OR($J25="CLOSED",$J25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:L26">
-    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>$J26="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
       <formula>$J26="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>$J26="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
       <formula>OR($J26="CLOSED",$J26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="2014年1季度" sheetId="1" r:id="rId1"/>
     <sheet name="2014年2季度" sheetId="3" r:id="rId2"/>
-    <sheet name="2014年3季度" sheetId="4" r:id="rId3"/>
+    <sheet name="2014年" sheetId="4" r:id="rId3"/>
     <sheet name="已完成任务" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$L$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2014年3季度'!$A$1:$M$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2014年'!$A$1:$M$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$L$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$L$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="242">
   <si>
     <r>
       <t>描述</t>
@@ -220,15 +220,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">批量Insert过程中，Split完成，导致数据Insert到错误的节点
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHARD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">索引排序、非索引排序针对数组时，需要把数组相同的内容放在一起，以保证聚集的正确性
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -361,11 +352,6 @@
   </si>
   <si>
     <t>RTN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">查询进行Memory总量，以及Dump内存信息
-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -698,385 +684,548 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">PMD启动重构，启动分两个阶段，第一阶段Init，用于建立端口，初始化资源；第二阶段启动定时器，开始业务
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Interrupt/Disconnect EDU命令，中断EDU操作
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">创建删除Domain，Domain中增加删除RG
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">mth match、ixm优化和去mongo影子
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ShardingKey需要加上0,1…的Field信息以方便外部显示
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">加载文件由于元数据损坏的文件如何rebuild
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内置SQL anti-join</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-238</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CATA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-159 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">定时将DMS中MMAP数据脏页持久化至磁盘，提升性能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PMD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘圳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">所有驱动增加多个连接的IP+端口，如果一个IP连接不成功自动选择下一个
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-120 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRIVER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>导入数据时，能够指定字段类型，并设置默认值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-132</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOOL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何嘉文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbexprt 加入新参数, 可以指定不导出_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-139</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-140 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王涛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加$isnull匹配条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-155</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MTH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉、武赟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉、武赟、谭钊波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武赟、谭钊波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-239</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">创建CS可指定域
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">显示查询的访问计划
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-243</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MTH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武赟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">会话关联：监控信息按会话关联，对外展现为关联信息
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>归属</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">支持存储大对象（LOB、文件系统、分布式KV）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2014Q3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Coord加入到系统管理，实现Coord自动负载均衡和监控（catalogaddr参数自动保存）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供sequence、time、count等field自动取值功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">split过程中保持数据不出现重复（split窗口开启范围检测，或split窗口禁止读写）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">本地数据文件损坏的恢复（独立元数据文件）优化
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">集群数据一致性校验功能（对CL中数据反复在一个组中的各节点比对，直至收敛到次数和阀值）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Coord流程重构（1、Coord采用session模式； 2、Coord各种操作抽象出几种模板；3、抽象出各种错误下的重试机制）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">批量insert在split窗口中数据会分发错误（批量insert和split互斥， 或者 数据节点转发）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">去除sharding key不能update的约束（ 数据节点转发 ）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LBS（1、2d索引；2、near操作；3、within）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LBS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">数据库审计，对接全文检索引擎（根据策略调用审计接口，推送数据文日志；提供基本的审计策略）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AUDIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">OM（自动部署）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">事务死锁检测
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRANS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">索引压缩优化（相同Key保存引用）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Query性能优化（端对端全程序优化，减少内存拷贝，io和锁延时）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain auto rebanlance
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">对于各种操作能够返回详细的错误信息和统计信息
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">日志关联：Data/Catalog/Coord等节点的日志能够通过会话的操作ID进程关联
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">主子表操作优化（1、主表下直接创建分区；2、只能attach被detach的分区；3、保持分区有效性）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">自动更改节点运行的用户（对于正式安装的版本，检测是否存在sdbadmin，如果存在则用该用户启动）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">disable/enable节点（用于让数据库不同步进行快速操作）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">全索引匹配后不需要再匹配match的优化
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">会话关联：Coord监控信息按会话关联，对外展现为关联信息
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">访问计划优化（1、基于规则优化；2、简单基于开销优化）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">索引or和and
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供以集合的方式访问repllog
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武赟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘圳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林友滨、何嘉文、谭钊波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">查询进程Memory总量，以及Dump内存信息
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2014Q4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供兼容mongoDB驱动的接口
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2014Q4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Coord上需要确保Insert时OID的自动生成
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COORD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">创建Collection默认调整为基于OID的Hash分区
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Collection需要支持在DMS层读写的并发性（可以考虑Collection Latch为Block Latch）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Coord/Data节点需要提供业务层的Rest接口
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PMD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">OM提供“节点监控管理”、“业务监控管理”功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">OM提供“告警”和“统计”功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">OM提供“配置管理”和“配置下发”功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">参数动态生效（getConfig/setConfig，需要区分出能批量修改的和不能批量修改的，以前批量修改时可否用系统变量替换等）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>正则表达式性能优化（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.14999847407452621"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1、匹配索引</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">；2、字符串匹配）
+</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SequoiaDB集群提供对IP地址和Hostname两种方式的支持
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">OM提供“操作日志”管理功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalog组提供删除节点功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">JS脚本Root用户信息保护
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OMA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供导出/导入SequoiaDB元数据信息工具
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOOL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">OMA对象功能加强，提供“listNode, getNodeConfig, setNodeConfig, updateNodeConfig”等功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OMA/SDB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">dropCS时，能自动关闭所有打开的context
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RTN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供LOB的导入和导出功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">读取LOB的完整性保证（如何保证在多幅本中的LOB是同一LOB对象，尤其是在LOB支持随机写时）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain中增加add group, del group操作
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">完善collection alter功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve">Truncate collection功能
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">PMD启动重构，启动分两个阶段，第一阶段Init，用于建立端口，初始化资源；第二阶段启动定时器，开始业务
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Interrupt/Disconnect EDU命令，中断EDU操作
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">创建删除Domain，Domain中增加删除RG
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">mth match、ixm优化和去mongo影子
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">ShardingKey需要加上0,1…的Field信息以方便外部显示
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">加载文件由于元数据损坏的文件如何rebuild
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>许建辉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内置SQL anti-join</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEQUOIADBMAINSTREAM-238</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CATA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DMS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">SEQUOIADBMAINSTREAM-159 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">定时将DMS中MMAP数据脏页持久化至磁盘，提升性能
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PMD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>许建辉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘圳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">所有驱动增加多个连接的IP+端口，如果一个IP连接不成功自动选择下一个
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">SEQUOIADBMAINSTREAM-120 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DRIVER</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>导入数据时，能够指定字段类型，并设置默认值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEQUOIADBMAINSTREAM-132</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TOOL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>何嘉文</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdbexprt 加入新参数, 可以指定不导出_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEQUOIADBMAINSTREAM-139</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">SEQUOIADBMAINSTREAM-140 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>王涛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增加$isnull匹配条件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEQUOIADBMAINSTREAM-155</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MTH</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>许建辉、武赟</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>许建辉、武赟、谭钊波</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武赟、谭钊波</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEQUOIADBMAINSTREAM-239</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEQUOIADBMAINSTREAM-240</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">创建CS可指定域
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">显示查询的访问计划
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEQUOIADBMAINSTREAM-243</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MTH</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武赟</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">会话关联：监控信息按会话关联，对外展现为关联信息
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>归属</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">支持存储大对象（LOB、文件系统、分布式KV）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2014Q3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Coord加入到系统管理，实现Coord自动负载均衡和监控（catalogaddr参数自动保存）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">提供sequence、time、count等field自动取值功能
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">split过程中保持数据不出现重复（split窗口开启范围检测，或split窗口禁止读写）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CLS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">本地数据文件损坏的恢复（独立元数据文件）优化
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">集群数据一致性校验功能（对CL中数据反复在一个组中的各节点比对，直至收敛到次数和阀值）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">参数动态生效（getConfig/setConfig，需要区分出能匹量修改的和不能匹量修改的，以前匹量修改时可否用系统变量替换等）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Coord流程重构（1、Coord采用session模式； 2、Coord各种操作抽象出几种模板；3、抽象出各种错误下的重试机制）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">批量insert在split窗口中数据会分发错误（批量insert和split互斥， 或者 数据节点转发）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">去除sharding key不能update的约束（ 数据节点转发 ）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">正则表达式性能优化（1、匹配索引；2、字符串匹配）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">SequoiaDB集群支持IP地址方式
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">LBS（1、2d索引；2、near操作；3、within）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LBS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">数据库审计，对接全文检索引擎（根据策略调用审计接口，推送数据文日志；提供基本的审计策略）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AUDIT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">OM（自动部署）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">OM（数据库监控）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">事务死锁检测
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TRANS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">索引压缩优化（相同Key保存引用）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Query性能优化（端对端全程序优化，减少内存拷贝，io和锁延时）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Domain auto rebanlance
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">对于各种操作能够返回详细的错误信息和统计信息
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">日志关联：Data/Catalog/Coord等节点的日志能够通过会话的操作ID进程关联
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">主子表操作优化（1、主表下直接创建分区；2、只能attach被detach的分区；3、保持分区有效性）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">自动更改节点运行的用户（对于正式安装的版本，检测是否存在sdbadmin，如果存在则用该用户启动）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">disable/enable节点（用于让数据库不同步进行快速操作）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">全索引匹配后不需要再匹配match的优化
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">会话关联：Coord监控信息按会话关联，对外展现为关联信息
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">访问计划优化（1、基于规则优化；2、简单基于开销优化）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OPT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">索引or和and
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">提供以集合的方式访问repllog
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DPS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武赟</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘圳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>许建辉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>林友滨、何嘉文、谭钊波</t>
+    <t xml:space="preserve">OM安装部署功能优化（各种异常下的恢复、遗留问题，参数检测等）
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1084,7 +1233,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1129,6 +1278,14 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1413,7 +1570,259 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="96">
+  <dxfs count="132">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2379,7 +2788,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -2404,10 +2813,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -2463,7 +2872,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -2532,10 +2941,10 @@
         <v>1</v>
       </c>
       <c r="I5" s="29" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J5" s="29" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="K5" s="30">
         <v>41679</v>
@@ -2544,7 +2953,7 @@
     </row>
     <row r="6" spans="1:12" ht="40.5">
       <c r="A6" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>25</v>
@@ -2552,15 +2961,17 @@
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3</v>
+      </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -2568,7 +2979,7 @@
     </row>
     <row r="7" spans="1:12" ht="40.5">
       <c r="A7" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>27</v>
@@ -2576,25 +2987,23 @@
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="2">
-        <v>3</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="1:12" ht="40.5">
+    <row r="8" spans="1:12" ht="67.5">
       <c r="A8" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>29</v>
@@ -2605,10 +3014,10 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -2616,25 +3025,27 @@
       <c r="K8" s="2"/>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="1:12" ht="67.5">
+    <row r="9" spans="1:12" ht="27">
       <c r="A9" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="H9" s="2">
+        <v>15</v>
+      </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -2642,7 +3053,7 @@
     </row>
     <row r="10" spans="1:12" ht="27">
       <c r="A10" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>32</v>
@@ -2650,16 +3061,16 @@
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="2" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H10" s="2">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -2668,7 +3079,7 @@
     </row>
     <row r="11" spans="1:12" ht="27">
       <c r="A11" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>34</v>
@@ -2676,16 +3087,16 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H11" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -2694,7 +3105,7 @@
     </row>
     <row r="12" spans="1:12" ht="27">
       <c r="A12" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>36</v>
@@ -2702,17 +3113,15 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2">
-        <v>8</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -2720,23 +3129,25 @@
     </row>
     <row r="13" spans="1:12" ht="27">
       <c r="A13" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="H13" s="2">
+        <v>5</v>
+      </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -2744,33 +3155,37 @@
     </row>
     <row r="14" spans="1:12" ht="27">
       <c r="A14" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H14" s="2">
-        <v>5</v>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="K14" s="2"/>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:12" ht="27">
       <c r="A15" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>40</v>
@@ -2778,43 +3193,39 @@
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H15" s="2">
-        <v>13</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>64</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="3"/>
     </row>
     <row r="16" spans="1:12" ht="27">
       <c r="A16" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="H16" s="2">
         <v>4</v>
@@ -2826,24 +3237,24 @@
     </row>
     <row r="17" spans="1:12" ht="27">
       <c r="A17" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -2852,24 +3263,24 @@
     </row>
     <row r="18" spans="1:12" ht="27">
       <c r="A18" s="1">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H18" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -2877,55 +3288,51 @@
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="1:12" ht="27">
-      <c r="A19" s="27">
+      <c r="A19" s="1">
+        <v>26</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="H19" s="29">
-        <v>8</v>
-      </c>
-      <c r="I19" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="J19" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="K19" s="29"/>
-      <c r="L19" s="31"/>
+      <c r="G19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="2">
+        <v>4</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="3"/>
     </row>
     <row r="20" spans="1:12" ht="27">
       <c r="A20" s="1">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H20" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -2934,24 +3341,24 @@
     </row>
     <row r="21" spans="1:12" ht="27">
       <c r="A21" s="1">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>50</v>
+        <v>207</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H21" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -2959,77 +3366,87 @@
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="1:12" ht="27">
-      <c r="A22" s="1">
-        <v>25</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="2" t="s">
+      <c r="A22" s="27">
+        <v>29</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="H22" s="2">
-        <v>10</v>
-      </c>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="3"/>
+      <c r="F22" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="H22" s="29">
+        <v>20</v>
+      </c>
+      <c r="I22" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="J22" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="K22" s="29"/>
+      <c r="L22" s="31"/>
     </row>
     <row r="23" spans="1:12" ht="27">
-      <c r="A23" s="1">
-        <v>26</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" s="2">
-        <v>4</v>
-      </c>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="1:12" ht="27">
+      <c r="A23" s="27">
+        <v>30</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="H23" s="29">
+        <v>20</v>
+      </c>
+      <c r="I23" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="J23" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="K23" s="29"/>
+      <c r="L23" s="31"/>
+    </row>
+    <row r="24" spans="1:12" ht="40.5">
       <c r="A24" s="1">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H24" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
@@ -3038,354 +3455,296 @@
     </row>
     <row r="25" spans="1:12" ht="27">
       <c r="A25" s="1">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="3"/>
     </row>
-    <row r="26" spans="1:12" ht="27">
-      <c r="A26" s="27">
-        <v>29</v>
-      </c>
-      <c r="B26" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="29" t="s">
+    <row r="26" spans="1:12" ht="40.5">
+      <c r="A26" s="1">
+        <v>33</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="H26" s="29">
-        <v>20</v>
-      </c>
-      <c r="I26" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="J26" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="K26" s="29"/>
-      <c r="L26" s="31"/>
-    </row>
-    <row r="27" spans="1:12" ht="27">
-      <c r="A27" s="27">
-        <v>30</v>
-      </c>
-      <c r="B27" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="E27" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="F27" s="29" t="s">
+      <c r="G26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H26" s="2">
+        <v>8</v>
+      </c>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="1:12" ht="54">
+      <c r="A27" s="1">
+        <v>34</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="H27" s="29">
-        <v>20</v>
-      </c>
-      <c r="I27" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="J27" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="K27" s="29"/>
-      <c r="L27" s="31"/>
-    </row>
-    <row r="28" spans="1:12" ht="40.5">
+      <c r="G27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H27" s="2">
+        <v>8</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="1:12" ht="27">
       <c r="A28" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="2" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="H28" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="3"/>
     </row>
-    <row r="29" spans="1:12" ht="27">
+    <row r="29" spans="1:12" ht="54">
       <c r="A29" s="1">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="H29" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
+      <c r="K29" s="21"/>
       <c r="L29" s="3"/>
     </row>
     <row r="30" spans="1:12" ht="40.5">
       <c r="A30" s="1">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="3"/>
     </row>
-    <row r="31" spans="1:12" ht="54">
+    <row r="31" spans="1:12" ht="27">
       <c r="A31" s="1">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="H31" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" s="3"/>
     </row>
-    <row r="32" spans="1:12" ht="27">
+    <row r="32" spans="1:12" ht="40.5">
       <c r="A32" s="1">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
+      <c r="D32" s="8" t="s">
+        <v>106</v>
+      </c>
       <c r="E32" s="2" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H32" s="2">
-        <v>2</v>
-      </c>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="1:12" ht="54">
-      <c r="A33" s="1">
-        <v>41</v>
+        <v>3</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K32" s="21">
+        <v>41679</v>
+      </c>
+      <c r="L32" s="22">
+        <v>41679</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="27">
+      <c r="A33" s="13">
+        <v>53</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="E33" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" s="2">
-        <v>2</v>
-      </c>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="1:12" ht="40.5">
-      <c r="A34" s="1">
-        <v>44</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>77</v>
-      </c>
+      <c r="G33" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="14"/>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="13"/>
+      <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
-      <c r="E34" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H34" s="2">
-        <v>15</v>
-      </c>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="1:12" ht="27">
-      <c r="A35" s="1">
-        <v>45</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>78</v>
-      </c>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="14"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="13"/>
+      <c r="B35" s="8"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
-      <c r="E35" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H35" s="2">
-        <v>15</v>
-      </c>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="36" spans="1:12" ht="40.5">
-      <c r="A36" s="1">
-        <v>46</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>118</v>
-      </c>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="14"/>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="13"/>
+      <c r="B36" s="8"/>
       <c r="C36" s="8"/>
-      <c r="D36" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H36" s="2">
-        <v>3</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K36" s="21">
-        <v>41679</v>
-      </c>
-      <c r="L36" s="22">
-        <v>41679</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="27">
-      <c r="A37" s="13">
-        <v>53</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>115</v>
-      </c>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="14"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="13"/>
+      <c r="B37" s="8"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
-      <c r="E37" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>20</v>
-      </c>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
@@ -3854,105 +4213,49 @@
       <c r="K70" s="8"/>
       <c r="L70" s="14"/>
     </row>
-    <row r="71" spans="1:12">
-      <c r="A71" s="13"/>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="14"/>
-    </row>
-    <row r="72" spans="1:12">
-      <c r="A72" s="13"/>
-      <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="14"/>
-    </row>
-    <row r="73" spans="1:12">
-      <c r="A73" s="13"/>
-      <c r="B73" s="8"/>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="8"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="14"/>
-    </row>
-    <row r="74" spans="1:12">
-      <c r="A74" s="13"/>
-      <c r="B74" s="8"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="14"/>
-    </row>
-    <row r="75" spans="1:12" ht="14.25" thickBot="1">
-      <c r="A75" s="15"/>
-      <c r="B75" s="16"/>
-      <c r="C75" s="16"/>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="16"/>
-      <c r="H75" s="16"/>
-      <c r="I75" s="16"/>
-      <c r="J75" s="16"/>
-      <c r="K75" s="16"/>
-      <c r="L75" s="17"/>
+    <row r="71" spans="1:12" ht="14.25" thickBot="1">
+      <c r="A71" s="15"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="16"/>
+      <c r="H71" s="16"/>
+      <c r="I71" s="16"/>
+      <c r="J71" s="16"/>
+      <c r="K71" s="16"/>
+      <c r="L71" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L37">
+  <autoFilter ref="A1:L33">
     <filterColumn colId="2"/>
     <filterColumn colId="3"/>
     <filterColumn colId="5"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:L186">
-    <cfRule type="expression" dxfId="95" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:L182">
+    <cfRule type="expression" dxfId="131" priority="1" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="130" priority="2" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="129" priority="3" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="128" priority="4" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E75">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E71">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F75">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F71">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J75">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J71">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3966,7 +4269,7 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -3991,10 +4294,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -4026,12 +4329,12 @@
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -4046,12 +4349,12 @@
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -4066,12 +4369,12 @@
         <v>4</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -4086,12 +4389,12 @@
         <v>5</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C5" s="28"/>
       <c r="D5" s="28"/>
       <c r="E5" s="29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F5" s="29"/>
       <c r="G5" s="29"/>
@@ -4106,12 +4409,12 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -4126,12 +4429,12 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -4146,12 +4449,12 @@
         <v>8</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -4166,12 +4469,12 @@
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -4181,47 +4484,41 @@
       <c r="K9" s="2"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="1:12" ht="27">
-      <c r="A10" s="1">
-        <v>11</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="3"/>
+    <row r="10" spans="1:12">
+      <c r="A10" s="27">
+        <v>19</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="31"/>
     </row>
     <row r="11" spans="1:12" ht="40.5">
       <c r="A11" s="1">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="2">
-        <v>5</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -4229,15 +4526,15 @@
     </row>
     <row r="12" spans="1:12" ht="27">
       <c r="A12" s="1">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -4248,64 +4545,46 @@
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="27">
-        <v>19</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="31"/>
-    </row>
-    <row r="14" spans="1:12" ht="40.5">
-      <c r="A14" s="1">
-        <v>27</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" ht="27">
-      <c r="A15" s="1">
-        <v>29</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="3"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="27"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="31"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="27"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="31"/>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="1"/>
@@ -4322,32 +4601,32 @@
       <c r="L16" s="3"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="27"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="31"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="3"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="27"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="31"/>
+      <c r="A18" s="1"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="3"/>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="1"/>
@@ -4458,7 +4737,7 @@
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
+      <c r="K26" s="21"/>
       <c r="L26" s="3"/>
     </row>
     <row r="27" spans="1:12">
@@ -4500,7 +4779,7 @@
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
-      <c r="K29" s="21"/>
+      <c r="K29" s="2"/>
       <c r="L29" s="3"/>
     </row>
     <row r="30" spans="1:12">
@@ -4514,8 +4793,8 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="3"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="22"/>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="1"/>
@@ -4532,46 +4811,46 @@
       <c r="L31" s="3"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1"/>
+      <c r="A32" s="13"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="3"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="14"/>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1"/>
+      <c r="A33" s="13"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="22"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="14"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1"/>
+      <c r="A34" s="13"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="3"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="14"/>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="13"/>
@@ -4598,7 +4877,7 @@
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
+      <c r="K36" s="32"/>
       <c r="L36" s="14"/>
     </row>
     <row r="37" spans="1:12">
@@ -4640,7 +4919,7 @@
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
-      <c r="K39" s="32"/>
+      <c r="K39" s="8"/>
       <c r="L39" s="14"/>
     </row>
     <row r="40" spans="1:12">
@@ -5119,100 +5398,44 @@
       <c r="K73" s="8"/>
       <c r="L73" s="14"/>
     </row>
-    <row r="74" spans="1:12">
-      <c r="A74" s="13"/>
-      <c r="B74" s="8"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="14"/>
-    </row>
-    <row r="75" spans="1:12">
-      <c r="A75" s="13"/>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="8"/>
-      <c r="I75" s="8"/>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8"/>
-      <c r="L75" s="14"/>
-    </row>
-    <row r="76" spans="1:12">
-      <c r="A76" s="13"/>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="14"/>
-    </row>
-    <row r="77" spans="1:12" ht="14.25" thickBot="1">
-      <c r="A77" s="15"/>
-      <c r="B77" s="16"/>
-      <c r="C77" s="16"/>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16"/>
-      <c r="H77" s="16"/>
-      <c r="I77" s="16"/>
-      <c r="J77" s="16"/>
-      <c r="K77" s="16"/>
-      <c r="L77" s="17"/>
+    <row r="74" spans="1:12" ht="14.25" thickBot="1">
+      <c r="A74" s="15"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="16"/>
+      <c r="I74" s="16"/>
+      <c r="J74" s="16"/>
+      <c r="K74" s="16"/>
+      <c r="L74" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:L188">
-    <cfRule type="expression" dxfId="91" priority="21" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:L185">
+    <cfRule type="expression" dxfId="3" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A11:L11">
-    <cfRule type="expression" dxfId="87" priority="17" stopIfTrue="1">
-      <formula>$J11="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="18" stopIfTrue="1">
-      <formula>$J11="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="19" stopIfTrue="1">
-      <formula>$J11="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="20" stopIfTrue="1">
-      <formula>OR($J11="CLOSED",$J11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J77">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J74">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F77">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F74">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E77">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E74">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5226,7 +5449,7 @@
   <sheetPr filterMode="1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -5251,13 +5474,13 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>1</v>
@@ -5284,361 +5507,337 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="27">
+    <row r="2" spans="1:13" ht="40.5">
       <c r="A2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="I2" s="2">
-        <v>28</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>87</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="3"/>
     </row>
     <row r="3" spans="1:13" ht="40.5" hidden="1">
       <c r="A3" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="2">
-        <v>8</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="3"/>
     </row>
-    <row r="4" spans="1:13" ht="40.5" hidden="1">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8" t="s">
+    <row r="4" spans="1:13" ht="40.5">
+      <c r="A4" s="27">
+        <v>4</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="I4" s="29">
+        <v>8</v>
+      </c>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="31"/>
+    </row>
+    <row r="5" spans="1:13" ht="40.5" hidden="1">
+      <c r="A5" s="1">
+        <v>5</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="2">
-        <v>8</v>
-      </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="3"/>
-    </row>
-    <row r="5" spans="1:13" ht="40.5" hidden="1">
-      <c r="A5" s="27">
-        <v>4</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="G5" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="I5" s="29">
-        <v>8</v>
-      </c>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="31"/>
-    </row>
-    <row r="6" spans="1:13" ht="40.5">
+      <c r="H5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="2">
+        <v>16</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" spans="1:13" ht="54" hidden="1">
       <c r="A6" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>180</v>
+        <v>223</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="I6" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:13" ht="54">
+    <row r="7" spans="1:13" ht="54" hidden="1">
       <c r="A7" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="I7" s="2">
-        <v>8</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>87</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="54">
+    <row r="8" spans="1:13" ht="40.5" hidden="1">
       <c r="A8" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I8" s="2">
-        <v>5</v>
-      </c>
+      <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:13" ht="54">
+    <row r="9" spans="1:13" ht="40.5" hidden="1">
       <c r="A9" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>13</v>
+        <v>157</v>
       </c>
       <c r="I9" s="2">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="1:13" ht="54">
+    <row r="10" spans="1:13" ht="27" hidden="1">
       <c r="A10" s="1">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I10" s="2">
-        <v>8</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>87</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" spans="1:13" ht="40.5" hidden="1">
+    <row r="11" spans="1:13" ht="54" hidden="1">
       <c r="A11" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I11" s="2">
-        <v>16</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="40.5" hidden="1">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="I12" s="2">
-        <v>5</v>
-      </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="3"/>
+    <row r="12" spans="1:13" ht="40.5">
+      <c r="A12" s="27">
+        <v>16</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="29">
+        <v>25</v>
+      </c>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="31"/>
     </row>
     <row r="13" spans="1:13" ht="27" hidden="1">
       <c r="A13" s="27">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C13" s="28"/>
       <c r="D13" s="28"/>
       <c r="E13" s="28" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F13" s="29" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G13" s="29" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H13" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="I13" s="29">
-        <v>3</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="I13" s="29"/>
       <c r="J13" s="29"/>
       <c r="K13" s="29"/>
       <c r="L13" s="29"/>
@@ -5646,7 +5845,7 @@
     </row>
     <row r="14" spans="1:13" ht="27" hidden="1">
       <c r="A14" s="1">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>188</v>
@@ -5654,255 +5853,237 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="I14" s="2">
-        <v>70</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:13" ht="54" hidden="1">
+    <row r="15" spans="1:13" ht="40.5" hidden="1">
       <c r="A15" s="1">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="I15" s="2">
-        <v>30</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:13" ht="27">
+    <row r="16" spans="1:13" ht="27" hidden="1">
       <c r="A16" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I16" s="2">
-        <v>80</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>87</v>
-      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="1:13" ht="27">
-      <c r="A17" s="27">
+    <row r="17" spans="1:13" ht="40.5">
+      <c r="A17" s="1">
+        <v>21</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17" s="2">
+        <v>20</v>
+      </c>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="1:13" ht="40.5" hidden="1">
+      <c r="A18" s="1">
+        <v>22</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="F17" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="I17" s="29">
-        <v>80</v>
-      </c>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="31"/>
-    </row>
-    <row r="18" spans="1:13" ht="27" hidden="1">
-      <c r="A18" s="27">
-        <v>17</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>194</v>
-      </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="F18" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="G18" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="I18" s="29">
-        <v>25</v>
-      </c>
-      <c r="J18" s="29"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="31"/>
-    </row>
-    <row r="19" spans="1:13" ht="27" hidden="1">
+      <c r="H18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="1:13" ht="40.5" hidden="1">
       <c r="A19" s="1">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I19" s="2">
-        <v>10</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:13" ht="40.5">
+    <row r="20" spans="1:13" ht="54" hidden="1">
       <c r="A20" s="1">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I20" s="2">
-        <v>8</v>
-      </c>
+      <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="1:13" ht="27" hidden="1">
+    <row r="21" spans="1:13" ht="40.5" hidden="1">
       <c r="A21" s="1">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I21" s="2">
-        <v>25</v>
-      </c>
+      <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:13" ht="40.5">
+    <row r="22" spans="1:13" ht="27">
       <c r="A22" s="1">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I22" s="2">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -5911,499 +6092,689 @@
     </row>
     <row r="23" spans="1:13" ht="40.5" hidden="1">
       <c r="A23" s="1">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I23" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
+      <c r="L23" s="21"/>
       <c r="M23" s="3"/>
     </row>
     <row r="24" spans="1:13" ht="40.5" hidden="1">
       <c r="A24" s="1">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I24" s="2">
-        <v>8</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" spans="1:13" ht="54" hidden="1">
+    <row r="25" spans="1:13" ht="27" hidden="1">
       <c r="A25" s="1">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I25" s="2">
-        <v>18</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="1:13" ht="54" hidden="1">
+    <row r="26" spans="1:13" ht="27" hidden="1">
       <c r="A26" s="1">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I26" s="2">
-        <v>4</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:13" ht="40.5" hidden="1">
+    <row r="27" spans="1:13" ht="27">
       <c r="A27" s="1">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="I27" s="2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="1:13" ht="27">
+      <c r="L27" s="21"/>
+      <c r="M27" s="22"/>
+    </row>
+    <row r="28" spans="1:13" ht="40.5" hidden="1">
       <c r="A28" s="1">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>84</v>
+        <v>211</v>
       </c>
       <c r="I28" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:13" ht="40.5">
+    <row r="29" spans="1:13" ht="27">
       <c r="A29" s="1">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>56</v>
+        <v>213</v>
       </c>
       <c r="I29" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="21"/>
+      <c r="L29" s="2"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" spans="1:13" ht="40.5" hidden="1">
+    <row r="30" spans="1:13" ht="40.5">
       <c r="A30" s="1">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="I30" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:13" ht="27" hidden="1">
+    <row r="31" spans="1:13" ht="54">
       <c r="A31" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="8" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>84</v>
+        <v>216</v>
       </c>
       <c r="I31" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="1:13" ht="27" hidden="1">
+    <row r="32" spans="1:13" ht="27">
       <c r="A32" s="1">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="I32" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" spans="1:13">
-      <c r="A33" s="1"/>
-      <c r="B33" s="8"/>
+    <row r="33" spans="1:13" ht="27" hidden="1">
+      <c r="A33" s="1">
+        <v>38</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>220</v>
+      </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
+      <c r="E33" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="I33" s="2">
+        <v>33</v>
+      </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="22"/>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="1"/>
-      <c r="B34" s="8"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="1:13" ht="27" hidden="1">
+      <c r="A34" s="1">
+        <v>39</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>222</v>
+      </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
+      <c r="E34" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="I34" s="2">
+        <v>10</v>
+      </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" spans="1:13">
-      <c r="A35" s="13"/>
-      <c r="B35" s="8"/>
+    <row r="35" spans="1:13" ht="27" hidden="1">
+      <c r="A35" s="13">
+        <v>40</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>226</v>
+      </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
+      <c r="E35" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="I35" s="8">
+        <v>10</v>
+      </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
       <c r="M35" s="14"/>
     </row>
-    <row r="36" spans="1:13">
-      <c r="A36" s="13"/>
-      <c r="B36" s="8"/>
+    <row r="36" spans="1:13" ht="27">
+      <c r="A36" s="13">
+        <v>41</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
+      <c r="E36" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="I36" s="8">
+        <v>5</v>
+      </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
       <c r="M36" s="14"/>
     </row>
-    <row r="37" spans="1:13">
-      <c r="A37" s="13"/>
-      <c r="B37" s="8"/>
+    <row r="37" spans="1:13" ht="27">
+      <c r="A37" s="13">
+        <v>42</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>228</v>
+      </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
+      <c r="E37" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="I37" s="8">
+        <v>8</v>
+      </c>
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
       <c r="M37" s="14"/>
     </row>
-    <row r="38" spans="1:13">
-      <c r="A38" s="13"/>
-      <c r="B38" s="8"/>
+    <row r="38" spans="1:13" ht="27" hidden="1">
+      <c r="A38" s="13">
+        <v>43</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>230</v>
+      </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
+      <c r="E38" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="I38" s="8">
+        <v>12</v>
+      </c>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
       <c r="M38" s="14"/>
     </row>
-    <row r="39" spans="1:13">
-      <c r="A39" s="13"/>
-      <c r="B39" s="8"/>
+    <row r="39" spans="1:13" ht="54">
+      <c r="A39" s="13">
+        <v>44</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>232</v>
+      </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
+      <c r="E39" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="I39" s="8">
+        <v>4</v>
+      </c>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
-      <c r="L39" s="32"/>
+      <c r="L39" s="8"/>
       <c r="M39" s="14"/>
     </row>
-    <row r="40" spans="1:13">
-      <c r="A40" s="13"/>
-      <c r="B40" s="8"/>
+    <row r="40" spans="1:13" ht="27" hidden="1">
+      <c r="A40" s="13">
+        <v>45</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>234</v>
+      </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8"/>
+      <c r="E40" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="I40" s="8">
+        <v>2</v>
+      </c>
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
       <c r="L40" s="8"/>
       <c r="M40" s="14"/>
     </row>
-    <row r="41" spans="1:13">
-      <c r="A41" s="13"/>
-      <c r="B41" s="8"/>
+    <row r="41" spans="1:13" ht="27">
+      <c r="A41" s="13">
+        <v>46</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>236</v>
+      </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
+      <c r="E41" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="I41" s="8">
+        <v>5</v>
+      </c>
       <c r="J41" s="8"/>
       <c r="K41" s="8"/>
       <c r="L41" s="8"/>
       <c r="M41" s="14"/>
     </row>
-    <row r="42" spans="1:13">
-      <c r="A42" s="13"/>
-      <c r="B42" s="8"/>
+    <row r="42" spans="1:13" ht="54" hidden="1">
+      <c r="A42" s="13">
+        <v>47</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>237</v>
+      </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8"/>
+      <c r="E42" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="I42" s="8">
+        <v>7</v>
+      </c>
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
       <c r="L42" s="8"/>
       <c r="M42" s="14"/>
     </row>
-    <row r="43" spans="1:13">
-      <c r="A43" s="13"/>
-      <c r="B43" s="8"/>
+    <row r="43" spans="1:13" ht="27" hidden="1">
+      <c r="A43" s="13">
+        <v>48</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>238</v>
+      </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
+      <c r="E43" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="I43" s="8">
+        <v>3</v>
+      </c>
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
       <c r="L43" s="8"/>
       <c r="M43" s="14"/>
     </row>
-    <row r="44" spans="1:13">
-      <c r="A44" s="13"/>
-      <c r="B44" s="8"/>
+    <row r="44" spans="1:13" ht="27" hidden="1">
+      <c r="A44" s="13">
+        <v>49</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>239</v>
+      </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8"/>
+      <c r="E44" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="I44" s="8">
+        <v>4</v>
+      </c>
       <c r="J44" s="8"/>
       <c r="K44" s="8"/>
       <c r="L44" s="8"/>
       <c r="M44" s="14"/>
     </row>
-    <row r="45" spans="1:13">
-      <c r="A45" s="13"/>
-      <c r="B45" s="8"/>
+    <row r="45" spans="1:13" ht="27" hidden="1">
+      <c r="A45" s="13">
+        <v>50</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>240</v>
+      </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
+      <c r="E45" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="I45" s="8">
+        <v>3</v>
+      </c>
       <c r="J45" s="8"/>
       <c r="K45" s="8"/>
       <c r="L45" s="8"/>
       <c r="M45" s="14"/>
     </row>
-    <row r="46" spans="1:13">
-      <c r="A46" s="13"/>
-      <c r="B46" s="8"/>
+    <row r="46" spans="1:13" ht="40.5">
+      <c r="A46" s="13">
+        <v>51</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>241</v>
+      </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
+      <c r="E46" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="I46" s="8">
+        <v>15</v>
+      </c>
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
@@ -6511,7 +6882,7 @@
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
       <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
+      <c r="L53" s="32"/>
       <c r="M53" s="14"/>
     </row>
     <row r="54" spans="1:13">
@@ -6859,23 +7230,233 @@
       <c r="L76" s="8"/>
       <c r="M76" s="14"/>
     </row>
-    <row r="77" spans="1:13" ht="14.25" thickBot="1">
-      <c r="A77" s="15"/>
-      <c r="B77" s="16"/>
-      <c r="C77" s="16"/>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16"/>
-      <c r="H77" s="16"/>
-      <c r="I77" s="16"/>
-      <c r="J77" s="16"/>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="17"/>
+    <row r="77" spans="1:13">
+      <c r="A77" s="13"/>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="8"/>
+      <c r="M77" s="14"/>
+    </row>
+    <row r="78" spans="1:13">
+      <c r="A78" s="13"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+      <c r="M78" s="14"/>
+    </row>
+    <row r="79" spans="1:13">
+      <c r="A79" s="13"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="8"/>
+      <c r="M79" s="14"/>
+    </row>
+    <row r="80" spans="1:13">
+      <c r="A80" s="13"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="8"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="8"/>
+      <c r="I80" s="8"/>
+      <c r="J80" s="8"/>
+      <c r="K80" s="8"/>
+      <c r="L80" s="8"/>
+      <c r="M80" s="14"/>
+    </row>
+    <row r="81" spans="1:13">
+      <c r="A81" s="13"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="8"/>
+      <c r="J81" s="8"/>
+      <c r="K81" s="8"/>
+      <c r="L81" s="8"/>
+      <c r="M81" s="14"/>
+    </row>
+    <row r="82" spans="1:13">
+      <c r="A82" s="13"/>
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8"/>
+      <c r="I82" s="8"/>
+      <c r="J82" s="8"/>
+      <c r="K82" s="8"/>
+      <c r="L82" s="8"/>
+      <c r="M82" s="14"/>
+    </row>
+    <row r="83" spans="1:13">
+      <c r="A83" s="13"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="8"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="8"/>
+      <c r="M83" s="14"/>
+    </row>
+    <row r="84" spans="1:13">
+      <c r="A84" s="13"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="8"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="8"/>
+      <c r="M84" s="14"/>
+    </row>
+    <row r="85" spans="1:13">
+      <c r="A85" s="13"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="8"/>
+      <c r="K85" s="8"/>
+      <c r="L85" s="8"/>
+      <c r="M85" s="14"/>
+    </row>
+    <row r="86" spans="1:13">
+      <c r="A86" s="13"/>
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="8"/>
+      <c r="J86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="8"/>
+      <c r="M86" s="14"/>
+    </row>
+    <row r="87" spans="1:13">
+      <c r="A87" s="13"/>
+      <c r="B87" s="8"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="8"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="8"/>
+      <c r="M87" s="14"/>
+    </row>
+    <row r="88" spans="1:13">
+      <c r="A88" s="13"/>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="8"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="8"/>
+      <c r="J88" s="8"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="8"/>
+      <c r="M88" s="14"/>
+    </row>
+    <row r="89" spans="1:13">
+      <c r="A89" s="13"/>
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="8"/>
+      <c r="F89" s="8"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="8"/>
+      <c r="J89" s="8"/>
+      <c r="K89" s="8"/>
+      <c r="L89" s="8"/>
+      <c r="M89" s="14"/>
+    </row>
+    <row r="90" spans="1:13">
+      <c r="A90" s="13"/>
+      <c r="B90" s="8"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="8"/>
+      <c r="E90" s="8"/>
+      <c r="F90" s="8"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="8"/>
+      <c r="J90" s="8"/>
+      <c r="K90" s="8"/>
+      <c r="L90" s="8"/>
+      <c r="M90" s="14"/>
+    </row>
+    <row r="91" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A91" s="15"/>
+      <c r="B91" s="16"/>
+      <c r="C91" s="16"/>
+      <c r="D91" s="16"/>
+      <c r="E91" s="16"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="16"/>
+      <c r="H91" s="16"/>
+      <c r="I91" s="16"/>
+      <c r="J91" s="16"/>
+      <c r="K91" s="16"/>
+      <c r="L91" s="16"/>
+      <c r="M91" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M32">
+  <autoFilter ref="A1:M46">
     <filterColumn colId="4"/>
     <filterColumn colId="6">
       <filters>
@@ -6884,42 +7465,42 @@
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:M188">
-    <cfRule type="expression" dxfId="83" priority="5" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:M202">
+    <cfRule type="expression" dxfId="11" priority="5" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="6" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="7" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="8" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A11:M11">
-    <cfRule type="expression" dxfId="79" priority="1" stopIfTrue="1">
-      <formula>$K11="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="78" priority="2" stopIfTrue="1">
-      <formula>$K11="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="3" stopIfTrue="1">
-      <formula>$K11="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="76" priority="4" stopIfTrue="1">
-      <formula>OR($K11="CLOSED",$K11="CANCEL")</formula>
+  <conditionalFormatting sqref="A8:M8">
+    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
+      <formula>$K8="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
+      <formula>$K8="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
+      <formula>$K8="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="4" stopIfTrue="1">
+      <formula>OR($K8="CLOSED",$K8="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F77">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F91">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G77">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G91">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K77">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K91">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6930,7 +7511,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.5" customWidth="1"/>
@@ -6955,10 +7536,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -6990,14 +7571,14 @@
         <v>55</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>22</v>
@@ -7009,10 +7590,10 @@
         <v>1</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K2" s="24">
         <v>41680</v>
@@ -7026,29 +7607,29 @@
         <v>49</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>22</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H3" s="10">
         <v>1</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K3" s="11">
         <v>41664</v>
@@ -7062,29 +7643,29 @@
         <v>50</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>22</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H4" s="10">
         <v>1</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K4" s="11">
         <v>41665</v>
@@ -7098,35 +7679,35 @@
         <v>47</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="26" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H5" s="10">
         <v>0</v>
       </c>
       <c r="I5" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="K5" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" s="19" t="s">
-        <v>89</v>
-      </c>
       <c r="L5" s="20" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="40.5">
@@ -7134,14 +7715,14 @@
         <v>42</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>12</v>
@@ -7153,10 +7734,10 @@
         <v>4</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K6" s="11">
         <v>41662</v>
@@ -7174,7 +7755,7 @@
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>14</v>
@@ -7189,10 +7770,10 @@
         <v>4</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K7" s="11">
         <v>41679</v>
@@ -7210,7 +7791,7 @@
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>11</v>
@@ -7225,10 +7806,10 @@
         <v>4</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K8" s="11">
         <v>41680</v>
@@ -7242,29 +7823,29 @@
         <v>51</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H9" s="8">
         <v>1</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K9" s="8"/>
       <c r="L9" s="14"/>
@@ -7274,7 +7855,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -7285,16 +7866,16 @@
         <v>22</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H10" s="8">
         <v>3</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K10" s="8"/>
       <c r="L10" s="14"/>
@@ -7308,7 +7889,7 @@
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
@@ -7323,10 +7904,10 @@
         <v>4</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="3"/>
@@ -7336,27 +7917,27 @@
         <v>48</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H12" s="2">
         <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="3"/>
@@ -7366,14 +7947,14 @@
         <v>57</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>12</v>
@@ -7383,10 +7964,10 @@
         <v>3</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K13" s="32">
         <v>41688</v>
@@ -7398,14 +7979,14 @@
         <v>1</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -7413,10 +7994,10 @@
         <v>5</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K14" s="21">
         <v>41754</v>
@@ -7430,29 +8011,29 @@
         <v>10</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="33" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H15" s="2">
         <v>7</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="3"/>
@@ -7462,172 +8043,172 @@
         <v>30</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H16" s="2">
         <v>4</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="1:12" ht="27">
+    <row r="17" spans="1:13" ht="27">
       <c r="A17" s="1">
         <v>31</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H17" s="2">
         <v>3</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>32</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" spans="1:12" ht="40.5">
+    <row r="19" spans="1:13" ht="40.5">
       <c r="A19" s="1">
         <v>28</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H19" s="2">
         <v>3</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="3"/>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>33</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" spans="1:12" ht="27">
+    <row r="21" spans="1:13" ht="27">
       <c r="A21" s="1">
         <v>17</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>22</v>
@@ -7637,311 +8218,470 @@
         <v>5</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="3"/>
     </row>
-    <row r="22" spans="1:12" ht="27">
+    <row r="22" spans="1:13" ht="27">
       <c r="A22" s="1">
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H22" s="2">
         <v>5</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="3"/>
     </row>
-    <row r="23" spans="1:12" ht="27">
+    <row r="23" spans="1:13" ht="27">
       <c r="A23" s="1">
         <v>15</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H23" s="2">
         <v>5</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="3"/>
     </row>
-    <row r="24" spans="1:12" ht="27">
+    <row r="24" spans="1:13" ht="27">
       <c r="A24" s="1">
         <v>13</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H24" s="2">
         <v>9</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="3"/>
     </row>
-    <row r="25" spans="1:12" ht="27">
+    <row r="25" spans="1:13" ht="27">
       <c r="A25" s="1">
         <v>16</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H25" s="2">
         <v>5</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="3"/>
     </row>
-    <row r="26" spans="1:12" ht="27">
+    <row r="26" spans="1:13" ht="27">
       <c r="A26" s="1">
         <v>34</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H26" s="2">
         <v>5</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K26" s="2"/>
       <c r="L26" s="3"/>
     </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="1"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="1"/>
-      <c r="B28" s="8"/>
+    <row r="27" spans="1:13" ht="27">
+      <c r="A27" s="27">
+        <v>22</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="H27" s="29">
+        <v>8</v>
+      </c>
+      <c r="I27" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="J27" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="K27" s="29"/>
+      <c r="L27" s="31"/>
+    </row>
+    <row r="28" spans="1:13" ht="27">
+      <c r="A28" s="1">
+        <v>23</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>47</v>
+      </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
+      <c r="E28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H28" s="2">
+        <v>5</v>
+      </c>
       <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
+      <c r="J28" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="K28" s="2"/>
       <c r="L28" s="3"/>
     </row>
-    <row r="29" spans="1:12">
-      <c r="A29" s="1"/>
-      <c r="B29" s="8"/>
+    <row r="29" spans="1:13" ht="40.5">
+      <c r="A29" s="1">
+        <v>12</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>128</v>
+      </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
+      <c r="E29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29" s="2">
+        <v>5</v>
+      </c>
       <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
+      <c r="J29" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="K29" s="2"/>
       <c r="L29" s="3"/>
     </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="1"/>
-      <c r="B30" s="8"/>
+    <row r="30" spans="1:13" ht="27">
+      <c r="A30" s="1">
+        <v>18</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>110</v>
+      </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
-      <c r="E30" s="2"/>
+      <c r="E30" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
+      <c r="J30" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="K30" s="2"/>
       <c r="L30" s="3"/>
     </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="1"/>
-      <c r="B31" s="8"/>
+    <row r="31" spans="1:13" ht="27">
+      <c r="A31" s="1">
+        <v>21</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
+      <c r="E31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H31" s="2">
+        <v>15</v>
+      </c>
       <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
+      <c r="J31" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="K31" s="2"/>
       <c r="L31" s="3"/>
     </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="1"/>
-      <c r="B32" s="8"/>
+    <row r="32" spans="1:13" ht="27">
+      <c r="A32" s="1">
+        <v>1</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" s="1"/>
-      <c r="B33" s="8"/>
+      <c r="E32" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32" s="2">
+        <v>28</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L32" s="2"/>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="1:13" ht="54">
+      <c r="A33" s="1">
+        <v>6</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>177</v>
+      </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="1:12">
-      <c r="A34" s="1"/>
-      <c r="B34" s="8"/>
+      <c r="E33" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I33" s="2">
+        <v>8</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="1:13" ht="54">
+      <c r="A34" s="1">
+        <v>9</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>179</v>
+      </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="1:12">
-      <c r="A35" s="1"/>
-      <c r="B35" s="8"/>
+      <c r="E34" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I34" s="2">
+        <v>8</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="1:13" ht="27">
+      <c r="A35" s="1">
+        <v>15</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>185</v>
+      </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="36" spans="1:12">
-      <c r="A36" s="1"/>
-      <c r="B36" s="8"/>
+      <c r="E35" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I35" s="2">
+        <v>80</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L35" s="2"/>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="36" spans="1:13" ht="54">
+      <c r="A36" s="1">
+        <v>25</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>194</v>
+      </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
+      <c r="E36" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I36" s="2">
+        <v>4</v>
+      </c>
       <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="3"/>
-    </row>
-    <row r="37" spans="1:12">
+      <c r="K36" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L36" s="2"/>
+      <c r="M36" s="3"/>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="1"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -7955,7 +8695,7 @@
       <c r="K37" s="2"/>
       <c r="L37" s="3"/>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:13">
       <c r="A38" s="1"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -7969,7 +8709,7 @@
       <c r="K38" s="2"/>
       <c r="L38" s="3"/>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:13">
       <c r="A39" s="1"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -7983,7 +8723,7 @@
       <c r="K39" s="21"/>
       <c r="L39" s="3"/>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:13">
       <c r="A40" s="1"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -7997,7 +8737,7 @@
       <c r="K40" s="2"/>
       <c r="L40" s="3"/>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:13">
       <c r="A41" s="1"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -8011,7 +8751,7 @@
       <c r="K41" s="2"/>
       <c r="L41" s="3"/>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:13">
       <c r="A42" s="1"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -8025,7 +8765,7 @@
       <c r="K42" s="2"/>
       <c r="L42" s="3"/>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:13">
       <c r="A43" s="1"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -8039,7 +8779,7 @@
       <c r="K43" s="2"/>
       <c r="L43" s="3"/>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:13">
       <c r="A44" s="1"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -8053,7 +8793,7 @@
       <c r="K44" s="2"/>
       <c r="L44" s="3"/>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:13">
       <c r="A45" s="1"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -8067,7 +8807,7 @@
       <c r="K45" s="2"/>
       <c r="L45" s="3"/>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:13">
       <c r="A46" s="1"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -8081,7 +8821,7 @@
       <c r="K46" s="2"/>
       <c r="L46" s="3"/>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:13">
       <c r="A47" s="1"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -8095,7 +8835,7 @@
       <c r="K47" s="2"/>
       <c r="L47" s="3"/>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:13">
       <c r="A48" s="1"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -8480,279 +9220,405 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:L9">
-    <cfRule type="expression" dxfId="75" priority="73" stopIfTrue="1">
+    <cfRule type="expression" dxfId="127" priority="109" stopIfTrue="1">
       <formula>$J9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="126" priority="110" stopIfTrue="1">
       <formula>$J9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="75" stopIfTrue="1">
+    <cfRule type="expression" dxfId="125" priority="111" stopIfTrue="1">
       <formula>$J9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="112" stopIfTrue="1">
       <formula>OR($J9="CLOSED",$J9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:L10">
-    <cfRule type="expression" dxfId="71" priority="69" stopIfTrue="1">
+    <cfRule type="expression" dxfId="123" priority="105" stopIfTrue="1">
       <formula>$J10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="106" stopIfTrue="1">
       <formula>$J10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="71" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="107" stopIfTrue="1">
       <formula>$J10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="108" stopIfTrue="1">
       <formula>OR($J10="CLOSED",$J10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:L11">
-    <cfRule type="expression" dxfId="67" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="101" stopIfTrue="1">
       <formula>$J11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="102" stopIfTrue="1">
       <formula>$J11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="117" priority="103" stopIfTrue="1">
       <formula>$J11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="116" priority="104" stopIfTrue="1">
       <formula>OR($J11="CLOSED",$J11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:L12">
-    <cfRule type="expression" dxfId="63" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="97" stopIfTrue="1">
       <formula>$J12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="98" stopIfTrue="1">
       <formula>$J12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="113" priority="99" stopIfTrue="1">
       <formula>$J12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="100" stopIfTrue="1">
       <formula>OR($J12="CLOSED",$J12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:L13">
-    <cfRule type="expression" dxfId="59" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="111" priority="93" stopIfTrue="1">
       <formula>$J13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="110" priority="94" stopIfTrue="1">
       <formula>$J13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="95" stopIfTrue="1">
       <formula>$J13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="96" stopIfTrue="1">
       <formula>OR($J13="CLOSED",$J13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:L14">
-    <cfRule type="expression" dxfId="55" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="89" stopIfTrue="1">
       <formula>$J14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="90" stopIfTrue="1">
       <formula>$J14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="91" stopIfTrue="1">
       <formula>$J14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="92" stopIfTrue="1">
       <formula>OR($J14="CLOSED",$J14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:L15">
-    <cfRule type="expression" dxfId="51" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="85" stopIfTrue="1">
       <formula>$J15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="86" stopIfTrue="1">
       <formula>$J15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="87" stopIfTrue="1">
       <formula>$J15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="88" stopIfTrue="1">
       <formula>OR($J15="CLOSED",$J15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:L16">
-    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="81" stopIfTrue="1">
       <formula>$J16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="82" stopIfTrue="1">
       <formula>$J16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="83" stopIfTrue="1">
       <formula>$J16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="84" stopIfTrue="1">
       <formula>OR($J16="CLOSED",$J16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:L17">
-    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="77" stopIfTrue="1">
       <formula>$J17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="78" stopIfTrue="1">
       <formula>$J17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="79" stopIfTrue="1">
       <formula>$J17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="80" stopIfTrue="1">
       <formula>OR($J17="CLOSED",$J17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:L18">
-    <cfRule type="expression" dxfId="39" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="73" stopIfTrue="1">
       <formula>$J18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="74" stopIfTrue="1">
       <formula>$J18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="75" stopIfTrue="1">
       <formula>$J18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="76" stopIfTrue="1">
       <formula>OR($J18="CLOSED",$J18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:L19">
-    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="69" stopIfTrue="1">
       <formula>$J19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="70" stopIfTrue="1">
       <formula>$J19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="71" stopIfTrue="1">
       <formula>$J19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="72" stopIfTrue="1">
       <formula>OR($J19="CLOSED",$J19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:L20">
-    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="65" stopIfTrue="1">
       <formula>$J20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="66" stopIfTrue="1">
       <formula>$J20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="67" stopIfTrue="1">
       <formula>$J20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="68" stopIfTrue="1">
       <formula>OR($J20="CLOSED",$J20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:L21">
-    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="61" stopIfTrue="1">
       <formula>$J21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="62" stopIfTrue="1">
       <formula>$J21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="63" stopIfTrue="1">
       <formula>$J21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="64" stopIfTrue="1">
       <formula>OR($J21="CLOSED",$J21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:L23">
-    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="57" stopIfTrue="1">
       <formula>$J22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="58" stopIfTrue="1">
       <formula>$J22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="59" stopIfTrue="1">
       <formula>$J22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="60" stopIfTrue="1">
       <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:H22">
-    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="53" stopIfTrue="1">
       <formula>$J22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="54" stopIfTrue="1">
       <formula>$J22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="55" stopIfTrue="1">
       <formula>$J22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="56" stopIfTrue="1">
       <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="49" stopIfTrue="1">
       <formula>$J23="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="50" stopIfTrue="1">
       <formula>$J23="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="51" stopIfTrue="1">
       <formula>$J23="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="52" stopIfTrue="1">
       <formula>OR($J23="CLOSED",$J23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:L25">
-    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="45" stopIfTrue="1">
       <formula>$J24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="46" stopIfTrue="1">
       <formula>$J24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="47" stopIfTrue="1">
       <formula>$J24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="48" stopIfTrue="1">
       <formula>OR($J24="CLOSED",$J24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="41" stopIfTrue="1">
       <formula>$J25="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="42" stopIfTrue="1">
       <formula>$J25="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="43" stopIfTrue="1">
       <formula>$J25="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="44" stopIfTrue="1">
       <formula>OR($J25="CLOSED",$J25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:L26">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="37" stopIfTrue="1">
       <formula>$J26="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="38" stopIfTrue="1">
       <formula>$J26="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="39" stopIfTrue="1">
       <formula>$J26="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="40" stopIfTrue="1">
       <formula>OR($J26="CLOSED",$J26="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27:L28">
+    <cfRule type="expression" dxfId="51" priority="33" stopIfTrue="1">
+      <formula>$J27="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="34" stopIfTrue="1">
+      <formula>$J27="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="35" stopIfTrue="1">
+      <formula>$J27="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="36" stopIfTrue="1">
+      <formula>OR($J27="CLOSED",$J27="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29:L30">
+    <cfRule type="expression" dxfId="47" priority="29" stopIfTrue="1">
+      <formula>$J29="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="46" priority="30" stopIfTrue="1">
+      <formula>$J29="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="31" stopIfTrue="1">
+      <formula>$J29="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="32" stopIfTrue="1">
+      <formula>OR($J29="CLOSED",$J29="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29:L29">
+    <cfRule type="expression" dxfId="43" priority="25" stopIfTrue="1">
+      <formula>$J29="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="26" stopIfTrue="1">
+      <formula>$J29="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="41" priority="27" stopIfTrue="1">
+      <formula>$J29="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="28" stopIfTrue="1">
+      <formula>OR($J29="CLOSED",$J29="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:L31">
+    <cfRule type="expression" dxfId="39" priority="21" stopIfTrue="1">
+      <formula>$J31="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="22" stopIfTrue="1">
+      <formula>$J31="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="23" stopIfTrue="1">
+      <formula>$J31="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="24" stopIfTrue="1">
+      <formula>OR($J31="CLOSED",$J31="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A32:M32">
+    <cfRule type="expression" dxfId="35" priority="17" stopIfTrue="1">
+      <formula>$K32="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="18" stopIfTrue="1">
+      <formula>$K32="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="19" stopIfTrue="1">
+      <formula>$K32="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="20" stopIfTrue="1">
+      <formula>OR($K32="CLOSED",$K32="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A33:M33">
+    <cfRule type="expression" dxfId="31" priority="13" stopIfTrue="1">
+      <formula>$K33="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="14" stopIfTrue="1">
+      <formula>$K33="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="15" stopIfTrue="1">
+      <formula>$K33="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="16" stopIfTrue="1">
+      <formula>OR($K33="CLOSED",$K33="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A34:M34">
+    <cfRule type="expression" dxfId="27" priority="9" stopIfTrue="1">
+      <formula>$K34="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="10" stopIfTrue="1">
+      <formula>$K34="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="11" stopIfTrue="1">
+      <formula>$K34="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="12" stopIfTrue="1">
+      <formula>OR($K34="CLOSED",$K34="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:M35">
+    <cfRule type="expression" dxfId="23" priority="5" stopIfTrue="1">
+      <formula>$K35="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="6" stopIfTrue="1">
+      <formula>$K35="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="7" stopIfTrue="1">
+      <formula>$K35="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="8" stopIfTrue="1">
+      <formula>OR($K35="CLOSED",$K35="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A36:M36">
+    <cfRule type="expression" dxfId="19" priority="1" stopIfTrue="1">
+      <formula>$K36="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="2" stopIfTrue="1">
+      <formula>$K36="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3" stopIfTrue="1">
+      <formula>$K36="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="4" stopIfTrue="1">
+      <formula>OR($K36="CLOSED",$K36="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J74">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J31 K32:K36 J37:J74">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F74">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F31 G32:G36 F37:F74">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E74">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E31 F32:F36 E37:E74">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
   </dataValidations>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -967,11 +967,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">对于各种操作能够返回详细的错误信息和统计信息
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">日志关联：Data/Catalog/Coord等节点的日志能够通过会话的操作ID进程关联
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1072,11 +1067,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">创建Collection默认调整为基于OID的Hash分区
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Collection需要支持在DMS层读写的并发性（可以考虑Collection Latch为Block Latch）
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1092,11 +1082,6 @@
   </si>
   <si>
     <t>PMD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">OM提供“节点监控管理”、“业务监控管理”功能
-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1228,12 +1213,27 @@
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">OM提供“主机监控管理”、“业务监控管理”功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">对于各种操作能够返回详细的错误信息和统计信息
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建Collection默认调整为基于OID的Hash分区
+--唯一索引怎么建？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1284,6 +1284,14 @@
       <color theme="0" tint="-0.14999847407452621"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1463,7 +1471,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1566,39 +1574,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="132">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="128">
     <dxf>
       <fill>
         <patternFill>
@@ -3344,7 +3327,7 @@
         <v>28</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -4235,16 +4218,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L182">
-    <cfRule type="expression" dxfId="131" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="127" priority="1" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="126" priority="2" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="125" priority="3" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="128" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="4" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5415,16 +5398,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L185">
-    <cfRule type="expression" dxfId="3" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="123" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5517,7 +5500,7 @@
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
@@ -5546,7 +5529,7 @@
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>69</v>
@@ -5573,7 +5556,7 @@
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F4" s="29" t="s">
         <v>80</v>
@@ -5602,7 +5585,7 @@
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>14</v>
@@ -5626,12 +5609,12 @@
         <v>7</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>52</v>
@@ -5660,7 +5643,7 @@
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>80</v>
@@ -5687,7 +5670,7 @@
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>80</v>
@@ -5709,12 +5692,12 @@
         <v>11</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>33</v>
@@ -5743,7 +5726,7 @@
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>69</v>
@@ -5770,7 +5753,7 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>69</v>
@@ -5792,12 +5775,12 @@
         <v>16</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="C12" s="28"/>
       <c r="D12" s="28"/>
       <c r="E12" s="28" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F12" s="29" t="s">
         <v>42</v>
@@ -5826,7 +5809,7 @@
       <c r="C13" s="28"/>
       <c r="D13" s="28"/>
       <c r="E13" s="28" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F13" s="29" t="s">
         <v>80</v>
@@ -5853,7 +5836,7 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>33</v>
@@ -5880,7 +5863,7 @@
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>33</v>
@@ -5907,7 +5890,7 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>69</v>
@@ -5928,13 +5911,13 @@
       <c r="A17" s="1">
         <v>21</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>191</v>
+      <c r="B17" s="34" t="s">
+        <v>240</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>52</v>
@@ -5963,7 +5946,7 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>69</v>
@@ -5985,12 +5968,12 @@
         <v>23</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>69</v>
@@ -6012,12 +5995,12 @@
         <v>24</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>80</v>
@@ -6039,12 +6022,12 @@
         <v>26</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>69</v>
@@ -6066,12 +6049,12 @@
         <v>27</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>33</v>
@@ -6095,12 +6078,12 @@
         <v>28</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>52</v>
@@ -6124,12 +6107,12 @@
         <v>29</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>33</v>
@@ -6138,7 +6121,7 @@
         <v>16</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
@@ -6151,12 +6134,12 @@
         <v>30</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>33</v>
@@ -6178,12 +6161,12 @@
         <v>31</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>
@@ -6192,7 +6175,7 @@
         <v>16</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
@@ -6205,12 +6188,12 @@
         <v>32</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>69</v>
@@ -6234,12 +6217,12 @@
         <v>33</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>69</v>
@@ -6248,7 +6231,7 @@
         <v>12</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I28" s="2">
         <v>5</v>
@@ -6263,12 +6246,12 @@
         <v>34</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>80</v>
@@ -6277,7 +6260,7 @@
         <v>22</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I29" s="2">
         <v>2</v>
@@ -6292,12 +6275,12 @@
         <v>35</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>80</v>
@@ -6306,7 +6289,7 @@
         <v>22</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I30" s="2">
         <v>2</v>
@@ -6321,12 +6304,12 @@
         <v>36</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>33</v>
@@ -6335,7 +6318,7 @@
         <v>22</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I31" s="2">
         <v>18</v>
@@ -6350,12 +6333,12 @@
         <v>37</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>69</v>
@@ -6364,7 +6347,7 @@
         <v>22</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I32" s="2">
         <v>15</v>
@@ -6379,12 +6362,12 @@
         <v>38</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>42</v>
@@ -6393,7 +6376,7 @@
         <v>12</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I33" s="2">
         <v>33</v>
@@ -6408,12 +6391,12 @@
         <v>39</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>42</v>
@@ -6422,7 +6405,7 @@
         <v>12</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I34" s="2">
         <v>10</v>
@@ -6437,12 +6420,12 @@
         <v>40</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
       <c r="E35" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>42</v>
@@ -6451,7 +6434,7 @@
         <v>12</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I35" s="8">
         <v>10</v>
@@ -6466,12 +6449,12 @@
         <v>41</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>69</v>
@@ -6480,7 +6463,7 @@
         <v>22</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I36" s="8">
         <v>5</v>
@@ -6495,12 +6478,12 @@
         <v>42</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>69</v>
@@ -6509,7 +6492,7 @@
         <v>22</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I37" s="8">
         <v>8</v>
@@ -6524,12 +6507,12 @@
         <v>43</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
       <c r="E38" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>69</v>
@@ -6538,7 +6521,7 @@
         <v>12</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I38" s="8">
         <v>12</v>
@@ -6553,12 +6536,12 @@
         <v>44</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>69</v>
@@ -6567,7 +6550,7 @@
         <v>22</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I39" s="8">
         <v>4</v>
@@ -6582,12 +6565,12 @@
         <v>45</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>80</v>
@@ -6596,7 +6579,7 @@
         <v>12</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I40" s="8">
         <v>2</v>
@@ -6611,12 +6594,12 @@
         <v>46</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
       <c r="E41" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>69</v>
@@ -6625,7 +6608,7 @@
         <v>22</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I41" s="8">
         <v>5</v>
@@ -6640,12 +6623,12 @@
         <v>47</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
       <c r="E42" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>69</v>
@@ -6654,7 +6637,7 @@
         <v>12</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I42" s="8">
         <v>7</v>
@@ -6669,12 +6652,12 @@
         <v>48</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
       <c r="E43" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>69</v>
@@ -6683,7 +6666,7 @@
         <v>12</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I43" s="8">
         <v>3</v>
@@ -6698,12 +6681,12 @@
         <v>49</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
       <c r="E44" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>69</v>
@@ -6712,7 +6695,7 @@
         <v>12</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I44" s="8">
         <v>4</v>
@@ -6727,12 +6710,12 @@
         <v>50</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
       <c r="E45" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>69</v>
@@ -6741,7 +6724,7 @@
         <v>12</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I45" s="8">
         <v>3</v>
@@ -6756,12 +6739,12 @@
         <v>51</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
       <c r="E46" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>42</v>
@@ -6770,7 +6753,7 @@
         <v>22</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I46" s="8">
         <v>15</v>
@@ -7466,30 +7449,30 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M202">
-    <cfRule type="expression" dxfId="11" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="5" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="6" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="117" priority="7" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="116" priority="8" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:M8">
-    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="1" stopIfTrue="1">
       <formula>$K8="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="2" stopIfTrue="1">
       <formula>$K8="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="113" priority="3" stopIfTrue="1">
       <formula>$K8="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="4" stopIfTrue="1">
       <formula>OR($K8="CLOSED",$K8="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8543,7 +8526,7 @@
         <v>28</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>84</v>
@@ -8576,7 +8559,7 @@
         <v>8</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>84</v>
@@ -8609,7 +8592,7 @@
         <v>8</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>84</v>
@@ -8642,7 +8625,7 @@
         <v>80</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>84</v>
@@ -8655,7 +8638,7 @@
         <v>25</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -9220,394 +9203,394 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:L9">
-    <cfRule type="expression" dxfId="127" priority="109" stopIfTrue="1">
+    <cfRule type="expression" dxfId="111" priority="109" stopIfTrue="1">
       <formula>$J9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="110" stopIfTrue="1">
+    <cfRule type="expression" dxfId="110" priority="110" stopIfTrue="1">
       <formula>$J9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="111" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="111" stopIfTrue="1">
       <formula>$J9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="112" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="112" stopIfTrue="1">
       <formula>OR($J9="CLOSED",$J9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:L10">
-    <cfRule type="expression" dxfId="123" priority="105" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="105" stopIfTrue="1">
       <formula>$J10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="106" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="106" stopIfTrue="1">
       <formula>$J10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="107" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="107" stopIfTrue="1">
       <formula>$J10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="108" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="108" stopIfTrue="1">
       <formula>OR($J10="CLOSED",$J10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:L11">
-    <cfRule type="expression" dxfId="119" priority="101" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="101" stopIfTrue="1">
       <formula>$J11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="102" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="102" stopIfTrue="1">
       <formula>$J11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="103" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="103" stopIfTrue="1">
       <formula>$J11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="104" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="104" stopIfTrue="1">
       <formula>OR($J11="CLOSED",$J11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:L12">
-    <cfRule type="expression" dxfId="115" priority="97" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="97" stopIfTrue="1">
       <formula>$J12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="98" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="98" stopIfTrue="1">
       <formula>$J12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="99" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="99" stopIfTrue="1">
       <formula>$J12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="100" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="100" stopIfTrue="1">
       <formula>OR($J12="CLOSED",$J12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:L13">
-    <cfRule type="expression" dxfId="111" priority="93" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="93" stopIfTrue="1">
       <formula>$J13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="94" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="94" stopIfTrue="1">
       <formula>$J13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="95" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="95" stopIfTrue="1">
       <formula>$J13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="96" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="96" stopIfTrue="1">
       <formula>OR($J13="CLOSED",$J13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:L14">
-    <cfRule type="expression" dxfId="107" priority="89" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="89" stopIfTrue="1">
       <formula>$J14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="90" stopIfTrue="1">
       <formula>$J14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="91" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="91" stopIfTrue="1">
       <formula>$J14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="92" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="92" stopIfTrue="1">
       <formula>OR($J14="CLOSED",$J14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:L15">
-    <cfRule type="expression" dxfId="103" priority="85" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="85" stopIfTrue="1">
       <formula>$J15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="86" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="86" stopIfTrue="1">
       <formula>$J15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="87" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="87" stopIfTrue="1">
       <formula>$J15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="88" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="88" stopIfTrue="1">
       <formula>OR($J15="CLOSED",$J15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:L16">
-    <cfRule type="expression" dxfId="99" priority="81" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="81" stopIfTrue="1">
       <formula>$J16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="82" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="82" stopIfTrue="1">
       <formula>$J16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="83" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="83" stopIfTrue="1">
       <formula>$J16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="84" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="84" stopIfTrue="1">
       <formula>OR($J16="CLOSED",$J16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:L17">
-    <cfRule type="expression" dxfId="95" priority="77" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="77" stopIfTrue="1">
       <formula>$J17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="78" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="78" stopIfTrue="1">
       <formula>$J17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="79" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="79" stopIfTrue="1">
       <formula>$J17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="80" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="80" stopIfTrue="1">
       <formula>OR($J17="CLOSED",$J17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:L18">
-    <cfRule type="expression" dxfId="91" priority="73" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="73" stopIfTrue="1">
       <formula>$J18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="74" stopIfTrue="1">
       <formula>$J18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="75" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="75" stopIfTrue="1">
       <formula>$J18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="76" stopIfTrue="1">
       <formula>OR($J18="CLOSED",$J18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:L19">
-    <cfRule type="expression" dxfId="87" priority="69" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="69" stopIfTrue="1">
       <formula>$J19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="70" stopIfTrue="1">
       <formula>$J19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="71" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="71" stopIfTrue="1">
       <formula>$J19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="72" stopIfTrue="1">
       <formula>OR($J19="CLOSED",$J19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:L20">
-    <cfRule type="expression" dxfId="83" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="65" stopIfTrue="1">
       <formula>$J20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="66" stopIfTrue="1">
       <formula>$J20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="67" stopIfTrue="1">
       <formula>$J20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="68" stopIfTrue="1">
       <formula>OR($J20="CLOSED",$J20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:L21">
-    <cfRule type="expression" dxfId="79" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="61" stopIfTrue="1">
       <formula>$J21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="62" stopIfTrue="1">
       <formula>$J21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="63" stopIfTrue="1">
       <formula>$J21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="64" stopIfTrue="1">
       <formula>OR($J21="CLOSED",$J21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:L23">
-    <cfRule type="expression" dxfId="75" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="57" stopIfTrue="1">
       <formula>$J22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="58" stopIfTrue="1">
       <formula>$J22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="59" stopIfTrue="1">
       <formula>$J22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="60" stopIfTrue="1">
       <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:H22">
-    <cfRule type="expression" dxfId="71" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="53" stopIfTrue="1">
       <formula>$J22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="54" stopIfTrue="1">
       <formula>$J22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="55" stopIfTrue="1">
       <formula>$J22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="56" stopIfTrue="1">
       <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="67" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="49" stopIfTrue="1">
       <formula>$J23="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="50" stopIfTrue="1">
       <formula>$J23="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="51" stopIfTrue="1">
       <formula>$J23="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="52" stopIfTrue="1">
       <formula>OR($J23="CLOSED",$J23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:L25">
-    <cfRule type="expression" dxfId="63" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
       <formula>$J24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
       <formula>$J24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
       <formula>$J24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
       <formula>OR($J24="CLOSED",$J24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="59" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
       <formula>$J25="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
       <formula>$J25="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="43" stopIfTrue="1">
       <formula>$J25="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="44" stopIfTrue="1">
       <formula>OR($J25="CLOSED",$J25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:L26">
-    <cfRule type="expression" dxfId="55" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="37" stopIfTrue="1">
       <formula>$J26="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="38" stopIfTrue="1">
       <formula>$J26="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="39" stopIfTrue="1">
       <formula>$J26="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="40" stopIfTrue="1">
       <formula>OR($J26="CLOSED",$J26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:L28">
-    <cfRule type="expression" dxfId="51" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
       <formula>$J27="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
       <formula>$J27="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
       <formula>$J27="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
       <formula>OR($J27="CLOSED",$J27="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:L30">
-    <cfRule type="expression" dxfId="47" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
       <formula>$J29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
       <formula>$J29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="31" stopIfTrue="1">
       <formula>$J29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
       <formula>OR($J29="CLOSED",$J29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:L29">
-    <cfRule type="expression" dxfId="43" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
       <formula>$J29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
       <formula>$J29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="27" stopIfTrue="1">
       <formula>$J29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="28" stopIfTrue="1">
       <formula>OR($J29="CLOSED",$J29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:L31">
-    <cfRule type="expression" dxfId="39" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
       <formula>$J31="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
       <formula>$J31="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
       <formula>$J31="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
       <formula>OR($J31="CLOSED",$J31="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A32:M32">
-    <cfRule type="expression" dxfId="35" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
       <formula>$K32="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
       <formula>$K32="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
       <formula>$K32="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
       <formula>OR($K32="CLOSED",$K32="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:M33">
-    <cfRule type="expression" dxfId="31" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
       <formula>$K33="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="14" stopIfTrue="1">
       <formula>$K33="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="15" stopIfTrue="1">
       <formula>$K33="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
       <formula>OR($K33="CLOSED",$K33="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A34:M34">
-    <cfRule type="expression" dxfId="27" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
       <formula>$K34="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
       <formula>$K34="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
       <formula>$K34="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
       <formula>OR($K34="CLOSED",$K34="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A35:M35">
-    <cfRule type="expression" dxfId="23" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
       <formula>$K35="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
       <formula>$K35="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
       <formula>$K35="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
       <formula>OR($K35="CLOSED",$K35="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36:M36">
-    <cfRule type="expression" dxfId="19" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>$K36="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
       <formula>$K36="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>$K36="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
       <formula>OR($K36="CLOSED",$K36="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="243">
   <si>
     <r>
       <t>描述</t>
@@ -1226,6 +1226,10 @@
   <si>
     <t>创建Collection默认调整为基于OID的Hash分区
 --唯一索引怎么建？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-420 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5437,8 +5441,8 @@
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
     <col min="2" max="2" width="39.75" customWidth="1"/>
-    <col min="3" max="3" width="20.125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="24.75" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="20.125" customWidth="1"/>
+    <col min="4" max="4" width="24.75" customWidth="1"/>
     <col min="5" max="6" width="9.375" customWidth="1"/>
     <col min="7" max="7" width="9.75" customWidth="1"/>
     <col min="8" max="8" width="9.875" customWidth="1"/>
@@ -6191,7 +6195,9 @@
         <v>208</v>
       </c>
       <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
+      <c r="D27" s="8" t="s">
+        <v>242</v>
+      </c>
       <c r="E27" s="8" t="s">
         <v>207</v>
       </c>
@@ -6208,8 +6214,12 @@
         <v>22</v>
       </c>
       <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="21"/>
+      <c r="K27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" s="21">
+        <v>41949</v>
+      </c>
       <c r="M27" s="22"/>
     </row>
     <row r="28" spans="1:13" ht="40.5" hidden="1">

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="247">
   <si>
     <r>
       <t>描述</t>
@@ -1230,6 +1230,22 @@
   </si>
   <si>
     <t xml:space="preserve">SEQUOIADBMAINSTREAM-420 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-434</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-438 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WUYUN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIUZHEN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1475,7 +1491,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1579,6 +1595,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6056,7 +6075,9 @@
         <v>195</v>
       </c>
       <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
+      <c r="D22" s="8" t="s">
+        <v>244</v>
+      </c>
       <c r="E22" s="8" t="s">
         <v>209</v>
       </c>
@@ -6072,9 +6093,15 @@
       <c r="I22" s="2">
         <v>3</v>
       </c>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
+      <c r="J22" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L22" s="21">
+        <v>41957</v>
+      </c>
       <c r="M22" s="3"/>
     </row>
     <row r="23" spans="1:13" ht="40.5" hidden="1">
@@ -6213,7 +6240,9 @@
       <c r="I27" s="2">
         <v>22</v>
       </c>
-      <c r="J27" s="2"/>
+      <c r="J27" s="2" t="s">
+        <v>246</v>
+      </c>
       <c r="K27" s="2" t="s">
         <v>61</v>
       </c>
@@ -6607,7 +6636,9 @@
         <v>233</v>
       </c>
       <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
+      <c r="D41" s="8" t="s">
+        <v>243</v>
+      </c>
       <c r="E41" s="8" t="s">
         <v>207</v>
       </c>
@@ -6623,10 +6654,18 @@
       <c r="I41" s="8">
         <v>5</v>
       </c>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="14"/>
+      <c r="J41" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L41" s="32">
+        <v>41944</v>
+      </c>
+      <c r="M41" s="35">
+        <v>41953</v>
+      </c>
     </row>
     <row r="42" spans="1:13" ht="54" hidden="1">
       <c r="A42" s="13">

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -6097,7 +6097,7 @@
         <v>245</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="L22" s="21">
         <v>41957</v>
@@ -6244,7 +6244,7 @@
         <v>246</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="L27" s="21">
         <v>41949</v>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -15,14 +15,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2014年'!$A$1:$M$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$L$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$L$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$M$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="256">
   <si>
     <r>
       <t>描述</t>
@@ -1028,10 +1028,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>许建辉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>林友滨、何嘉文、谭钊波</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1101,6 +1097,127 @@
   <si>
     <t xml:space="preserve">参数动态生效（getConfig/setConfig，需要区分出能批量修改的和不能批量修改的，以前批量修改时可否用系统变量替换等）
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SequoiaDB集群提供对IP地址和Hostname两种方式的支持
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">OM提供“操作日志”管理功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalog组提供删除节点功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">JS脚本Root用户信息保护
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OMA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供导出/导入SequoiaDB元数据信息工具
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOOL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">OMA对象功能加强，提供“listNode, getNodeConfig, setNodeConfig, updateNodeConfig”等功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OMA/SDB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">dropCS时，能自动关闭所有打开的context
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RTN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供LOB的导入和导出功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">读取LOB的完整性保证（如何保证在多幅本中的LOB是同一LOB对象，尤其是在LOB支持随机写时）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain中增加add group, del group操作
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">完善collection alter功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Truncate collection功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">OM安装部署功能优化（各种异常下的恢复、遗留问题，参数检测等）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">OM提供“主机监控管理”、“业务监控管理”功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">对于各种操作能够返回详细的错误信息和统计信息
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建Collection默认调整为基于OID的Hash分区
+--唯一索引怎么建？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-420 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-434</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-438 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WUYUN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIUZHEN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-419  
+SEQUOIADBMAINSTREAM-330</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1110,7 +1227,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="0" tint="-0.14999847407452621"/>
+        <color theme="1"/>
         <rFont val="宋体"/>
         <family val="3"/>
         <charset val="134"/>
@@ -1133,119 +1250,42 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">SequoiaDB集群提供对IP地址和Hostname两种方式的支持
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">OM提供“操作日志”管理功能
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalog组提供删除节点功能
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">JS脚本Root用户信息保护
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OMA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">提供导出/导入SequoiaDB元数据信息工具
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TOOL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">OMA对象功能加强，提供“listNode, getNodeConfig, setNodeConfig, updateNodeConfig”等功能
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OMA/SDB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">dropCS时，能自动关闭所有打开的context
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RTN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">提供LOB的导入和导出功能
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">读取LOB的完整性保证（如何保证在多幅本中的LOB是同一LOB对象，尤其是在LOB支持随机写时）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Domain中增加add group, del group操作
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">完善collection alter功能
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Truncate collection功能
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">OM安装部署功能优化（各种异常下的恢复、遗留问题，参数检测等）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">OM提供“主机监控管理”、“业务监控管理”功能
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">对于各种操作能够返回详细的错误信息和统计信息
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建Collection默认调整为基于OID的Hash分区
---唯一索引怎么建？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">SEQUOIADBMAINSTREAM-420 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEQUOIADBMAINSTREAM-434</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">SEQUOIADBMAINSTREAM-438 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WUYUN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIUZHEN</t>
+    <t>许建辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴易达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">数组全匹配在该字段有索引的情况下不能匹配记录，如 db.my.my.find({a:[1,2]})，如果a字段上有索引，是不能全匹配记录的
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2014Q4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MTH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">数组操作增加$slice操作
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">update中的$each, $sort, $slice, $position操作
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-497 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李伟超</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1301,17 +1341,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.14999847407452621"/>
+      <color rgb="FF00B050"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1594,7 +1634,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1604,91 +1644,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="128">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="116">
     <dxf>
       <fill>
         <patternFill>
@@ -3350,7 +3306,7 @@
         <v>28</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -4241,16 +4197,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L182">
-    <cfRule type="expression" dxfId="127" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="1" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="2" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="113" priority="3" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="4" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5421,16 +5377,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L185">
-    <cfRule type="expression" dxfId="123" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="111" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="110" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5455,7 +5411,7 @@
   <sheetPr filterMode="1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -5523,7 +5479,7 @@
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
@@ -5552,7 +5508,7 @@
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>69</v>
@@ -5579,7 +5535,7 @@
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F4" s="29" t="s">
         <v>80</v>
@@ -5608,7 +5564,7 @@
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>14</v>
@@ -5632,12 +5588,12 @@
         <v>7</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>52</v>
@@ -5666,7 +5622,7 @@
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>80</v>
@@ -5693,7 +5649,7 @@
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>80</v>
@@ -5710,46 +5666,44 @@
       <c r="L8" s="2"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:13" ht="40.5" hidden="1">
+    <row r="9" spans="1:13" ht="27" hidden="1">
       <c r="A9" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I9" s="2">
-        <v>3</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="1:13" ht="27" hidden="1">
+    <row r="10" spans="1:13" ht="54" hidden="1">
       <c r="A10" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>69</v>
@@ -5758,7 +5712,7 @@
         <v>16</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -5766,100 +5720,100 @@
       <c r="L10" s="2"/>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" spans="1:13" ht="54" hidden="1">
-      <c r="A11" s="1">
-        <v>14</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="2" t="s">
+    <row r="11" spans="1:13" ht="40.5">
+      <c r="A11" s="27">
         <v>16</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" ht="40.5">
+      <c r="B11" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28" t="s">
+        <v>208</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="29">
+        <v>25</v>
+      </c>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="31"/>
+    </row>
+    <row r="12" spans="1:13" ht="27" hidden="1">
       <c r="A12" s="27">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>239</v>
+        <v>186</v>
       </c>
       <c r="C12" s="28"/>
       <c r="D12" s="28"/>
       <c r="E12" s="28" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H12" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" s="29">
-        <v>25</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="I12" s="29"/>
       <c r="J12" s="29"/>
       <c r="K12" s="29"/>
       <c r="L12" s="29"/>
       <c r="M12" s="31"/>
     </row>
     <row r="13" spans="1:13" ht="27" hidden="1">
-      <c r="A13" s="27">
-        <v>17</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="F13" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="G13" s="29" t="s">
+      <c r="A13" s="1">
+        <v>18</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="31"/>
-    </row>
-    <row r="14" spans="1:13" ht="27" hidden="1">
+      <c r="H13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" ht="40.5" hidden="1">
       <c r="A14" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>33</v>
@@ -5868,7 +5822,7 @@
         <v>16</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -5876,26 +5830,26 @@
       <c r="L14" s="2"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:13" ht="40.5" hidden="1">
+    <row r="15" spans="1:13" ht="27" hidden="1">
       <c r="A15" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>79</v>
+        <v>175</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -5903,57 +5857,57 @@
       <c r="L15" s="2"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:13" ht="27" hidden="1">
+    <row r="16" spans="1:13" ht="40.5">
       <c r="A16" s="1">
-        <v>20</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>190</v>
+        <v>21</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>238</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="I16" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="I16" s="2">
+        <v>20</v>
+      </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="1:13" ht="40.5">
+    <row r="17" spans="1:13" ht="40.5" hidden="1">
       <c r="A17" s="1">
-        <v>21</v>
-      </c>
-      <c r="B17" s="34" t="s">
-        <v>240</v>
+        <v>22</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>122</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I17" s="2">
-        <v>20</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -5961,15 +5915,15 @@
     </row>
     <row r="18" spans="1:13" ht="40.5" hidden="1">
       <c r="A18" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>122</v>
+        <v>191</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>69</v>
@@ -5986,26 +5940,26 @@
       <c r="L18" s="2"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="1:13" ht="40.5" hidden="1">
+    <row r="19" spans="1:13" ht="54" hidden="1">
       <c r="A19" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>54</v>
+        <v>175</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -6013,20 +5967,20 @@
       <c r="L19" s="2"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:13" ht="54" hidden="1">
+    <row r="20" spans="1:13" ht="40.5" hidden="1">
       <c r="A20" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>16</v>
@@ -6042,117 +5996,107 @@
     </row>
     <row r="21" spans="1:13" ht="40.5" hidden="1">
       <c r="A21" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="I21" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="I21" s="2">
+        <v>10</v>
+      </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
+      <c r="L21" s="21"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:13" ht="27">
+    <row r="22" spans="1:13" ht="40.5" hidden="1">
       <c r="A22" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C22" s="8"/>
-      <c r="D22" s="8" t="s">
-        <v>244</v>
-      </c>
+      <c r="D22" s="8"/>
       <c r="E22" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I22" s="2">
-        <v>3</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="L22" s="21">
-        <v>41957</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:13" ht="40.5" hidden="1">
+    <row r="23" spans="1:13" ht="27" hidden="1">
       <c r="A23" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I23" s="2">
-        <v>10</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-      <c r="L23" s="21"/>
+      <c r="L23" s="2"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:13" ht="40.5" hidden="1">
+    <row r="24" spans="1:13" ht="27" hidden="1">
       <c r="A24" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
@@ -6160,55 +6104,67 @@
       <c r="L24" s="2"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" spans="1:13" ht="27" hidden="1">
+    <row r="25" spans="1:13" ht="27">
       <c r="A25" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
+      <c r="D25" s="8" t="s">
+        <v>240</v>
+      </c>
       <c r="E25" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I25" s="2">
+        <v>22</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L25" s="21">
+        <v>41949</v>
+      </c>
+      <c r="M25" s="22"/>
+    </row>
+    <row r="26" spans="1:13" ht="40.5" hidden="1">
+      <c r="A26" s="1">
         <v>33</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="1:13" ht="27" hidden="1">
-      <c r="A26" s="1">
-        <v>31</v>
-      </c>
       <c r="B26" s="8" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="I26" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="I26" s="2">
+        <v>5</v>
+      </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
@@ -6216,180 +6172,172 @@
     </row>
     <row r="27" spans="1:13" ht="27">
       <c r="A27" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C27" s="8"/>
-      <c r="D27" s="8" t="s">
-        <v>242</v>
-      </c>
+      <c r="D27" s="8"/>
       <c r="E27" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="I27" s="2">
-        <v>22</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="L27" s="21">
-        <v>41949</v>
-      </c>
-      <c r="M27" s="22"/>
-    </row>
-    <row r="28" spans="1:13" ht="40.5" hidden="1">
+        <v>2</v>
+      </c>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="1:13" ht="40.5">
       <c r="A28" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I28" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:13" ht="27">
+    <row r="29" spans="1:13" ht="54">
       <c r="A29" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I29" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" spans="1:13" ht="40.5">
+    <row r="30" spans="1:13" ht="27">
       <c r="A30" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>241</v>
+        <v>214</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="I30" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:13" ht="54">
+    <row r="31" spans="1:13" ht="27" hidden="1">
       <c r="A31" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I31" s="2">
         <v>33</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I31" s="2">
-        <v>18</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="1:13" ht="27">
+    <row r="32" spans="1:13" ht="27" hidden="1">
       <c r="A32" s="1">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I32" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
@@ -6397,66 +6345,66 @@
       <c r="M32" s="3"/>
     </row>
     <row r="33" spans="1:13" ht="27" hidden="1">
-      <c r="A33" s="1">
-        <v>38</v>
+      <c r="A33" s="13">
+        <v>40</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="F33" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I33" s="2">
-        <v>33</v>
-      </c>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="1:13" ht="27" hidden="1">
-      <c r="A34" s="1">
-        <v>39</v>
+      <c r="H33" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I33" s="8">
+        <v>10</v>
+      </c>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="14"/>
+    </row>
+    <row r="34" spans="1:13" ht="27">
+      <c r="A34" s="13">
+        <v>41</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="F34" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="I34" s="8">
+        <v>5</v>
+      </c>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="14"/>
+    </row>
+    <row r="35" spans="1:13" ht="27">
+      <c r="A35" s="13">
         <v>42</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I34" s="2">
-        <v>10</v>
-      </c>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="1:13" ht="27" hidden="1">
-      <c r="A35" s="13">
-        <v>40</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>223</v>
@@ -6464,65 +6412,65 @@
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
       <c r="E35" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I35" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
       <c r="M35" s="14"/>
     </row>
-    <row r="36" spans="1:13" ht="27">
+    <row r="36" spans="1:13" ht="27" hidden="1">
       <c r="A36" s="13">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>69</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="I36" s="8">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
       <c r="M36" s="14"/>
     </row>
-    <row r="37" spans="1:13" ht="27">
+    <row r="37" spans="1:13" ht="54">
       <c r="A37" s="13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>69</v>
@@ -6531,10 +6479,10 @@
         <v>22</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I37" s="8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
@@ -6543,56 +6491,56 @@
     </row>
     <row r="38" spans="1:13" ht="27" hidden="1">
       <c r="A38" s="13">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
       <c r="E38" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>12</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I38" s="8">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
       <c r="M38" s="14"/>
     </row>
-    <row r="39" spans="1:13" ht="54">
+    <row r="39" spans="1:13" ht="54" hidden="1">
       <c r="A39" s="13">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>69</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H39" s="8" t="s">
         <v>230</v>
       </c>
       <c r="I39" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
@@ -6601,83 +6549,73 @@
     </row>
     <row r="40" spans="1:13" ht="27" hidden="1">
       <c r="A40" s="13">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G40" s="8" t="s">
         <v>12</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="I40" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
       <c r="L40" s="8"/>
       <c r="M40" s="14"/>
     </row>
-    <row r="41" spans="1:13" ht="27">
+    <row r="41" spans="1:13" ht="27" hidden="1">
       <c r="A41" s="13">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C41" s="8"/>
-      <c r="D41" s="8" t="s">
-        <v>243</v>
-      </c>
+      <c r="D41" s="8"/>
       <c r="E41" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>69</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="I41" s="8">
-        <v>5</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K41" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="L41" s="32">
-        <v>41944</v>
-      </c>
-      <c r="M41" s="35">
-        <v>41953</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="54" hidden="1">
+        <v>4</v>
+      </c>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="14"/>
+    </row>
+    <row r="42" spans="1:13" ht="27" hidden="1">
       <c r="A42" s="13">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
       <c r="E42" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>69</v>
@@ -6686,98 +6624,96 @@
         <v>12</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I42" s="8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
       <c r="L42" s="8"/>
       <c r="M42" s="14"/>
     </row>
-    <row r="43" spans="1:13" ht="27" hidden="1">
+    <row r="43" spans="1:13" ht="40.5">
       <c r="A43" s="13">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
       <c r="E43" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="I43" s="8">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
       <c r="L43" s="8"/>
       <c r="M43" s="14"/>
     </row>
-    <row r="44" spans="1:13" ht="27" hidden="1">
+    <row r="44" spans="1:13" ht="54">
       <c r="A44" s="13">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
+      <c r="D44" s="8" t="s">
+        <v>254</v>
+      </c>
       <c r="E44" s="8" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>210</v>
+        <v>251</v>
       </c>
       <c r="I44" s="8">
-        <v>4</v>
-      </c>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
+        <v>5</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>61</v>
+      </c>
       <c r="L44" s="8"/>
       <c r="M44" s="14"/>
     </row>
-    <row r="45" spans="1:13" ht="27" hidden="1">
+    <row r="45" spans="1:13" ht="27">
       <c r="A45" s="13">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
-      <c r="E45" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>69</v>
-      </c>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
       <c r="G45" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="I45" s="8">
-        <v>3</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
       <c r="J45" s="8"/>
       <c r="K45" s="8"/>
       <c r="L45" s="8"/>
@@ -6785,28 +6721,20 @@
     </row>
     <row r="46" spans="1:13" ht="40.5">
       <c r="A46" s="13">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
-      <c r="E46" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
       <c r="G46" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H46" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="I46" s="8">
-        <v>15</v>
-      </c>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
@@ -6869,7 +6797,7 @@
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
       <c r="K50" s="8"/>
-      <c r="L50" s="8"/>
+      <c r="L50" s="32"/>
       <c r="M50" s="14"/>
     </row>
     <row r="51" spans="1:13">
@@ -6914,7 +6842,7 @@
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
       <c r="K53" s="8"/>
-      <c r="L53" s="32"/>
+      <c r="L53" s="8"/>
       <c r="M53" s="14"/>
     </row>
     <row r="54" spans="1:13">
@@ -7427,65 +7355,20 @@
       <c r="L87" s="8"/>
       <c r="M87" s="14"/>
     </row>
-    <row r="88" spans="1:13">
-      <c r="A88" s="13"/>
-      <c r="B88" s="8"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="8"/>
-      <c r="G88" s="8"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="8"/>
-      <c r="J88" s="8"/>
-      <c r="K88" s="8"/>
-      <c r="L88" s="8"/>
-      <c r="M88" s="14"/>
-    </row>
-    <row r="89" spans="1:13">
-      <c r="A89" s="13"/>
-      <c r="B89" s="8"/>
-      <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="8"/>
-      <c r="J89" s="8"/>
-      <c r="K89" s="8"/>
-      <c r="L89" s="8"/>
-      <c r="M89" s="14"/>
-    </row>
-    <row r="90" spans="1:13">
-      <c r="A90" s="13"/>
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="8"/>
-      <c r="J90" s="8"/>
-      <c r="K90" s="8"/>
-      <c r="L90" s="8"/>
-      <c r="M90" s="14"/>
-    </row>
-    <row r="91" spans="1:13" ht="14.25" thickBot="1">
-      <c r="A91" s="15"/>
-      <c r="B91" s="16"/>
-      <c r="C91" s="16"/>
-      <c r="D91" s="16"/>
-      <c r="E91" s="16"/>
-      <c r="F91" s="16"/>
-      <c r="G91" s="16"/>
-      <c r="H91" s="16"/>
-      <c r="I91" s="16"/>
-      <c r="J91" s="16"/>
-      <c r="K91" s="16"/>
-      <c r="L91" s="16"/>
-      <c r="M91" s="17"/>
+    <row r="88" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A88" s="15"/>
+      <c r="B88" s="16"/>
+      <c r="C88" s="16"/>
+      <c r="D88" s="16"/>
+      <c r="E88" s="16"/>
+      <c r="F88" s="16"/>
+      <c r="G88" s="16"/>
+      <c r="H88" s="16"/>
+      <c r="I88" s="16"/>
+      <c r="J88" s="16"/>
+      <c r="K88" s="16"/>
+      <c r="L88" s="16"/>
+      <c r="M88" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M46">
@@ -7497,42 +7380,42 @@
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:M202">
-    <cfRule type="expression" dxfId="119" priority="5" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:M199">
+    <cfRule type="expression" dxfId="107" priority="5" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="6" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="7" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="8" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:M8">
-    <cfRule type="expression" dxfId="115" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="1" stopIfTrue="1">
       <formula>$K8="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="2" stopIfTrue="1">
       <formula>$K8="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="3" stopIfTrue="1">
       <formula>$K8="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="4" stopIfTrue="1">
       <formula>OR($K8="CLOSED",$K8="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F91">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F88">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G91">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G88">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K91">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K88">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7550,17 +7433,18 @@
     <col min="2" max="2" width="39.75" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="25.5" customWidth="1"/>
-    <col min="5" max="5" width="9.375" customWidth="1"/>
-    <col min="6" max="6" width="9.75" customWidth="1"/>
-    <col min="7" max="7" width="9.875" customWidth="1"/>
-    <col min="8" max="8" width="14.125" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="15.875" customWidth="1"/>
-    <col min="12" max="12" width="17.375" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="9.375" customWidth="1"/>
+    <col min="7" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="9" width="14.125" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="15.875" customWidth="1"/>
+    <col min="13" max="13" width="17.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="29.45" customHeight="1">
+    <row r="1" spans="1:13" ht="29.45" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
@@ -7573,32 +7457,33 @@
       <c r="D1" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="54">
+    <row r="2" spans="1:13" ht="54">
       <c r="A2" s="23">
         <v>55</v>
       </c>
@@ -7609,32 +7494,33 @@
       <c r="D2" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="12"/>
+      <c r="F2" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="H2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="12">
+      <c r="I2" s="12">
         <v>1</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="J2" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="K2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K2" s="24">
+      <c r="L2" s="24">
         <v>41680</v>
       </c>
-      <c r="L2" s="25">
+      <c r="M2" s="25">
         <v>41680</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="27">
+    <row r="3" spans="1:13" ht="27">
       <c r="A3" s="9">
         <v>49</v>
       </c>
@@ -7645,32 +7531,33 @@
       <c r="D3" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="G3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="H3" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="10">
+      <c r="I3" s="10">
         <v>1</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="K3" s="11">
+      <c r="L3" s="11">
         <v>41664</v>
       </c>
-      <c r="L3" s="18">
+      <c r="M3" s="18">
         <v>41664</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="27">
+    <row r="4" spans="1:13" ht="27">
       <c r="A4" s="9">
         <v>50</v>
       </c>
@@ -7681,32 +7568,33 @@
       <c r="D4" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="10">
+      <c r="I4" s="10">
         <v>1</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="J4" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="K4" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="K4" s="11">
+      <c r="L4" s="11">
         <v>41665</v>
       </c>
-      <c r="L4" s="18">
+      <c r="M4" s="18">
         <v>41665</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="27">
+    <row r="5" spans="1:13" ht="27">
       <c r="A5" s="9">
         <v>47</v>
       </c>
@@ -7717,32 +7605,33 @@
       <c r="D5" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="26"/>
+      <c r="F5" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="G5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="H5" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="H5" s="10">
+      <c r="I5" s="10">
         <v>0</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="J5" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="K5" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="L5" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="L5" s="20" t="s">
+      <c r="M5" s="20" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="40.5">
+    <row r="6" spans="1:13" ht="40.5">
       <c r="A6" s="9">
         <v>42</v>
       </c>
@@ -7753,32 +7642,33 @@
       <c r="D6" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="12"/>
+      <c r="F6" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="G6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="H6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="10">
+      <c r="I6" s="10">
         <v>4</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="J6" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="K6" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="11">
+      <c r="L6" s="11">
         <v>41662</v>
       </c>
-      <c r="L6" s="18">
+      <c r="M6" s="18">
         <v>41670</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="54">
+    <row r="7" spans="1:13" ht="54">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -7789,32 +7679,33 @@
       <c r="D7" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="12"/>
+      <c r="F7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="G7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="H7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="10">
+      <c r="I7" s="10">
         <v>4</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="J7" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="K7" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="K7" s="11">
+      <c r="L7" s="11">
         <v>41679</v>
       </c>
-      <c r="L7" s="18">
+      <c r="M7" s="18">
         <v>41687</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="54">
+    <row r="8" spans="1:13" ht="54">
       <c r="A8" s="9">
         <v>5</v>
       </c>
@@ -7825,32 +7716,33 @@
       <c r="D8" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="12"/>
+      <c r="F8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="H8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="10">
+      <c r="I8" s="10">
         <v>4</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="J8" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="K8" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="K8" s="11">
+      <c r="L8" s="11">
         <v>41680</v>
       </c>
-      <c r="L8" s="18">
+      <c r="M8" s="18">
         <v>41683</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="40.5">
+    <row r="9" spans="1:13" ht="40.5">
       <c r="A9" s="13">
         <v>51</v>
       </c>
@@ -7861,28 +7753,29 @@
       <c r="D9" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="8"/>
+      <c r="F9" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="H9" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="H9" s="8">
+      <c r="I9" s="8">
         <v>1</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="J9" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="K9" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="14"/>
-    </row>
-    <row r="10" spans="1:12" ht="27">
+      <c r="L9" s="8"/>
+      <c r="M9" s="14"/>
+    </row>
+    <row r="10" spans="1:13" ht="27">
       <c r="A10" s="13">
         <v>54</v>
       </c>
@@ -7891,28 +7784,29 @@
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="8"/>
+      <c r="F10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="G10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="H10" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="H10" s="8">
+      <c r="I10" s="8">
         <v>3</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="J10" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="K10" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="K10" s="8"/>
-      <c r="L10" s="14"/>
-    </row>
-    <row r="11" spans="1:12" ht="40.5">
+      <c r="L10" s="8"/>
+      <c r="M10" s="14"/>
+    </row>
+    <row r="11" spans="1:13" ht="40.5">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -7923,28 +7817,29 @@
       <c r="D11" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="8"/>
+      <c r="F11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="2">
+      <c r="I11" s="2">
         <v>4</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" ht="40.5">
+      <c r="L11" s="2"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" ht="40.5">
       <c r="A12" s="1">
         <v>48</v>
       </c>
@@ -7953,28 +7848,29 @@
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="8"/>
+      <c r="F12" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="2">
+      <c r="I12" s="2">
         <v>14</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" ht="27">
+      <c r="L12" s="2"/>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" ht="27">
       <c r="A13" s="13">
         <v>57</v>
       </c>
@@ -7985,28 +7881,29 @@
       <c r="D13" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="8"/>
+      <c r="F13" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="G13" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8">
+      <c r="H13" s="8"/>
+      <c r="I13" s="8">
         <v>3</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="J13" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="K13" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="K13" s="32">
+      <c r="L13" s="32">
         <v>41688</v>
       </c>
-      <c r="L13" s="14"/>
-    </row>
-    <row r="14" spans="1:12" ht="40.5">
+      <c r="M13" s="14"/>
+    </row>
+    <row r="14" spans="1:13" ht="40.5">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -8017,28 +7914,29 @@
       <c r="D14" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="8"/>
+      <c r="F14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="2">
+      <c r="H14" s="2"/>
+      <c r="I14" s="2">
         <v>5</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K14" s="21">
+      <c r="L14" s="21">
         <v>41754</v>
       </c>
-      <c r="L14" s="22">
+      <c r="M14" s="22">
         <v>41757</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="54">
+    <row r="15" spans="1:13" ht="54">
       <c r="A15" s="1">
         <v>10</v>
       </c>
@@ -8049,28 +7947,29 @@
       <c r="D15" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="33"/>
+      <c r="F15" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="H15" s="2">
+      <c r="I15" s="2">
         <v>7</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K15" s="2"/>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" ht="40.5">
+      <c r="L15" s="2"/>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" ht="40.5">
       <c r="A16" s="1">
         <v>30</v>
       </c>
@@ -8081,26 +7980,27 @@
       <c r="D16" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="8"/>
+      <c r="F16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H16" s="2">
+      <c r="I16" s="2">
         <v>4</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="3"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="3"/>
     </row>
     <row r="17" spans="1:13" ht="27">
       <c r="A17" s="1">
@@ -8113,26 +8013,27 @@
       <c r="D17" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="8"/>
+      <c r="F17" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="H17" s="2">
+      <c r="I17" s="2">
         <v>3</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K17" s="2"/>
-      <c r="L17" s="3"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="3"/>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="1">
@@ -8145,26 +8046,27 @@
       <c r="D18" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="8"/>
+      <c r="F18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <v>1</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="J18" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K18" s="2"/>
-      <c r="L18" s="3"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="3"/>
     </row>
     <row r="19" spans="1:13" ht="40.5">
       <c r="A19" s="1">
@@ -8177,26 +8079,27 @@
       <c r="D19" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="8"/>
+      <c r="F19" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="H19" s="2">
+      <c r="I19" s="2">
         <v>3</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="J19" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="K19" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K19" s="2"/>
-      <c r="L19" s="3"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="3"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1">
@@ -8209,26 +8112,27 @@
       <c r="D20" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="8"/>
+      <c r="F20" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="H20" s="2">
+      <c r="I20" s="2">
         <v>1</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="J20" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="K20" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K20" s="2"/>
-      <c r="L20" s="3"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="3"/>
     </row>
     <row r="21" spans="1:13" ht="27">
       <c r="A21" s="1">
@@ -8239,24 +8143,25 @@
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="8"/>
+      <c r="F21" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2">
+      <c r="H21" s="2"/>
+      <c r="I21" s="2">
         <v>5</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="J21" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="K21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K21" s="2"/>
-      <c r="L21" s="3"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="3"/>
     </row>
     <row r="22" spans="1:13" ht="27">
       <c r="A22" s="1">
@@ -8267,26 +8172,27 @@
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="8"/>
+      <c r="F22" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="H22" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="2">
+      <c r="I22" s="2">
         <v>5</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="J22" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="K22" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K22" s="2"/>
-      <c r="L22" s="3"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="3"/>
     </row>
     <row r="23" spans="1:13" ht="27">
       <c r="A23" s="1">
@@ -8297,26 +8203,27 @@
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="8"/>
+      <c r="F23" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H23" s="2">
+      <c r="I23" s="2">
         <v>5</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="J23" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="K23" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K23" s="2"/>
-      <c r="L23" s="3"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="3"/>
     </row>
     <row r="24" spans="1:13" ht="27">
       <c r="A24" s="1">
@@ -8329,26 +8236,27 @@
       <c r="D24" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="8"/>
+      <c r="F24" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H24" s="2">
+      <c r="I24" s="2">
         <v>9</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="J24" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="K24" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K24" s="2"/>
-      <c r="L24" s="3"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="3"/>
     </row>
     <row r="25" spans="1:13" ht="27">
       <c r="A25" s="1">
@@ -8361,26 +8269,27 @@
       <c r="D25" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="8"/>
+      <c r="F25" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H25" s="2">
+      <c r="I25" s="2">
         <v>5</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="J25" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="K25" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K25" s="2"/>
-      <c r="L25" s="3"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="3"/>
     </row>
     <row r="26" spans="1:13" ht="27">
       <c r="A26" s="1">
@@ -8393,26 +8302,27 @@
       <c r="D26" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="8"/>
+      <c r="F26" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H26" s="2">
+      <c r="I26" s="2">
         <v>5</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="J26" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="K26" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K26" s="2"/>
-      <c r="L26" s="3"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="3"/>
     </row>
     <row r="27" spans="1:13" ht="27">
       <c r="A27" s="27">
@@ -8423,26 +8333,27 @@
       </c>
       <c r="C27" s="28"/>
       <c r="D27" s="28"/>
-      <c r="E27" s="29" t="s">
+      <c r="E27" s="28"/>
+      <c r="F27" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="29" t="s">
+      <c r="G27" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="29" t="s">
+      <c r="H27" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="H27" s="29">
+      <c r="I27" s="29">
         <v>8</v>
       </c>
-      <c r="I27" s="29" t="s">
+      <c r="J27" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="J27" s="29" t="s">
+      <c r="K27" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="K27" s="29"/>
-      <c r="L27" s="31"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="31"/>
     </row>
     <row r="28" spans="1:13" ht="27">
       <c r="A28" s="1">
@@ -8453,24 +8364,25 @@
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="8"/>
+      <c r="F28" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="G28" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="H28" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H28" s="2">
+      <c r="I28" s="2">
         <v>5</v>
       </c>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2" t="s">
+      <c r="J28" s="2"/>
+      <c r="K28" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K28" s="2"/>
-      <c r="L28" s="3"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="3"/>
     </row>
     <row r="29" spans="1:13" ht="40.5">
       <c r="A29" s="1">
@@ -8481,24 +8393,25 @@
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="8"/>
+      <c r="F29" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H29" s="2">
+      <c r="I29" s="2">
         <v>5</v>
       </c>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2" t="s">
+      <c r="J29" s="2"/>
+      <c r="K29" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K29" s="2"/>
-      <c r="L29" s="3"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="3"/>
     </row>
     <row r="30" spans="1:13" ht="27">
       <c r="A30" s="1">
@@ -8509,18 +8422,19 @@
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="8"/>
+      <c r="F30" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="2" t="s">
+      <c r="J30" s="2"/>
+      <c r="K30" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K30" s="2"/>
-      <c r="L30" s="3"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="3"/>
     </row>
     <row r="31" spans="1:13" ht="27">
       <c r="A31" s="1">
@@ -8531,24 +8445,25 @@
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="8"/>
+      <c r="F31" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="G31" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H31" s="2">
+      <c r="I31" s="2">
         <v>15</v>
       </c>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2" t="s">
+      <c r="J31" s="2"/>
+      <c r="K31" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K31" s="2"/>
-      <c r="L31" s="3"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="3"/>
     </row>
     <row r="32" spans="1:13" ht="27">
       <c r="A32" s="1">
@@ -8641,7 +8556,7 @@
         <v>8</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>204</v>
+        <v>83</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>84</v>
@@ -8673,8 +8588,8 @@
       <c r="I35" s="2">
         <v>80</v>
       </c>
-      <c r="J35" s="2" t="s">
-        <v>205</v>
+      <c r="J35" s="8" t="s">
+        <v>204</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>84</v>
@@ -8706,350 +8621,442 @@
       <c r="I36" s="2">
         <v>4</v>
       </c>
-      <c r="J36" s="2"/>
+      <c r="J36" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="K36" s="2" t="s">
         <v>84</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" spans="1:13">
-      <c r="A37" s="1"/>
-      <c r="B37" s="8"/>
+    <row r="37" spans="1:13" ht="40.5">
+      <c r="A37" s="1">
+        <v>11</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>246</v>
+      </c>
       <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="3"/>
-    </row>
-    <row r="38" spans="1:13">
-      <c r="A38" s="1"/>
-      <c r="B38" s="8"/>
+      <c r="D37" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I37" s="2">
+        <v>3</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" s="3"/>
+    </row>
+    <row r="38" spans="1:13" ht="27">
+      <c r="A38" s="1">
+        <v>27</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>195</v>
+      </c>
       <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="3"/>
-    </row>
-    <row r="39" spans="1:13">
-      <c r="A39" s="1"/>
-      <c r="B39" s="8"/>
+      <c r="D38" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I38" s="2">
+        <v>3</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L38" s="21">
+        <v>41957</v>
+      </c>
+      <c r="M38" s="3"/>
+    </row>
+    <row r="39" spans="1:13" ht="27">
+      <c r="A39" s="13">
+        <v>46</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>231</v>
+      </c>
       <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="3"/>
+      <c r="D39" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="I39" s="8">
+        <v>5</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L39" s="32">
+        <v>41944</v>
+      </c>
+      <c r="M39" s="35">
+        <v>41953</v>
+      </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
-      <c r="E40" s="2"/>
+      <c r="E40" s="8"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
-      <c r="L40" s="3"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="3"/>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
-      <c r="E41" s="2"/>
+      <c r="E41" s="8"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
-      <c r="L41" s="3"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="3"/>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
-      <c r="E42" s="2"/>
+      <c r="E42" s="8"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
-      <c r="L42" s="3"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="3"/>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
-      <c r="E43" s="2"/>
+      <c r="E43" s="8"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
-      <c r="L43" s="3"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="3"/>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
-      <c r="E44" s="2"/>
+      <c r="E44" s="8"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
-      <c r="L44" s="3"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="3"/>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
-      <c r="E45" s="2"/>
+      <c r="E45" s="8"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
-      <c r="L45" s="3"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="3"/>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
-      <c r="E46" s="2"/>
+      <c r="E46" s="8"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
-      <c r="L46" s="3"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="3"/>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
-      <c r="E47" s="2"/>
+      <c r="E47" s="8"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
-      <c r="L47" s="3"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="3"/>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
-      <c r="E48" s="2"/>
+      <c r="E48" s="8"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="1:12">
+      <c r="L48" s="2"/>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="1"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
-      <c r="E49" s="2"/>
+      <c r="E49" s="8"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="1:12">
+      <c r="L49" s="2"/>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="1"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
-      <c r="E50" s="2"/>
+      <c r="E50" s="8"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="1:12">
+      <c r="L50" s="2"/>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="1"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
-      <c r="E51" s="2"/>
+      <c r="E51" s="8"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="1:12">
+      <c r="L51" s="2"/>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="1"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
-      <c r="E52" s="2"/>
+      <c r="E52" s="8"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="1:12">
+      <c r="L52" s="2"/>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="1"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
-      <c r="E53" s="2"/>
+      <c r="E53" s="8"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="1:12">
+      <c r="L53" s="2"/>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="1"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
-      <c r="E54" s="2"/>
+      <c r="E54" s="8"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="1:12">
+      <c r="L54" s="2"/>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="1"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
-      <c r="E55" s="2"/>
+      <c r="E55" s="8"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
-      <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="1:12">
+      <c r="L55" s="2"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" s="1"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
-      <c r="E56" s="2"/>
+      <c r="E56" s="8"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
-      <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="1:12">
+      <c r="L56" s="2"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" s="1"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
-      <c r="E57" s="2"/>
+      <c r="E57" s="8"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="1:12">
+      <c r="L57" s="2"/>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" s="1"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
-      <c r="E58" s="2"/>
+      <c r="E58" s="8"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="1:12">
+      <c r="L58" s="2"/>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="1:13">
       <c r="A59" s="1"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
-      <c r="E59" s="2"/>
+      <c r="E59" s="8"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
-      <c r="K59" s="21"/>
-      <c r="L59" s="22"/>
-    </row>
-    <row r="60" spans="1:12">
+      <c r="K59" s="2"/>
+      <c r="L59" s="21"/>
+      <c r="M59" s="22"/>
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" s="1"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
-      <c r="E60" s="2"/>
+      <c r="E60" s="8"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="1:12">
+      <c r="L60" s="2"/>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="1:13">
       <c r="A61" s="13"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
@@ -9061,9 +9068,10 @@
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
       <c r="K61" s="8"/>
-      <c r="L61" s="14"/>
-    </row>
-    <row r="62" spans="1:12">
+      <c r="L61" s="8"/>
+      <c r="M61" s="14"/>
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" s="13"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -9075,9 +9083,10 @@
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
       <c r="K62" s="8"/>
-      <c r="L62" s="14"/>
-    </row>
-    <row r="63" spans="1:12">
+      <c r="L62" s="8"/>
+      <c r="M62" s="14"/>
+    </row>
+    <row r="63" spans="1:13">
       <c r="A63" s="13"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -9089,9 +9098,10 @@
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
       <c r="K63" s="8"/>
-      <c r="L63" s="14"/>
-    </row>
-    <row r="64" spans="1:12">
+      <c r="L63" s="8"/>
+      <c r="M63" s="14"/>
+    </row>
+    <row r="64" spans="1:13">
       <c r="A64" s="13"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -9103,9 +9113,10 @@
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
       <c r="K64" s="8"/>
-      <c r="L64" s="14"/>
-    </row>
-    <row r="65" spans="1:12">
+      <c r="L64" s="8"/>
+      <c r="M64" s="14"/>
+    </row>
+    <row r="65" spans="1:13">
       <c r="A65" s="13"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -9117,9 +9128,10 @@
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
       <c r="K65" s="8"/>
-      <c r="L65" s="14"/>
-    </row>
-    <row r="66" spans="1:12">
+      <c r="L65" s="8"/>
+      <c r="M65" s="14"/>
+    </row>
+    <row r="66" spans="1:13">
       <c r="A66" s="13"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -9131,9 +9143,10 @@
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
       <c r="K66" s="8"/>
-      <c r="L66" s="14"/>
-    </row>
-    <row r="67" spans="1:12">
+      <c r="L66" s="8"/>
+      <c r="M66" s="14"/>
+    </row>
+    <row r="67" spans="1:13">
       <c r="A67" s="13"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -9145,9 +9158,10 @@
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
       <c r="K67" s="8"/>
-      <c r="L67" s="14"/>
-    </row>
-    <row r="68" spans="1:12">
+      <c r="L67" s="8"/>
+      <c r="M67" s="14"/>
+    </row>
+    <row r="68" spans="1:13">
       <c r="A68" s="13"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -9159,9 +9173,10 @@
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
       <c r="K68" s="8"/>
-      <c r="L68" s="14"/>
-    </row>
-    <row r="69" spans="1:12">
+      <c r="L68" s="8"/>
+      <c r="M68" s="14"/>
+    </row>
+    <row r="69" spans="1:13">
       <c r="A69" s="13"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -9173,9 +9188,10 @@
       <c r="I69" s="8"/>
       <c r="J69" s="8"/>
       <c r="K69" s="8"/>
-      <c r="L69" s="14"/>
-    </row>
-    <row r="70" spans="1:12">
+      <c r="L69" s="8"/>
+      <c r="M69" s="14"/>
+    </row>
+    <row r="70" spans="1:13">
       <c r="A70" s="13"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
@@ -9187,9 +9203,10 @@
       <c r="I70" s="8"/>
       <c r="J70" s="8"/>
       <c r="K70" s="8"/>
-      <c r="L70" s="14"/>
-    </row>
-    <row r="71" spans="1:12">
+      <c r="L70" s="8"/>
+      <c r="M70" s="14"/>
+    </row>
+    <row r="71" spans="1:13">
       <c r="A71" s="13"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
@@ -9201,9 +9218,10 @@
       <c r="I71" s="8"/>
       <c r="J71" s="8"/>
       <c r="K71" s="8"/>
-      <c r="L71" s="14"/>
-    </row>
-    <row r="72" spans="1:12">
+      <c r="L71" s="8"/>
+      <c r="M71" s="14"/>
+    </row>
+    <row r="72" spans="1:13">
       <c r="A72" s="13"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
@@ -9215,9 +9233,10 @@
       <c r="I72" s="8"/>
       <c r="J72" s="8"/>
       <c r="K72" s="8"/>
-      <c r="L72" s="14"/>
-    </row>
-    <row r="73" spans="1:12">
+      <c r="L72" s="8"/>
+      <c r="M72" s="14"/>
+    </row>
+    <row r="73" spans="1:13">
       <c r="A73" s="13"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
@@ -9229,9 +9248,10 @@
       <c r="I73" s="8"/>
       <c r="J73" s="8"/>
       <c r="K73" s="8"/>
-      <c r="L73" s="14"/>
-    </row>
-    <row r="74" spans="1:12" ht="14.25" thickBot="1">
+      <c r="L73" s="8"/>
+      <c r="M73" s="14"/>
+    </row>
+    <row r="74" spans="1:13" ht="14.25" thickBot="1">
       <c r="A74" s="15"/>
       <c r="B74" s="16"/>
       <c r="C74" s="16"/>
@@ -9243,414 +9263,374 @@
       <c r="I74" s="16"/>
       <c r="J74" s="16"/>
       <c r="K74" s="16"/>
-      <c r="L74" s="17"/>
+      <c r="L74" s="16"/>
+      <c r="M74" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L64">
+  <autoFilter ref="A1:M64">
     <filterColumn colId="2"/>
     <filterColumn colId="3"/>
+    <filterColumn colId="4"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A9:L9">
-    <cfRule type="expression" dxfId="111" priority="109" stopIfTrue="1">
-      <formula>$J9="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="110" priority="110" stopIfTrue="1">
-      <formula>$J9="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="109" priority="111" stopIfTrue="1">
-      <formula>$J9="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="108" priority="112" stopIfTrue="1">
-      <formula>OR($J9="CLOSED",$J9="CANCEL")</formula>
+  <conditionalFormatting sqref="A9:M9 A32:M37">
+    <cfRule type="expression" dxfId="99" priority="121" stopIfTrue="1">
+      <formula>$K9="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="122" stopIfTrue="1">
+      <formula>$K9="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="123" stopIfTrue="1">
+      <formula>$K9="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="124" stopIfTrue="1">
+      <formula>OR($K9="CLOSED",$K9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A10:L10">
-    <cfRule type="expression" dxfId="107" priority="105" stopIfTrue="1">
-      <formula>$J10="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="106" priority="106" stopIfTrue="1">
-      <formula>$J10="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="105" priority="107" stopIfTrue="1">
-      <formula>$J10="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="104" priority="108" stopIfTrue="1">
-      <formula>OR($J10="CLOSED",$J10="CANCEL")</formula>
+  <conditionalFormatting sqref="A10:M10">
+    <cfRule type="expression" dxfId="95" priority="117" stopIfTrue="1">
+      <formula>$K10="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="94" priority="118" stopIfTrue="1">
+      <formula>$K10="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="93" priority="119" stopIfTrue="1">
+      <formula>$K10="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="92" priority="120" stopIfTrue="1">
+      <formula>OR($K10="CLOSED",$K10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A11:L11">
-    <cfRule type="expression" dxfId="103" priority="101" stopIfTrue="1">
-      <formula>$J11="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="102" priority="102" stopIfTrue="1">
-      <formula>$J11="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="101" priority="103" stopIfTrue="1">
-      <formula>$J11="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="100" priority="104" stopIfTrue="1">
-      <formula>OR($J11="CLOSED",$J11="CANCEL")</formula>
+  <conditionalFormatting sqref="A11:M11">
+    <cfRule type="expression" dxfId="91" priority="113" stopIfTrue="1">
+      <formula>$K11="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="90" priority="114" stopIfTrue="1">
+      <formula>$K11="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="89" priority="115" stopIfTrue="1">
+      <formula>$K11="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="88" priority="116" stopIfTrue="1">
+      <formula>OR($K11="CLOSED",$K11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:L12">
-    <cfRule type="expression" dxfId="99" priority="97" stopIfTrue="1">
-      <formula>$J12="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="98" priority="98" stopIfTrue="1">
-      <formula>$J12="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="97" priority="99" stopIfTrue="1">
-      <formula>$J12="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="96" priority="100" stopIfTrue="1">
-      <formula>OR($J12="CLOSED",$J12="CANCEL")</formula>
+  <conditionalFormatting sqref="A12:M12">
+    <cfRule type="expression" dxfId="87" priority="109" stopIfTrue="1">
+      <formula>$K12="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="110" stopIfTrue="1">
+      <formula>$K12="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="111" stopIfTrue="1">
+      <formula>$K12="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="112" stopIfTrue="1">
+      <formula>OR($K12="CLOSED",$K12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13:L13">
-    <cfRule type="expression" dxfId="95" priority="93" stopIfTrue="1">
-      <formula>$J13="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="94" priority="94" stopIfTrue="1">
-      <formula>$J13="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="93" priority="95" stopIfTrue="1">
-      <formula>$J13="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="92" priority="96" stopIfTrue="1">
-      <formula>OR($J13="CLOSED",$J13="CANCEL")</formula>
+  <conditionalFormatting sqref="A13:M13">
+    <cfRule type="expression" dxfId="83" priority="105" stopIfTrue="1">
+      <formula>$K13="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="106" stopIfTrue="1">
+      <formula>$K13="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="107" stopIfTrue="1">
+      <formula>$K13="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="108" stopIfTrue="1">
+      <formula>OR($K13="CLOSED",$K13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A14:L14">
-    <cfRule type="expression" dxfId="91" priority="89" stopIfTrue="1">
-      <formula>$J14="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="90" priority="90" stopIfTrue="1">
-      <formula>$J14="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="89" priority="91" stopIfTrue="1">
-      <formula>$J14="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="88" priority="92" stopIfTrue="1">
-      <formula>OR($J14="CLOSED",$J14="CANCEL")</formula>
+  <conditionalFormatting sqref="A14:M14">
+    <cfRule type="expression" dxfId="79" priority="101" stopIfTrue="1">
+      <formula>$K14="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="102" stopIfTrue="1">
+      <formula>$K14="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="103" stopIfTrue="1">
+      <formula>$K14="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="104" stopIfTrue="1">
+      <formula>OR($K14="CLOSED",$K14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A15:L15">
-    <cfRule type="expression" dxfId="87" priority="85" stopIfTrue="1">
-      <formula>$J15="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="86" stopIfTrue="1">
-      <formula>$J15="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="87" stopIfTrue="1">
-      <formula>$J15="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="88" stopIfTrue="1">
-      <formula>OR($J15="CLOSED",$J15="CANCEL")</formula>
+  <conditionalFormatting sqref="A15:M15">
+    <cfRule type="expression" dxfId="75" priority="97" stopIfTrue="1">
+      <formula>$K15="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="98" stopIfTrue="1">
+      <formula>$K15="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="73" priority="99" stopIfTrue="1">
+      <formula>$K15="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="100" stopIfTrue="1">
+      <formula>OR($K15="CLOSED",$K15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A16:L16">
-    <cfRule type="expression" dxfId="83" priority="81" stopIfTrue="1">
-      <formula>$J16="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="82" priority="82" stopIfTrue="1">
-      <formula>$J16="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="83" stopIfTrue="1">
-      <formula>$J16="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="80" priority="84" stopIfTrue="1">
-      <formula>OR($J16="CLOSED",$J16="CANCEL")</formula>
+  <conditionalFormatting sqref="A16:M16">
+    <cfRule type="expression" dxfId="71" priority="93" stopIfTrue="1">
+      <formula>$K16="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="94" stopIfTrue="1">
+      <formula>$K16="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="69" priority="95" stopIfTrue="1">
+      <formula>$K16="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="68" priority="96" stopIfTrue="1">
+      <formula>OR($K16="CLOSED",$K16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A17:L17">
-    <cfRule type="expression" dxfId="79" priority="77" stopIfTrue="1">
-      <formula>$J17="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="78" priority="78" stopIfTrue="1">
-      <formula>$J17="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="79" stopIfTrue="1">
-      <formula>$J17="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="76" priority="80" stopIfTrue="1">
-      <formula>OR($J17="CLOSED",$J17="CANCEL")</formula>
+  <conditionalFormatting sqref="A17:M17">
+    <cfRule type="expression" dxfId="67" priority="89" stopIfTrue="1">
+      <formula>$K17="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="66" priority="90" stopIfTrue="1">
+      <formula>$K17="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="91" stopIfTrue="1">
+      <formula>$K17="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="92" stopIfTrue="1">
+      <formula>OR($K17="CLOSED",$K17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A18:L18">
-    <cfRule type="expression" dxfId="75" priority="73" stopIfTrue="1">
-      <formula>$J18="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="74" priority="74" stopIfTrue="1">
-      <formula>$J18="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="73" priority="75" stopIfTrue="1">
-      <formula>$J18="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="72" priority="76" stopIfTrue="1">
-      <formula>OR($J18="CLOSED",$J18="CANCEL")</formula>
+  <conditionalFormatting sqref="A18:M18">
+    <cfRule type="expression" dxfId="63" priority="85" stopIfTrue="1">
+      <formula>$K18="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="86" stopIfTrue="1">
+      <formula>$K18="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="87" stopIfTrue="1">
+      <formula>$K18="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="60" priority="88" stopIfTrue="1">
+      <formula>OR($K18="CLOSED",$K18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A19:L19">
-    <cfRule type="expression" dxfId="71" priority="69" stopIfTrue="1">
-      <formula>$J19="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="70" priority="70" stopIfTrue="1">
-      <formula>$J19="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="69" priority="71" stopIfTrue="1">
-      <formula>$J19="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="68" priority="72" stopIfTrue="1">
-      <formula>OR($J19="CLOSED",$J19="CANCEL")</formula>
+  <conditionalFormatting sqref="A19:M19">
+    <cfRule type="expression" dxfId="59" priority="81" stopIfTrue="1">
+      <formula>$K19="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="82" stopIfTrue="1">
+      <formula>$K19="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="57" priority="83" stopIfTrue="1">
+      <formula>$K19="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="84" stopIfTrue="1">
+      <formula>OR($K19="CLOSED",$K19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A20:L20">
-    <cfRule type="expression" dxfId="67" priority="65" stopIfTrue="1">
-      <formula>$J20="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="66" priority="66" stopIfTrue="1">
-      <formula>$J20="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="67" stopIfTrue="1">
-      <formula>$J20="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="64" priority="68" stopIfTrue="1">
-      <formula>OR($J20="CLOSED",$J20="CANCEL")</formula>
+  <conditionalFormatting sqref="A20:M20">
+    <cfRule type="expression" dxfId="55" priority="77" stopIfTrue="1">
+      <formula>$K20="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="78" stopIfTrue="1">
+      <formula>$K20="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="79" stopIfTrue="1">
+      <formula>$K20="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="80" stopIfTrue="1">
+      <formula>OR($K20="CLOSED",$K20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A21:L21">
-    <cfRule type="expression" dxfId="63" priority="61" stopIfTrue="1">
-      <formula>$J21="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="62" priority="62" stopIfTrue="1">
-      <formula>$J21="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="63" stopIfTrue="1">
-      <formula>$J21="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="64" stopIfTrue="1">
-      <formula>OR($J21="CLOSED",$J21="CANCEL")</formula>
+  <conditionalFormatting sqref="A21:M21">
+    <cfRule type="expression" dxfId="51" priority="73" stopIfTrue="1">
+      <formula>$K21="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="74" stopIfTrue="1">
+      <formula>$K21="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="75" stopIfTrue="1">
+      <formula>$K21="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="76" stopIfTrue="1">
+      <formula>OR($K21="CLOSED",$K21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A22:L23">
-    <cfRule type="expression" dxfId="59" priority="57" stopIfTrue="1">
-      <formula>$J22="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="58" stopIfTrue="1">
-      <formula>$J22="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="57" priority="59" stopIfTrue="1">
-      <formula>$J22="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="56" priority="60" stopIfTrue="1">
-      <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
+  <conditionalFormatting sqref="A22:M23">
+    <cfRule type="expression" dxfId="47" priority="69" stopIfTrue="1">
+      <formula>$K22="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="46" priority="70" stopIfTrue="1">
+      <formula>$K22="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="71" stopIfTrue="1">
+      <formula>$K22="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="72" stopIfTrue="1">
+      <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B22:H22">
-    <cfRule type="expression" dxfId="55" priority="53" stopIfTrue="1">
-      <formula>$J22="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="54" stopIfTrue="1">
-      <formula>$J22="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="53" priority="55" stopIfTrue="1">
-      <formula>$J22="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="56" stopIfTrue="1">
-      <formula>OR($J22="CLOSED",$J22="CANCEL")</formula>
+  <conditionalFormatting sqref="B22:I22">
+    <cfRule type="expression" dxfId="43" priority="65" stopIfTrue="1">
+      <formula>$K22="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="66" stopIfTrue="1">
+      <formula>$K22="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="41" priority="67" stopIfTrue="1">
+      <formula>$K22="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="68" stopIfTrue="1">
+      <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="51" priority="49" stopIfTrue="1">
-      <formula>$J23="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="50" priority="50" stopIfTrue="1">
-      <formula>$J23="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="51" stopIfTrue="1">
-      <formula>$J23="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="52" stopIfTrue="1">
-      <formula>OR($J23="CLOSED",$J23="CANCEL")</formula>
+    <cfRule type="expression" dxfId="39" priority="61" stopIfTrue="1">
+      <formula>$K23="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="62" stopIfTrue="1">
+      <formula>$K23="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="63" stopIfTrue="1">
+      <formula>$K23="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="64" stopIfTrue="1">
+      <formula>OR($K23="CLOSED",$K23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A24:L25">
-    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
-      <formula>$J24="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
-      <formula>$J24="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
-      <formula>$J24="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
-      <formula>OR($J24="CLOSED",$J24="CANCEL")</formula>
+  <conditionalFormatting sqref="A24:M25">
+    <cfRule type="expression" dxfId="35" priority="57" stopIfTrue="1">
+      <formula>$K24="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="58" stopIfTrue="1">
+      <formula>$K24="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="59" stopIfTrue="1">
+      <formula>$K24="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="60" stopIfTrue="1">
+      <formula>OR($K24="CLOSED",$K24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
-      <formula>$J25="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
-      <formula>$J25="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="41" priority="43" stopIfTrue="1">
-      <formula>$J25="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="44" stopIfTrue="1">
-      <formula>OR($J25="CLOSED",$J25="CANCEL")</formula>
+    <cfRule type="expression" dxfId="31" priority="53" stopIfTrue="1">
+      <formula>$K25="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="54" stopIfTrue="1">
+      <formula>$K25="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="55" stopIfTrue="1">
+      <formula>$K25="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="56" stopIfTrue="1">
+      <formula>OR($K25="CLOSED",$K25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26:L26">
-    <cfRule type="expression" dxfId="39" priority="37" stopIfTrue="1">
-      <formula>$J26="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="38" stopIfTrue="1">
-      <formula>$J26="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="39" stopIfTrue="1">
-      <formula>$J26="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="40" stopIfTrue="1">
-      <formula>OR($J26="CLOSED",$J26="CANCEL")</formula>
+  <conditionalFormatting sqref="A26:M26">
+    <cfRule type="expression" dxfId="27" priority="49" stopIfTrue="1">
+      <formula>$K26="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="50" stopIfTrue="1">
+      <formula>$K26="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="51" stopIfTrue="1">
+      <formula>$K26="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="52" stopIfTrue="1">
+      <formula>OR($K26="CLOSED",$K26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A27:L28">
-    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
-      <formula>$J27="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
-      <formula>$J27="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
-      <formula>$J27="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
-      <formula>OR($J27="CLOSED",$J27="CANCEL")</formula>
+  <conditionalFormatting sqref="A27:M28">
+    <cfRule type="expression" dxfId="23" priority="45" stopIfTrue="1">
+      <formula>$K27="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="46" stopIfTrue="1">
+      <formula>$K27="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="47" stopIfTrue="1">
+      <formula>$K27="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="48" stopIfTrue="1">
+      <formula>OR($K27="CLOSED",$K27="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A29:L30">
-    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
-      <formula>$J29="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
-      <formula>$J29="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="31" stopIfTrue="1">
-      <formula>$J29="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
-      <formula>OR($J29="CLOSED",$J29="CANCEL")</formula>
+  <conditionalFormatting sqref="A29:M30">
+    <cfRule type="expression" dxfId="19" priority="41" stopIfTrue="1">
+      <formula>$K29="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="42" stopIfTrue="1">
+      <formula>$K29="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="43" stopIfTrue="1">
+      <formula>$K29="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="44" stopIfTrue="1">
+      <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A29:L29">
-    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
-      <formula>$J29="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
-      <formula>$J29="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="27" stopIfTrue="1">
-      <formula>$J29="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="28" stopIfTrue="1">
-      <formula>OR($J29="CLOSED",$J29="CANCEL")</formula>
+  <conditionalFormatting sqref="A29:M29">
+    <cfRule type="expression" dxfId="15" priority="37" stopIfTrue="1">
+      <formula>$K29="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="38" stopIfTrue="1">
+      <formula>$K29="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="39" stopIfTrue="1">
+      <formula>$K29="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="40" stopIfTrue="1">
+      <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A31:L31">
-    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
-      <formula>$J31="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
-      <formula>$J31="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
-      <formula>$J31="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
-      <formula>OR($J31="CLOSED",$J31="CANCEL")</formula>
+  <conditionalFormatting sqref="A31:M31">
+    <cfRule type="expression" dxfId="11" priority="33" stopIfTrue="1">
+      <formula>$K31="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="34" stopIfTrue="1">
+      <formula>$K31="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="35" stopIfTrue="1">
+      <formula>$K31="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="36" stopIfTrue="1">
+      <formula>OR($K31="CLOSED",$K31="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A32:M32">
-    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
-      <formula>$K32="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
-      <formula>$K32="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
-      <formula>$K32="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
-      <formula>OR($K32="CLOSED",$K32="CANCEL")</formula>
+  <conditionalFormatting sqref="A38:M38">
+    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
+      <formula>$K38="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+      <formula>$K38="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+      <formula>$K38="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+      <formula>OR($K38="CLOSED",$K38="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A33:M33">
-    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
-      <formula>$K33="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14" stopIfTrue="1">
-      <formula>$K33="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="15" stopIfTrue="1">
-      <formula>$K33="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
-      <formula>OR($K33="CLOSED",$K33="CANCEL")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A34:M34">
-    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
-      <formula>$K34="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
-      <formula>$K34="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
-      <formula>$K34="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
-      <formula>OR($K34="CLOSED",$K34="CANCEL")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:M35">
-    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
-      <formula>$K35="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
-      <formula>$K35="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
-      <formula>$K35="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
-      <formula>OR($K35="CLOSED",$K35="CANCEL")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A36:M36">
+  <conditionalFormatting sqref="A39:M39">
     <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
-      <formula>$K36="HANG-UP"</formula>
+      <formula>$K39="HANG-UP"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
-      <formula>$K36="PLAN"</formula>
+      <formula>$K39="PLAN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
-      <formula>$K36="OPEN"</formula>
+      <formula>$K39="OPEN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
-      <formula>OR($K36="CLOSED",$K36="CANCEL")</formula>
+      <formula>OR($K39="CLOSED",$K39="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J31 K32:K36 J37:J74">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K74">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F31 G32:G36 F37:F74">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G74">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E31 F32:F36 E37:E74">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F74">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
   </dataValidations>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -13,7 +13,7 @@
     <sheet name="已完成任务" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2014年'!$A$1:$M$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2014年'!$A$1:$M$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$L$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$M$64</definedName>
   </definedNames>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="257">
   <si>
     <r>
       <t>描述</t>
@@ -1286,6 +1286,11 @@
   </si>
   <si>
     <t>李伟超</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">query的selector提供对field选取或排除两种模式
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5408,7 +5413,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:M88"/>
@@ -5498,7 +5503,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:13" ht="40.5" hidden="1">
+    <row r="3" spans="1:13" ht="40.5">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -5554,7 +5559,7 @@
       <c r="L4" s="30"/>
       <c r="M4" s="31"/>
     </row>
-    <row r="5" spans="1:13" ht="40.5" hidden="1">
+    <row r="5" spans="1:13" ht="40.5">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -5583,7 +5588,7 @@
       <c r="L5" s="2"/>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:13" ht="54" hidden="1">
+    <row r="6" spans="1:13" ht="54">
       <c r="A6" s="1">
         <v>7</v>
       </c>
@@ -5612,7 +5617,7 @@
       <c r="L6" s="2"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:13" ht="54" hidden="1">
+    <row r="7" spans="1:13" ht="54">
       <c r="A7" s="1">
         <v>8</v>
       </c>
@@ -5639,7 +5644,7 @@
       <c r="L7" s="2"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="40.5" hidden="1">
+    <row r="8" spans="1:13" ht="40.5">
       <c r="A8" s="1">
         <v>10</v>
       </c>
@@ -5666,7 +5671,7 @@
       <c r="L8" s="2"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:13" ht="27" hidden="1">
+    <row r="9" spans="1:13" ht="27">
       <c r="A9" s="1">
         <v>13</v>
       </c>
@@ -5693,7 +5698,7 @@
       <c r="L9" s="2"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="1:13" ht="54" hidden="1">
+    <row r="10" spans="1:13" ht="54">
       <c r="A10" s="1">
         <v>14</v>
       </c>
@@ -5749,7 +5754,7 @@
       <c r="L11" s="29"/>
       <c r="M11" s="31"/>
     </row>
-    <row r="12" spans="1:13" ht="27" hidden="1">
+    <row r="12" spans="1:13" ht="27">
       <c r="A12" s="27">
         <v>17</v>
       </c>
@@ -5776,7 +5781,7 @@
       <c r="L12" s="29"/>
       <c r="M12" s="31"/>
     </row>
-    <row r="13" spans="1:13" ht="27" hidden="1">
+    <row r="13" spans="1:13" ht="27">
       <c r="A13" s="1">
         <v>18</v>
       </c>
@@ -5803,7 +5808,7 @@
       <c r="L13" s="2"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" ht="40.5" hidden="1">
+    <row r="14" spans="1:13" ht="40.5">
       <c r="A14" s="1">
         <v>19</v>
       </c>
@@ -5830,7 +5835,7 @@
       <c r="L14" s="2"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:13" ht="27" hidden="1">
+    <row r="15" spans="1:13" ht="27">
       <c r="A15" s="1">
         <v>20</v>
       </c>
@@ -5886,7 +5891,7 @@
       <c r="L16" s="2"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="1:13" ht="40.5" hidden="1">
+    <row r="17" spans="1:13" ht="40.5">
       <c r="A17" s="1">
         <v>22</v>
       </c>
@@ -5913,7 +5918,7 @@
       <c r="L17" s="2"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" ht="40.5" hidden="1">
+    <row r="18" spans="1:13" ht="40.5">
       <c r="A18" s="1">
         <v>23</v>
       </c>
@@ -5940,7 +5945,7 @@
       <c r="L18" s="2"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="1:13" ht="54" hidden="1">
+    <row r="19" spans="1:13" ht="54">
       <c r="A19" s="1">
         <v>24</v>
       </c>
@@ -5967,7 +5972,7 @@
       <c r="L19" s="2"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:13" ht="40.5" hidden="1">
+    <row r="20" spans="1:13" ht="40.5">
       <c r="A20" s="1">
         <v>26</v>
       </c>
@@ -5994,7 +5999,7 @@
       <c r="L20" s="2"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="1:13" ht="40.5" hidden="1">
+    <row r="21" spans="1:13" ht="40.5">
       <c r="A21" s="1">
         <v>28</v>
       </c>
@@ -6023,7 +6028,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:13" ht="40.5" hidden="1">
+    <row r="22" spans="1:13" ht="40.5">
       <c r="A22" s="1">
         <v>29</v>
       </c>
@@ -6050,7 +6055,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:13" ht="27" hidden="1">
+    <row r="23" spans="1:13" ht="27">
       <c r="A23" s="1">
         <v>30</v>
       </c>
@@ -6077,7 +6082,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:13" ht="27" hidden="1">
+    <row r="24" spans="1:13" ht="27">
       <c r="A24" s="1">
         <v>31</v>
       </c>
@@ -6141,7 +6146,7 @@
       </c>
       <c r="M25" s="22"/>
     </row>
-    <row r="26" spans="1:13" ht="40.5" hidden="1">
+    <row r="26" spans="1:13" ht="40.5">
       <c r="A26" s="1">
         <v>33</v>
       </c>
@@ -6286,7 +6291,7 @@
       <c r="L30" s="2"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:13" ht="27" hidden="1">
+    <row r="31" spans="1:13" ht="27">
       <c r="A31" s="1">
         <v>38</v>
       </c>
@@ -6315,7 +6320,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="1:13" ht="27" hidden="1">
+    <row r="32" spans="1:13" ht="27">
       <c r="A32" s="1">
         <v>39</v>
       </c>
@@ -6344,7 +6349,7 @@
       <c r="L32" s="2"/>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" spans="1:13" ht="27" hidden="1">
+    <row r="33" spans="1:13" ht="27">
       <c r="A33" s="13">
         <v>40</v>
       </c>
@@ -6431,7 +6436,7 @@
       <c r="L35" s="8"/>
       <c r="M35" s="14"/>
     </row>
-    <row r="36" spans="1:13" ht="27" hidden="1">
+    <row r="36" spans="1:13" ht="27">
       <c r="A36" s="13">
         <v>43</v>
       </c>
@@ -6489,7 +6494,7 @@
       <c r="L37" s="8"/>
       <c r="M37" s="14"/>
     </row>
-    <row r="38" spans="1:13" ht="27" hidden="1">
+    <row r="38" spans="1:13" ht="27">
       <c r="A38" s="13">
         <v>45</v>
       </c>
@@ -6518,7 +6523,7 @@
       <c r="L38" s="8"/>
       <c r="M38" s="14"/>
     </row>
-    <row r="39" spans="1:13" ht="54" hidden="1">
+    <row r="39" spans="1:13" ht="54">
       <c r="A39" s="13">
         <v>47</v>
       </c>
@@ -6547,7 +6552,7 @@
       <c r="L39" s="8"/>
       <c r="M39" s="14"/>
     </row>
-    <row r="40" spans="1:13" ht="27" hidden="1">
+    <row r="40" spans="1:13" ht="27">
       <c r="A40" s="13">
         <v>48</v>
       </c>
@@ -6576,7 +6581,7 @@
       <c r="L40" s="8"/>
       <c r="M40" s="14"/>
     </row>
-    <row r="41" spans="1:13" ht="27" hidden="1">
+    <row r="41" spans="1:13" ht="27">
       <c r="A41" s="13">
         <v>49</v>
       </c>
@@ -6605,7 +6610,7 @@
       <c r="L41" s="8"/>
       <c r="M41" s="14"/>
     </row>
-    <row r="42" spans="1:13" ht="27" hidden="1">
+    <row r="42" spans="1:13" ht="27">
       <c r="A42" s="13">
         <v>50</v>
       </c>
@@ -6708,7 +6713,9 @@
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
+      <c r="F45" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="G45" s="8" t="s">
         <v>22</v>
       </c>
@@ -6729,7 +6736,9 @@
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
+      <c r="F46" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="G46" s="8" t="s">
         <v>22</v>
       </c>
@@ -6740,14 +6749,22 @@
       <c r="L46" s="8"/>
       <c r="M46" s="14"/>
     </row>
-    <row r="47" spans="1:13">
-      <c r="A47" s="13"/>
-      <c r="B47" s="8"/>
+    <row r="47" spans="1:13" ht="40.5">
+      <c r="A47" s="13">
+        <v>55</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>256</v>
+      </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
+      <c r="F47" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
@@ -7371,13 +7388,9 @@
       <c r="M88" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M46">
+  <autoFilter ref="A1:M47">
     <filterColumn colId="4"/>
-    <filterColumn colId="6">
-      <filters>
-        <filter val="高"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="6"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M199">

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -13,8 +13,8 @@
     <sheet name="已完成任务" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2014年'!$A$1:$M$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$L$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2014年'!$A$1:$M$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$M$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$M$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="263">
   <si>
     <r>
       <t>描述</t>
@@ -403,11 +403,6 @@
   </si>
   <si>
     <t xml:space="preserve">管理界面增加错误告警（节点故障，重启，操作失败等）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">手动降备命令
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1291,6 +1286,37 @@
   <si>
     <t xml:space="preserve">query的selector提供对field选取或排除两种模式
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIWEICHAO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">权值选主
+手动降备命令
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武赟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-581
+SEQUOIADBMAINSTREAM-582  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李建华</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-583 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1649,7 +1675,427 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="116">
+  <dxfs count="176">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2755,24 +3201,25 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
     <col min="2" max="2" width="39.75" customWidth="1"/>
     <col min="3" max="3" width="20.125" customWidth="1"/>
     <col min="4" max="4" width="24.75" customWidth="1"/>
-    <col min="5" max="5" width="9.375" customWidth="1"/>
-    <col min="6" max="6" width="9.75" customWidth="1"/>
-    <col min="7" max="7" width="9.875" customWidth="1"/>
-    <col min="8" max="8" width="14.125" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="15.875" customWidth="1"/>
-    <col min="12" max="12" width="17.375" customWidth="1"/>
+    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col min="6" max="6" width="9.375" customWidth="1"/>
+    <col min="7" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="9" width="14.125" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="15.875" customWidth="1"/>
+    <col min="13" max="13" width="17.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="29.45" customHeight="1">
+    <row r="1" spans="1:13" ht="29.45" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
@@ -2780,37 +3227,38 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E1" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="54">
+    <row r="2" spans="1:13" ht="54">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2819,48 +3267,50 @@
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="8"/>
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" ht="67.5">
+      <c r="L2" s="2"/>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" spans="1:13" ht="67.5">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>7</v>
       </c>
-      <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12" ht="67.5">
+      <c r="L3" s="2"/>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" spans="1:13" ht="67.5">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2869,24 +3319,25 @@
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="8"/>
+      <c r="F4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>7</v>
       </c>
-      <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
-      <c r="L4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" ht="40.5">
+      <c r="L4" s="2"/>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="1:13" ht="40.5">
       <c r="A5" s="27">
         <v>8</v>
       </c>
@@ -2895,30 +3346,31 @@
       </c>
       <c r="C5" s="28"/>
       <c r="D5" s="28"/>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="28"/>
+      <c r="F5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="G5" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="H5" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="29">
+      <c r="I5" s="29">
         <v>1</v>
       </c>
-      <c r="I5" s="29" t="s">
-        <v>83</v>
-      </c>
       <c r="J5" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="K5" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="K5" s="30">
+      <c r="L5" s="30">
         <v>41679</v>
       </c>
-      <c r="L5" s="31"/>
-    </row>
-    <row r="6" spans="1:12" ht="40.5">
+      <c r="M5" s="31"/>
+    </row>
+    <row r="6" spans="1:13" ht="40.5">
       <c r="A6" s="1">
         <v>10</v>
       </c>
@@ -2927,24 +3379,25 @@
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="8"/>
+      <c r="F6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>3</v>
       </c>
-      <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
-      <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" ht="40.5">
+      <c r="L6" s="2"/>
+      <c r="M6" s="3"/>
+    </row>
+    <row r="7" spans="1:13" ht="40.5">
       <c r="A7" s="1">
         <v>11</v>
       </c>
@@ -2953,22 +3406,23 @@
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="8"/>
+      <c r="F7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-      <c r="L7" s="3"/>
-    </row>
-    <row r="8" spans="1:12" ht="67.5">
+      <c r="L7" s="2"/>
+      <c r="M7" s="3"/>
+    </row>
+    <row r="8" spans="1:13" ht="67.5">
       <c r="A8" s="1">
         <v>12</v>
       </c>
@@ -2977,22 +3431,23 @@
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="8"/>
+      <c r="F8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" ht="27">
+      <c r="L8" s="2"/>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" ht="27">
       <c r="A9" s="1">
         <v>13</v>
       </c>
@@ -3001,24 +3456,25 @@
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="8"/>
+      <c r="F9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I9" s="2">
         <v>15</v>
       </c>
-      <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" ht="27">
+      <c r="L9" s="2"/>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" ht="27">
       <c r="A10" s="1">
         <v>14</v>
       </c>
@@ -3027,24 +3483,25 @@
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="8"/>
+      <c r="F10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <v>4</v>
       </c>
-      <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" ht="27">
+      <c r="L10" s="2"/>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" ht="27">
       <c r="A11" s="1">
         <v>15</v>
       </c>
@@ -3053,24 +3510,25 @@
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="8"/>
+      <c r="F11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="2">
+      <c r="I11" s="2">
         <v>8</v>
       </c>
-      <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" ht="27">
+      <c r="L11" s="2"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" ht="27">
       <c r="A12" s="1">
         <v>16</v>
       </c>
@@ -3079,22 +3537,23 @@
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="8"/>
+      <c r="F12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" ht="27">
+      <c r="L12" s="2"/>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" ht="27">
       <c r="A13" s="1">
         <v>17</v>
       </c>
@@ -3103,24 +3562,25 @@
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="8"/>
+      <c r="F13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="2">
+      <c r="I13" s="2">
         <v>5</v>
       </c>
-      <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" ht="27">
+      <c r="L13" s="2"/>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" ht="27">
       <c r="A14" s="1">
         <v>18</v>
       </c>
@@ -3129,28 +3589,29 @@
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="8"/>
+      <c r="F14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H14" s="2">
+      <c r="I14" s="2">
         <v>13</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="J14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" ht="27">
+      <c r="L14" s="2"/>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" ht="27">
       <c r="A15" s="1">
         <v>19</v>
       </c>
@@ -3159,24 +3620,25 @@
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="8"/>
+      <c r="F15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="2">
+      <c r="I15" s="2">
         <v>4</v>
       </c>
-      <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" ht="27">
+      <c r="L15" s="2"/>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" ht="27">
       <c r="A16" s="1">
         <v>20</v>
       </c>
@@ -3185,24 +3647,25 @@
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="8"/>
+      <c r="F16" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H16" s="2">
+      <c r="I16" s="2">
         <v>4</v>
       </c>
-      <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
-      <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="1:12" ht="27">
+      <c r="L16" s="2"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="1:13" ht="27">
       <c r="A17" s="1">
         <v>24</v>
       </c>
@@ -3211,24 +3674,25 @@
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="8"/>
+      <c r="F17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H17" s="2">
+      <c r="I17" s="2">
         <v>15</v>
       </c>
-      <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="1:12" ht="27">
+      <c r="L17" s="2"/>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="1:13" ht="27">
       <c r="A18" s="1">
         <v>25</v>
       </c>
@@ -3237,24 +3701,25 @@
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="8"/>
+      <c r="F18" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <v>10</v>
       </c>
-      <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="1:12" ht="27">
+      <c r="L18" s="2"/>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="1:13" ht="27">
       <c r="A19" s="1">
         <v>26</v>
       </c>
@@ -3263,24 +3728,25 @@
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="8"/>
+      <c r="F19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="2">
+      <c r="I19" s="2">
         <v>4</v>
       </c>
-      <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
-      <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="1:12" ht="27">
+      <c r="L19" s="2"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="1:13" ht="27">
       <c r="A20" s="1">
         <v>27</v>
       </c>
@@ -3289,380 +3755,342 @@
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="8"/>
+      <c r="F20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H20" s="2">
+      <c r="I20" s="2">
         <v>4</v>
       </c>
-      <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="1:12" ht="27">
+      <c r="L20" s="2"/>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="1:13" ht="27">
       <c r="A21" s="1">
         <v>28</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="8"/>
+      <c r="F21" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="H21" s="2">
+      <c r="I21" s="2">
         <v>8</v>
       </c>
-      <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="1:12" ht="27">
-      <c r="A22" s="27">
-        <v>29</v>
-      </c>
-      <c r="B22" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="29" t="s">
+      <c r="L21" s="2"/>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="1:13" ht="40.5">
+      <c r="A22" s="1">
+        <v>31</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F22" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="H22" s="29">
-        <v>20</v>
-      </c>
-      <c r="I22" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="J22" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="K22" s="29"/>
-      <c r="L22" s="31"/>
-    </row>
-    <row r="23" spans="1:12" ht="27">
-      <c r="A23" s="27">
-        <v>30</v>
-      </c>
-      <c r="B23" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="E23" s="29" t="s">
+      <c r="G22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I22" s="2">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="1:13" ht="27">
+      <c r="A23" s="1">
+        <v>32</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F23" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="H23" s="29">
-        <v>20</v>
-      </c>
-      <c r="I23" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="J23" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="K23" s="29"/>
-      <c r="L23" s="31"/>
-    </row>
-    <row r="24" spans="1:12" ht="40.5">
+      <c r="G23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" s="2">
+        <v>6</v>
+      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="1:13" ht="40.5">
       <c r="A24" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="8"/>
+      <c r="F24" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="G24" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H24" s="2">
+        <v>12</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="2">
         <v>8</v>
       </c>
-      <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="1:12" ht="27">
+      <c r="L24" s="2"/>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="1:13" ht="54">
       <c r="A25" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="8"/>
+      <c r="F25" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="G25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H25" s="2">
-        <v>6</v>
-      </c>
-      <c r="I25" s="2"/>
+      <c r="I25" s="2">
+        <v>8</v>
+      </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="1:12" ht="40.5">
+      <c r="L25" s="2"/>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="1:13" ht="40.5">
       <c r="A26" s="1">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>66</v>
+        <v>257</v>
       </c>
       <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="2" t="s">
-        <v>52</v>
-      </c>
+      <c r="D26" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="E26" s="8"/>
       <c r="F26" s="2" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H26" s="2">
-        <v>8</v>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="1:12" ht="54">
+        <v>22</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I26" s="2">
+        <v>2</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L26" s="2"/>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="1:13" ht="40.5">
       <c r="A27" s="1">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
-      <c r="E27" s="2" t="s">
-        <v>52</v>
-      </c>
+      <c r="E27" s="8"/>
       <c r="F27" s="2" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H27" s="2">
-        <v>8</v>
-      </c>
-      <c r="I27" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I27" s="2">
+        <v>15</v>
+      </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="1:12" ht="27">
+      <c r="L27" s="2"/>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="1:13" ht="40.5">
       <c r="A28" s="1">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="2" t="s">
-        <v>68</v>
-      </c>
+      <c r="D28" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E28" s="8"/>
       <c r="F28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H28" s="2">
-        <v>2</v>
-      </c>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="1:12" ht="54">
-      <c r="A29" s="1">
-        <v>41</v>
+      <c r="H28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I28" s="2">
+        <v>3</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L28" s="21">
+        <v>41679</v>
+      </c>
+      <c r="M28" s="22">
+        <v>41679</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="27">
+      <c r="A29" s="13">
+        <v>53</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
-      <c r="E29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="E29" s="8"/>
+      <c r="F29" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" s="2">
-        <v>2</v>
-      </c>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="1:12" ht="40.5">
-      <c r="A30" s="1">
-        <v>44</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>74</v>
-      </c>
+      <c r="H29" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="14"/>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="13"/>
+      <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
-      <c r="E30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H30" s="2">
-        <v>15</v>
-      </c>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="1:12" ht="27">
-      <c r="A31" s="1">
-        <v>45</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>75</v>
-      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="14"/>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="13"/>
+      <c r="B31" s="8"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
-      <c r="E31" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H31" s="2">
-        <v>15</v>
-      </c>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="1:12" ht="40.5">
-      <c r="A32" s="1">
-        <v>46</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>115</v>
-      </c>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="14"/>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="13"/>
+      <c r="B32" s="8"/>
       <c r="C32" s="8"/>
-      <c r="D32" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H32" s="2">
-        <v>3</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K32" s="21">
-        <v>41679</v>
-      </c>
-      <c r="L32" s="22">
-        <v>41679</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="27">
-      <c r="A33" s="13">
-        <v>53</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>112</v>
-      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="14"/>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="13"/>
+      <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>20</v>
-      </c>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
-      <c r="L33" s="14"/>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="L33" s="8"/>
+      <c r="M33" s="14"/>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="13"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -3674,9 +4102,10 @@
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
-      <c r="L34" s="14"/>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="L34" s="8"/>
+      <c r="M34" s="14"/>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="13"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -3688,9 +4117,10 @@
       <c r="I35" s="8"/>
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
-      <c r="L35" s="14"/>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="L35" s="8"/>
+      <c r="M35" s="14"/>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="13"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -3702,9 +4132,10 @@
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
-      <c r="L36" s="14"/>
-    </row>
-    <row r="37" spans="1:12">
+      <c r="L36" s="8"/>
+      <c r="M36" s="14"/>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="13"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -3716,9 +4147,10 @@
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
-      <c r="L37" s="14"/>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="L37" s="8"/>
+      <c r="M37" s="14"/>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="13"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -3730,9 +4162,10 @@
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
-      <c r="L38" s="14"/>
-    </row>
-    <row r="39" spans="1:12">
+      <c r="L38" s="8"/>
+      <c r="M38" s="14"/>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="13"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -3744,9 +4177,10 @@
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
-      <c r="L39" s="14"/>
-    </row>
-    <row r="40" spans="1:12">
+      <c r="L39" s="8"/>
+      <c r="M39" s="14"/>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="13"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -3758,9 +4192,10 @@
       <c r="I40" s="8"/>
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
-      <c r="L40" s="14"/>
-    </row>
-    <row r="41" spans="1:12">
+      <c r="L40" s="8"/>
+      <c r="M40" s="14"/>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="13"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -3772,9 +4207,10 @@
       <c r="I41" s="8"/>
       <c r="J41" s="8"/>
       <c r="K41" s="8"/>
-      <c r="L41" s="14"/>
-    </row>
-    <row r="42" spans="1:12">
+      <c r="L41" s="8"/>
+      <c r="M41" s="14"/>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="13"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -3786,9 +4222,10 @@
       <c r="I42" s="8"/>
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
-      <c r="L42" s="14"/>
-    </row>
-    <row r="43" spans="1:12">
+      <c r="L42" s="8"/>
+      <c r="M42" s="14"/>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="13"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -3800,9 +4237,10 @@
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
-      <c r="L43" s="14"/>
-    </row>
-    <row r="44" spans="1:12">
+      <c r="L43" s="8"/>
+      <c r="M43" s="14"/>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="13"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -3814,9 +4252,10 @@
       <c r="I44" s="8"/>
       <c r="J44" s="8"/>
       <c r="K44" s="8"/>
-      <c r="L44" s="14"/>
-    </row>
-    <row r="45" spans="1:12">
+      <c r="L44" s="8"/>
+      <c r="M44" s="14"/>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="13"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -3828,9 +4267,10 @@
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
       <c r="K45" s="8"/>
-      <c r="L45" s="14"/>
-    </row>
-    <row r="46" spans="1:12">
+      <c r="L45" s="8"/>
+      <c r="M45" s="14"/>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="13"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -3842,9 +4282,10 @@
       <c r="I46" s="8"/>
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
-      <c r="L46" s="14"/>
-    </row>
-    <row r="47" spans="1:12">
+      <c r="L46" s="8"/>
+      <c r="M46" s="14"/>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="13"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -3856,9 +4297,10 @@
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
       <c r="K47" s="8"/>
-      <c r="L47" s="14"/>
-    </row>
-    <row r="48" spans="1:12">
+      <c r="L47" s="8"/>
+      <c r="M47" s="14"/>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="13"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -3870,9 +4312,10 @@
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
       <c r="K48" s="8"/>
-      <c r="L48" s="14"/>
-    </row>
-    <row r="49" spans="1:12">
+      <c r="L48" s="8"/>
+      <c r="M48" s="14"/>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="13"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -3884,9 +4327,10 @@
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
       <c r="K49" s="8"/>
-      <c r="L49" s="14"/>
-    </row>
-    <row r="50" spans="1:12">
+      <c r="L49" s="8"/>
+      <c r="M49" s="14"/>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="13"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -3898,9 +4342,10 @@
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
       <c r="K50" s="8"/>
-      <c r="L50" s="14"/>
-    </row>
-    <row r="51" spans="1:12">
+      <c r="L50" s="8"/>
+      <c r="M50" s="14"/>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="13"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -3912,9 +4357,10 @@
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
       <c r="K51" s="8"/>
-      <c r="L51" s="14"/>
-    </row>
-    <row r="52" spans="1:12">
+      <c r="L51" s="8"/>
+      <c r="M51" s="14"/>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="13"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -3926,9 +4372,10 @@
       <c r="I52" s="8"/>
       <c r="J52" s="8"/>
       <c r="K52" s="8"/>
-      <c r="L52" s="14"/>
-    </row>
-    <row r="53" spans="1:12">
+      <c r="L52" s="8"/>
+      <c r="M52" s="14"/>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="13"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -3940,9 +4387,10 @@
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
       <c r="K53" s="8"/>
-      <c r="L53" s="14"/>
-    </row>
-    <row r="54" spans="1:12">
+      <c r="L53" s="8"/>
+      <c r="M53" s="14"/>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="13"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -3954,9 +4402,10 @@
       <c r="I54" s="8"/>
       <c r="J54" s="8"/>
       <c r="K54" s="8"/>
-      <c r="L54" s="14"/>
-    </row>
-    <row r="55" spans="1:12">
+      <c r="L54" s="8"/>
+      <c r="M54" s="14"/>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="13"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -3968,9 +4417,10 @@
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
       <c r="K55" s="8"/>
-      <c r="L55" s="14"/>
-    </row>
-    <row r="56" spans="1:12">
+      <c r="L55" s="8"/>
+      <c r="M55" s="14"/>
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" s="13"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -3982,9 +4432,10 @@
       <c r="I56" s="8"/>
       <c r="J56" s="8"/>
       <c r="K56" s="8"/>
-      <c r="L56" s="14"/>
-    </row>
-    <row r="57" spans="1:12">
+      <c r="L56" s="8"/>
+      <c r="M56" s="14"/>
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" s="13"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -3996,9 +4447,10 @@
       <c r="I57" s="8"/>
       <c r="J57" s="8"/>
       <c r="K57" s="8"/>
-      <c r="L57" s="14"/>
-    </row>
-    <row r="58" spans="1:12">
+      <c r="L57" s="8"/>
+      <c r="M57" s="14"/>
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" s="13"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -4010,9 +4462,10 @@
       <c r="I58" s="8"/>
       <c r="J58" s="8"/>
       <c r="K58" s="8"/>
-      <c r="L58" s="14"/>
-    </row>
-    <row r="59" spans="1:12">
+      <c r="L58" s="8"/>
+      <c r="M58" s="14"/>
+    </row>
+    <row r="59" spans="1:13">
       <c r="A59" s="13"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
@@ -4024,9 +4477,10 @@
       <c r="I59" s="8"/>
       <c r="J59" s="8"/>
       <c r="K59" s="8"/>
-      <c r="L59" s="14"/>
-    </row>
-    <row r="60" spans="1:12">
+      <c r="L59" s="8"/>
+      <c r="M59" s="14"/>
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" s="13"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
@@ -4038,9 +4492,10 @@
       <c r="I60" s="8"/>
       <c r="J60" s="8"/>
       <c r="K60" s="8"/>
-      <c r="L60" s="14"/>
-    </row>
-    <row r="61" spans="1:12">
+      <c r="L60" s="8"/>
+      <c r="M60" s="14"/>
+    </row>
+    <row r="61" spans="1:13">
       <c r="A61" s="13"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
@@ -4052,9 +4507,10 @@
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
       <c r="K61" s="8"/>
-      <c r="L61" s="14"/>
-    </row>
-    <row r="62" spans="1:12">
+      <c r="L61" s="8"/>
+      <c r="M61" s="14"/>
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" s="13"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -4066,9 +4522,10 @@
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
       <c r="K62" s="8"/>
-      <c r="L62" s="14"/>
-    </row>
-    <row r="63" spans="1:12">
+      <c r="L62" s="8"/>
+      <c r="M62" s="14"/>
+    </row>
+    <row r="63" spans="1:13">
       <c r="A63" s="13"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -4080,9 +4537,10 @@
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
       <c r="K63" s="8"/>
-      <c r="L63" s="14"/>
-    </row>
-    <row r="64" spans="1:12">
+      <c r="L63" s="8"/>
+      <c r="M63" s="14"/>
+    </row>
+    <row r="64" spans="1:13">
       <c r="A64" s="13"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -4094,9 +4552,10 @@
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
       <c r="K64" s="8"/>
-      <c r="L64" s="14"/>
-    </row>
-    <row r="65" spans="1:12">
+      <c r="L64" s="8"/>
+      <c r="M64" s="14"/>
+    </row>
+    <row r="65" spans="1:13">
       <c r="A65" s="13"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -4108,9 +4567,10 @@
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
       <c r="K65" s="8"/>
-      <c r="L65" s="14"/>
-    </row>
-    <row r="66" spans="1:12">
+      <c r="L65" s="8"/>
+      <c r="M65" s="14"/>
+    </row>
+    <row r="66" spans="1:13">
       <c r="A66" s="13"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -4122,107 +4582,54 @@
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
       <c r="K66" s="8"/>
-      <c r="L66" s="14"/>
-    </row>
-    <row r="67" spans="1:12">
-      <c r="A67" s="13"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="8"/>
-      <c r="J67" s="8"/>
-      <c r="K67" s="8"/>
-      <c r="L67" s="14"/>
-    </row>
-    <row r="68" spans="1:12">
-      <c r="A68" s="13"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="14"/>
-    </row>
-    <row r="69" spans="1:12">
-      <c r="A69" s="13"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="14"/>
-    </row>
-    <row r="70" spans="1:12">
-      <c r="A70" s="13"/>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="14"/>
-    </row>
-    <row r="71" spans="1:12" ht="14.25" thickBot="1">
-      <c r="A71" s="15"/>
-      <c r="B71" s="16"/>
-      <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="16"/>
-      <c r="H71" s="16"/>
-      <c r="I71" s="16"/>
-      <c r="J71" s="16"/>
-      <c r="K71" s="16"/>
-      <c r="L71" s="17"/>
+      <c r="L66" s="8"/>
+      <c r="M66" s="14"/>
+    </row>
+    <row r="67" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A67" s="15"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="16"/>
+      <c r="H67" s="16"/>
+      <c r="I67" s="16"/>
+      <c r="J67" s="16"/>
+      <c r="K67" s="16"/>
+      <c r="L67" s="16"/>
+      <c r="M67" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L33">
+  <autoFilter ref="A1:M29">
     <filterColumn colId="2"/>
     <filterColumn colId="3"/>
-    <filterColumn colId="5"/>
+    <filterColumn colId="4"/>
+    <filterColumn colId="6"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:L182">
-    <cfRule type="expression" dxfId="115" priority="1" stopIfTrue="1">
-      <formula>$J2="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="114" priority="2" stopIfTrue="1">
-      <formula>$J2="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="113" priority="3" stopIfTrue="1">
-      <formula>$J2="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="112" priority="4" stopIfTrue="1">
-      <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
+  <conditionalFormatting sqref="A2:M178">
+    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
+      <formula>$K2="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
+      <formula>$K2="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
+      <formula>$K2="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
+      <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E71">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F67">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F71">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G67">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J71">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K67">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4261,10 +4668,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -4296,7 +4703,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
@@ -4316,7 +4723,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -4336,7 +4743,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4356,7 +4763,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C5" s="28"/>
       <c r="D5" s="28"/>
@@ -4376,7 +4783,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -4396,7 +4803,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -4416,7 +4823,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -4436,7 +4843,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -4456,12 +4863,12 @@
         <v>19</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="28"/>
       <c r="E10" s="29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F10" s="29"/>
       <c r="G10" s="29"/>
@@ -4476,12 +4883,12 @@
         <v>27</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -4496,12 +4903,12 @@
         <v>29</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -5382,16 +5789,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L185">
-    <cfRule type="expression" dxfId="111" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="175" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="174" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="173" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="172" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5416,7 +5823,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -5441,13 +5848,13 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>1</v>
@@ -5479,15 +5886,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>22</v>
@@ -5508,15 +5915,15 @@
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>16</v>
@@ -5535,21 +5942,21 @@
         <v>4</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G4" s="29" t="s">
         <v>22</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I4" s="29">
         <v>8</v>
@@ -5564,12 +5971,12 @@
         <v>5</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>14</v>
@@ -5593,12 +6000,12 @@
         <v>7</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>52</v>
@@ -5607,7 +6014,7 @@
         <v>12</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I6" s="2">
         <v>7</v>
@@ -5622,15 +6029,15 @@
         <v>8</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>12</v>
@@ -5649,21 +6056,21 @@
         <v>10</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -5676,21 +6083,21 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -5703,21 +6110,21 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -5730,12 +6137,12 @@
         <v>16</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="28"/>
       <c r="E11" s="28" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F11" s="29" t="s">
         <v>42</v>
@@ -5759,21 +6166,21 @@
         <v>17</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C12" s="28"/>
       <c r="D12" s="28"/>
       <c r="E12" s="28" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G12" s="29" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -5786,12 +6193,12 @@
         <v>18</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>33</v>
@@ -5800,7 +6207,7 @@
         <v>16</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -5813,12 +6220,12 @@
         <v>19</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>33</v>
@@ -5827,7 +6234,7 @@
         <v>16</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -5840,21 +6247,21 @@
         <v>20</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -5867,12 +6274,12 @@
         <v>21</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>52</v>
@@ -5881,7 +6288,7 @@
         <v>22</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I16" s="2">
         <v>20</v>
@@ -5896,15 +6303,15 @@
         <v>22</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>16</v>
@@ -5923,15 +6330,15 @@
         <v>23</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>16</v>
@@ -5950,21 +6357,21 @@
         <v>24</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -5977,21 +6384,21 @@
         <v>26</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -6004,12 +6411,12 @@
         <v>28</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>52</v>
@@ -6033,12 +6440,12 @@
         <v>29</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>33</v>
@@ -6047,7 +6454,7 @@
         <v>16</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
@@ -6060,12 +6467,12 @@
         <v>30</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>33</v>
@@ -6074,7 +6481,7 @@
         <v>16</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -6087,21 +6494,21 @@
         <v>31</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
@@ -6111,151 +6518,143 @@
     </row>
     <row r="25" spans="1:13" ht="27">
       <c r="A25" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C25" s="8"/>
-      <c r="D25" s="8" t="s">
-        <v>240</v>
-      </c>
+      <c r="D25" s="8"/>
       <c r="E25" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>79</v>
+        <v>210</v>
       </c>
       <c r="I25" s="2">
-        <v>22</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="L25" s="21">
-        <v>41949</v>
-      </c>
-      <c r="M25" s="22"/>
+        <v>2</v>
+      </c>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="3"/>
     </row>
     <row r="26" spans="1:13" ht="40.5">
       <c r="A26" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I26" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:13" ht="27">
+    <row r="27" spans="1:13" ht="54">
       <c r="A27" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I27" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:13" ht="40.5">
+    <row r="28" spans="1:13" ht="27">
       <c r="A28" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="I28" s="2">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:13" ht="54">
+    <row r="29" spans="1:13" ht="27">
       <c r="A29" s="1">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I29" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -6263,144 +6662,148 @@
       <c r="M29" s="3"/>
     </row>
     <row r="30" spans="1:13" ht="27">
-      <c r="A30" s="1">
-        <v>37</v>
+      <c r="A30" s="13">
+        <v>40</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G30" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="I30" s="8">
+        <v>10</v>
+      </c>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="14"/>
+    </row>
+    <row r="31" spans="1:13" ht="27">
+      <c r="A31" s="13">
+        <v>41</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="I30" s="2">
-        <v>15</v>
-      </c>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="1:13" ht="27">
-      <c r="A31" s="1">
-        <v>38</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="F31" s="2" t="s">
+      <c r="H31" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="I31" s="8">
+        <v>5</v>
+      </c>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L31" s="8"/>
+      <c r="M31" s="14"/>
+    </row>
+    <row r="32" spans="1:13" ht="27">
+      <c r="A32" s="13">
         <v>42</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="I31" s="2">
-        <v>33</v>
-      </c>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="1:13" ht="27">
-      <c r="A32" s="1">
-        <v>39</v>
-      </c>
       <c r="B32" s="8" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="I32" s="2">
-        <v>10</v>
-      </c>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="3"/>
+        <v>205</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="I32" s="8">
+        <v>8</v>
+      </c>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="14"/>
     </row>
     <row r="33" spans="1:13" ht="27">
       <c r="A33" s="13">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>12</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="I33" s="8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
       <c r="M33" s="14"/>
     </row>
-    <row r="34" spans="1:13" ht="27">
+    <row r="34" spans="1:13" ht="54">
       <c r="A34" s="13">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G34" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="I34" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
@@ -6409,85 +6812,85 @@
     </row>
     <row r="35" spans="1:13" ht="27">
       <c r="A35" s="13">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
       <c r="E35" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="I35" s="8">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
       <c r="M35" s="14"/>
     </row>
-    <row r="36" spans="1:13" ht="27">
+    <row r="36" spans="1:13" ht="54">
       <c r="A36" s="13">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>12</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I36" s="8">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
       <c r="M36" s="14"/>
     </row>
-    <row r="37" spans="1:13" ht="54">
+    <row r="37" spans="1:13" ht="27">
       <c r="A37" s="13">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="I37" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
@@ -6496,252 +6899,202 @@
     </row>
     <row r="38" spans="1:13" ht="27">
       <c r="A38" s="13">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
       <c r="E38" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>12</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="I38" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
       <c r="M38" s="14"/>
     </row>
-    <row r="39" spans="1:13" ht="54">
+    <row r="39" spans="1:13" ht="27">
       <c r="A39" s="13">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>12</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I39" s="8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
       <c r="M39" s="14"/>
     </row>
-    <row r="40" spans="1:13" ht="27">
+    <row r="40" spans="1:13" ht="40.5">
       <c r="A40" s="13">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="I40" s="8">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
       <c r="L40" s="8"/>
       <c r="M40" s="14"/>
     </row>
-    <row r="41" spans="1:13" ht="27">
+    <row r="41" spans="1:13" ht="54">
       <c r="A41" s="13">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
+      <c r="D41" s="8" t="s">
+        <v>253</v>
+      </c>
       <c r="E41" s="8" t="s">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="I41" s="8">
-        <v>4</v>
-      </c>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
+        <v>5</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>61</v>
+      </c>
       <c r="L41" s="8"/>
       <c r="M41" s="14"/>
     </row>
-    <row r="42" spans="1:13" ht="27">
+    <row r="42" spans="1:13" ht="40.5">
       <c r="A42" s="13">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
-      <c r="E42" s="8" t="s">
-        <v>206</v>
-      </c>
+      <c r="E42" s="8"/>
       <c r="F42" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="I42" s="8">
-        <v>3</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
       <c r="L42" s="8"/>
       <c r="M42" s="14"/>
     </row>
-    <row r="43" spans="1:13" ht="40.5">
-      <c r="A43" s="13">
-        <v>51</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>236</v>
-      </c>
+    <row r="43" spans="1:13">
+      <c r="A43" s="13"/>
+      <c r="B43" s="8"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
-      <c r="E43" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="I43" s="8">
-        <v>15</v>
-      </c>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
       <c r="L43" s="8"/>
       <c r="M43" s="14"/>
     </row>
-    <row r="44" spans="1:13" ht="54">
-      <c r="A44" s="13">
-        <v>52</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>249</v>
-      </c>
+    <row r="44" spans="1:13">
+      <c r="A44" s="13"/>
+      <c r="B44" s="8"/>
       <c r="C44" s="8"/>
-      <c r="D44" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="I44" s="8">
-        <v>5</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>61</v>
-      </c>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
       <c r="L44" s="8"/>
       <c r="M44" s="14"/>
     </row>
-    <row r="45" spans="1:13" ht="27">
-      <c r="A45" s="13">
-        <v>53</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>252</v>
-      </c>
+    <row r="45" spans="1:13">
+      <c r="A45" s="13"/>
+      <c r="B45" s="8"/>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
-      <c r="F45" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>22</v>
-      </c>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
       <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
+      <c r="L45" s="32"/>
       <c r="M45" s="14"/>
     </row>
-    <row r="46" spans="1:13" ht="40.5">
-      <c r="A46" s="13">
-        <v>54</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>253</v>
-      </c>
+    <row r="46" spans="1:13">
+      <c r="A46" s="13"/>
+      <c r="B46" s="8"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
-      <c r="F46" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>22</v>
-      </c>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
       <c r="J46" s="8"/>
@@ -6749,22 +7102,14 @@
       <c r="L46" s="8"/>
       <c r="M46" s="14"/>
     </row>
-    <row r="47" spans="1:13" ht="40.5">
-      <c r="A47" s="13">
-        <v>55</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>256</v>
-      </c>
+    <row r="47" spans="1:13">
+      <c r="A47" s="13"/>
+      <c r="B47" s="8"/>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
-      <c r="F47" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>22</v>
-      </c>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
@@ -6814,7 +7159,7 @@
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
       <c r="K50" s="8"/>
-      <c r="L50" s="32"/>
+      <c r="L50" s="8"/>
       <c r="M50" s="14"/>
     </row>
     <row r="51" spans="1:13">
@@ -7297,138 +7642,63 @@
       <c r="L82" s="8"/>
       <c r="M82" s="14"/>
     </row>
-    <row r="83" spans="1:13">
-      <c r="A83" s="13"/>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="8"/>
-      <c r="I83" s="8"/>
-      <c r="J83" s="8"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="8"/>
-      <c r="M83" s="14"/>
-    </row>
-    <row r="84" spans="1:13">
-      <c r="A84" s="13"/>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="8"/>
-      <c r="I84" s="8"/>
-      <c r="J84" s="8"/>
-      <c r="K84" s="8"/>
-      <c r="L84" s="8"/>
-      <c r="M84" s="14"/>
-    </row>
-    <row r="85" spans="1:13">
-      <c r="A85" s="13"/>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="8"/>
-      <c r="K85" s="8"/>
-      <c r="L85" s="8"/>
-      <c r="M85" s="14"/>
-    </row>
-    <row r="86" spans="1:13">
-      <c r="A86" s="13"/>
-      <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
-      <c r="G86" s="8"/>
-      <c r="H86" s="8"/>
-      <c r="I86" s="8"/>
-      <c r="J86" s="8"/>
-      <c r="K86" s="8"/>
-      <c r="L86" s="8"/>
-      <c r="M86" s="14"/>
-    </row>
-    <row r="87" spans="1:13">
-      <c r="A87" s="13"/>
-      <c r="B87" s="8"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
-      <c r="G87" s="8"/>
-      <c r="H87" s="8"/>
-      <c r="I87" s="8"/>
-      <c r="J87" s="8"/>
-      <c r="K87" s="8"/>
-      <c r="L87" s="8"/>
-      <c r="M87" s="14"/>
-    </row>
-    <row r="88" spans="1:13" ht="14.25" thickBot="1">
-      <c r="A88" s="15"/>
-      <c r="B88" s="16"/>
-      <c r="C88" s="16"/>
-      <c r="D88" s="16"/>
-      <c r="E88" s="16"/>
-      <c r="F88" s="16"/>
-      <c r="G88" s="16"/>
-      <c r="H88" s="16"/>
-      <c r="I88" s="16"/>
-      <c r="J88" s="16"/>
-      <c r="K88" s="16"/>
-      <c r="L88" s="16"/>
-      <c r="M88" s="17"/>
+    <row r="83" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A83" s="15"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="16"/>
+      <c r="H83" s="16"/>
+      <c r="I83" s="16"/>
+      <c r="J83" s="16"/>
+      <c r="K83" s="16"/>
+      <c r="L83" s="16"/>
+      <c r="M83" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M47">
+  <autoFilter ref="A1:M42">
     <filterColumn colId="4"/>
     <filterColumn colId="6"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:M199">
-    <cfRule type="expression" dxfId="107" priority="5" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:M194">
+    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:M8">
-    <cfRule type="expression" dxfId="103" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>$K8="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
       <formula>$K8="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>$K8="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
       <formula>OR($K8="CLOSED",$K8="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F88">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F83">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G88">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G83">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K88">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K83">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7465,10 +7735,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5" t="s">
@@ -7501,15 +7771,15 @@
         <v>55</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E2" s="12"/>
       <c r="F2" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>22</v>
@@ -7521,10 +7791,10 @@
         <v>1</v>
       </c>
       <c r="J2" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="K2" s="12" t="s">
         <v>83</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>84</v>
       </c>
       <c r="L2" s="24">
         <v>41680</v>
@@ -7538,15 +7808,15 @@
         <v>49</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>22</v>
@@ -7558,10 +7828,10 @@
         <v>1</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L3" s="11">
         <v>41664</v>
@@ -7575,15 +7845,15 @@
         <v>50</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>22</v>
@@ -7595,10 +7865,10 @@
         <v>1</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L4" s="11">
         <v>41665</v>
@@ -7612,36 +7882,36 @@
         <v>47</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E5" s="26"/>
       <c r="F5" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I5" s="10">
         <v>0</v>
       </c>
       <c r="J5" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="K5" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="K5" s="10" t="s">
-        <v>84</v>
-      </c>
       <c r="L5" s="19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M5" s="20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="40.5">
@@ -7649,15 +7919,15 @@
         <v>42</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>12</v>
@@ -7669,10 +7939,10 @@
         <v>4</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L6" s="11">
         <v>41662</v>
@@ -7690,7 +7960,7 @@
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="10" t="s">
@@ -7706,10 +7976,10 @@
         <v>4</v>
       </c>
       <c r="J7" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7" s="10" t="s">
         <v>83</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>84</v>
       </c>
       <c r="L7" s="11">
         <v>41679</v>
@@ -7727,7 +7997,7 @@
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="10" t="s">
@@ -7743,10 +8013,10 @@
         <v>4</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L8" s="11">
         <v>41680</v>
@@ -7760,30 +8030,30 @@
         <v>51</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I9" s="8">
         <v>1</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L9" s="8"/>
       <c r="M9" s="14"/>
@@ -7793,7 +8063,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -7805,16 +8075,16 @@
         <v>22</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I10" s="8">
         <v>3</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L10" s="8"/>
       <c r="M10" s="14"/>
@@ -7828,7 +8098,7 @@
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="2" t="s">
@@ -7844,10 +8114,10 @@
         <v>4</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="3"/>
@@ -7857,13 +8127,13 @@
         <v>48</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>12</v>
@@ -7875,10 +8145,10 @@
         <v>14</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="3"/>
@@ -7888,15 +8158,15 @@
         <v>57</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>12</v>
@@ -7906,10 +8176,10 @@
         <v>3</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L13" s="32">
         <v>41688</v>
@@ -7921,11 +8191,11 @@
         <v>1</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="2" t="s">
@@ -7937,10 +8207,10 @@
         <v>5</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L14" s="21">
         <v>41754</v>
@@ -7954,30 +8224,30 @@
         <v>10</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E15" s="33"/>
       <c r="F15" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I15" s="2">
         <v>7</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="3"/>
@@ -7987,30 +8257,30 @@
         <v>30</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I16" s="2">
         <v>4</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="3"/>
@@ -8020,30 +8290,30 @@
         <v>31</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I17" s="2">
         <v>3</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="3"/>
@@ -8053,30 +8323,30 @@
         <v>32</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I18" s="2">
         <v>1</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="3"/>
@@ -8086,30 +8356,30 @@
         <v>28</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I19" s="2">
         <v>3</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="3"/>
@@ -8119,30 +8389,30 @@
         <v>33</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I20" s="2">
         <v>1</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="3"/>
@@ -8152,13 +8422,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>22</v>
@@ -8168,10 +8438,10 @@
         <v>5</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="3"/>
@@ -8181,28 +8451,28 @@
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I22" s="2">
         <v>5</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="3"/>
@@ -8212,28 +8482,28 @@
         <v>15</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I23" s="2">
         <v>5</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="3"/>
@@ -8243,30 +8513,30 @@
         <v>13</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I24" s="2">
         <v>9</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="3"/>
@@ -8276,30 +8546,30 @@
         <v>16</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I25" s="2">
         <v>5</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="3"/>
@@ -8309,30 +8579,30 @@
         <v>34</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I26" s="2">
         <v>5</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="3"/>
@@ -8363,7 +8633,7 @@
         <v>62</v>
       </c>
       <c r="K27" s="29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L27" s="29"/>
       <c r="M27" s="31"/>
@@ -8392,7 +8662,7 @@
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="3"/>
@@ -8402,7 +8672,7 @@
         <v>12</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -8421,7 +8691,7 @@
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="3"/>
@@ -8431,20 +8701,20 @@
         <v>18</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="3"/>
@@ -8473,7 +8743,7 @@
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="3"/>
@@ -8483,15 +8753,15 @@
         <v>1</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>22</v>
@@ -8503,10 +8773,10 @@
         <v>28</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="3"/>
@@ -8516,12 +8786,12 @@
         <v>6</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>14</v>
@@ -8530,16 +8800,16 @@
         <v>22</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I33" s="2">
         <v>8</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="3"/>
@@ -8549,12 +8819,12 @@
         <v>9</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>11</v>
@@ -8563,16 +8833,16 @@
         <v>22</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I34" s="2">
         <v>8</v>
       </c>
       <c r="J34" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K34" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="3"/>
@@ -8582,12 +8852,12 @@
         <v>15</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
       <c r="E35" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>42</v>
@@ -8602,10 +8872,10 @@
         <v>80</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="3"/>
@@ -8615,15 +8885,15 @@
         <v>25</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>12</v>
@@ -8635,10 +8905,10 @@
         <v>4</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="3"/>
@@ -8648,14 +8918,14 @@
         <v>11</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>33</v>
@@ -8664,16 +8934,16 @@
         <v>12</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I37" s="2">
         <v>3</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" s="3"/>
@@ -8683,14 +8953,14 @@
         <v>27</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>33</v>
@@ -8699,16 +8969,16 @@
         <v>22</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I38" s="2">
         <v>3</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L38" s="21">
         <v>41957</v>
@@ -8720,32 +8990,32 @@
         <v>46</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I39" s="8">
         <v>5</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L39" s="32">
         <v>41944</v>
@@ -8754,138 +9024,284 @@
         <v>41953</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
-      <c r="A40" s="1"/>
-      <c r="B40" s="8"/>
+    <row r="40" spans="1:13" ht="40.5">
+      <c r="A40" s="13">
+        <v>55</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>255</v>
+      </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="1:13">
-      <c r="A41" s="1"/>
-      <c r="B41" s="8"/>
+      <c r="F40" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="L40" s="8"/>
+      <c r="M40" s="14"/>
+    </row>
+    <row r="41" spans="1:13" ht="27">
+      <c r="A41" s="13">
+        <v>53</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>251</v>
+      </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" s="1"/>
-      <c r="B42" s="8"/>
+      <c r="F41" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="L41" s="8"/>
+      <c r="M41" s="14"/>
+    </row>
+    <row r="42" spans="1:13" ht="27">
+      <c r="A42" s="1">
+        <v>37</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>213</v>
+      </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
+      <c r="E42" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="I42" s="2">
+        <v>15</v>
+      </c>
       <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
+      <c r="K42" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="L42" s="2"/>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" spans="1:13">
-      <c r="A43" s="1"/>
-      <c r="B43" s="8"/>
+    <row r="43" spans="1:13" ht="27">
+      <c r="A43" s="1">
+        <v>32</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>206</v>
+      </c>
       <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="1:13">
-      <c r="A44" s="1"/>
-      <c r="B44" s="8"/>
+      <c r="D43" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I43" s="2">
+        <v>22</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L43" s="21">
+        <v>41949</v>
+      </c>
+      <c r="M43" s="22"/>
+    </row>
+    <row r="44" spans="1:13" ht="40.5">
+      <c r="A44" s="1">
+        <v>33</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>219</v>
+      </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
+      <c r="E44" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="I44" s="2">
+        <v>5</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="L44" s="2"/>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" spans="1:13">
-      <c r="A45" s="1"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="1:13">
-      <c r="A46" s="1"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="1:13">
-      <c r="A47" s="1"/>
-      <c r="B47" s="8"/>
+    <row r="45" spans="1:13" ht="27">
+      <c r="A45" s="27">
+        <v>29</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G45" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="H45" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="I45" s="29">
+        <v>20</v>
+      </c>
+      <c r="J45" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="K45" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="L45" s="29"/>
+      <c r="M45" s="31"/>
+    </row>
+    <row r="46" spans="1:13" ht="27">
+      <c r="A46" s="27">
+        <v>30</v>
+      </c>
+      <c r="B46" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="E46" s="28"/>
+      <c r="F46" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G46" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="H46" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="I46" s="29">
+        <v>20</v>
+      </c>
+      <c r="J46" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="K46" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="L46" s="29"/>
+      <c r="M46" s="31"/>
+    </row>
+    <row r="47" spans="1:13" ht="54">
+      <c r="A47" s="1">
+        <v>41</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
+      <c r="F47" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="2">
+        <v>2</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L47" s="21"/>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" spans="1:13">
-      <c r="A48" s="1"/>
-      <c r="B48" s="8"/>
+    <row r="48" spans="1:13" ht="27">
+      <c r="A48" s="1">
+        <v>45</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
+      <c r="F48" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I48" s="2">
+        <v>15</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="L48" s="2"/>
       <c r="M48" s="3"/>
     </row>
@@ -9287,353 +9703,451 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:M9 A32:M37">
-    <cfRule type="expression" dxfId="99" priority="121" stopIfTrue="1">
+    <cfRule type="expression" dxfId="143" priority="149" stopIfTrue="1">
       <formula>$K9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="122" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="150" stopIfTrue="1">
       <formula>$K9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="123" stopIfTrue="1">
+    <cfRule type="expression" dxfId="141" priority="151" stopIfTrue="1">
       <formula>$K9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="124" stopIfTrue="1">
+    <cfRule type="expression" dxfId="140" priority="152" stopIfTrue="1">
       <formula>OR($K9="CLOSED",$K9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:M10">
-    <cfRule type="expression" dxfId="95" priority="117" stopIfTrue="1">
+    <cfRule type="expression" dxfId="139" priority="145" stopIfTrue="1">
       <formula>$K10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="118" stopIfTrue="1">
+    <cfRule type="expression" dxfId="138" priority="146" stopIfTrue="1">
       <formula>$K10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="119" stopIfTrue="1">
+    <cfRule type="expression" dxfId="137" priority="147" stopIfTrue="1">
       <formula>$K10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="120" stopIfTrue="1">
+    <cfRule type="expression" dxfId="136" priority="148" stopIfTrue="1">
       <formula>OR($K10="CLOSED",$K10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:M11">
-    <cfRule type="expression" dxfId="91" priority="113" stopIfTrue="1">
+    <cfRule type="expression" dxfId="135" priority="141" stopIfTrue="1">
       <formula>$K11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="114" stopIfTrue="1">
+    <cfRule type="expression" dxfId="134" priority="142" stopIfTrue="1">
       <formula>$K11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="115" stopIfTrue="1">
+    <cfRule type="expression" dxfId="133" priority="143" stopIfTrue="1">
       <formula>$K11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="116" stopIfTrue="1">
+    <cfRule type="expression" dxfId="132" priority="144" stopIfTrue="1">
       <formula>OR($K11="CLOSED",$K11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:M12">
-    <cfRule type="expression" dxfId="87" priority="109" stopIfTrue="1">
+    <cfRule type="expression" dxfId="131" priority="137" stopIfTrue="1">
       <formula>$K12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="110" stopIfTrue="1">
+    <cfRule type="expression" dxfId="130" priority="138" stopIfTrue="1">
       <formula>$K12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="111" stopIfTrue="1">
+    <cfRule type="expression" dxfId="129" priority="139" stopIfTrue="1">
       <formula>$K12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="112" stopIfTrue="1">
+    <cfRule type="expression" dxfId="128" priority="140" stopIfTrue="1">
       <formula>OR($K12="CLOSED",$K12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:M13">
-    <cfRule type="expression" dxfId="83" priority="105" stopIfTrue="1">
+    <cfRule type="expression" dxfId="127" priority="133" stopIfTrue="1">
       <formula>$K13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="106" stopIfTrue="1">
+    <cfRule type="expression" dxfId="126" priority="134" stopIfTrue="1">
       <formula>$K13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="107" stopIfTrue="1">
+    <cfRule type="expression" dxfId="125" priority="135" stopIfTrue="1">
       <formula>$K13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="108" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="136" stopIfTrue="1">
       <formula>OR($K13="CLOSED",$K13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:M14">
-    <cfRule type="expression" dxfId="79" priority="101" stopIfTrue="1">
+    <cfRule type="expression" dxfId="123" priority="129" stopIfTrue="1">
       <formula>$K14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="102" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="130" stopIfTrue="1">
       <formula>$K14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="103" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="131" stopIfTrue="1">
       <formula>$K14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="104" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="132" stopIfTrue="1">
       <formula>OR($K14="CLOSED",$K14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:M15">
-    <cfRule type="expression" dxfId="75" priority="97" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="125" stopIfTrue="1">
       <formula>$K15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="98" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="126" stopIfTrue="1">
       <formula>$K15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="99" stopIfTrue="1">
+    <cfRule type="expression" dxfId="117" priority="127" stopIfTrue="1">
       <formula>$K15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="100" stopIfTrue="1">
+    <cfRule type="expression" dxfId="116" priority="128" stopIfTrue="1">
       <formula>OR($K15="CLOSED",$K15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:M16">
-    <cfRule type="expression" dxfId="71" priority="93" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="121" stopIfTrue="1">
       <formula>$K16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="94" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="122" stopIfTrue="1">
       <formula>$K16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="95" stopIfTrue="1">
+    <cfRule type="expression" dxfId="113" priority="123" stopIfTrue="1">
       <formula>$K16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="96" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="124" stopIfTrue="1">
       <formula>OR($K16="CLOSED",$K16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:M17">
-    <cfRule type="expression" dxfId="67" priority="89" stopIfTrue="1">
+    <cfRule type="expression" dxfId="111" priority="117" stopIfTrue="1">
       <formula>$K17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="110" priority="118" stopIfTrue="1">
       <formula>$K17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="91" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="119" stopIfTrue="1">
       <formula>$K17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="92" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="120" stopIfTrue="1">
       <formula>OR($K17="CLOSED",$K17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:M18">
-    <cfRule type="expression" dxfId="63" priority="85" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="113" stopIfTrue="1">
       <formula>$K18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="86" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="114" stopIfTrue="1">
       <formula>$K18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="87" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="115" stopIfTrue="1">
       <formula>$K18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="88" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="116" stopIfTrue="1">
       <formula>OR($K18="CLOSED",$K18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:M19">
-    <cfRule type="expression" dxfId="59" priority="81" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="109" stopIfTrue="1">
       <formula>$K19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="82" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="110" stopIfTrue="1">
       <formula>$K19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="83" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="111" stopIfTrue="1">
       <formula>$K19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="84" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="112" stopIfTrue="1">
       <formula>OR($K19="CLOSED",$K19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:M20">
-    <cfRule type="expression" dxfId="55" priority="77" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="105" stopIfTrue="1">
       <formula>$K20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="78" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="106" stopIfTrue="1">
       <formula>$K20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="79" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="107" stopIfTrue="1">
       <formula>$K20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="80" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="108" stopIfTrue="1">
       <formula>OR($K20="CLOSED",$K20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:M21">
-    <cfRule type="expression" dxfId="51" priority="73" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="101" stopIfTrue="1">
       <formula>$K21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="102" stopIfTrue="1">
       <formula>$K21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="75" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="103" stopIfTrue="1">
       <formula>$K21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="104" stopIfTrue="1">
       <formula>OR($K21="CLOSED",$K21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:M23">
-    <cfRule type="expression" dxfId="47" priority="69" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="97" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="98" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="71" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="99" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="100" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:I22">
-    <cfRule type="expression" dxfId="43" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="93" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="94" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="95" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="96" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="39" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="89" stopIfTrue="1">
       <formula>$K23="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="90" stopIfTrue="1">
       <formula>$K23="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="91" stopIfTrue="1">
       <formula>$K23="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="92" stopIfTrue="1">
       <formula>OR($K23="CLOSED",$K23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:M25">
-    <cfRule type="expression" dxfId="35" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="85" stopIfTrue="1">
       <formula>$K24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="86" stopIfTrue="1">
       <formula>$K24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="87" stopIfTrue="1">
       <formula>$K24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="88" stopIfTrue="1">
       <formula>OR($K24="CLOSED",$K24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="31" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="81" stopIfTrue="1">
       <formula>$K25="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="82" stopIfTrue="1">
       <formula>$K25="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="83" stopIfTrue="1">
       <formula>$K25="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="84" stopIfTrue="1">
       <formula>OR($K25="CLOSED",$K25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:M26">
-    <cfRule type="expression" dxfId="27" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="77" stopIfTrue="1">
       <formula>$K26="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="78" stopIfTrue="1">
       <formula>$K26="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="79" stopIfTrue="1">
       <formula>$K26="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="80" stopIfTrue="1">
       <formula>OR($K26="CLOSED",$K26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:M28">
-    <cfRule type="expression" dxfId="23" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="73" stopIfTrue="1">
       <formula>$K27="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="74" stopIfTrue="1">
       <formula>$K27="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="75" stopIfTrue="1">
       <formula>$K27="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="76" stopIfTrue="1">
       <formula>OR($K27="CLOSED",$K27="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M30">
-    <cfRule type="expression" dxfId="19" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="69" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="70" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="71" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="72" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M29">
-    <cfRule type="expression" dxfId="15" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="65" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="66" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="67" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="68" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:M31">
-    <cfRule type="expression" dxfId="11" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="61" stopIfTrue="1">
       <formula>$K31="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="62" stopIfTrue="1">
       <formula>$K31="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="63" stopIfTrue="1">
       <formula>$K31="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="64" stopIfTrue="1">
       <formula>OR($K31="CLOSED",$K31="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:M38">
-    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="33" stopIfTrue="1">
       <formula>$K38="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="34" stopIfTrue="1">
       <formula>$K38="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="35" stopIfTrue="1">
       <formula>$K38="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="36" stopIfTrue="1">
       <formula>OR($K38="CLOSED",$K38="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:M39">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="29" stopIfTrue="1">
       <formula>$K39="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="30" stopIfTrue="1">
       <formula>$K39="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="31" stopIfTrue="1">
       <formula>$K39="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="32" stopIfTrue="1">
       <formula>OR($K39="CLOSED",$K39="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A40:M40">
+    <cfRule type="expression" dxfId="43" priority="25" stopIfTrue="1">
+      <formula>$K40="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="26" stopIfTrue="1">
+      <formula>$K40="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="41" priority="27" stopIfTrue="1">
+      <formula>$K40="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="28" stopIfTrue="1">
+      <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A41:M41">
+    <cfRule type="expression" dxfId="39" priority="21" stopIfTrue="1">
+      <formula>$K41="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="22" stopIfTrue="1">
+      <formula>$K41="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="23" stopIfTrue="1">
+      <formula>$K41="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="24" stopIfTrue="1">
+      <formula>OR($K41="CLOSED",$K41="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A42:M42">
+    <cfRule type="expression" dxfId="35" priority="17" stopIfTrue="1">
+      <formula>$K42="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="18" stopIfTrue="1">
+      <formula>$K42="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="19" stopIfTrue="1">
+      <formula>$K42="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="20" stopIfTrue="1">
+      <formula>OR($K42="CLOSED",$K42="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A43:M44">
+    <cfRule type="expression" dxfId="31" priority="13" stopIfTrue="1">
+      <formula>$K43="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="14" stopIfTrue="1">
+      <formula>$K43="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="15" stopIfTrue="1">
+      <formula>$K43="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="16" stopIfTrue="1">
+      <formula>OR($K43="CLOSED",$K43="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A45:M46">
+    <cfRule type="expression" dxfId="23" priority="9" stopIfTrue="1">
+      <formula>$K45="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="10" stopIfTrue="1">
+      <formula>$K45="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="11" stopIfTrue="1">
+      <formula>$K45="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="12" stopIfTrue="1">
+      <formula>OR($K45="CLOSED",$K45="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A47:M47">
+    <cfRule type="expression" dxfId="19" priority="5" stopIfTrue="1">
+      <formula>$K47="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="6" stopIfTrue="1">
+      <formula>$K47="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="7" stopIfTrue="1">
+      <formula>$K47="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="8" stopIfTrue="1">
+      <formula>OR($K47="CLOSED",$K47="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48:M48">
+    <cfRule type="expression" dxfId="15" priority="1" stopIfTrue="1">
+      <formula>$K48="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="2" stopIfTrue="1">
+      <formula>$K48="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="3" stopIfTrue="1">
+      <formula>$K48="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="4" stopIfTrue="1">
+      <formula>OR($K48="CLOSED",$K48="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -13,8 +13,8 @@
     <sheet name="已完成任务" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2014年'!$A$1:$M$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$M$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2014年'!$A$1:$M$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$M$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$M$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="266">
   <si>
     <r>
       <t>描述</t>
@@ -1319,12 +1319,25 @@
     <t xml:space="preserve">SEQUOIADBMAINSTREAM-583 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">提供 findAndModify 和 findAndRemove的原子操作功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-663 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1385,6 +1398,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1557,12 +1577,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1671,8 +1695,12 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="176">
@@ -3201,7 +3229,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -3910,120 +3938,80 @@
     </row>
     <row r="26" spans="1:13" ht="40.5">
       <c r="A26" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>257</v>
+        <v>73</v>
       </c>
       <c r="C26" s="8"/>
-      <c r="D26" s="8" t="s">
-        <v>259</v>
-      </c>
+      <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="I26" s="2">
-        <v>2</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>61</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:13" ht="40.5">
-      <c r="A27" s="1">
-        <v>44</v>
+    <row r="27" spans="1:13" ht="27">
+      <c r="A27" s="13">
+        <v>53</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I27" s="2">
-        <v>15</v>
-      </c>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="1:13" ht="40.5">
-      <c r="A28" s="1">
-        <v>46</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>114</v>
-      </c>
+      <c r="G27" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="14"/>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="13"/>
+      <c r="B28" s="8"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="8" t="s">
-        <v>105</v>
-      </c>
+      <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I28" s="2">
-        <v>3</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="L28" s="21">
-        <v>41679</v>
-      </c>
-      <c r="M28" s="22">
-        <v>41679</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="27">
-      <c r="A29" s="13">
-        <v>53</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>111</v>
-      </c>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="14"/>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="13"/>
+      <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
-      <c r="F29" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>20</v>
-      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
       <c r="I29" s="8"/>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
@@ -4555,81 +4543,51 @@
       <c r="L64" s="8"/>
       <c r="M64" s="14"/>
     </row>
-    <row r="65" spans="1:13">
-      <c r="A65" s="13"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="8"/>
-      <c r="K65" s="8"/>
-      <c r="L65" s="8"/>
-      <c r="M65" s="14"/>
-    </row>
-    <row r="66" spans="1:13">
-      <c r="A66" s="13"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
-      <c r="I66" s="8"/>
-      <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="8"/>
-      <c r="M66" s="14"/>
-    </row>
-    <row r="67" spans="1:13" ht="14.25" thickBot="1">
-      <c r="A67" s="15"/>
-      <c r="B67" s="16"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
-      <c r="H67" s="16"/>
-      <c r="I67" s="16"/>
-      <c r="J67" s="16"/>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="17"/>
+    <row r="65" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A65" s="15"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="16"/>
+      <c r="H65" s="16"/>
+      <c r="I65" s="16"/>
+      <c r="J65" s="16"/>
+      <c r="K65" s="16"/>
+      <c r="L65" s="16"/>
+      <c r="M65" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M29">
+  <autoFilter ref="A1:M27">
     <filterColumn colId="2"/>
     <filterColumn colId="3"/>
     <filterColumn colId="4"/>
     <filterColumn colId="6"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:M178">
-    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:M176">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F67">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F65">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G67">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G65">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K67">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K65">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5823,7 +5781,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -6692,15 +6650,13 @@
     </row>
     <row r="31" spans="1:13" ht="27">
       <c r="A31" s="13">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C31" s="8"/>
-      <c r="D31" s="8" t="s">
-        <v>262</v>
-      </c>
+      <c r="D31" s="8"/>
       <c r="E31" s="8" t="s">
         <v>205</v>
       </c>
@@ -6711,24 +6667,22 @@
         <v>22</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="I31" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J31" s="8"/>
-      <c r="K31" s="8" t="s">
-        <v>61</v>
-      </c>
+      <c r="K31" s="8"/>
       <c r="L31" s="8"/>
       <c r="M31" s="14"/>
     </row>
     <row r="32" spans="1:13" ht="27">
       <c r="A32" s="13">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -6739,25 +6693,25 @@
         <v>68</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I32" s="8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
       <c r="M32" s="14"/>
     </row>
-    <row r="33" spans="1:13" ht="27">
+    <row r="33" spans="1:13" ht="54">
       <c r="A33" s="13">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -6768,25 +6722,25 @@
         <v>68</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I33" s="8">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
       <c r="M33" s="14"/>
     </row>
-    <row r="34" spans="1:13" ht="54">
+    <row r="34" spans="1:13" ht="27">
       <c r="A34" s="13">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -6794,28 +6748,28 @@
         <v>205</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I34" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
       <c r="M34" s="14"/>
     </row>
-    <row r="35" spans="1:13" ht="27">
+    <row r="35" spans="1:13" ht="54">
       <c r="A35" s="13">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -6823,7 +6777,7 @@
         <v>205</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>12</v>
@@ -6832,19 +6786,19 @@
         <v>229</v>
       </c>
       <c r="I35" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
       <c r="M35" s="14"/>
     </row>
-    <row r="36" spans="1:13" ht="54">
+    <row r="36" spans="1:13" ht="27">
       <c r="A36" s="13">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -6858,10 +6812,10 @@
         <v>12</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="I36" s="8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
@@ -6870,10 +6824,10 @@
     </row>
     <row r="37" spans="1:13" ht="27">
       <c r="A37" s="13">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
@@ -6890,7 +6844,7 @@
         <v>208</v>
       </c>
       <c r="I37" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
@@ -6899,10 +6853,10 @@
     </row>
     <row r="38" spans="1:13" ht="27">
       <c r="A38" s="13">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
@@ -6916,22 +6870,22 @@
         <v>12</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="I38" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
       <c r="M38" s="14"/>
     </row>
-    <row r="39" spans="1:13" ht="27">
+    <row r="39" spans="1:13" ht="40.5">
       <c r="A39" s="13">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -6939,16 +6893,16 @@
         <v>205</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="I39" s="8">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
@@ -6957,84 +6911,66 @@
     </row>
     <row r="40" spans="1:13" ht="40.5">
       <c r="A40" s="13">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
-      <c r="E40" s="8" t="s">
-        <v>205</v>
-      </c>
+      <c r="E40" s="8"/>
       <c r="F40" s="8" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="G40" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H40" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="I40" s="8">
-        <v>15</v>
-      </c>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
       <c r="L40" s="8"/>
       <c r="M40" s="14"/>
     </row>
-    <row r="41" spans="1:13" ht="54">
+    <row r="41" spans="1:13" ht="40.5">
       <c r="A41" s="13">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="C41" s="8"/>
-      <c r="D41" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>249</v>
-      </c>
+      <c r="D41" s="36" t="s">
+        <v>265</v>
+      </c>
+      <c r="E41" s="8"/>
       <c r="F41" s="8" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="I41" s="8">
-        <v>5</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>254</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J41" s="8"/>
       <c r="K41" s="8" t="s">
         <v>61</v>
       </c>
       <c r="L41" s="8"/>
       <c r="M41" s="14"/>
     </row>
-    <row r="42" spans="1:13" ht="40.5">
-      <c r="A42" s="13">
-        <v>54</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>252</v>
-      </c>
+    <row r="42" spans="1:13">
+      <c r="A42" s="13"/>
+      <c r="B42" s="8"/>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
-      <c r="F42" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>22</v>
-      </c>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
       <c r="J42" s="8"/>
@@ -7054,7 +6990,7 @@
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
+      <c r="L43" s="32"/>
       <c r="M43" s="14"/>
     </row>
     <row r="44" spans="1:13">
@@ -7084,7 +7020,7 @@
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
       <c r="K45" s="8"/>
-      <c r="L45" s="32"/>
+      <c r="L45" s="8"/>
       <c r="M45" s="14"/>
     </row>
     <row r="46" spans="1:13">
@@ -7612,98 +7548,71 @@
       <c r="L80" s="8"/>
       <c r="M80" s="14"/>
     </row>
-    <row r="81" spans="1:13">
-      <c r="A81" s="13"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="8"/>
-      <c r="J81" s="8"/>
-      <c r="K81" s="8"/>
-      <c r="L81" s="8"/>
-      <c r="M81" s="14"/>
-    </row>
-    <row r="82" spans="1:13">
-      <c r="A82" s="13"/>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="8"/>
-      <c r="J82" s="8"/>
-      <c r="K82" s="8"/>
-      <c r="L82" s="8"/>
-      <c r="M82" s="14"/>
-    </row>
-    <row r="83" spans="1:13" ht="14.25" thickBot="1">
-      <c r="A83" s="15"/>
-      <c r="B83" s="16"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
-      <c r="F83" s="16"/>
-      <c r="G83" s="16"/>
-      <c r="H83" s="16"/>
-      <c r="I83" s="16"/>
-      <c r="J83" s="16"/>
-      <c r="K83" s="16"/>
-      <c r="L83" s="16"/>
-      <c r="M83" s="17"/>
+    <row r="81" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A81" s="15"/>
+      <c r="B81" s="16"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="16"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="16"/>
+      <c r="H81" s="16"/>
+      <c r="I81" s="16"/>
+      <c r="J81" s="16"/>
+      <c r="K81" s="16"/>
+      <c r="L81" s="16"/>
+      <c r="M81" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M42">
+  <autoFilter ref="A1:M40">
     <filterColumn colId="4"/>
     <filterColumn colId="6"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:M194">
-    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:M192">
+    <cfRule type="expression" dxfId="163" priority="5" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="162" priority="6" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="161" priority="7" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="160" priority="8" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:M8">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="159" priority="1" stopIfTrue="1">
       <formula>$K8="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="158" priority="2" stopIfTrue="1">
       <formula>$K8="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="157" priority="3" stopIfTrue="1">
       <formula>$K8="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="156" priority="4" stopIfTrue="1">
       <formula>OR($K8="CLOSED",$K8="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F83">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F81">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G83">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G81">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K83">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K81">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="D41" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -9305,65 +9214,143 @@
       <c r="L48" s="2"/>
       <c r="M48" s="3"/>
     </row>
-    <row r="49" spans="1:13">
-      <c r="A49" s="1"/>
-      <c r="B49" s="8"/>
+    <row r="49" spans="1:13" ht="27">
+      <c r="A49" s="13">
+        <v>41</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>221</v>
+      </c>
       <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="1:13">
-      <c r="A50" s="1"/>
-      <c r="B50" s="8"/>
+      <c r="D49" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="I49" s="8">
+        <v>5</v>
+      </c>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="L49" s="8"/>
+      <c r="M49" s="14"/>
+    </row>
+    <row r="50" spans="1:13" ht="54">
+      <c r="A50" s="13">
+        <v>52</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>248</v>
+      </c>
       <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="1:13">
-      <c r="A51" s="1"/>
-      <c r="B51" s="8"/>
+      <c r="D50" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="I50" s="8">
+        <v>5</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="L50" s="8"/>
+      <c r="M50" s="14"/>
+    </row>
+    <row r="51" spans="1:13" ht="40.5">
+      <c r="A51" s="1">
+        <v>36</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>257</v>
+      </c>
       <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
+      <c r="D51" s="8" t="s">
+        <v>259</v>
+      </c>
       <c r="E51" s="8"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
+      <c r="F51" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I51" s="2">
+        <v>2</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="L51" s="2"/>
       <c r="M51" s="3"/>
     </row>
-    <row r="52" spans="1:13">
-      <c r="A52" s="1"/>
-      <c r="B52" s="8"/>
+    <row r="52" spans="1:13" ht="40.5">
+      <c r="A52" s="1">
+        <v>46</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>114</v>
+      </c>
       <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
+      <c r="D52" s="8" t="s">
+        <v>105</v>
+      </c>
       <c r="E52" s="8"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-      <c r="M52" s="3"/>
+      <c r="F52" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I52" s="2">
+        <v>3</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L52" s="21">
+        <v>41679</v>
+      </c>
+      <c r="M52" s="22">
+        <v>41679</v>
+      </c>
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1"/>
@@ -9703,451 +9690,507 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:M9 A32:M37">
-    <cfRule type="expression" dxfId="143" priority="149" stopIfTrue="1">
+    <cfRule type="expression" dxfId="147" priority="165" stopIfTrue="1">
       <formula>$K9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="142" priority="150" stopIfTrue="1">
+    <cfRule type="expression" dxfId="146" priority="166" stopIfTrue="1">
       <formula>$K9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="141" priority="151" stopIfTrue="1">
+    <cfRule type="expression" dxfId="145" priority="167" stopIfTrue="1">
       <formula>$K9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="140" priority="152" stopIfTrue="1">
+    <cfRule type="expression" dxfId="144" priority="168" stopIfTrue="1">
       <formula>OR($K9="CLOSED",$K9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:M10">
-    <cfRule type="expression" dxfId="139" priority="145" stopIfTrue="1">
+    <cfRule type="expression" dxfId="143" priority="161" stopIfTrue="1">
       <formula>$K10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="146" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="162" stopIfTrue="1">
       <formula>$K10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="137" priority="147" stopIfTrue="1">
+    <cfRule type="expression" dxfId="141" priority="163" stopIfTrue="1">
       <formula>$K10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="148" stopIfTrue="1">
+    <cfRule type="expression" dxfId="140" priority="164" stopIfTrue="1">
       <formula>OR($K10="CLOSED",$K10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:M11">
-    <cfRule type="expression" dxfId="135" priority="141" stopIfTrue="1">
+    <cfRule type="expression" dxfId="139" priority="157" stopIfTrue="1">
       <formula>$K11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="142" stopIfTrue="1">
+    <cfRule type="expression" dxfId="138" priority="158" stopIfTrue="1">
       <formula>$K11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="133" priority="143" stopIfTrue="1">
+    <cfRule type="expression" dxfId="137" priority="159" stopIfTrue="1">
       <formula>$K11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="144" stopIfTrue="1">
+    <cfRule type="expression" dxfId="136" priority="160" stopIfTrue="1">
       <formula>OR($K11="CLOSED",$K11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:M12">
-    <cfRule type="expression" dxfId="131" priority="137" stopIfTrue="1">
+    <cfRule type="expression" dxfId="135" priority="153" stopIfTrue="1">
       <formula>$K12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="138" stopIfTrue="1">
+    <cfRule type="expression" dxfId="134" priority="154" stopIfTrue="1">
       <formula>$K12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="139" stopIfTrue="1">
+    <cfRule type="expression" dxfId="133" priority="155" stopIfTrue="1">
       <formula>$K12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="128" priority="140" stopIfTrue="1">
+    <cfRule type="expression" dxfId="132" priority="156" stopIfTrue="1">
       <formula>OR($K12="CLOSED",$K12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:M13">
-    <cfRule type="expression" dxfId="127" priority="133" stopIfTrue="1">
+    <cfRule type="expression" dxfId="131" priority="149" stopIfTrue="1">
       <formula>$K13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="134" stopIfTrue="1">
+    <cfRule type="expression" dxfId="130" priority="150" stopIfTrue="1">
       <formula>$K13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="135" stopIfTrue="1">
+    <cfRule type="expression" dxfId="129" priority="151" stopIfTrue="1">
       <formula>$K13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="136" stopIfTrue="1">
+    <cfRule type="expression" dxfId="128" priority="152" stopIfTrue="1">
       <formula>OR($K13="CLOSED",$K13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:M14">
-    <cfRule type="expression" dxfId="123" priority="129" stopIfTrue="1">
+    <cfRule type="expression" dxfId="127" priority="145" stopIfTrue="1">
       <formula>$K14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="130" stopIfTrue="1">
+    <cfRule type="expression" dxfId="126" priority="146" stopIfTrue="1">
       <formula>$K14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="131" stopIfTrue="1">
+    <cfRule type="expression" dxfId="125" priority="147" stopIfTrue="1">
       <formula>$K14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="132" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="148" stopIfTrue="1">
       <formula>OR($K14="CLOSED",$K14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:M15">
-    <cfRule type="expression" dxfId="119" priority="125" stopIfTrue="1">
+    <cfRule type="expression" dxfId="123" priority="141" stopIfTrue="1">
       <formula>$K15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="126" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="142" stopIfTrue="1">
       <formula>$K15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="127" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="143" stopIfTrue="1">
       <formula>$K15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="128" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="144" stopIfTrue="1">
       <formula>OR($K15="CLOSED",$K15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:M16">
-    <cfRule type="expression" dxfId="115" priority="121" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="137" stopIfTrue="1">
       <formula>$K16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="122" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="138" stopIfTrue="1">
       <formula>$K16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="123" stopIfTrue="1">
+    <cfRule type="expression" dxfId="117" priority="139" stopIfTrue="1">
       <formula>$K16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="124" stopIfTrue="1">
+    <cfRule type="expression" dxfId="116" priority="140" stopIfTrue="1">
       <formula>OR($K16="CLOSED",$K16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:M17">
-    <cfRule type="expression" dxfId="111" priority="117" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="133" stopIfTrue="1">
       <formula>$K17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="118" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="134" stopIfTrue="1">
       <formula>$K17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="119" stopIfTrue="1">
+    <cfRule type="expression" dxfId="113" priority="135" stopIfTrue="1">
       <formula>$K17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="120" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="136" stopIfTrue="1">
       <formula>OR($K17="CLOSED",$K17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:M18">
-    <cfRule type="expression" dxfId="107" priority="113" stopIfTrue="1">
+    <cfRule type="expression" dxfId="111" priority="129" stopIfTrue="1">
       <formula>$K18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="114" stopIfTrue="1">
+    <cfRule type="expression" dxfId="110" priority="130" stopIfTrue="1">
       <formula>$K18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="115" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="131" stopIfTrue="1">
       <formula>$K18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="116" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="132" stopIfTrue="1">
       <formula>OR($K18="CLOSED",$K18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:M19">
-    <cfRule type="expression" dxfId="103" priority="109" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="125" stopIfTrue="1">
       <formula>$K19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="110" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="126" stopIfTrue="1">
       <formula>$K19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="111" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="127" stopIfTrue="1">
       <formula>$K19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="112" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="128" stopIfTrue="1">
       <formula>OR($K19="CLOSED",$K19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:M20">
-    <cfRule type="expression" dxfId="99" priority="105" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="121" stopIfTrue="1">
       <formula>$K20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="106" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="122" stopIfTrue="1">
       <formula>$K20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="107" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="123" stopIfTrue="1">
       <formula>$K20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="108" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="124" stopIfTrue="1">
       <formula>OR($K20="CLOSED",$K20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:M21">
-    <cfRule type="expression" dxfId="95" priority="101" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="117" stopIfTrue="1">
       <formula>$K21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="102" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="118" stopIfTrue="1">
       <formula>$K21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="103" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="119" stopIfTrue="1">
       <formula>$K21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="104" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="120" stopIfTrue="1">
       <formula>OR($K21="CLOSED",$K21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:M23">
-    <cfRule type="expression" dxfId="91" priority="97" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="113" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="98" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="114" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="99" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="115" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="100" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="116" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:I22">
-    <cfRule type="expression" dxfId="87" priority="93" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="109" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="94" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="110" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="95" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="111" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="96" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="112" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="83" priority="89" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="105" stopIfTrue="1">
       <formula>$K23="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="106" stopIfTrue="1">
       <formula>$K23="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="91" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="107" stopIfTrue="1">
       <formula>$K23="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="92" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="108" stopIfTrue="1">
       <formula>OR($K23="CLOSED",$K23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:M25">
-    <cfRule type="expression" dxfId="79" priority="85" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="101" stopIfTrue="1">
       <formula>$K24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="86" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="102" stopIfTrue="1">
       <formula>$K24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="87" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="103" stopIfTrue="1">
       <formula>$K24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="88" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="104" stopIfTrue="1">
       <formula>OR($K24="CLOSED",$K24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="75" priority="81" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="97" stopIfTrue="1">
       <formula>$K25="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="82" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="98" stopIfTrue="1">
       <formula>$K25="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="83" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="99" stopIfTrue="1">
       <formula>$K25="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="84" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="100" stopIfTrue="1">
       <formula>OR($K25="CLOSED",$K25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:M26">
-    <cfRule type="expression" dxfId="71" priority="77" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="93" stopIfTrue="1">
       <formula>$K26="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="78" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="94" stopIfTrue="1">
       <formula>$K26="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="79" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="95" stopIfTrue="1">
       <formula>$K26="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="80" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="96" stopIfTrue="1">
       <formula>OR($K26="CLOSED",$K26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:M28">
-    <cfRule type="expression" dxfId="67" priority="73" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="89" stopIfTrue="1">
       <formula>$K27="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="90" stopIfTrue="1">
       <formula>$K27="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="75" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="91" stopIfTrue="1">
       <formula>$K27="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="92" stopIfTrue="1">
       <formula>OR($K27="CLOSED",$K27="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M30">
-    <cfRule type="expression" dxfId="63" priority="69" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="85" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="86" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="71" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="87" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="88" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M29">
-    <cfRule type="expression" dxfId="59" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="81" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="82" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="83" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="84" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:M31">
-    <cfRule type="expression" dxfId="55" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="77" stopIfTrue="1">
       <formula>$K31="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="78" stopIfTrue="1">
       <formula>$K31="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="79" stopIfTrue="1">
       <formula>$K31="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="80" stopIfTrue="1">
       <formula>OR($K31="CLOSED",$K31="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:M38">
-    <cfRule type="expression" dxfId="51" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="49" stopIfTrue="1">
       <formula>$K38="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="50" stopIfTrue="1">
       <formula>$K38="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="51" stopIfTrue="1">
       <formula>$K38="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="52" stopIfTrue="1">
       <formula>OR($K38="CLOSED",$K38="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:M39">
-    <cfRule type="expression" dxfId="47" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="45" stopIfTrue="1">
       <formula>$K39="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="46" stopIfTrue="1">
       <formula>$K39="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="47" stopIfTrue="1">
       <formula>$K39="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="48" stopIfTrue="1">
       <formula>OR($K39="CLOSED",$K39="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:M40">
-    <cfRule type="expression" dxfId="43" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="41" stopIfTrue="1">
       <formula>$K40="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="42" stopIfTrue="1">
       <formula>$K40="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="43" stopIfTrue="1">
       <formula>$K40="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="44" stopIfTrue="1">
       <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:M41">
-    <cfRule type="expression" dxfId="39" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="37" stopIfTrue="1">
       <formula>$K41="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="38" stopIfTrue="1">
       <formula>$K41="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="39" stopIfTrue="1">
       <formula>$K41="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="40" stopIfTrue="1">
       <formula>OR($K41="CLOSED",$K41="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:M42">
-    <cfRule type="expression" dxfId="35" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="33" stopIfTrue="1">
       <formula>$K42="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="34" stopIfTrue="1">
       <formula>$K42="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="35" stopIfTrue="1">
       <formula>$K42="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="36" stopIfTrue="1">
       <formula>OR($K42="CLOSED",$K42="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:M44">
-    <cfRule type="expression" dxfId="31" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="29" stopIfTrue="1">
       <formula>$K43="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="30" stopIfTrue="1">
       <formula>$K43="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="31" stopIfTrue="1">
       <formula>$K43="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="32" stopIfTrue="1">
       <formula>OR($K43="CLOSED",$K43="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45:M46">
-    <cfRule type="expression" dxfId="23" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="25" stopIfTrue="1">
       <formula>$K45="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="26" stopIfTrue="1">
       <formula>$K45="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="27" stopIfTrue="1">
       <formula>$K45="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="28" stopIfTrue="1">
       <formula>OR($K45="CLOSED",$K45="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:M47">
-    <cfRule type="expression" dxfId="19" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="21" stopIfTrue="1">
       <formula>$K47="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="22" stopIfTrue="1">
       <formula>$K47="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="23" stopIfTrue="1">
       <formula>$K47="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="24" stopIfTrue="1">
       <formula>OR($K47="CLOSED",$K47="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:M48">
-    <cfRule type="expression" dxfId="15" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="17" stopIfTrue="1">
       <formula>$K48="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="18" stopIfTrue="1">
       <formula>$K48="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="19" stopIfTrue="1">
       <formula>$K48="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="20" stopIfTrue="1">
       <formula>OR($K48="CLOSED",$K48="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A49:M49">
+    <cfRule type="expression" dxfId="19" priority="13" stopIfTrue="1">
+      <formula>$K49="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="14" stopIfTrue="1">
+      <formula>$K49="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="15" stopIfTrue="1">
+      <formula>$K49="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="16" stopIfTrue="1">
+      <formula>OR($K49="CLOSED",$K49="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A50:M50">
+    <cfRule type="expression" dxfId="15" priority="9" stopIfTrue="1">
+      <formula>$K50="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="10" stopIfTrue="1">
+      <formula>$K50="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="11" stopIfTrue="1">
+      <formula>$K50="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="12" stopIfTrue="1">
+      <formula>OR($K50="CLOSED",$K50="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51:M51">
+    <cfRule type="expression" dxfId="11" priority="5" stopIfTrue="1">
+      <formula>$K51="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="6" stopIfTrue="1">
+      <formula>$K51="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="7" stopIfTrue="1">
+      <formula>$K51="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="8" stopIfTrue="1">
+      <formula>OR($K51="CLOSED",$K51="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A52:M52">
+    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
+      <formula>$K52="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
+      <formula>$K52="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
+      <formula>$K52="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="4" stopIfTrue="1">
+      <formula>OR($K52="CLOSED",$K52="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="2014年1季度" sheetId="1" r:id="rId1"/>
     <sheet name="2014年2季度" sheetId="3" r:id="rId2"/>
-    <sheet name="2014年" sheetId="4" r:id="rId3"/>
+    <sheet name="2015年" sheetId="4" r:id="rId3"/>
     <sheet name="已完成任务" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2014年'!$A$1:$M$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$M$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$M$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2015年'!$A$1:$M$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$M$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="282">
   <si>
     <r>
       <t>描述</t>
@@ -215,11 +215,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">数据同步大压力时，会出现节点间sharing-break
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">索引排序、非索引排序针对数组时，需要把数组相同的内容放在一起，以保证聚集的正确性
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -329,15 +324,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">提升文档质量（正确性、全面性）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DOC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">动态参数修改和查看
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -389,11 +375,6 @@
   </si>
   <si>
     <t xml:space="preserve">Snapshot和list命令完善，能灵活查看系统状态
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Coord节点的监控
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -900,11 +881,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Coord流程重构（1、Coord采用session模式； 2、Coord各种操作抽象出几种模板；3、抽象出各种错误下的重试机制）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">批量insert在split窗口中数据会分发错误（批量insert和split互斥， 或者 数据节点转发）
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1167,16 +1143,6 @@
   </si>
   <si>
     <t xml:space="preserve">Truncate collection功能
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">OM安装部署功能优化（各种异常下的恢复、遗留问题，参数检测等）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">OM提供“主机监控管理”、“业务监控管理”功能
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1332,12 +1298,121 @@
     <t xml:space="preserve">SEQUOIADBMAINSTREAM-663 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>2015Q1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-742 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李伟超</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、出错重试的流程
+2、在升主阶段的阻塞，确保操作不会立即失败
+3、其它功能点的优化（Command接口调整，交互流程参数和返回信息规范，性能优化等）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">数据同步大压力时，会出现节点间sharing-break
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、首次add的节点超时时间为shifttime
+2、数据的消息可以当作心跳消息
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">文档中心构建
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、文档分类、规划，要求（check list）
+2、文档内容写作，整理
+3、文档排版组织和发布
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DOC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">集成Spark的安装部署和卸载
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">数据中心灾备
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RTN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SequoiaDB业务操作管理（CollectionSpace, Collection, Group, Domain, Record等）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">第二代存储引擎开发
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalog元数据操作在并发时保证一致性要求
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在数据节点创建CS时会加Bucket锁， 通过Bucket锁解决并发创建的冲突问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过truncate来优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">OM提供“主机鉴控管理”（主机状态，内存，CPU利用率，磁盘等）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">通过post event到游标的线程，并能激活该线程立即处理
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1382,14 +1457,6 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1581,12 +1648,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1689,13 +1756,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1703,7 +1767,63 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="176">
+  <dxfs count="184">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3229,7 +3349,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -3255,10 +3375,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5" t="s">
@@ -3286,18 +3406,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54">
+    <row r="2" spans="1:13" ht="67.5">
       <c r="A2" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>12</v>
@@ -3305,18 +3425,20 @@
       <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="2"/>
+      <c r="I2" s="2">
+        <v>7</v>
+      </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:13" ht="67.5">
+    <row r="3" spans="1:13" ht="40.5">
       <c r="A3" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -3325,149 +3447,143 @@
         <v>14</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I3" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="3"/>
     </row>
-    <row r="4" spans="1:13" ht="67.5">
+    <row r="4" spans="1:13" ht="40.5">
       <c r="A4" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="2">
-        <v>7</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" spans="1:13" ht="40.5">
-      <c r="A5" s="27">
-        <v>8</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="29">
-        <v>1</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="K5" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="L5" s="30">
-        <v>41679</v>
-      </c>
-      <c r="M5" s="31"/>
-    </row>
-    <row r="6" spans="1:13" ht="40.5">
+    <row r="5" spans="1:13" ht="27">
+      <c r="A5" s="1">
+        <v>13</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2">
+        <v>15</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" spans="1:13" ht="27">
       <c r="A6" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="2" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I6" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:13" ht="40.5">
+    <row r="7" spans="1:13" ht="27">
       <c r="A7" s="1">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8</v>
+      </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="67.5">
+    <row r="8" spans="1:13" ht="27">
       <c r="A8" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -3477,25 +3593,25 @@
     </row>
     <row r="9" spans="1:13" ht="27">
       <c r="A9" s="1">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="2" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I9" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -3504,52 +3620,56 @@
     </row>
     <row r="10" spans="1:13" ht="27">
       <c r="A10" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I10" s="2">
-        <v>4</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="3"/>
     </row>
     <row r="11" spans="1:13" ht="27">
       <c r="A11" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -3558,24 +3678,26 @@
     </row>
     <row r="12" spans="1:13" ht="27">
       <c r="A12" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="I12" s="2">
+        <v>15</v>
+      </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -3583,25 +3705,25 @@
     </row>
     <row r="13" spans="1:13" ht="27">
       <c r="A13" s="1">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I13" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -3610,164 +3732,160 @@
     </row>
     <row r="14" spans="1:13" ht="27">
       <c r="A14" s="1">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I14" s="2">
-        <v>13</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>61</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="1:13" ht="27">
       <c r="A15" s="1">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>40</v>
+        <v>199</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
       <c r="F15" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="I15" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:13" ht="27">
+    <row r="16" spans="1:13" ht="40.5">
       <c r="A16" s="1">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="I16" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="1:13" ht="27">
+    <row r="17" spans="1:13" ht="40.5">
       <c r="A17" s="1">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I17" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" ht="27">
+    <row r="18" spans="1:13" ht="54">
       <c r="A18" s="1">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I18" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="1:13" ht="27">
+    <row r="19" spans="1:13" ht="40.5">
       <c r="A19" s="1">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="I19" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -3775,213 +3893,129 @@
       <c r="M19" s="3"/>
     </row>
     <row r="20" spans="1:13" ht="27">
-      <c r="A20" s="1">
-        <v>27</v>
+      <c r="A20" s="13">
+        <v>53</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
-      <c r="F20" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="F20" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I20" s="2">
-        <v>4</v>
-      </c>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="1:13" ht="27">
-      <c r="A21" s="1">
-        <v>28</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>204</v>
-      </c>
+      <c r="H20" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="14"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="13"/>
+      <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I21" s="2">
-        <v>8</v>
-      </c>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="1:13" ht="40.5">
-      <c r="A22" s="1">
-        <v>31</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>63</v>
-      </c>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="14"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="13"/>
+      <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I22" s="2">
-        <v>8</v>
-      </c>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="1:13" ht="27">
-      <c r="A23" s="1">
-        <v>32</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>64</v>
-      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="14"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="13"/>
+      <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I23" s="2">
-        <v>6</v>
-      </c>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="1:13" ht="40.5">
-      <c r="A24" s="1">
-        <v>33</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>66</v>
-      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="14"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="13"/>
+      <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I24" s="2">
-        <v>8</v>
-      </c>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="1:13" ht="54">
-      <c r="A25" s="1">
-        <v>34</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>77</v>
-      </c>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="14"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="13"/>
+      <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I25" s="2">
-        <v>8</v>
-      </c>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="1:13" ht="40.5">
-      <c r="A26" s="1">
-        <v>44</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>73</v>
-      </c>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="14"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="13"/>
+      <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I26" s="2">
-        <v>15</v>
-      </c>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="1:13" ht="27">
-      <c r="A27" s="13">
-        <v>53</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>111</v>
-      </c>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="14"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="13"/>
+      <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>20</v>
-      </c>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
       <c r="I27" s="8"/>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
@@ -4438,156 +4472,51 @@
       <c r="L57" s="8"/>
       <c r="M57" s="14"/>
     </row>
-    <row r="58" spans="1:13">
-      <c r="A58" s="13"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
-      <c r="L58" s="8"/>
-      <c r="M58" s="14"/>
-    </row>
-    <row r="59" spans="1:13">
-      <c r="A59" s="13"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="8"/>
-      <c r="J59" s="8"/>
-      <c r="K59" s="8"/>
-      <c r="L59" s="8"/>
-      <c r="M59" s="14"/>
-    </row>
-    <row r="60" spans="1:13">
-      <c r="A60" s="13"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-      <c r="I60" s="8"/>
-      <c r="J60" s="8"/>
-      <c r="K60" s="8"/>
-      <c r="L60" s="8"/>
-      <c r="M60" s="14"/>
-    </row>
-    <row r="61" spans="1:13">
-      <c r="A61" s="13"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="8"/>
-      <c r="J61" s="8"/>
-      <c r="K61" s="8"/>
-      <c r="L61" s="8"/>
-      <c r="M61" s="14"/>
-    </row>
-    <row r="62" spans="1:13">
-      <c r="A62" s="13"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
-      <c r="M62" s="14"/>
-    </row>
-    <row r="63" spans="1:13">
-      <c r="A63" s="13"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-      <c r="I63" s="8"/>
-      <c r="J63" s="8"/>
-      <c r="K63" s="8"/>
-      <c r="L63" s="8"/>
-      <c r="M63" s="14"/>
-    </row>
-    <row r="64" spans="1:13">
-      <c r="A64" s="13"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
-      <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="14"/>
-    </row>
-    <row r="65" spans="1:13" ht="14.25" thickBot="1">
-      <c r="A65" s="15"/>
-      <c r="B65" s="16"/>
-      <c r="C65" s="16"/>
-      <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
-      <c r="H65" s="16"/>
-      <c r="I65" s="16"/>
-      <c r="J65" s="16"/>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="17"/>
+    <row r="58" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A58" s="15"/>
+      <c r="B58" s="16"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="16"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="16"/>
+      <c r="J58" s="16"/>
+      <c r="K58" s="16"/>
+      <c r="L58" s="16"/>
+      <c r="M58" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M27">
+  <autoFilter ref="A1:M20">
     <filterColumn colId="2"/>
     <filterColumn colId="3"/>
     <filterColumn colId="4"/>
     <filterColumn colId="6"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:M176">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:M169">
+    <cfRule type="expression" dxfId="183" priority="1" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="182" priority="2" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="181" priority="3" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="180" priority="4" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F65">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F58">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G65">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G58">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K65">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K58">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4626,10 +4555,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -4661,12 +4590,12 @@
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -4681,12 +4610,12 @@
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -4701,12 +4630,12 @@
         <v>4</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -4721,12 +4650,12 @@
         <v>5</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C5" s="28"/>
       <c r="D5" s="28"/>
       <c r="E5" s="29" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F5" s="29"/>
       <c r="G5" s="29"/>
@@ -4741,12 +4670,12 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -4761,12 +4690,12 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -4781,12 +4710,12 @@
         <v>8</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -4801,12 +4730,12 @@
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -4821,12 +4750,12 @@
         <v>19</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="28"/>
       <c r="E10" s="29" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F10" s="29"/>
       <c r="G10" s="29"/>
@@ -4841,12 +4770,12 @@
         <v>27</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -4861,12 +4790,12 @@
         <v>29</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -5747,16 +5676,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L185">
-    <cfRule type="expression" dxfId="175" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="179" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="174" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="178" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="177" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="172" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="176" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5778,10 +5707,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -5806,13 +5735,13 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>1</v>
@@ -5844,15 +5773,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>22</v>
@@ -5861,33 +5790,31 @@
         <v>13</v>
       </c>
       <c r="I2" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:13" ht="40.5">
+    <row r="3" spans="1:13" ht="40.5" hidden="1">
       <c r="A3" s="1">
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
-      <c r="E3" s="8" t="s">
-        <v>207</v>
-      </c>
+      <c r="E3" s="8"/>
       <c r="F3" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -5895,26 +5822,24 @@
       <c r="L3" s="2"/>
       <c r="M3" s="3"/>
     </row>
-    <row r="4" spans="1:13" ht="40.5">
+    <row r="4" spans="1:13" ht="40.5" hidden="1">
       <c r="A4" s="27">
         <v>4</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
-      <c r="E4" s="28" t="s">
-        <v>207</v>
-      </c>
+      <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G4" s="29" t="s">
         <v>22</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I4" s="29">
         <v>8</v>
@@ -5924,18 +5849,16 @@
       <c r="L4" s="30"/>
       <c r="M4" s="31"/>
     </row>
-    <row r="5" spans="1:13" ht="40.5">
+    <row r="5" spans="1:13" ht="40.5" hidden="1">
       <c r="A5" s="1">
         <v>5</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="8" t="s">
-        <v>207</v>
-      </c>
+      <c r="E5" s="8"/>
       <c r="F5" s="2" t="s">
         <v>14</v>
       </c>
@@ -5943,7 +5866,7 @@
         <v>12</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I5" s="2">
         <v>16</v>
@@ -5958,50 +5881,48 @@
         <v>7</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I6" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:13" ht="54">
+    <row r="7" spans="1:13" ht="40.5" hidden="1">
       <c r="A7" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
-      <c r="E7" s="8" t="s">
-        <v>207</v>
-      </c>
+      <c r="E7" s="8"/>
       <c r="F7" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -6009,26 +5930,24 @@
       <c r="L7" s="2"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="40.5">
+    <row r="8" spans="1:13" ht="27" hidden="1">
       <c r="A8" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="8" t="s">
-        <v>207</v>
-      </c>
+      <c r="E8" s="8"/>
       <c r="F8" s="2" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -6036,26 +5955,24 @@
       <c r="L8" s="2"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:13" ht="27">
+    <row r="9" spans="1:13" ht="54" hidden="1">
       <c r="A9" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
-      <c r="E9" s="8" t="s">
-        <v>207</v>
-      </c>
+      <c r="E9" s="8"/>
       <c r="F9" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -6063,109 +5980,103 @@
       <c r="L9" s="2"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="1:13" ht="54">
-      <c r="A10" s="1">
-        <v>14</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="2" t="s">
+    <row r="10" spans="1:13" ht="40.5">
+      <c r="A10" s="27">
         <v>16</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" ht="40.5">
+      <c r="B10" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="29">
+        <v>25</v>
+      </c>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="31"/>
+    </row>
+    <row r="11" spans="1:13" ht="27" hidden="1">
       <c r="A11" s="27">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="28"/>
-      <c r="E11" s="28" t="s">
-        <v>207</v>
-      </c>
+      <c r="E11" s="28"/>
       <c r="F11" s="29" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H11" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="29">
-        <v>25</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="I11" s="29"/>
       <c r="J11" s="29"/>
       <c r="K11" s="29"/>
       <c r="L11" s="29"/>
       <c r="M11" s="31"/>
     </row>
-    <row r="12" spans="1:13" ht="27">
-      <c r="A12" s="27">
-        <v>17</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="F12" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="G12" s="29" t="s">
+    <row r="12" spans="1:13" ht="27" hidden="1">
+      <c r="A12" s="1">
+        <v>18</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="31"/>
-    </row>
-    <row r="13" spans="1:13" ht="27">
+      <c r="H12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" ht="40.5" hidden="1">
       <c r="A13" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="8" t="s">
-        <v>207</v>
-      </c>
+      <c r="E13" s="8"/>
       <c r="F13" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -6173,26 +6084,24 @@
       <c r="L13" s="2"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" ht="40.5">
+    <row r="14" spans="1:13" ht="27" hidden="1">
       <c r="A14" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="8" t="s">
-        <v>207</v>
-      </c>
+      <c r="E14" s="8"/>
       <c r="F14" s="2" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -6200,82 +6109,78 @@
       <c r="L14" s="2"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:13" ht="27">
+    <row r="15" spans="1:13" ht="40.5">
       <c r="A15" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>189</v>
+        <v>230</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I15" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="I15" s="2">
+        <v>22</v>
+      </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:13" ht="40.5">
+    <row r="16" spans="1:13" ht="40.5" hidden="1">
       <c r="A16" s="1">
-        <v>21</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>237</v>
+        <v>22</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>117</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="8" t="s">
-        <v>207</v>
-      </c>
+      <c r="E16" s="8"/>
       <c r="F16" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I16" s="2">
-        <v>20</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="1:13" ht="40.5">
+    <row r="17" spans="1:13" ht="40.5" hidden="1">
       <c r="A17" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>121</v>
+        <v>185</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="8" t="s">
-        <v>207</v>
-      </c>
+      <c r="E17" s="8"/>
       <c r="F17" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -6283,26 +6188,24 @@
       <c r="L17" s="2"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" ht="40.5">
+    <row r="18" spans="1:13" ht="54" hidden="1">
       <c r="A18" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="8" t="s">
-        <v>207</v>
-      </c>
+      <c r="E18" s="8"/>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -6310,26 +6213,24 @@
       <c r="L18" s="2"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="1:13" ht="54">
+    <row r="19" spans="1:13" ht="40.5" hidden="1">
       <c r="A19" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="8" t="s">
-        <v>207</v>
-      </c>
+      <c r="E19" s="8"/>
       <c r="F19" s="2" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -6339,80 +6240,76 @@
     </row>
     <row r="20" spans="1:13" ht="40.5">
       <c r="A20" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="G20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I20" s="2">
         <v>16</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
+      <c r="L20" s="21"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="1:13" ht="40.5">
+    <row r="21" spans="1:13" ht="40.5" hidden="1">
       <c r="A21" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
-      <c r="E21" s="8" t="s">
-        <v>207</v>
-      </c>
+      <c r="E21" s="8"/>
       <c r="F21" s="2" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I21" s="2">
-        <v>10</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-      <c r="L21" s="21"/>
+      <c r="L21" s="2"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:13" ht="40.5">
+    <row r="22" spans="1:13" ht="27" hidden="1">
       <c r="A22" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="8" t="s">
-        <v>207</v>
-      </c>
+      <c r="E22" s="8"/>
       <c r="F22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>197</v>
+        <v>76</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
@@ -6420,26 +6317,24 @@
       <c r="L22" s="2"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:13" ht="27">
+    <row r="23" spans="1:13" ht="27" hidden="1">
       <c r="A23" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="8" t="s">
-        <v>207</v>
-      </c>
+      <c r="E23" s="8"/>
       <c r="F23" s="2" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -6449,257 +6344,245 @@
     </row>
     <row r="24" spans="1:13" ht="27">
       <c r="A24" s="1">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I24" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="I24" s="2">
+        <v>2</v>
+      </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" spans="1:13" ht="27">
+    <row r="25" spans="1:13" ht="40.5">
       <c r="A25" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8" t="s">
-        <v>205</v>
+        <v>259</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="I25" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="1:13" ht="40.5">
+    <row r="26" spans="1:13" ht="54" hidden="1">
       <c r="A26" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
-      <c r="E26" s="8" t="s">
-        <v>205</v>
-      </c>
+      <c r="E26" s="8"/>
       <c r="F26" s="2" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I26" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:13" ht="54">
+    <row r="27" spans="1:13" ht="27" hidden="1">
       <c r="A27" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
-      <c r="E27" s="8" t="s">
-        <v>205</v>
-      </c>
+      <c r="E27" s="8"/>
       <c r="F27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="I27" s="2">
         <v>33</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="I27" s="2">
-        <v>18</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:13" ht="27">
+    <row r="28" spans="1:13" ht="27" hidden="1">
       <c r="A28" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="8" t="s">
-        <v>205</v>
-      </c>
+      <c r="E28" s="8"/>
       <c r="F28" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="I28" s="2">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:13" ht="27">
-      <c r="A29" s="1">
-        <v>39</v>
+    <row r="29" spans="1:13" ht="27" hidden="1">
+      <c r="A29" s="13">
+        <v>40</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
-      <c r="E29" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="E29" s="8"/>
+      <c r="F29" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="I29" s="8">
+        <v>10</v>
+      </c>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="14"/>
+    </row>
+    <row r="30" spans="1:13" ht="27" hidden="1">
+      <c r="A30" s="13">
         <v>42</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="I29" s="2">
-        <v>10</v>
-      </c>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="1:13" ht="27">
-      <c r="A30" s="13">
-        <v>40</v>
-      </c>
       <c r="B30" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
-      <c r="E30" s="8" t="s">
-        <v>205</v>
-      </c>
+      <c r="E30" s="8"/>
       <c r="F30" s="8" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I30" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
       <c r="M30" s="14"/>
     </row>
-    <row r="31" spans="1:13" ht="27">
+    <row r="31" spans="1:13" ht="27" hidden="1">
       <c r="A31" s="13">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
-      <c r="E31" s="8" t="s">
-        <v>205</v>
-      </c>
+      <c r="E31" s="8"/>
       <c r="F31" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I31" s="8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J31" s="8"/>
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
       <c r="M31" s="14"/>
     </row>
-    <row r="32" spans="1:13" ht="27">
+    <row r="32" spans="1:13" ht="54" hidden="1">
       <c r="A32" s="13">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
-      <c r="E32" s="8" t="s">
-        <v>205</v>
-      </c>
+      <c r="E32" s="8"/>
       <c r="F32" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I32" s="8">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
@@ -6708,114 +6591,110 @@
     </row>
     <row r="33" spans="1:13" ht="54">
       <c r="A33" s="13">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="C33" s="8"/>
+        <v>223</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>281</v>
+      </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8" t="s">
-        <v>205</v>
+        <v>259</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I33" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
       <c r="M33" s="14"/>
     </row>
-    <row r="34" spans="1:13" ht="27">
+    <row r="34" spans="1:13" ht="54" hidden="1">
       <c r="A34" s="13">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
-      <c r="E34" s="8" t="s">
-        <v>205</v>
-      </c>
+      <c r="E34" s="8"/>
       <c r="F34" s="8" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="G34" s="8" t="s">
         <v>12</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I34" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
       <c r="M34" s="14"/>
     </row>
-    <row r="35" spans="1:13" ht="54">
+    <row r="35" spans="1:13" ht="27" hidden="1">
       <c r="A35" s="13">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
-      <c r="E35" s="8" t="s">
-        <v>205</v>
-      </c>
+      <c r="E35" s="8"/>
       <c r="F35" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>12</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="I35" s="8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
       <c r="M35" s="14"/>
     </row>
-    <row r="36" spans="1:13" ht="27">
+    <row r="36" spans="1:13" ht="27" hidden="1">
       <c r="A36" s="13">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
-      <c r="E36" s="8" t="s">
-        <v>205</v>
-      </c>
+      <c r="E36" s="8"/>
       <c r="F36" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>12</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="I36" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
@@ -6824,57 +6703,51 @@
     </row>
     <row r="37" spans="1:13" ht="27">
       <c r="A37" s="13">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="8" t="s">
-        <v>205</v>
+        <v>259</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G37" s="8" t="s">
         <v>12</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="I37" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
       <c r="M37" s="14"/>
     </row>
-    <row r="38" spans="1:13" ht="27">
+    <row r="38" spans="1:13" ht="40.5" hidden="1">
       <c r="A38" s="13">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
-      <c r="E38" s="8" t="s">
-        <v>205</v>
-      </c>
+      <c r="E38" s="8"/>
       <c r="F38" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="I38" s="8">
-        <v>3</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
@@ -6882,191 +6755,323 @@
     </row>
     <row r="39" spans="1:13" ht="40.5">
       <c r="A39" s="13">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
+      <c r="D39" s="35" t="s">
+        <v>258</v>
+      </c>
       <c r="E39" s="8" t="s">
-        <v>205</v>
+        <v>259</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="I39" s="8">
-        <v>15</v>
-      </c>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
+        <v>7</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="L39" s="8"/>
       <c r="M39" s="14"/>
     </row>
-    <row r="40" spans="1:13" ht="40.5">
-      <c r="A40" s="13">
-        <v>54</v>
+    <row r="40" spans="1:13" ht="121.5">
+      <c r="A40" s="1">
+        <v>56</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G40" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="D40" s="35" t="s">
+        <v>260</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="8"/>
-      <c r="L40" s="8"/>
-      <c r="M40" s="14"/>
-    </row>
-    <row r="41" spans="1:13" ht="40.5">
-      <c r="A41" s="13">
-        <v>55</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="C41" s="8"/>
-      <c r="D41" s="36" t="s">
+      <c r="H40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="2">
+        <v>18</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L40" s="2"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="1:13" ht="67.5">
+      <c r="A41" s="27">
+        <v>57</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="C41" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G41" s="8" t="s">
+      <c r="D41" s="28"/>
+      <c r="E41" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F41" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="G41" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="H41" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="I41" s="8">
-        <v>10</v>
-      </c>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="L41" s="8"/>
-      <c r="M41" s="14"/>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" s="13"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
+      <c r="H41" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="29">
+        <v>2</v>
+      </c>
+      <c r="J41" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="K41" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="L41" s="30"/>
+      <c r="M41" s="31"/>
+    </row>
+    <row r="42" spans="1:13" ht="94.5">
+      <c r="A42" s="13">
+        <v>58</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>267</v>
+      </c>
       <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8"/>
+      <c r="E42" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="I42" s="8">
+        <v>120</v>
+      </c>
       <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
+      <c r="K42" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="L42" s="8"/>
       <c r="M42" s="14"/>
     </row>
-    <row r="43" spans="1:13">
-      <c r="A43" s="13"/>
-      <c r="B43" s="8"/>
+    <row r="43" spans="1:13" ht="27">
+      <c r="A43" s="13">
+        <v>59</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>270</v>
+      </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
+      <c r="E43" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="I43" s="8">
+        <v>90</v>
+      </c>
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
-      <c r="L43" s="32"/>
+      <c r="L43" s="8"/>
       <c r="M43" s="14"/>
     </row>
-    <row r="44" spans="1:13">
-      <c r="A44" s="13"/>
-      <c r="B44" s="8"/>
+    <row r="44" spans="1:13" ht="27">
+      <c r="A44" s="13">
+        <v>60</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>271</v>
+      </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
+      <c r="E44" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="I44" s="8">
+        <v>20</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="L44" s="8"/>
       <c r="M44" s="14"/>
     </row>
-    <row r="45" spans="1:13">
-      <c r="A45" s="13"/>
-      <c r="B45" s="8"/>
+    <row r="45" spans="1:13" ht="40.5">
+      <c r="A45" s="13">
+        <v>61</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>273</v>
+      </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
+      <c r="E45" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="I45" s="8">
+        <v>100</v>
+      </c>
       <c r="J45" s="8"/>
       <c r="K45" s="8"/>
       <c r="L45" s="8"/>
       <c r="M45" s="14"/>
     </row>
-    <row r="46" spans="1:13">
-      <c r="A46" s="13"/>
-      <c r="B46" s="8"/>
+    <row r="46" spans="1:13" ht="27">
+      <c r="A46" s="13">
+        <v>62</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>275</v>
+      </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
+      <c r="E46" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="I46" s="8">
+        <v>140</v>
+      </c>
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
       <c r="M46" s="14"/>
     </row>
-    <row r="47" spans="1:13">
-      <c r="A47" s="13"/>
-      <c r="B47" s="8"/>
+    <row r="47" spans="1:13" ht="27">
+      <c r="A47" s="13">
+        <v>63</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>277</v>
+      </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
+      <c r="E47" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="I47" s="8">
+        <v>20</v>
+      </c>
       <c r="J47" s="8"/>
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
       <c r="M47" s="14"/>
     </row>
-    <row r="48" spans="1:13">
-      <c r="A48" s="13"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
+    <row r="48" spans="1:13" ht="27">
+      <c r="A48" s="1">
+        <v>64</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>279</v>
+      </c>
       <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8"/>
-      <c r="L48" s="8"/>
-      <c r="M48" s="14"/>
+      <c r="E48" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I48" s="2">
+        <v>4</v>
+      </c>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="3"/>
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="13"/>
@@ -7533,86 +7538,132 @@
       <c r="L79" s="8"/>
       <c r="M79" s="14"/>
     </row>
-    <row r="80" spans="1:13">
-      <c r="A80" s="13"/>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
-      <c r="I80" s="8"/>
-      <c r="J80" s="8"/>
-      <c r="K80" s="8"/>
-      <c r="L80" s="8"/>
-      <c r="M80" s="14"/>
-    </row>
-    <row r="81" spans="1:13" ht="14.25" thickBot="1">
-      <c r="A81" s="15"/>
-      <c r="B81" s="16"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="16"/>
-      <c r="F81" s="16"/>
-      <c r="G81" s="16"/>
-      <c r="H81" s="16"/>
-      <c r="I81" s="16"/>
-      <c r="J81" s="16"/>
-      <c r="K81" s="16"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="17"/>
+    <row r="80" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A80" s="15"/>
+      <c r="B80" s="16"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="16"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="16"/>
+      <c r="H80" s="16"/>
+      <c r="I80" s="16"/>
+      <c r="J80" s="16"/>
+      <c r="K80" s="16"/>
+      <c r="L80" s="16"/>
+      <c r="M80" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M40">
-    <filterColumn colId="4"/>
+  <autoFilter ref="A1:M48">
+    <filterColumn colId="4">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
     <filterColumn colId="6"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:M192">
-    <cfRule type="expression" dxfId="163" priority="5" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:M191">
+    <cfRule type="expression" dxfId="175" priority="21" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="162" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="174" priority="22" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="161" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="173" priority="23" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="160" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="172" priority="24" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A8:M8">
-    <cfRule type="expression" dxfId="159" priority="1" stopIfTrue="1">
-      <formula>$K8="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="158" priority="2" stopIfTrue="1">
-      <formula>$K8="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="157" priority="3" stopIfTrue="1">
-      <formula>$K8="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="156" priority="4" stopIfTrue="1">
-      <formula>OR($K8="CLOSED",$K8="CANCEL")</formula>
+  <conditionalFormatting sqref="A7:M7">
+    <cfRule type="expression" dxfId="171" priority="17" stopIfTrue="1">
+      <formula>$K7="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="170" priority="18" stopIfTrue="1">
+      <formula>$K7="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="169" priority="19" stopIfTrue="1">
+      <formula>$K7="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="168" priority="20" stopIfTrue="1">
+      <formula>OR($K7="CLOSED",$K7="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A40:M40">
+    <cfRule type="expression" dxfId="167" priority="13" stopIfTrue="1">
+      <formula>$K40="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="166" priority="14" stopIfTrue="1">
+      <formula>$K40="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="165" priority="15" stopIfTrue="1">
+      <formula>$K40="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="164" priority="16" stopIfTrue="1">
+      <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A41:M41">
+    <cfRule type="expression" dxfId="163" priority="9" stopIfTrue="1">
+      <formula>$K41="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="162" priority="10" stopIfTrue="1">
+      <formula>$K41="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="161" priority="11" stopIfTrue="1">
+      <formula>$K41="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="160" priority="12" stopIfTrue="1">
+      <formula>OR($K41="CLOSED",$K41="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E41">
+    <cfRule type="expression" dxfId="159" priority="5" stopIfTrue="1">
+      <formula>$K41="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="158" priority="6" stopIfTrue="1">
+      <formula>$K41="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="157" priority="7" stopIfTrue="1">
+      <formula>$K41="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="156" priority="8" stopIfTrue="1">
+      <formula>OR($K41="CLOSED",$K41="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48:M48">
+    <cfRule type="expression" dxfId="155" priority="1" stopIfTrue="1">
+      <formula>$K48="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="154" priority="2" stopIfTrue="1">
+      <formula>$K48="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="153" priority="3" stopIfTrue="1">
+      <formula>$K48="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="152" priority="4" stopIfTrue="1">
+      <formula>OR($K48="CLOSED",$K48="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F81">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F80">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G81">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G80">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K81">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K80">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D41" r:id="rId1"/>
+    <hyperlink ref="D39" r:id="rId1"/>
+    <hyperlink ref="D40" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -7644,10 +7695,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5" t="s">
@@ -7680,15 +7731,15 @@
         <v>55</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E2" s="12"/>
       <c r="F2" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>22</v>
@@ -7700,10 +7751,10 @@
         <v>1</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L2" s="24">
         <v>41680</v>
@@ -7717,30 +7768,30 @@
         <v>49</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I3" s="10">
         <v>1</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L3" s="11">
         <v>41664</v>
@@ -7754,30 +7805,30 @@
         <v>50</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I4" s="10">
         <v>1</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L4" s="11">
         <v>41665</v>
@@ -7791,36 +7842,36 @@
         <v>47</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="26" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E5" s="26"/>
       <c r="F5" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I5" s="10">
         <v>0</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M5" s="20" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="40.5">
@@ -7828,15 +7879,15 @@
         <v>42</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>12</v>
@@ -7848,10 +7899,10 @@
         <v>4</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L6" s="11">
         <v>41662</v>
@@ -7869,7 +7920,7 @@
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="10" t="s">
@@ -7885,10 +7936,10 @@
         <v>4</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L7" s="11">
         <v>41679</v>
@@ -7906,7 +7957,7 @@
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="10" t="s">
@@ -7922,10 +7973,10 @@
         <v>4</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L8" s="11">
         <v>41680</v>
@@ -7939,30 +7990,30 @@
         <v>51</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I9" s="8">
         <v>1</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L9" s="8"/>
       <c r="M9" s="14"/>
@@ -7972,7 +8023,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -7984,16 +8035,16 @@
         <v>22</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I10" s="8">
         <v>3</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L10" s="8"/>
       <c r="M10" s="14"/>
@@ -8007,7 +8058,7 @@
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="2" t="s">
@@ -8023,10 +8074,10 @@
         <v>4</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="3"/>
@@ -8036,28 +8087,28 @@
         <v>48</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I12" s="2">
         <v>14</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="3"/>
@@ -8067,15 +8118,15 @@
         <v>57</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>12</v>
@@ -8085,10 +8136,10 @@
         <v>3</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L13" s="32">
         <v>41688</v>
@@ -8100,15 +8151,15 @@
         <v>1</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -8116,10 +8167,10 @@
         <v>5</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L14" s="21">
         <v>41754</v>
@@ -8133,30 +8184,30 @@
         <v>10</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="33" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E15" s="33"/>
       <c r="F15" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I15" s="2">
         <v>7</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="3"/>
@@ -8166,30 +8217,30 @@
         <v>30</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="I16" s="2">
         <v>4</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="3"/>
@@ -8199,30 +8250,30 @@
         <v>31</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I17" s="2">
         <v>3</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="3"/>
@@ -8232,30 +8283,30 @@
         <v>32</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I18" s="2">
         <v>1</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="3"/>
@@ -8265,30 +8316,30 @@
         <v>28</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I19" s="2">
         <v>3</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="3"/>
@@ -8298,30 +8349,30 @@
         <v>33</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I20" s="2">
         <v>1</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="3"/>
@@ -8331,13 +8382,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>22</v>
@@ -8347,10 +8398,10 @@
         <v>5</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="3"/>
@@ -8360,28 +8411,28 @@
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I22" s="2">
         <v>5</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="3"/>
@@ -8391,28 +8442,28 @@
         <v>15</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I23" s="2">
         <v>5</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="3"/>
@@ -8422,30 +8473,30 @@
         <v>13</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I24" s="2">
         <v>9</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="3"/>
@@ -8455,30 +8506,30 @@
         <v>16</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I25" s="2">
         <v>5</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="3"/>
@@ -8488,30 +8539,30 @@
         <v>34</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I26" s="2">
         <v>5</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="3"/>
@@ -8521,28 +8572,28 @@
         <v>22</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" s="28"/>
       <c r="D27" s="28"/>
       <c r="E27" s="28"/>
       <c r="F27" s="29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G27" s="29" t="s">
         <v>22</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I27" s="29">
         <v>8</v>
       </c>
       <c r="J27" s="29" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K27" s="29" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L27" s="29"/>
       <c r="M27" s="31"/>
@@ -8552,26 +8603,26 @@
         <v>23</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
       <c r="F28" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I28" s="2">
         <v>5</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="3"/>
@@ -8581,13 +8632,13 @@
         <v>12</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
       <c r="F29" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>22</v>
@@ -8600,7 +8651,7 @@
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="3"/>
@@ -8610,20 +8661,20 @@
         <v>18</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
       <c r="F30" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="3"/>
@@ -8633,26 +8684,26 @@
         <v>21</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
       <c r="F31" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I31" s="2">
         <v>15</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="3"/>
@@ -8662,30 +8713,30 @@
         <v>1</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I32" s="2">
         <v>28</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="3"/>
@@ -8695,12 +8746,12 @@
         <v>6</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>14</v>
@@ -8709,16 +8760,16 @@
         <v>22</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I33" s="2">
         <v>8</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="3"/>
@@ -8728,12 +8779,12 @@
         <v>9</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>11</v>
@@ -8742,16 +8793,16 @@
         <v>22</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I34" s="2">
         <v>8</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="3"/>
@@ -8761,30 +8812,30 @@
         <v>15</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
       <c r="E35" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I35" s="2">
         <v>80</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="3"/>
@@ -8794,30 +8845,30 @@
         <v>25</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I36" s="2">
         <v>4</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="3"/>
@@ -8827,32 +8878,32 @@
         <v>11</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I37" s="2">
         <v>3</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" s="3"/>
@@ -8862,32 +8913,32 @@
         <v>27</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I38" s="2">
         <v>3</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L38" s="21">
         <v>41957</v>
@@ -8899,37 +8950,37 @@
         <v>46</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I39" s="8">
         <v>5</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L39" s="32">
         <v>41944</v>
       </c>
-      <c r="M39" s="35">
+      <c r="M39" s="34">
         <v>41953</v>
       </c>
     </row>
@@ -8938,13 +8989,13 @@
         <v>55</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G40" s="8" t="s">
         <v>22</v>
@@ -8952,10 +9003,10 @@
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
       <c r="J40" s="8" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L40" s="8"/>
       <c r="M40" s="14"/>
@@ -8965,13 +9016,13 @@
         <v>53</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>22</v>
@@ -8979,10 +9030,10 @@
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
       <c r="J41" s="8" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L41" s="8"/>
       <c r="M41" s="14"/>
@@ -8992,28 +9043,28 @@
         <v>37</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
       <c r="E42" s="8" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I42" s="2">
         <v>15</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="3"/>
@@ -9023,32 +9074,32 @@
         <v>32</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I43" s="2">
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L43" s="21">
         <v>41949</v>
@@ -9060,30 +9111,30 @@
         <v>33</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
       <c r="E44" s="8" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="I44" s="2">
         <v>5</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="3"/>
@@ -9093,28 +9144,28 @@
         <v>29</v>
       </c>
       <c r="B45" s="28" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C45" s="28"/>
       <c r="D45" s="28"/>
       <c r="E45" s="28"/>
       <c r="F45" s="29" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G45" s="29" t="s">
         <v>12</v>
       </c>
       <c r="H45" s="29" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I45" s="29">
         <v>20</v>
       </c>
       <c r="J45" s="29" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="K45" s="29" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L45" s="29"/>
       <c r="M45" s="31"/>
@@ -9124,30 +9175,30 @@
         <v>30</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C46" s="28"/>
       <c r="D46" s="28" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E46" s="28"/>
       <c r="F46" s="29" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G46" s="29" t="s">
         <v>12</v>
       </c>
       <c r="H46" s="29" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I46" s="29">
         <v>20</v>
       </c>
       <c r="J46" s="29" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K46" s="29" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L46" s="29"/>
       <c r="M46" s="31"/>
@@ -9157,13 +9208,13 @@
         <v>41</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
       <c r="F47" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>12</v>
@@ -9175,10 +9226,10 @@
         <v>2</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L47" s="21"/>
       <c r="M47" s="3"/>
@@ -9188,28 +9239,28 @@
         <v>45</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
       <c r="F48" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I48" s="2">
         <v>15</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="3"/>
@@ -9219,30 +9270,30 @@
         <v>41</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G49" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="I49" s="8">
         <v>5</v>
       </c>
       <c r="J49" s="8"/>
       <c r="K49" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L49" s="8"/>
       <c r="M49" s="14"/>
@@ -9252,14 +9303,14 @@
         <v>52</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>11</v>
@@ -9268,16 +9319,16 @@
         <v>22</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="I50" s="8">
         <v>5</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L50" s="8"/>
       <c r="M50" s="14"/>
@@ -9287,30 +9338,30 @@
         <v>36</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E51" s="8"/>
       <c r="F51" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I51" s="2">
         <v>2</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="3"/>
@@ -9320,30 +9371,30 @@
         <v>46</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E52" s="8"/>
       <c r="F52" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I52" s="2">
         <v>3</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L52" s="21">
         <v>41679</v>
@@ -9352,33 +9403,59 @@
         <v>41679</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
-      <c r="A53" s="1"/>
-      <c r="B53" s="8"/>
+    <row r="53" spans="1:13" ht="54">
+      <c r="A53" s="1">
+        <v>1</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>10</v>
+      </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
+      <c r="F53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
+      <c r="K53" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="L53" s="2"/>
       <c r="M53" s="3"/>
     </row>
-    <row r="54" spans="1:13">
-      <c r="A54" s="1"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
+    <row r="54" spans="1:13" ht="67.5">
+      <c r="A54" s="1">
+        <v>12</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>278</v>
+      </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
+      <c r="F54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
+      <c r="K54" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="L54" s="2"/>
       <c r="M54" s="3"/>
     </row>
@@ -9690,507 +9767,535 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:M9 A32:M37">
-    <cfRule type="expression" dxfId="147" priority="165" stopIfTrue="1">
+    <cfRule type="expression" dxfId="151" priority="173" stopIfTrue="1">
       <formula>$K9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="146" priority="166" stopIfTrue="1">
+    <cfRule type="expression" dxfId="150" priority="174" stopIfTrue="1">
       <formula>$K9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="145" priority="167" stopIfTrue="1">
+    <cfRule type="expression" dxfId="149" priority="175" stopIfTrue="1">
       <formula>$K9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="144" priority="168" stopIfTrue="1">
+    <cfRule type="expression" dxfId="148" priority="176" stopIfTrue="1">
       <formula>OR($K9="CLOSED",$K9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:M10">
-    <cfRule type="expression" dxfId="143" priority="161" stopIfTrue="1">
+    <cfRule type="expression" dxfId="147" priority="169" stopIfTrue="1">
       <formula>$K10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="142" priority="162" stopIfTrue="1">
+    <cfRule type="expression" dxfId="146" priority="170" stopIfTrue="1">
       <formula>$K10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="141" priority="163" stopIfTrue="1">
+    <cfRule type="expression" dxfId="145" priority="171" stopIfTrue="1">
       <formula>$K10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="140" priority="164" stopIfTrue="1">
+    <cfRule type="expression" dxfId="144" priority="172" stopIfTrue="1">
       <formula>OR($K10="CLOSED",$K10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:M11">
-    <cfRule type="expression" dxfId="139" priority="157" stopIfTrue="1">
+    <cfRule type="expression" dxfId="143" priority="165" stopIfTrue="1">
       <formula>$K11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="158" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="166" stopIfTrue="1">
       <formula>$K11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="137" priority="159" stopIfTrue="1">
+    <cfRule type="expression" dxfId="141" priority="167" stopIfTrue="1">
       <formula>$K11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="160" stopIfTrue="1">
+    <cfRule type="expression" dxfId="140" priority="168" stopIfTrue="1">
       <formula>OR($K11="CLOSED",$K11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:M12">
-    <cfRule type="expression" dxfId="135" priority="153" stopIfTrue="1">
+    <cfRule type="expression" dxfId="139" priority="161" stopIfTrue="1">
       <formula>$K12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="154" stopIfTrue="1">
+    <cfRule type="expression" dxfId="138" priority="162" stopIfTrue="1">
       <formula>$K12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="133" priority="155" stopIfTrue="1">
+    <cfRule type="expression" dxfId="137" priority="163" stopIfTrue="1">
       <formula>$K12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="156" stopIfTrue="1">
+    <cfRule type="expression" dxfId="136" priority="164" stopIfTrue="1">
       <formula>OR($K12="CLOSED",$K12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:M13">
-    <cfRule type="expression" dxfId="131" priority="149" stopIfTrue="1">
+    <cfRule type="expression" dxfId="135" priority="157" stopIfTrue="1">
       <formula>$K13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="150" stopIfTrue="1">
+    <cfRule type="expression" dxfId="134" priority="158" stopIfTrue="1">
       <formula>$K13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="151" stopIfTrue="1">
+    <cfRule type="expression" dxfId="133" priority="159" stopIfTrue="1">
       <formula>$K13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="128" priority="152" stopIfTrue="1">
+    <cfRule type="expression" dxfId="132" priority="160" stopIfTrue="1">
       <formula>OR($K13="CLOSED",$K13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:M14">
-    <cfRule type="expression" dxfId="127" priority="145" stopIfTrue="1">
+    <cfRule type="expression" dxfId="131" priority="153" stopIfTrue="1">
       <formula>$K14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="146" stopIfTrue="1">
+    <cfRule type="expression" dxfId="130" priority="154" stopIfTrue="1">
       <formula>$K14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="147" stopIfTrue="1">
+    <cfRule type="expression" dxfId="129" priority="155" stopIfTrue="1">
       <formula>$K14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="148" stopIfTrue="1">
+    <cfRule type="expression" dxfId="128" priority="156" stopIfTrue="1">
       <formula>OR($K14="CLOSED",$K14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:M15">
-    <cfRule type="expression" dxfId="123" priority="141" stopIfTrue="1">
+    <cfRule type="expression" dxfId="127" priority="149" stopIfTrue="1">
       <formula>$K15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="142" stopIfTrue="1">
+    <cfRule type="expression" dxfId="126" priority="150" stopIfTrue="1">
       <formula>$K15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="143" stopIfTrue="1">
+    <cfRule type="expression" dxfId="125" priority="151" stopIfTrue="1">
       <formula>$K15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="144" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="152" stopIfTrue="1">
       <formula>OR($K15="CLOSED",$K15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:M16">
-    <cfRule type="expression" dxfId="119" priority="137" stopIfTrue="1">
+    <cfRule type="expression" dxfId="123" priority="145" stopIfTrue="1">
       <formula>$K16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="138" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="146" stopIfTrue="1">
       <formula>$K16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="139" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="147" stopIfTrue="1">
       <formula>$K16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="140" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="148" stopIfTrue="1">
       <formula>OR($K16="CLOSED",$K16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:M17">
-    <cfRule type="expression" dxfId="115" priority="133" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="141" stopIfTrue="1">
       <formula>$K17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="134" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="142" stopIfTrue="1">
       <formula>$K17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="135" stopIfTrue="1">
+    <cfRule type="expression" dxfId="117" priority="143" stopIfTrue="1">
       <formula>$K17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="136" stopIfTrue="1">
+    <cfRule type="expression" dxfId="116" priority="144" stopIfTrue="1">
       <formula>OR($K17="CLOSED",$K17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:M18">
-    <cfRule type="expression" dxfId="111" priority="129" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="137" stopIfTrue="1">
       <formula>$K18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="130" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="138" stopIfTrue="1">
       <formula>$K18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="131" stopIfTrue="1">
+    <cfRule type="expression" dxfId="113" priority="139" stopIfTrue="1">
       <formula>$K18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="132" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="140" stopIfTrue="1">
       <formula>OR($K18="CLOSED",$K18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:M19">
-    <cfRule type="expression" dxfId="107" priority="125" stopIfTrue="1">
+    <cfRule type="expression" dxfId="111" priority="133" stopIfTrue="1">
       <formula>$K19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="126" stopIfTrue="1">
+    <cfRule type="expression" dxfId="110" priority="134" stopIfTrue="1">
       <formula>$K19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="127" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="135" stopIfTrue="1">
       <formula>$K19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="128" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="136" stopIfTrue="1">
       <formula>OR($K19="CLOSED",$K19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:M20">
-    <cfRule type="expression" dxfId="103" priority="121" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="129" stopIfTrue="1">
       <formula>$K20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="122" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="130" stopIfTrue="1">
       <formula>$K20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="123" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="131" stopIfTrue="1">
       <formula>$K20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="124" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="132" stopIfTrue="1">
       <formula>OR($K20="CLOSED",$K20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:M21">
-    <cfRule type="expression" dxfId="99" priority="117" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="125" stopIfTrue="1">
       <formula>$K21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="118" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="126" stopIfTrue="1">
       <formula>$K21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="119" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="127" stopIfTrue="1">
       <formula>$K21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="120" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="128" stopIfTrue="1">
       <formula>OR($K21="CLOSED",$K21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:M23">
-    <cfRule type="expression" dxfId="95" priority="113" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="121" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="114" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="122" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="115" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="123" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="116" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="124" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:I22">
-    <cfRule type="expression" dxfId="91" priority="109" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="117" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="110" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="118" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="111" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="119" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="112" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="120" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="87" priority="105" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="113" stopIfTrue="1">
       <formula>$K23="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="106" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="114" stopIfTrue="1">
       <formula>$K23="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="107" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="115" stopIfTrue="1">
       <formula>$K23="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="108" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="116" stopIfTrue="1">
       <formula>OR($K23="CLOSED",$K23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:M25">
-    <cfRule type="expression" dxfId="83" priority="101" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="109" stopIfTrue="1">
       <formula>$K24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="102" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="110" stopIfTrue="1">
       <formula>$K24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="103" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="111" stopIfTrue="1">
       <formula>$K24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="104" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="112" stopIfTrue="1">
       <formula>OR($K24="CLOSED",$K24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="79" priority="97" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="105" stopIfTrue="1">
       <formula>$K25="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="98" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="106" stopIfTrue="1">
       <formula>$K25="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="99" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="107" stopIfTrue="1">
       <formula>$K25="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="100" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="108" stopIfTrue="1">
       <formula>OR($K25="CLOSED",$K25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:M26">
-    <cfRule type="expression" dxfId="75" priority="93" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="101" stopIfTrue="1">
       <formula>$K26="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="94" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="102" stopIfTrue="1">
       <formula>$K26="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="95" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="103" stopIfTrue="1">
       <formula>$K26="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="96" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="104" stopIfTrue="1">
       <formula>OR($K26="CLOSED",$K26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:M28">
-    <cfRule type="expression" dxfId="71" priority="89" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="97" stopIfTrue="1">
       <formula>$K27="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="98" stopIfTrue="1">
       <formula>$K27="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="91" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="99" stopIfTrue="1">
       <formula>$K27="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="92" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="100" stopIfTrue="1">
       <formula>OR($K27="CLOSED",$K27="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M30">
-    <cfRule type="expression" dxfId="67" priority="85" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="93" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="86" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="94" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="87" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="95" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="88" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="96" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M29">
-    <cfRule type="expression" dxfId="63" priority="81" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="89" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="82" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="90" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="83" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="91" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="84" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="92" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:M31">
-    <cfRule type="expression" dxfId="59" priority="77" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="85" stopIfTrue="1">
       <formula>$K31="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="78" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="86" stopIfTrue="1">
       <formula>$K31="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="79" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="87" stopIfTrue="1">
       <formula>$K31="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="80" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="88" stopIfTrue="1">
       <formula>OR($K31="CLOSED",$K31="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:M38">
-    <cfRule type="expression" dxfId="55" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="57" stopIfTrue="1">
       <formula>$K38="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="58" stopIfTrue="1">
       <formula>$K38="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="59" stopIfTrue="1">
       <formula>$K38="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="60" stopIfTrue="1">
       <formula>OR($K38="CLOSED",$K38="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:M39">
-    <cfRule type="expression" dxfId="51" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="53" stopIfTrue="1">
       <formula>$K39="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="54" stopIfTrue="1">
       <formula>$K39="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="55" stopIfTrue="1">
       <formula>$K39="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="56" stopIfTrue="1">
       <formula>OR($K39="CLOSED",$K39="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:M40">
-    <cfRule type="expression" dxfId="47" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="49" stopIfTrue="1">
       <formula>$K40="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="50" stopIfTrue="1">
       <formula>$K40="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="51" stopIfTrue="1">
       <formula>$K40="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="52" stopIfTrue="1">
       <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:M41">
-    <cfRule type="expression" dxfId="43" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
       <formula>$K41="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
       <formula>$K41="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
       <formula>$K41="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
       <formula>OR($K41="CLOSED",$K41="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:M42">
-    <cfRule type="expression" dxfId="39" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
       <formula>$K42="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
       <formula>$K42="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="43" stopIfTrue="1">
       <formula>$K42="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="44" stopIfTrue="1">
       <formula>OR($K42="CLOSED",$K42="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:M44">
-    <cfRule type="expression" dxfId="35" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="37" stopIfTrue="1">
       <formula>$K43="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="38" stopIfTrue="1">
       <formula>$K43="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="39" stopIfTrue="1">
       <formula>$K43="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="40" stopIfTrue="1">
       <formula>OR($K43="CLOSED",$K43="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45:M46">
-    <cfRule type="expression" dxfId="31" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
       <formula>$K45="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
       <formula>$K45="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
       <formula>$K45="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
       <formula>OR($K45="CLOSED",$K45="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:M47">
-    <cfRule type="expression" dxfId="27" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
       <formula>$K47="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
       <formula>$K47="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="31" stopIfTrue="1">
       <formula>$K47="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
       <formula>OR($K47="CLOSED",$K47="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:M48">
-    <cfRule type="expression" dxfId="23" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
       <formula>$K48="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
       <formula>$K48="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="27" stopIfTrue="1">
       <formula>$K48="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="28" stopIfTrue="1">
       <formula>OR($K48="CLOSED",$K48="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:M49">
-    <cfRule type="expression" dxfId="19" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
       <formula>$K49="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
       <formula>$K49="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
       <formula>$K49="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
       <formula>OR($K49="CLOSED",$K49="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:M50">
-    <cfRule type="expression" dxfId="15" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
       <formula>$K50="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
       <formula>$K50="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
       <formula>$K50="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
       <formula>OR($K50="CLOSED",$K50="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:M51">
-    <cfRule type="expression" dxfId="11" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
       <formula>$K51="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="14" stopIfTrue="1">
       <formula>$K51="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="15" stopIfTrue="1">
       <formula>$K51="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
       <formula>OR($K51="CLOSED",$K51="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:M52">
-    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
       <formula>$K52="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
       <formula>$K52="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
       <formula>$K52="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
       <formula>OR($K52="CLOSED",$K52="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53:M53">
+    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
+      <formula>$K53="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+      <formula>$K53="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+      <formula>$K53="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+      <formula>OR($K53="CLOSED",$K53="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54:M54">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+      <formula>$K54="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+      <formula>$K54="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+      <formula>$K54="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+      <formula>OR($K54="CLOSED",$K54="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="11010" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="9300" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="2014年1季度" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="284">
   <si>
     <r>
       <t>描述</t>
@@ -1299,10 +1299,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2015Q1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">SEQUOIADBMAINSTREAM-742 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1367,11 +1363,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">SequoiaDB业务操作管理（CollectionSpace, Collection, Group, Domain, Record等）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OM</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1398,13 +1389,55 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">OM提供“主机鉴控管理”（主机状态，内存，CPU利用率，磁盘等）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">通过post event到游标的线程，并能激活该线程立即处理
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2015Q2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">OM提供“主机监控管理”（主机状态，内存，CPU利用率，磁盘等）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM HA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SequoiaDB</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>业务操作</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">管理（CollectionSpace, Collection, Group, Domain, Record等，性能监控，扩容减容）
+</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注册成OM业务，能访问自身监控页面</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1412,7 +1445,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1472,6 +1505,15 @@
       <color theme="10"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -4806,8 +4848,12 @@
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="1">
+        <v>30</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>281</v>
+      </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="2"/>
@@ -5778,13 +5824,13 @@
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>13</v>
@@ -5886,7 +5932,7 @@
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>49</v>
@@ -5989,14 +6035,14 @@
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="28"/>
-      <c r="E10" s="28" t="s">
-        <v>259</v>
+      <c r="E10" s="8" t="s">
+        <v>279</v>
       </c>
       <c r="F10" s="29" t="s">
         <v>41</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H10" s="29" t="s">
         <v>45</v>
@@ -6119,13 +6165,13 @@
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>49</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>74</v>
@@ -6248,7 +6294,7 @@
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>49</v>
@@ -6352,7 +6398,7 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>75</v>
@@ -6381,7 +6427,7 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>75</v>
@@ -6597,11 +6643,11 @@
         <v>223</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>75</v>
@@ -6711,7 +6757,7 @@
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>64</v>
@@ -6765,7 +6811,7 @@
         <v>258</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>64</v>
@@ -6780,7 +6826,7 @@
         <v>7</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K39" s="8" t="s">
         <v>58</v>
@@ -6796,13 +6842,13 @@
         <v>83</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D40" s="35" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>14</v>
@@ -6817,7 +6863,7 @@
         <v>18</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>58</v>
@@ -6830,14 +6876,14 @@
         <v>57</v>
       </c>
       <c r="B41" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="C41" s="28" t="s">
         <v>264</v>
-      </c>
-      <c r="C41" s="28" t="s">
-        <v>265</v>
       </c>
       <c r="D41" s="28"/>
       <c r="E41" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F41" s="29" t="s">
         <v>75</v>
@@ -6865,14 +6911,14 @@
         <v>58</v>
       </c>
       <c r="B42" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>266</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>267</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>41</v>
@@ -6881,7 +6927,7 @@
         <v>22</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I42" s="8">
         <v>120</v>
@@ -6898,12 +6944,14 @@
         <v>59</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="C43" s="8"/>
+        <v>269</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>283</v>
+      </c>
       <c r="D43" s="8"/>
       <c r="E43" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>64</v>
@@ -6912,7 +6960,7 @@
         <v>22</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I43" s="8">
         <v>90</v>
@@ -6927,12 +6975,12 @@
         <v>60</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
       <c r="E44" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>64</v>
@@ -6941,13 +6989,13 @@
         <v>22</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I44" s="8">
         <v>20</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K44" s="8" t="s">
         <v>58</v>
@@ -6955,17 +7003,17 @@
       <c r="L44" s="8"/>
       <c r="M44" s="14"/>
     </row>
-    <row r="45" spans="1:13" ht="40.5">
+    <row r="45" spans="1:13" ht="54">
       <c r="A45" s="13">
         <v>61</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
       <c r="E45" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>64</v>
@@ -6974,7 +7022,7 @@
         <v>22</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I45" s="8">
         <v>100</v>
@@ -6989,12 +7037,12 @@
         <v>62</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
       <c r="E46" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>64</v>
@@ -7003,7 +7051,7 @@
         <v>22</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I46" s="8">
         <v>140</v>
@@ -7018,12 +7066,12 @@
         <v>63</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>14</v>
@@ -7032,7 +7080,7 @@
         <v>12</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I47" s="8">
         <v>20</v>
@@ -7050,11 +7098,11 @@
         <v>39</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="8" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>32</v>
@@ -7561,6 +7609,9 @@
       </customFilters>
     </filterColumn>
     <filterColumn colId="6"/>
+    <sortState ref="A2:M48">
+      <sortCondition ref="A1:A48"/>
+    </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M191">
@@ -9438,7 +9489,7 @@
         <v>28</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$M$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2015年'!$A$1:$M$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2015年'!$A$1:$M$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$M$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="286">
   <si>
     <r>
       <t>描述</t>
@@ -1438,6 +1438,14 @@
   </si>
   <si>
     <t>注册成OM业务，能访问自身监控页面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-769 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武赟</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1809,7 +1817,63 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="184">
+  <dxfs count="192">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4538,16 +4602,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M169">
-    <cfRule type="expression" dxfId="183" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="191" priority="1" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="182" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="190" priority="2" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="181" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="189" priority="3" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="180" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="188" priority="4" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5722,16 +5786,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L185">
-    <cfRule type="expression" dxfId="179" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="187" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="178" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="186" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="177" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="185" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="176" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="184" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5756,7 +5820,7 @@
   <sheetPr filterMode="1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -6755,7 +6819,9 @@
         <v>229</v>
       </c>
       <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
+      <c r="D37" s="35" t="s">
+        <v>284</v>
+      </c>
       <c r="E37" s="8" t="s">
         <v>279</v>
       </c>
@@ -6771,8 +6837,12 @@
       <c r="I37" s="8">
         <v>3</v>
       </c>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
+      <c r="J37" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="L37" s="8"/>
       <c r="M37" s="14"/>
     </row>
@@ -6799,156 +6869,150 @@
       <c r="L38" s="8"/>
       <c r="M38" s="14"/>
     </row>
-    <row r="39" spans="1:13" ht="40.5">
-      <c r="A39" s="13">
-        <v>55</v>
+    <row r="39" spans="1:13" ht="121.5">
+      <c r="A39" s="1">
+        <v>56</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="C39" s="8"/>
+        <v>83</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>262</v>
+      </c>
       <c r="D39" s="35" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="F39" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G39" s="8" t="s">
+      <c r="F39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H39" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="I39" s="8">
-        <v>7</v>
-      </c>
-      <c r="J39" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="K39" s="8" t="s">
+      <c r="H39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="2">
+        <v>18</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="K39" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L39" s="8"/>
-      <c r="M39" s="14"/>
-    </row>
-    <row r="40" spans="1:13" ht="121.5">
-      <c r="A40" s="1">
-        <v>56</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="D40" s="35" t="s">
-        <v>259</v>
-      </c>
+      <c r="L39" s="2"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="1:13" ht="67.5">
+      <c r="A40" s="27">
+        <v>57</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="D40" s="28"/>
       <c r="E40" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="F40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40" s="2" t="s">
+      <c r="F40" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="G40" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="H40" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I40" s="2">
-        <v>18</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="K40" s="2" t="s">
+      <c r="H40" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="I40" s="29">
+        <v>2</v>
+      </c>
+      <c r="J40" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="K40" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L40" s="2"/>
-      <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="1:13" ht="67.5">
-      <c r="A41" s="27">
-        <v>57</v>
-      </c>
-      <c r="B41" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="C41" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="D41" s="28"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="31"/>
+    </row>
+    <row r="41" spans="1:13" ht="94.5">
+      <c r="A41" s="13">
+        <v>58</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="D41" s="8"/>
       <c r="E41" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="F41" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="G41" s="29" t="s">
+      <c r="F41" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G41" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H41" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="I41" s="29">
-        <v>2</v>
-      </c>
-      <c r="J41" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="K41" s="29" t="s">
+      <c r="H41" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="I41" s="8">
+        <v>120</v>
+      </c>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="L41" s="30"/>
-      <c r="M41" s="31"/>
-    </row>
-    <row r="42" spans="1:13" ht="94.5">
+      <c r="L41" s="8"/>
+      <c r="M41" s="14"/>
+    </row>
+    <row r="42" spans="1:13" ht="27">
       <c r="A42" s="13">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8" t="s">
         <v>279</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I42" s="8">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J42" s="8"/>
-      <c r="K42" s="8" t="s">
-        <v>58</v>
-      </c>
+      <c r="K42" s="8"/>
       <c r="L42" s="8"/>
       <c r="M42" s="14"/>
     </row>
     <row r="43" spans="1:13" ht="27">
       <c r="A43" s="13">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>283</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="C43" s="8"/>
       <c r="D43" s="8"/>
       <c r="E43" s="8" t="s">
         <v>279</v>
@@ -6960,22 +7024,26 @@
         <v>22</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I43" s="8">
-        <v>90</v>
-      </c>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
+        <v>20</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="L43" s="8"/>
       <c r="M43" s="14"/>
     </row>
-    <row r="44" spans="1:13" ht="27">
+    <row r="44" spans="1:13" ht="54">
       <c r="A44" s="13">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -6989,26 +7057,22 @@
         <v>22</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I44" s="8">
-        <v>20</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>58</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
       <c r="L44" s="8"/>
       <c r="M44" s="14"/>
     </row>
-    <row r="45" spans="1:13" ht="54">
+    <row r="45" spans="1:13" ht="27">
       <c r="A45" s="13">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
@@ -7022,10 +7086,10 @@
         <v>22</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I45" s="8">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="J45" s="8"/>
       <c r="K45" s="8"/>
@@ -7034,10 +7098,10 @@
     </row>
     <row r="46" spans="1:13" ht="27">
       <c r="A46" s="13">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
@@ -7045,16 +7109,16 @@
         <v>279</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="I46" s="8">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
@@ -7062,64 +7126,50 @@
       <c r="M46" s="14"/>
     </row>
     <row r="47" spans="1:13" ht="27">
-      <c r="A47" s="13">
-        <v>63</v>
+      <c r="A47" s="1">
+        <v>64</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="C47" s="8"/>
+        <v>39</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>277</v>
+      </c>
       <c r="D47" s="8"/>
       <c r="E47" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="F47" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="I47" s="8">
-        <v>20</v>
-      </c>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="14"/>
-    </row>
-    <row r="48" spans="1:13" ht="27">
-      <c r="A48" s="1">
-        <v>64</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>277</v>
-      </c>
+      <c r="F47" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I47" s="2">
+        <v>4</v>
+      </c>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="13"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
       <c r="D48" s="8"/>
-      <c r="E48" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I48" s="2">
-        <v>4</v>
-      </c>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
-      <c r="M48" s="3"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="14"/>
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="13"/>
@@ -7571,38 +7621,23 @@
       <c r="L78" s="8"/>
       <c r="M78" s="14"/>
     </row>
-    <row r="79" spans="1:13">
-      <c r="A79" s="13"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8"/>
-      <c r="J79" s="8"/>
-      <c r="K79" s="8"/>
-      <c r="L79" s="8"/>
-      <c r="M79" s="14"/>
-    </row>
-    <row r="80" spans="1:13" ht="14.25" thickBot="1">
-      <c r="A80" s="15"/>
-      <c r="B80" s="16"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="16"/>
-      <c r="H80" s="16"/>
-      <c r="I80" s="16"/>
-      <c r="J80" s="16"/>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="17"/>
+    <row r="79" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A79" s="15"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16"/>
+      <c r="H79" s="16"/>
+      <c r="I79" s="16"/>
+      <c r="J79" s="16"/>
+      <c r="K79" s="16"/>
+      <c r="L79" s="16"/>
+      <c r="M79" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M48">
+  <autoFilter ref="A1:M47">
     <filterColumn colId="4">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7614,104 +7649,104 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:M191">
-    <cfRule type="expression" dxfId="175" priority="21" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:M190">
+    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="174" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="172" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:M7">
-    <cfRule type="expression" dxfId="171" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
       <formula>$K7="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="170" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
       <formula>$K7="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="169" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
       <formula>$K7="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="168" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
       <formula>OR($K7="CLOSED",$K7="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:M39">
+    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
+      <formula>$K39="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="14" stopIfTrue="1">
+      <formula>$K39="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="15" stopIfTrue="1">
+      <formula>$K39="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
+      <formula>OR($K39="CLOSED",$K39="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:M40">
-    <cfRule type="expression" dxfId="167" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
       <formula>$K40="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="166" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
       <formula>$K40="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="165" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
       <formula>$K40="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="164" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
       <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A41:M41">
-    <cfRule type="expression" dxfId="163" priority="9" stopIfTrue="1">
-      <formula>$K41="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="162" priority="10" stopIfTrue="1">
-      <formula>$K41="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="161" priority="11" stopIfTrue="1">
-      <formula>$K41="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="160" priority="12" stopIfTrue="1">
-      <formula>OR($K41="CLOSED",$K41="CANCEL")</formula>
+  <conditionalFormatting sqref="E40">
+    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
+      <formula>$K40="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+      <formula>$K40="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+      <formula>$K40="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+      <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E41">
-    <cfRule type="expression" dxfId="159" priority="5" stopIfTrue="1">
-      <formula>$K41="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="158" priority="6" stopIfTrue="1">
-      <formula>$K41="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="157" priority="7" stopIfTrue="1">
-      <formula>$K41="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="156" priority="8" stopIfTrue="1">
-      <formula>OR($K41="CLOSED",$K41="CANCEL")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A48:M48">
-    <cfRule type="expression" dxfId="155" priority="1" stopIfTrue="1">
-      <formula>$K48="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="154" priority="2" stopIfTrue="1">
-      <formula>$K48="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="153" priority="3" stopIfTrue="1">
-      <formula>$K48="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="152" priority="4" stopIfTrue="1">
-      <formula>OR($K48="CLOSED",$K48="CANCEL")</formula>
+  <conditionalFormatting sqref="A47:M47">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+      <formula>$K47="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+      <formula>$K47="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+      <formula>$K47="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+      <formula>OR($K47="CLOSED",$K47="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F80">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F79">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G80">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G79">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K80">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K79">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D39" r:id="rId1"/>
-    <hyperlink ref="D40" r:id="rId2"/>
+    <hyperlink ref="D37" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
@@ -9510,20 +9545,40 @@
       <c r="L54" s="2"/>
       <c r="M54" s="3"/>
     </row>
-    <row r="55" spans="1:13">
-      <c r="A55" s="1"/>
-      <c r="B55" s="8"/>
+    <row r="55" spans="1:13" ht="40.5">
+      <c r="A55" s="13">
+        <v>55</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>256</v>
+      </c>
       <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-      <c r="L55" s="2"/>
-      <c r="M55" s="3"/>
+      <c r="D55" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="I55" s="8">
+        <v>7</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L55" s="8"/>
+      <c r="M55" s="14"/>
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="1"/>
@@ -9818,535 +9873,549 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:M9 A32:M37">
-    <cfRule type="expression" dxfId="151" priority="173" stopIfTrue="1">
+    <cfRule type="expression" dxfId="179" priority="177" stopIfTrue="1">
       <formula>$K9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="150" priority="174" stopIfTrue="1">
+    <cfRule type="expression" dxfId="178" priority="178" stopIfTrue="1">
       <formula>$K9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="149" priority="175" stopIfTrue="1">
+    <cfRule type="expression" dxfId="177" priority="179" stopIfTrue="1">
       <formula>$K9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="148" priority="176" stopIfTrue="1">
+    <cfRule type="expression" dxfId="176" priority="180" stopIfTrue="1">
       <formula>OR($K9="CLOSED",$K9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:M10">
-    <cfRule type="expression" dxfId="147" priority="169" stopIfTrue="1">
+    <cfRule type="expression" dxfId="175" priority="173" stopIfTrue="1">
       <formula>$K10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="146" priority="170" stopIfTrue="1">
+    <cfRule type="expression" dxfId="174" priority="174" stopIfTrue="1">
       <formula>$K10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="145" priority="171" stopIfTrue="1">
+    <cfRule type="expression" dxfId="173" priority="175" stopIfTrue="1">
       <formula>$K10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="144" priority="172" stopIfTrue="1">
+    <cfRule type="expression" dxfId="172" priority="176" stopIfTrue="1">
       <formula>OR($K10="CLOSED",$K10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:M11">
-    <cfRule type="expression" dxfId="143" priority="165" stopIfTrue="1">
+    <cfRule type="expression" dxfId="171" priority="169" stopIfTrue="1">
       <formula>$K11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="142" priority="166" stopIfTrue="1">
+    <cfRule type="expression" dxfId="170" priority="170" stopIfTrue="1">
       <formula>$K11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="141" priority="167" stopIfTrue="1">
+    <cfRule type="expression" dxfId="169" priority="171" stopIfTrue="1">
       <formula>$K11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="140" priority="168" stopIfTrue="1">
+    <cfRule type="expression" dxfId="168" priority="172" stopIfTrue="1">
       <formula>OR($K11="CLOSED",$K11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:M12">
-    <cfRule type="expression" dxfId="139" priority="161" stopIfTrue="1">
+    <cfRule type="expression" dxfId="167" priority="165" stopIfTrue="1">
       <formula>$K12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="162" stopIfTrue="1">
+    <cfRule type="expression" dxfId="166" priority="166" stopIfTrue="1">
       <formula>$K12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="137" priority="163" stopIfTrue="1">
+    <cfRule type="expression" dxfId="165" priority="167" stopIfTrue="1">
       <formula>$K12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="164" stopIfTrue="1">
+    <cfRule type="expression" dxfId="164" priority="168" stopIfTrue="1">
       <formula>OR($K12="CLOSED",$K12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:M13">
-    <cfRule type="expression" dxfId="135" priority="157" stopIfTrue="1">
+    <cfRule type="expression" dxfId="163" priority="161" stopIfTrue="1">
       <formula>$K13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="158" stopIfTrue="1">
+    <cfRule type="expression" dxfId="162" priority="162" stopIfTrue="1">
       <formula>$K13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="133" priority="159" stopIfTrue="1">
+    <cfRule type="expression" dxfId="161" priority="163" stopIfTrue="1">
       <formula>$K13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="160" stopIfTrue="1">
+    <cfRule type="expression" dxfId="160" priority="164" stopIfTrue="1">
       <formula>OR($K13="CLOSED",$K13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:M14">
-    <cfRule type="expression" dxfId="131" priority="153" stopIfTrue="1">
+    <cfRule type="expression" dxfId="159" priority="157" stopIfTrue="1">
       <formula>$K14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="154" stopIfTrue="1">
+    <cfRule type="expression" dxfId="158" priority="158" stopIfTrue="1">
       <formula>$K14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="155" stopIfTrue="1">
+    <cfRule type="expression" dxfId="157" priority="159" stopIfTrue="1">
       <formula>$K14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="128" priority="156" stopIfTrue="1">
+    <cfRule type="expression" dxfId="156" priority="160" stopIfTrue="1">
       <formula>OR($K14="CLOSED",$K14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:M15">
-    <cfRule type="expression" dxfId="127" priority="149" stopIfTrue="1">
+    <cfRule type="expression" dxfId="155" priority="153" stopIfTrue="1">
       <formula>$K15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="150" stopIfTrue="1">
+    <cfRule type="expression" dxfId="154" priority="154" stopIfTrue="1">
       <formula>$K15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="151" stopIfTrue="1">
+    <cfRule type="expression" dxfId="153" priority="155" stopIfTrue="1">
       <formula>$K15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="152" stopIfTrue="1">
+    <cfRule type="expression" dxfId="152" priority="156" stopIfTrue="1">
       <formula>OR($K15="CLOSED",$K15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:M16">
-    <cfRule type="expression" dxfId="123" priority="145" stopIfTrue="1">
+    <cfRule type="expression" dxfId="151" priority="149" stopIfTrue="1">
       <formula>$K16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="146" stopIfTrue="1">
+    <cfRule type="expression" dxfId="150" priority="150" stopIfTrue="1">
       <formula>$K16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="147" stopIfTrue="1">
+    <cfRule type="expression" dxfId="149" priority="151" stopIfTrue="1">
       <formula>$K16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="148" stopIfTrue="1">
+    <cfRule type="expression" dxfId="148" priority="152" stopIfTrue="1">
       <formula>OR($K16="CLOSED",$K16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:M17">
-    <cfRule type="expression" dxfId="119" priority="141" stopIfTrue="1">
+    <cfRule type="expression" dxfId="147" priority="145" stopIfTrue="1">
       <formula>$K17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="142" stopIfTrue="1">
+    <cfRule type="expression" dxfId="146" priority="146" stopIfTrue="1">
       <formula>$K17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="143" stopIfTrue="1">
+    <cfRule type="expression" dxfId="145" priority="147" stopIfTrue="1">
       <formula>$K17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="144" stopIfTrue="1">
+    <cfRule type="expression" dxfId="144" priority="148" stopIfTrue="1">
       <formula>OR($K17="CLOSED",$K17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:M18">
-    <cfRule type="expression" dxfId="115" priority="137" stopIfTrue="1">
+    <cfRule type="expression" dxfId="143" priority="141" stopIfTrue="1">
       <formula>$K18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="138" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="142" stopIfTrue="1">
       <formula>$K18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="139" stopIfTrue="1">
+    <cfRule type="expression" dxfId="141" priority="143" stopIfTrue="1">
       <formula>$K18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="140" stopIfTrue="1">
+    <cfRule type="expression" dxfId="140" priority="144" stopIfTrue="1">
       <formula>OR($K18="CLOSED",$K18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:M19">
-    <cfRule type="expression" dxfId="111" priority="133" stopIfTrue="1">
+    <cfRule type="expression" dxfId="139" priority="137" stopIfTrue="1">
       <formula>$K19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="134" stopIfTrue="1">
+    <cfRule type="expression" dxfId="138" priority="138" stopIfTrue="1">
       <formula>$K19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="135" stopIfTrue="1">
+    <cfRule type="expression" dxfId="137" priority="139" stopIfTrue="1">
       <formula>$K19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="136" stopIfTrue="1">
+    <cfRule type="expression" dxfId="136" priority="140" stopIfTrue="1">
       <formula>OR($K19="CLOSED",$K19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:M20">
-    <cfRule type="expression" dxfId="107" priority="129" stopIfTrue="1">
+    <cfRule type="expression" dxfId="135" priority="133" stopIfTrue="1">
       <formula>$K20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="130" stopIfTrue="1">
+    <cfRule type="expression" dxfId="134" priority="134" stopIfTrue="1">
       <formula>$K20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="131" stopIfTrue="1">
+    <cfRule type="expression" dxfId="133" priority="135" stopIfTrue="1">
       <formula>$K20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="132" stopIfTrue="1">
+    <cfRule type="expression" dxfId="132" priority="136" stopIfTrue="1">
       <formula>OR($K20="CLOSED",$K20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:M21">
-    <cfRule type="expression" dxfId="103" priority="125" stopIfTrue="1">
+    <cfRule type="expression" dxfId="131" priority="129" stopIfTrue="1">
       <formula>$K21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="126" stopIfTrue="1">
+    <cfRule type="expression" dxfId="130" priority="130" stopIfTrue="1">
       <formula>$K21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="127" stopIfTrue="1">
+    <cfRule type="expression" dxfId="129" priority="131" stopIfTrue="1">
       <formula>$K21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="128" stopIfTrue="1">
+    <cfRule type="expression" dxfId="128" priority="132" stopIfTrue="1">
       <formula>OR($K21="CLOSED",$K21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:M23">
-    <cfRule type="expression" dxfId="99" priority="121" stopIfTrue="1">
+    <cfRule type="expression" dxfId="127" priority="125" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="122" stopIfTrue="1">
+    <cfRule type="expression" dxfId="126" priority="126" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="123" stopIfTrue="1">
+    <cfRule type="expression" dxfId="125" priority="127" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="124" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="128" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:I22">
-    <cfRule type="expression" dxfId="95" priority="117" stopIfTrue="1">
+    <cfRule type="expression" dxfId="123" priority="121" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="118" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="122" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="119" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="123" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="120" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="124" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="91" priority="113" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="117" stopIfTrue="1">
       <formula>$K23="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="114" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="118" stopIfTrue="1">
       <formula>$K23="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="115" stopIfTrue="1">
+    <cfRule type="expression" dxfId="117" priority="119" stopIfTrue="1">
       <formula>$K23="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="116" stopIfTrue="1">
+    <cfRule type="expression" dxfId="116" priority="120" stopIfTrue="1">
       <formula>OR($K23="CLOSED",$K23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:M25">
-    <cfRule type="expression" dxfId="87" priority="109" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="113" stopIfTrue="1">
       <formula>$K24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="110" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="114" stopIfTrue="1">
       <formula>$K24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="111" stopIfTrue="1">
+    <cfRule type="expression" dxfId="113" priority="115" stopIfTrue="1">
       <formula>$K24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="112" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="116" stopIfTrue="1">
       <formula>OR($K24="CLOSED",$K24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="83" priority="105" stopIfTrue="1">
+    <cfRule type="expression" dxfId="111" priority="109" stopIfTrue="1">
       <formula>$K25="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="106" stopIfTrue="1">
+    <cfRule type="expression" dxfId="110" priority="110" stopIfTrue="1">
       <formula>$K25="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="107" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="111" stopIfTrue="1">
       <formula>$K25="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="108" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="112" stopIfTrue="1">
       <formula>OR($K25="CLOSED",$K25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:M26">
-    <cfRule type="expression" dxfId="79" priority="101" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="105" stopIfTrue="1">
       <formula>$K26="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="102" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="106" stopIfTrue="1">
       <formula>$K26="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="103" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="107" stopIfTrue="1">
       <formula>$K26="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="104" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="108" stopIfTrue="1">
       <formula>OR($K26="CLOSED",$K26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:M28">
-    <cfRule type="expression" dxfId="75" priority="97" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="101" stopIfTrue="1">
       <formula>$K27="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="98" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="102" stopIfTrue="1">
       <formula>$K27="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="99" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="103" stopIfTrue="1">
       <formula>$K27="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="100" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="104" stopIfTrue="1">
       <formula>OR($K27="CLOSED",$K27="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M30">
-    <cfRule type="expression" dxfId="71" priority="93" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="97" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="94" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="98" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="95" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="99" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="96" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="100" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M29">
-    <cfRule type="expression" dxfId="67" priority="89" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="93" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="94" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="91" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="95" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="92" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="96" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:M31">
-    <cfRule type="expression" dxfId="63" priority="85" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="89" stopIfTrue="1">
       <formula>$K31="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="86" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="90" stopIfTrue="1">
       <formula>$K31="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="87" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="91" stopIfTrue="1">
       <formula>$K31="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="88" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="92" stopIfTrue="1">
       <formula>OR($K31="CLOSED",$K31="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:M38">
-    <cfRule type="expression" dxfId="59" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="61" stopIfTrue="1">
       <formula>$K38="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="62" stopIfTrue="1">
       <formula>$K38="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="63" stopIfTrue="1">
       <formula>$K38="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="64" stopIfTrue="1">
       <formula>OR($K38="CLOSED",$K38="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:M39">
-    <cfRule type="expression" dxfId="55" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="57" stopIfTrue="1">
       <formula>$K39="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="58" stopIfTrue="1">
       <formula>$K39="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="59" stopIfTrue="1">
       <formula>$K39="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="60" stopIfTrue="1">
       <formula>OR($K39="CLOSED",$K39="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:M40">
-    <cfRule type="expression" dxfId="51" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="53" stopIfTrue="1">
       <formula>$K40="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="54" stopIfTrue="1">
       <formula>$K40="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="55" stopIfTrue="1">
       <formula>$K40="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="56" stopIfTrue="1">
       <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:M41">
-    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="49" stopIfTrue="1">
       <formula>$K41="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="50" stopIfTrue="1">
       <formula>$K41="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="51" stopIfTrue="1">
       <formula>$K41="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="52" stopIfTrue="1">
       <formula>OR($K41="CLOSED",$K41="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:M42">
-    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="45" stopIfTrue="1">
       <formula>$K42="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="46" stopIfTrue="1">
       <formula>$K42="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="47" stopIfTrue="1">
       <formula>$K42="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="48" stopIfTrue="1">
       <formula>OR($K42="CLOSED",$K42="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:M44">
-    <cfRule type="expression" dxfId="39" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="41" stopIfTrue="1">
       <formula>$K43="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="42" stopIfTrue="1">
       <formula>$K43="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="43" stopIfTrue="1">
       <formula>$K43="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="44" stopIfTrue="1">
       <formula>OR($K43="CLOSED",$K43="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45:M46">
-    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="37" stopIfTrue="1">
       <formula>$K45="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="38" stopIfTrue="1">
       <formula>$K45="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="39" stopIfTrue="1">
       <formula>$K45="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="40" stopIfTrue="1">
       <formula>OR($K45="CLOSED",$K45="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:M47">
-    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="33" stopIfTrue="1">
       <formula>$K47="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="34" stopIfTrue="1">
       <formula>$K47="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="35" stopIfTrue="1">
       <formula>$K47="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="36" stopIfTrue="1">
       <formula>OR($K47="CLOSED",$K47="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:M48">
-    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="29" stopIfTrue="1">
       <formula>$K48="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="30" stopIfTrue="1">
       <formula>$K48="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="31" stopIfTrue="1">
       <formula>$K48="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="32" stopIfTrue="1">
       <formula>OR($K48="CLOSED",$K48="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:M49">
-    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="25" stopIfTrue="1">
       <formula>$K49="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="26" stopIfTrue="1">
       <formula>$K49="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="27" stopIfTrue="1">
       <formula>$K49="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="28" stopIfTrue="1">
       <formula>OR($K49="CLOSED",$K49="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:M50">
-    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="21" stopIfTrue="1">
       <formula>$K50="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="22" stopIfTrue="1">
       <formula>$K50="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="23" stopIfTrue="1">
       <formula>$K50="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="24" stopIfTrue="1">
       <formula>OR($K50="CLOSED",$K50="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:M51">
-    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="17" stopIfTrue="1">
       <formula>$K51="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="18" stopIfTrue="1">
       <formula>$K51="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="19" stopIfTrue="1">
       <formula>$K51="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="20" stopIfTrue="1">
       <formula>OR($K51="CLOSED",$K51="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:M52">
-    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="13" stopIfTrue="1">
       <formula>$K52="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="14" stopIfTrue="1">
       <formula>$K52="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="15" stopIfTrue="1">
       <formula>$K52="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="16" stopIfTrue="1">
       <formula>OR($K52="CLOSED",$K52="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:M53">
-    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="9" stopIfTrue="1">
       <formula>$K53="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="10" stopIfTrue="1">
       <formula>$K53="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="11" stopIfTrue="1">
       <formula>$K53="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="12" stopIfTrue="1">
       <formula>OR($K53="CLOSED",$K53="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:M54">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="5" stopIfTrue="1">
       <formula>$K54="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="6" stopIfTrue="1">
       <formula>$K54="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="7" stopIfTrue="1">
       <formula>$K54="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="8" stopIfTrue="1">
       <formula>OR($K54="CLOSED",$K54="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55:M55">
+    <cfRule type="expression" dxfId="27" priority="1" stopIfTrue="1">
+      <formula>$K55="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="2" stopIfTrue="1">
+      <formula>$K55="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="3" stopIfTrue="1">
+      <formula>$K55="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="4" stopIfTrue="1">
+      <formula>OR($K55="CLOSED",$K55="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -10360,7 +10429,10 @@
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="D55" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId2"/>
 </worksheet>
 </file>
--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="9300" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="9300"/>
   </bookViews>
   <sheets>
     <sheet name="2014年1季度" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="290">
   <si>
     <r>
       <t>描述</t>
@@ -1446,6 +1446,22 @@
   </si>
   <si>
     <t>武赟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林友滨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何嘉文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴易达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李伟超</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1817,35 +1833,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="192">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="188">
     <dxf>
       <fill>
         <patternFill>
@@ -3667,8 +3655,12 @@
       <c r="I7" s="2">
         <v>8</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="3"/>
     </row>
@@ -4602,16 +4594,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M169">
-    <cfRule type="expression" dxfId="191" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="187" priority="1" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="190" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="186" priority="2" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="189" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="185" priority="3" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="188" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="184" priority="4" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5786,16 +5778,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L185">
-    <cfRule type="expression" dxfId="187" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="183" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="186" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="182" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="185" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="181" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="184" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="180" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7000,8 +6992,12 @@
       <c r="I42" s="8">
         <v>90</v>
       </c>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
+      <c r="J42" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="L42" s="8"/>
       <c r="M42" s="14"/>
     </row>
@@ -7062,8 +7058,12 @@
       <c r="I44" s="8">
         <v>100</v>
       </c>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
+      <c r="J44" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="L44" s="8"/>
       <c r="M44" s="14"/>
     </row>
@@ -7091,8 +7091,12 @@
       <c r="I45" s="8">
         <v>140</v>
       </c>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
+      <c r="J45" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="L45" s="8"/>
       <c r="M45" s="14"/>
     </row>
@@ -7650,86 +7654,86 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M190">
-    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="179" priority="21" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="178" priority="22" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="177" priority="23" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="176" priority="24" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:M7">
-    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="175" priority="17" stopIfTrue="1">
       <formula>$K7="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="174" priority="18" stopIfTrue="1">
       <formula>$K7="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="173" priority="19" stopIfTrue="1">
       <formula>$K7="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="172" priority="20" stopIfTrue="1">
       <formula>OR($K7="CLOSED",$K7="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:M39">
-    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="171" priority="13" stopIfTrue="1">
       <formula>$K39="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="170" priority="14" stopIfTrue="1">
       <formula>$K39="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="169" priority="15" stopIfTrue="1">
       <formula>$K39="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="168" priority="16" stopIfTrue="1">
       <formula>OR($K39="CLOSED",$K39="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:M40">
-    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="167" priority="9" stopIfTrue="1">
       <formula>$K40="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="166" priority="10" stopIfTrue="1">
       <formula>$K40="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="165" priority="11" stopIfTrue="1">
       <formula>$K40="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="164" priority="12" stopIfTrue="1">
       <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E40">
-    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="163" priority="5" stopIfTrue="1">
       <formula>$K40="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="162" priority="6" stopIfTrue="1">
       <formula>$K40="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="161" priority="7" stopIfTrue="1">
       <formula>$K40="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="160" priority="8" stopIfTrue="1">
       <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:M47">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="159" priority="1" stopIfTrue="1">
       <formula>$K47="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="158" priority="2" stopIfTrue="1">
       <formula>$K47="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="157" priority="3" stopIfTrue="1">
       <formula>$K47="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="156" priority="4" stopIfTrue="1">
       <formula>OR($K47="CLOSED",$K47="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9873,548 +9877,548 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:M9 A32:M37">
-    <cfRule type="expression" dxfId="179" priority="177" stopIfTrue="1">
+    <cfRule type="expression" dxfId="155" priority="177" stopIfTrue="1">
       <formula>$K9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="178" priority="178" stopIfTrue="1">
+    <cfRule type="expression" dxfId="154" priority="178" stopIfTrue="1">
       <formula>$K9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="177" priority="179" stopIfTrue="1">
+    <cfRule type="expression" dxfId="153" priority="179" stopIfTrue="1">
       <formula>$K9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="176" priority="180" stopIfTrue="1">
+    <cfRule type="expression" dxfId="152" priority="180" stopIfTrue="1">
       <formula>OR($K9="CLOSED",$K9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:M10">
-    <cfRule type="expression" dxfId="175" priority="173" stopIfTrue="1">
+    <cfRule type="expression" dxfId="151" priority="173" stopIfTrue="1">
       <formula>$K10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="174" priority="174" stopIfTrue="1">
+    <cfRule type="expression" dxfId="150" priority="174" stopIfTrue="1">
       <formula>$K10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="175" stopIfTrue="1">
+    <cfRule type="expression" dxfId="149" priority="175" stopIfTrue="1">
       <formula>$K10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="172" priority="176" stopIfTrue="1">
+    <cfRule type="expression" dxfId="148" priority="176" stopIfTrue="1">
       <formula>OR($K10="CLOSED",$K10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:M11">
-    <cfRule type="expression" dxfId="171" priority="169" stopIfTrue="1">
+    <cfRule type="expression" dxfId="147" priority="169" stopIfTrue="1">
       <formula>$K11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="170" priority="170" stopIfTrue="1">
+    <cfRule type="expression" dxfId="146" priority="170" stopIfTrue="1">
       <formula>$K11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="169" priority="171" stopIfTrue="1">
+    <cfRule type="expression" dxfId="145" priority="171" stopIfTrue="1">
       <formula>$K11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="168" priority="172" stopIfTrue="1">
+    <cfRule type="expression" dxfId="144" priority="172" stopIfTrue="1">
       <formula>OR($K11="CLOSED",$K11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:M12">
-    <cfRule type="expression" dxfId="167" priority="165" stopIfTrue="1">
+    <cfRule type="expression" dxfId="143" priority="165" stopIfTrue="1">
       <formula>$K12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="166" priority="166" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="166" stopIfTrue="1">
       <formula>$K12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="165" priority="167" stopIfTrue="1">
+    <cfRule type="expression" dxfId="141" priority="167" stopIfTrue="1">
       <formula>$K12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="164" priority="168" stopIfTrue="1">
+    <cfRule type="expression" dxfId="140" priority="168" stopIfTrue="1">
       <formula>OR($K12="CLOSED",$K12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:M13">
-    <cfRule type="expression" dxfId="163" priority="161" stopIfTrue="1">
+    <cfRule type="expression" dxfId="139" priority="161" stopIfTrue="1">
       <formula>$K13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="162" priority="162" stopIfTrue="1">
+    <cfRule type="expression" dxfId="138" priority="162" stopIfTrue="1">
       <formula>$K13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="161" priority="163" stopIfTrue="1">
+    <cfRule type="expression" dxfId="137" priority="163" stopIfTrue="1">
       <formula>$K13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="160" priority="164" stopIfTrue="1">
+    <cfRule type="expression" dxfId="136" priority="164" stopIfTrue="1">
       <formula>OR($K13="CLOSED",$K13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:M14">
-    <cfRule type="expression" dxfId="159" priority="157" stopIfTrue="1">
+    <cfRule type="expression" dxfId="135" priority="157" stopIfTrue="1">
       <formula>$K14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="158" priority="158" stopIfTrue="1">
+    <cfRule type="expression" dxfId="134" priority="158" stopIfTrue="1">
       <formula>$K14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="157" priority="159" stopIfTrue="1">
+    <cfRule type="expression" dxfId="133" priority="159" stopIfTrue="1">
       <formula>$K14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="156" priority="160" stopIfTrue="1">
+    <cfRule type="expression" dxfId="132" priority="160" stopIfTrue="1">
       <formula>OR($K14="CLOSED",$K14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:M15">
-    <cfRule type="expression" dxfId="155" priority="153" stopIfTrue="1">
+    <cfRule type="expression" dxfId="131" priority="153" stopIfTrue="1">
       <formula>$K15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="154" priority="154" stopIfTrue="1">
+    <cfRule type="expression" dxfId="130" priority="154" stopIfTrue="1">
       <formula>$K15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="153" priority="155" stopIfTrue="1">
+    <cfRule type="expression" dxfId="129" priority="155" stopIfTrue="1">
       <formula>$K15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="152" priority="156" stopIfTrue="1">
+    <cfRule type="expression" dxfId="128" priority="156" stopIfTrue="1">
       <formula>OR($K15="CLOSED",$K15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:M16">
-    <cfRule type="expression" dxfId="151" priority="149" stopIfTrue="1">
+    <cfRule type="expression" dxfId="127" priority="149" stopIfTrue="1">
       <formula>$K16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="150" priority="150" stopIfTrue="1">
+    <cfRule type="expression" dxfId="126" priority="150" stopIfTrue="1">
       <formula>$K16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="149" priority="151" stopIfTrue="1">
+    <cfRule type="expression" dxfId="125" priority="151" stopIfTrue="1">
       <formula>$K16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="148" priority="152" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="152" stopIfTrue="1">
       <formula>OR($K16="CLOSED",$K16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:M17">
-    <cfRule type="expression" dxfId="147" priority="145" stopIfTrue="1">
+    <cfRule type="expression" dxfId="123" priority="145" stopIfTrue="1">
       <formula>$K17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="146" priority="146" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="146" stopIfTrue="1">
       <formula>$K17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="145" priority="147" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="147" stopIfTrue="1">
       <formula>$K17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="144" priority="148" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="148" stopIfTrue="1">
       <formula>OR($K17="CLOSED",$K17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:M18">
-    <cfRule type="expression" dxfId="143" priority="141" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="141" stopIfTrue="1">
       <formula>$K18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="142" priority="142" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="142" stopIfTrue="1">
       <formula>$K18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="141" priority="143" stopIfTrue="1">
+    <cfRule type="expression" dxfId="117" priority="143" stopIfTrue="1">
       <formula>$K18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="140" priority="144" stopIfTrue="1">
+    <cfRule type="expression" dxfId="116" priority="144" stopIfTrue="1">
       <formula>OR($K18="CLOSED",$K18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:M19">
-    <cfRule type="expression" dxfId="139" priority="137" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="137" stopIfTrue="1">
       <formula>$K19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="138" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="138" stopIfTrue="1">
       <formula>$K19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="137" priority="139" stopIfTrue="1">
+    <cfRule type="expression" dxfId="113" priority="139" stopIfTrue="1">
       <formula>$K19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="140" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="140" stopIfTrue="1">
       <formula>OR($K19="CLOSED",$K19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:M20">
-    <cfRule type="expression" dxfId="135" priority="133" stopIfTrue="1">
+    <cfRule type="expression" dxfId="111" priority="133" stopIfTrue="1">
       <formula>$K20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="134" stopIfTrue="1">
+    <cfRule type="expression" dxfId="110" priority="134" stopIfTrue="1">
       <formula>$K20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="133" priority="135" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="135" stopIfTrue="1">
       <formula>$K20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="136" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="136" stopIfTrue="1">
       <formula>OR($K20="CLOSED",$K20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:M21">
-    <cfRule type="expression" dxfId="131" priority="129" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="129" stopIfTrue="1">
       <formula>$K21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="130" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="130" stopIfTrue="1">
       <formula>$K21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="131" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="131" stopIfTrue="1">
       <formula>$K21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="128" priority="132" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="132" stopIfTrue="1">
       <formula>OR($K21="CLOSED",$K21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:M23">
-    <cfRule type="expression" dxfId="127" priority="125" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="125" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="126" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="126" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="127" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="127" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="128" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="128" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:I22">
-    <cfRule type="expression" dxfId="123" priority="121" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="121" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="122" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="122" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="123" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="123" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="124" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="124" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="119" priority="117" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="117" stopIfTrue="1">
       <formula>$K23="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="118" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="118" stopIfTrue="1">
       <formula>$K23="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="119" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="119" stopIfTrue="1">
       <formula>$K23="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="120" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="120" stopIfTrue="1">
       <formula>OR($K23="CLOSED",$K23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:M25">
-    <cfRule type="expression" dxfId="115" priority="113" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="113" stopIfTrue="1">
       <formula>$K24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="114" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="114" stopIfTrue="1">
       <formula>$K24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="115" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="115" stopIfTrue="1">
       <formula>$K24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="116" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="116" stopIfTrue="1">
       <formula>OR($K24="CLOSED",$K24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="111" priority="109" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="109" stopIfTrue="1">
       <formula>$K25="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="110" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="110" stopIfTrue="1">
       <formula>$K25="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="111" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="111" stopIfTrue="1">
       <formula>$K25="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="112" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="112" stopIfTrue="1">
       <formula>OR($K25="CLOSED",$K25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:M26">
-    <cfRule type="expression" dxfId="107" priority="105" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="105" stopIfTrue="1">
       <formula>$K26="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="106" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="106" stopIfTrue="1">
       <formula>$K26="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="107" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="107" stopIfTrue="1">
       <formula>$K26="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="108" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="108" stopIfTrue="1">
       <formula>OR($K26="CLOSED",$K26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:M28">
-    <cfRule type="expression" dxfId="103" priority="101" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="101" stopIfTrue="1">
       <formula>$K27="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="102" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="102" stopIfTrue="1">
       <formula>$K27="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="103" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="103" stopIfTrue="1">
       <formula>$K27="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="104" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="104" stopIfTrue="1">
       <formula>OR($K27="CLOSED",$K27="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M30">
-    <cfRule type="expression" dxfId="99" priority="97" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="97" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="98" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="98" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="99" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="99" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="100" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="100" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M29">
-    <cfRule type="expression" dxfId="95" priority="93" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="93" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="94" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="94" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="95" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="95" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="96" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="96" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:M31">
-    <cfRule type="expression" dxfId="91" priority="89" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="89" stopIfTrue="1">
       <formula>$K31="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="90" stopIfTrue="1">
       <formula>$K31="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="91" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="91" stopIfTrue="1">
       <formula>$K31="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="92" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="92" stopIfTrue="1">
       <formula>OR($K31="CLOSED",$K31="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:M38">
-    <cfRule type="expression" dxfId="87" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="61" stopIfTrue="1">
       <formula>$K38="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="62" stopIfTrue="1">
       <formula>$K38="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="63" stopIfTrue="1">
       <formula>$K38="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="64" stopIfTrue="1">
       <formula>OR($K38="CLOSED",$K38="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:M39">
-    <cfRule type="expression" dxfId="83" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="57" stopIfTrue="1">
       <formula>$K39="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="58" stopIfTrue="1">
       <formula>$K39="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="59" stopIfTrue="1">
       <formula>$K39="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="60" stopIfTrue="1">
       <formula>OR($K39="CLOSED",$K39="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:M40">
-    <cfRule type="expression" dxfId="79" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="53" stopIfTrue="1">
       <formula>$K40="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="54" stopIfTrue="1">
       <formula>$K40="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="55" stopIfTrue="1">
       <formula>$K40="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="56" stopIfTrue="1">
       <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:M41">
-    <cfRule type="expression" dxfId="75" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="49" stopIfTrue="1">
       <formula>$K41="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="50" stopIfTrue="1">
       <formula>$K41="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="51" stopIfTrue="1">
       <formula>$K41="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="52" stopIfTrue="1">
       <formula>OR($K41="CLOSED",$K41="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:M42">
-    <cfRule type="expression" dxfId="71" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
       <formula>$K42="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
       <formula>$K42="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
       <formula>$K42="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
       <formula>OR($K42="CLOSED",$K42="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:M44">
-    <cfRule type="expression" dxfId="67" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
       <formula>$K43="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
       <formula>$K43="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="43" stopIfTrue="1">
       <formula>$K43="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="44" stopIfTrue="1">
       <formula>OR($K43="CLOSED",$K43="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45:M46">
-    <cfRule type="expression" dxfId="63" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="37" stopIfTrue="1">
       <formula>$K45="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="38" stopIfTrue="1">
       <formula>$K45="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="39" stopIfTrue="1">
       <formula>$K45="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="40" stopIfTrue="1">
       <formula>OR($K45="CLOSED",$K45="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:M47">
-    <cfRule type="expression" dxfId="59" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
       <formula>$K47="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
       <formula>$K47="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
       <formula>$K47="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
       <formula>OR($K47="CLOSED",$K47="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:M48">
-    <cfRule type="expression" dxfId="55" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
       <formula>$K48="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
       <formula>$K48="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="31" stopIfTrue="1">
       <formula>$K48="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
       <formula>OR($K48="CLOSED",$K48="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:M49">
-    <cfRule type="expression" dxfId="51" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
       <formula>$K49="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
       <formula>$K49="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="27" stopIfTrue="1">
       <formula>$K49="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="28" stopIfTrue="1">
       <formula>OR($K49="CLOSED",$K49="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:M50">
-    <cfRule type="expression" dxfId="47" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
       <formula>$K50="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
       <formula>$K50="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
       <formula>$K50="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
       <formula>OR($K50="CLOSED",$K50="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:M51">
-    <cfRule type="expression" dxfId="43" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
       <formula>$K51="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
       <formula>$K51="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
       <formula>$K51="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
       <formula>OR($K51="CLOSED",$K51="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:M52">
-    <cfRule type="expression" dxfId="39" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
       <formula>$K52="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="14" stopIfTrue="1">
       <formula>$K52="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="15" stopIfTrue="1">
       <formula>$K52="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
       <formula>OR($K52="CLOSED",$K52="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:M53">
-    <cfRule type="expression" dxfId="35" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
       <formula>$K53="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
       <formula>$K53="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
       <formula>$K53="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
       <formula>OR($K53="CLOSED",$K53="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:M54">
-    <cfRule type="expression" dxfId="31" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
       <formula>$K54="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
       <formula>$K54="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
       <formula>$K54="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
       <formula>OR($K54="CLOSED",$K54="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:M55">
-    <cfRule type="expression" dxfId="27" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>$K55="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
       <formula>$K55="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>$K55="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
       <formula>OR($K55="CLOSED",$K55="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="9300"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="9300" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="2014年1季度" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$M$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2015年'!$A$1:$M$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2015年'!$A$1:$M$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$M$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -1833,7 +1833,175 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="188">
+  <dxfs count="212">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4594,16 +4762,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M169">
-    <cfRule type="expression" dxfId="187" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="211" priority="1" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="186" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="210" priority="2" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="185" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="209" priority="3" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="184" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="208" priority="4" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5778,16 +5946,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L185">
-    <cfRule type="expression" dxfId="183" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="207" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="182" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="206" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="181" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="205" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="180" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="204" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5812,7 +5980,7 @@
   <sheetPr filterMode="1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -6803,179 +6971,175 @@
       <c r="L36" s="8"/>
       <c r="M36" s="14"/>
     </row>
-    <row r="37" spans="1:13" ht="27">
+    <row r="37" spans="1:13" ht="40.5" hidden="1">
       <c r="A37" s="13">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="C37" s="8"/>
-      <c r="D37" s="35" t="s">
-        <v>284</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>279</v>
-      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
       <c r="F37" s="8" t="s">
         <v>64</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="I37" s="8">
-        <v>3</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="K37" s="8" t="s">
-        <v>58</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
       <c r="L37" s="8"/>
       <c r="M37" s="14"/>
     </row>
-    <row r="38" spans="1:13" ht="40.5" hidden="1">
-      <c r="A38" s="13">
-        <v>54</v>
+    <row r="38" spans="1:13" ht="121.5">
+      <c r="A38" s="1">
+        <v>56</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G38" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D38" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="14"/>
-    </row>
-    <row r="39" spans="1:13" ht="121.5">
-      <c r="A39" s="1">
-        <v>56</v>
+      <c r="H38" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I38" s="2">
+        <v>18</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L38" s="2"/>
+      <c r="M38" s="3"/>
+    </row>
+    <row r="39" spans="1:13" ht="94.5">
+      <c r="A39" s="13">
+        <v>58</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>83</v>
+        <v>265</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="D39" s="35" t="s">
-        <v>259</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="D39" s="8"/>
       <c r="E39" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G39" s="2" t="s">
+      <c r="F39" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G39" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H39" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I39" s="2">
-        <v>18</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="K39" s="2" t="s">
+      <c r="H39" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="I39" s="8">
+        <v>120</v>
+      </c>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="L39" s="2"/>
-      <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="1:13" ht="67.5">
-      <c r="A40" s="27">
-        <v>57</v>
-      </c>
-      <c r="B40" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="C40" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="D40" s="28"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="14"/>
+    </row>
+    <row r="40" spans="1:13" ht="27">
+      <c r="A40" s="13">
+        <v>59</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="D40" s="8"/>
       <c r="E40" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="F40" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="G40" s="29" t="s">
+      <c r="F40" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H40" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="I40" s="29">
-        <v>2</v>
-      </c>
-      <c r="J40" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="K40" s="29" t="s">
+      <c r="H40" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="I40" s="8">
+        <v>90</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="K40" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="L40" s="30"/>
-      <c r="M40" s="31"/>
-    </row>
-    <row r="41" spans="1:13" ht="94.5">
+      <c r="L40" s="8"/>
+      <c r="M40" s="14"/>
+    </row>
+    <row r="41" spans="1:13" ht="27">
       <c r="A41" s="13">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>266</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="C41" s="8"/>
       <c r="D41" s="8"/>
       <c r="E41" s="8" t="s">
         <v>279</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="I41" s="8">
-        <v>120</v>
-      </c>
-      <c r="J41" s="8"/>
+        <v>20</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>260</v>
+      </c>
       <c r="K41" s="8" t="s">
         <v>58</v>
       </c>
       <c r="L41" s="8"/>
       <c r="M41" s="14"/>
     </row>
-    <row r="42" spans="1:13" ht="27">
+    <row r="42" spans="1:13" ht="54">
       <c r="A42" s="13">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>283</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="C42" s="8"/>
       <c r="D42" s="8"/>
       <c r="E42" s="8" t="s">
         <v>279</v>
@@ -6987,13 +7151,13 @@
         <v>22</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="I42" s="8">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K42" s="8" t="s">
         <v>58</v>
@@ -7003,10 +7167,10 @@
     </row>
     <row r="43" spans="1:13" ht="27">
       <c r="A43" s="13">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -7020,13 +7184,13 @@
         <v>22</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I43" s="8">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="K43" s="8" t="s">
         <v>58</v>
@@ -7034,12 +7198,12 @@
       <c r="L43" s="8"/>
       <c r="M43" s="14"/>
     </row>
-    <row r="44" spans="1:13" ht="54">
+    <row r="44" spans="1:13" ht="27">
       <c r="A44" s="13">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -7047,118 +7211,82 @@
         <v>279</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I44" s="8">
-        <v>100</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>58</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
       <c r="L44" s="8"/>
       <c r="M44" s="14"/>
     </row>
     <row r="45" spans="1:13" ht="27">
-      <c r="A45" s="13">
-        <v>62</v>
+      <c r="A45" s="1">
+        <v>64</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="C45" s="8"/>
+        <v>39</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>277</v>
+      </c>
       <c r="D45" s="8"/>
       <c r="E45" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="F45" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G45" s="8" t="s">
+      <c r="F45" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H45" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="I45" s="8">
-        <v>140</v>
-      </c>
-      <c r="J45" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="L45" s="8"/>
-      <c r="M45" s="14"/>
-    </row>
-    <row r="46" spans="1:13" ht="27">
-      <c r="A46" s="13">
-        <v>63</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>275</v>
-      </c>
+      <c r="H45" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I45" s="2">
+        <v>4</v>
+      </c>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="13"/>
+      <c r="B46" s="8"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
-      <c r="E46" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="I46" s="8">
-        <v>20</v>
-      </c>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
       <c r="M46" s="14"/>
     </row>
-    <row r="47" spans="1:13" ht="27">
-      <c r="A47" s="1">
-        <v>64</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>277</v>
-      </c>
+    <row r="47" spans="1:13">
+      <c r="A47" s="13"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
       <c r="D47" s="8"/>
-      <c r="E47" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I47" s="2">
-        <v>4</v>
-      </c>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
-      <c r="M47" s="3"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="14"/>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="13"/>
@@ -7595,53 +7723,23 @@
       <c r="L76" s="8"/>
       <c r="M76" s="14"/>
     </row>
-    <row r="77" spans="1:13">
-      <c r="A77" s="13"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="8"/>
-      <c r="M77" s="14"/>
-    </row>
-    <row r="78" spans="1:13">
-      <c r="A78" s="13"/>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="8"/>
-      <c r="J78" s="8"/>
-      <c r="K78" s="8"/>
-      <c r="L78" s="8"/>
-      <c r="M78" s="14"/>
-    </row>
-    <row r="79" spans="1:13" ht="14.25" thickBot="1">
-      <c r="A79" s="15"/>
-      <c r="B79" s="16"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16"/>
-      <c r="H79" s="16"/>
-      <c r="I79" s="16"/>
-      <c r="J79" s="16"/>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="17"/>
+    <row r="77" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A77" s="15"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16"/>
+      <c r="H77" s="16"/>
+      <c r="I77" s="16"/>
+      <c r="J77" s="16"/>
+      <c r="K77" s="16"/>
+      <c r="L77" s="16"/>
+      <c r="M77" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M47">
+  <autoFilter ref="A1:M45">
     <filterColumn colId="4">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7653,107 +7751,78 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:M190">
-    <cfRule type="expression" dxfId="179" priority="21" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:M188">
+    <cfRule type="expression" dxfId="15" priority="21" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="178" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="22" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="177" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="23" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="176" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="24" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:M7">
-    <cfRule type="expression" dxfId="175" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="17" stopIfTrue="1">
       <formula>$K7="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="174" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="18" stopIfTrue="1">
       <formula>$K7="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="19" stopIfTrue="1">
       <formula>$K7="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="172" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="20" stopIfTrue="1">
       <formula>OR($K7="CLOSED",$K7="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A39:M39">
-    <cfRule type="expression" dxfId="171" priority="13" stopIfTrue="1">
-      <formula>$K39="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="170" priority="14" stopIfTrue="1">
-      <formula>$K39="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="169" priority="15" stopIfTrue="1">
-      <formula>$K39="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="168" priority="16" stopIfTrue="1">
-      <formula>OR($K39="CLOSED",$K39="CANCEL")</formula>
+  <conditionalFormatting sqref="A38:M38">
+    <cfRule type="expression" dxfId="7" priority="13" stopIfTrue="1">
+      <formula>$K38="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="14" stopIfTrue="1">
+      <formula>$K38="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="15" stopIfTrue="1">
+      <formula>$K38="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="16" stopIfTrue="1">
+      <formula>OR($K38="CLOSED",$K38="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A40:M40">
-    <cfRule type="expression" dxfId="167" priority="9" stopIfTrue="1">
-      <formula>$K40="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="166" priority="10" stopIfTrue="1">
-      <formula>$K40="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="165" priority="11" stopIfTrue="1">
-      <formula>$K40="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="164" priority="12" stopIfTrue="1">
-      <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E40">
-    <cfRule type="expression" dxfId="163" priority="5" stopIfTrue="1">
-      <formula>$K40="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="162" priority="6" stopIfTrue="1">
-      <formula>$K40="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="161" priority="7" stopIfTrue="1">
-      <formula>$K40="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="160" priority="8" stopIfTrue="1">
-      <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A47:M47">
-    <cfRule type="expression" dxfId="159" priority="1" stopIfTrue="1">
-      <formula>$K47="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="158" priority="2" stopIfTrue="1">
-      <formula>$K47="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="157" priority="3" stopIfTrue="1">
-      <formula>$K47="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="156" priority="4" stopIfTrue="1">
-      <formula>OR($K47="CLOSED",$K47="CANCEL")</formula>
+  <conditionalFormatting sqref="A45:M45">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+      <formula>$K45="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+      <formula>$K45="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+      <formula>$K45="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+      <formula>OR($K45="CLOSED",$K45="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F79">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F77">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G79">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G77">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K79">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K77">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D39" r:id="rId1"/>
-    <hyperlink ref="D37" r:id="rId2"/>
+    <hyperlink ref="D38" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -9584,35 +9653,75 @@
       <c r="L55" s="8"/>
       <c r="M55" s="14"/>
     </row>
-    <row r="56" spans="1:13">
-      <c r="A56" s="1"/>
-      <c r="B56" s="8"/>
+    <row r="56" spans="1:13" ht="27">
+      <c r="A56" s="13">
+        <v>50</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>229</v>
+      </c>
       <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-      <c r="L56" s="2"/>
-      <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="1:13">
-      <c r="A57" s="1"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
-      <c r="L57" s="2"/>
-      <c r="M57" s="3"/>
+      <c r="D56" s="35" t="s">
+        <v>284</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="I56" s="8">
+        <v>3</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L56" s="8"/>
+      <c r="M56" s="14"/>
+    </row>
+    <row r="57" spans="1:13" ht="67.5">
+      <c r="A57" s="27">
+        <v>57</v>
+      </c>
+      <c r="B57" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="C57" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="D57" s="28"/>
+      <c r="E57" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="F57" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="G57" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" s="29">
+        <v>2</v>
+      </c>
+      <c r="J57" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="K57" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="L57" s="30"/>
+      <c r="M57" s="31"/>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="1"/>
@@ -9877,549 +9986,605 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:M9 A32:M37">
-    <cfRule type="expression" dxfId="155" priority="177" stopIfTrue="1">
+    <cfRule type="expression" dxfId="187" priority="193" stopIfTrue="1">
       <formula>$K9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="154" priority="178" stopIfTrue="1">
+    <cfRule type="expression" dxfId="186" priority="194" stopIfTrue="1">
       <formula>$K9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="153" priority="179" stopIfTrue="1">
+    <cfRule type="expression" dxfId="185" priority="195" stopIfTrue="1">
       <formula>$K9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="152" priority="180" stopIfTrue="1">
+    <cfRule type="expression" dxfId="184" priority="196" stopIfTrue="1">
       <formula>OR($K9="CLOSED",$K9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:M10">
-    <cfRule type="expression" dxfId="151" priority="173" stopIfTrue="1">
+    <cfRule type="expression" dxfId="183" priority="189" stopIfTrue="1">
       <formula>$K10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="150" priority="174" stopIfTrue="1">
+    <cfRule type="expression" dxfId="182" priority="190" stopIfTrue="1">
       <formula>$K10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="149" priority="175" stopIfTrue="1">
+    <cfRule type="expression" dxfId="181" priority="191" stopIfTrue="1">
       <formula>$K10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="148" priority="176" stopIfTrue="1">
+    <cfRule type="expression" dxfId="180" priority="192" stopIfTrue="1">
       <formula>OR($K10="CLOSED",$K10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:M11">
-    <cfRule type="expression" dxfId="147" priority="169" stopIfTrue="1">
+    <cfRule type="expression" dxfId="179" priority="185" stopIfTrue="1">
       <formula>$K11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="146" priority="170" stopIfTrue="1">
+    <cfRule type="expression" dxfId="178" priority="186" stopIfTrue="1">
       <formula>$K11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="145" priority="171" stopIfTrue="1">
+    <cfRule type="expression" dxfId="177" priority="187" stopIfTrue="1">
       <formula>$K11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="144" priority="172" stopIfTrue="1">
+    <cfRule type="expression" dxfId="176" priority="188" stopIfTrue="1">
       <formula>OR($K11="CLOSED",$K11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:M12">
-    <cfRule type="expression" dxfId="143" priority="165" stopIfTrue="1">
+    <cfRule type="expression" dxfId="175" priority="181" stopIfTrue="1">
       <formula>$K12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="142" priority="166" stopIfTrue="1">
+    <cfRule type="expression" dxfId="174" priority="182" stopIfTrue="1">
       <formula>$K12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="141" priority="167" stopIfTrue="1">
+    <cfRule type="expression" dxfId="173" priority="183" stopIfTrue="1">
       <formula>$K12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="140" priority="168" stopIfTrue="1">
+    <cfRule type="expression" dxfId="172" priority="184" stopIfTrue="1">
       <formula>OR($K12="CLOSED",$K12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:M13">
-    <cfRule type="expression" dxfId="139" priority="161" stopIfTrue="1">
+    <cfRule type="expression" dxfId="171" priority="177" stopIfTrue="1">
       <formula>$K13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="162" stopIfTrue="1">
+    <cfRule type="expression" dxfId="170" priority="178" stopIfTrue="1">
       <formula>$K13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="137" priority="163" stopIfTrue="1">
+    <cfRule type="expression" dxfId="169" priority="179" stopIfTrue="1">
       <formula>$K13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="164" stopIfTrue="1">
+    <cfRule type="expression" dxfId="168" priority="180" stopIfTrue="1">
       <formula>OR($K13="CLOSED",$K13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:M14">
-    <cfRule type="expression" dxfId="135" priority="157" stopIfTrue="1">
+    <cfRule type="expression" dxfId="167" priority="173" stopIfTrue="1">
       <formula>$K14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="158" stopIfTrue="1">
+    <cfRule type="expression" dxfId="166" priority="174" stopIfTrue="1">
       <formula>$K14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="133" priority="159" stopIfTrue="1">
+    <cfRule type="expression" dxfId="165" priority="175" stopIfTrue="1">
       <formula>$K14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="160" stopIfTrue="1">
+    <cfRule type="expression" dxfId="164" priority="176" stopIfTrue="1">
       <formula>OR($K14="CLOSED",$K14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:M15">
-    <cfRule type="expression" dxfId="131" priority="153" stopIfTrue="1">
+    <cfRule type="expression" dxfId="163" priority="169" stopIfTrue="1">
       <formula>$K15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="154" stopIfTrue="1">
+    <cfRule type="expression" dxfId="162" priority="170" stopIfTrue="1">
       <formula>$K15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="155" stopIfTrue="1">
+    <cfRule type="expression" dxfId="161" priority="171" stopIfTrue="1">
       <formula>$K15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="128" priority="156" stopIfTrue="1">
+    <cfRule type="expression" dxfId="160" priority="172" stopIfTrue="1">
       <formula>OR($K15="CLOSED",$K15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:M16">
-    <cfRule type="expression" dxfId="127" priority="149" stopIfTrue="1">
+    <cfRule type="expression" dxfId="159" priority="165" stopIfTrue="1">
       <formula>$K16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="150" stopIfTrue="1">
+    <cfRule type="expression" dxfId="158" priority="166" stopIfTrue="1">
       <formula>$K16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="151" stopIfTrue="1">
+    <cfRule type="expression" dxfId="157" priority="167" stopIfTrue="1">
       <formula>$K16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="152" stopIfTrue="1">
+    <cfRule type="expression" dxfId="156" priority="168" stopIfTrue="1">
       <formula>OR($K16="CLOSED",$K16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:M17">
-    <cfRule type="expression" dxfId="123" priority="145" stopIfTrue="1">
+    <cfRule type="expression" dxfId="155" priority="161" stopIfTrue="1">
       <formula>$K17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="146" stopIfTrue="1">
+    <cfRule type="expression" dxfId="154" priority="162" stopIfTrue="1">
       <formula>$K17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="147" stopIfTrue="1">
+    <cfRule type="expression" dxfId="153" priority="163" stopIfTrue="1">
       <formula>$K17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="148" stopIfTrue="1">
+    <cfRule type="expression" dxfId="152" priority="164" stopIfTrue="1">
       <formula>OR($K17="CLOSED",$K17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:M18">
-    <cfRule type="expression" dxfId="119" priority="141" stopIfTrue="1">
+    <cfRule type="expression" dxfId="151" priority="157" stopIfTrue="1">
       <formula>$K18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="142" stopIfTrue="1">
+    <cfRule type="expression" dxfId="150" priority="158" stopIfTrue="1">
       <formula>$K18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="143" stopIfTrue="1">
+    <cfRule type="expression" dxfId="149" priority="159" stopIfTrue="1">
       <formula>$K18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="144" stopIfTrue="1">
+    <cfRule type="expression" dxfId="148" priority="160" stopIfTrue="1">
       <formula>OR($K18="CLOSED",$K18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:M19">
-    <cfRule type="expression" dxfId="115" priority="137" stopIfTrue="1">
+    <cfRule type="expression" dxfId="147" priority="153" stopIfTrue="1">
       <formula>$K19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="138" stopIfTrue="1">
+    <cfRule type="expression" dxfId="146" priority="154" stopIfTrue="1">
       <formula>$K19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="139" stopIfTrue="1">
+    <cfRule type="expression" dxfId="145" priority="155" stopIfTrue="1">
       <formula>$K19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="140" stopIfTrue="1">
+    <cfRule type="expression" dxfId="144" priority="156" stopIfTrue="1">
       <formula>OR($K19="CLOSED",$K19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:M20">
-    <cfRule type="expression" dxfId="111" priority="133" stopIfTrue="1">
+    <cfRule type="expression" dxfId="143" priority="149" stopIfTrue="1">
       <formula>$K20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="134" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="150" stopIfTrue="1">
       <formula>$K20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="135" stopIfTrue="1">
+    <cfRule type="expression" dxfId="141" priority="151" stopIfTrue="1">
       <formula>$K20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="136" stopIfTrue="1">
+    <cfRule type="expression" dxfId="140" priority="152" stopIfTrue="1">
       <formula>OR($K20="CLOSED",$K20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:M21">
-    <cfRule type="expression" dxfId="107" priority="129" stopIfTrue="1">
+    <cfRule type="expression" dxfId="139" priority="145" stopIfTrue="1">
       <formula>$K21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="130" stopIfTrue="1">
+    <cfRule type="expression" dxfId="138" priority="146" stopIfTrue="1">
       <formula>$K21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="131" stopIfTrue="1">
+    <cfRule type="expression" dxfId="137" priority="147" stopIfTrue="1">
       <formula>$K21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="132" stopIfTrue="1">
+    <cfRule type="expression" dxfId="136" priority="148" stopIfTrue="1">
       <formula>OR($K21="CLOSED",$K21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:M23">
-    <cfRule type="expression" dxfId="103" priority="125" stopIfTrue="1">
+    <cfRule type="expression" dxfId="135" priority="141" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="126" stopIfTrue="1">
+    <cfRule type="expression" dxfId="134" priority="142" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="127" stopIfTrue="1">
+    <cfRule type="expression" dxfId="133" priority="143" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="128" stopIfTrue="1">
+    <cfRule type="expression" dxfId="132" priority="144" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:I22">
-    <cfRule type="expression" dxfId="99" priority="121" stopIfTrue="1">
+    <cfRule type="expression" dxfId="131" priority="137" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="122" stopIfTrue="1">
+    <cfRule type="expression" dxfId="130" priority="138" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="123" stopIfTrue="1">
+    <cfRule type="expression" dxfId="129" priority="139" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="124" stopIfTrue="1">
+    <cfRule type="expression" dxfId="128" priority="140" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="95" priority="117" stopIfTrue="1">
+    <cfRule type="expression" dxfId="127" priority="133" stopIfTrue="1">
       <formula>$K23="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="118" stopIfTrue="1">
+    <cfRule type="expression" dxfId="126" priority="134" stopIfTrue="1">
       <formula>$K23="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="119" stopIfTrue="1">
+    <cfRule type="expression" dxfId="125" priority="135" stopIfTrue="1">
       <formula>$K23="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="120" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="136" stopIfTrue="1">
       <formula>OR($K23="CLOSED",$K23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:M25">
-    <cfRule type="expression" dxfId="91" priority="113" stopIfTrue="1">
+    <cfRule type="expression" dxfId="123" priority="129" stopIfTrue="1">
       <formula>$K24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="114" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="130" stopIfTrue="1">
       <formula>$K24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="115" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="131" stopIfTrue="1">
       <formula>$K24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="116" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="132" stopIfTrue="1">
       <formula>OR($K24="CLOSED",$K24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="87" priority="109" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="125" stopIfTrue="1">
       <formula>$K25="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="110" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="126" stopIfTrue="1">
       <formula>$K25="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="111" stopIfTrue="1">
+    <cfRule type="expression" dxfId="117" priority="127" stopIfTrue="1">
       <formula>$K25="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="112" stopIfTrue="1">
+    <cfRule type="expression" dxfId="116" priority="128" stopIfTrue="1">
       <formula>OR($K25="CLOSED",$K25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:M26">
-    <cfRule type="expression" dxfId="83" priority="105" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="121" stopIfTrue="1">
       <formula>$K26="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="106" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="122" stopIfTrue="1">
       <formula>$K26="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="107" stopIfTrue="1">
+    <cfRule type="expression" dxfId="113" priority="123" stopIfTrue="1">
       <formula>$K26="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="108" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="124" stopIfTrue="1">
       <formula>OR($K26="CLOSED",$K26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:M28">
-    <cfRule type="expression" dxfId="79" priority="101" stopIfTrue="1">
+    <cfRule type="expression" dxfId="111" priority="117" stopIfTrue="1">
       <formula>$K27="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="102" stopIfTrue="1">
+    <cfRule type="expression" dxfId="110" priority="118" stopIfTrue="1">
       <formula>$K27="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="103" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="119" stopIfTrue="1">
       <formula>$K27="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="104" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="120" stopIfTrue="1">
       <formula>OR($K27="CLOSED",$K27="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M30">
-    <cfRule type="expression" dxfId="75" priority="97" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="113" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="98" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="114" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="99" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="115" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="100" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="116" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M29">
-    <cfRule type="expression" dxfId="71" priority="93" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="109" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="94" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="110" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="95" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="111" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="96" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="112" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:M31">
-    <cfRule type="expression" dxfId="67" priority="89" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="105" stopIfTrue="1">
       <formula>$K31="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="106" stopIfTrue="1">
       <formula>$K31="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="91" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="107" stopIfTrue="1">
       <formula>$K31="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="92" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="108" stopIfTrue="1">
       <formula>OR($K31="CLOSED",$K31="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:M38">
-    <cfRule type="expression" dxfId="63" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="77" stopIfTrue="1">
       <formula>$K38="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="78" stopIfTrue="1">
       <formula>$K38="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="79" stopIfTrue="1">
       <formula>$K38="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="80" stopIfTrue="1">
       <formula>OR($K38="CLOSED",$K38="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:M39">
-    <cfRule type="expression" dxfId="59" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="73" stopIfTrue="1">
       <formula>$K39="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="74" stopIfTrue="1">
       <formula>$K39="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="75" stopIfTrue="1">
       <formula>$K39="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="76" stopIfTrue="1">
       <formula>OR($K39="CLOSED",$K39="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:M40">
-    <cfRule type="expression" dxfId="55" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="69" stopIfTrue="1">
       <formula>$K40="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="70" stopIfTrue="1">
       <formula>$K40="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="71" stopIfTrue="1">
       <formula>$K40="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="72" stopIfTrue="1">
       <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:M41">
-    <cfRule type="expression" dxfId="51" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="65" stopIfTrue="1">
       <formula>$K41="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="66" stopIfTrue="1">
       <formula>$K41="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="67" stopIfTrue="1">
       <formula>$K41="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="68" stopIfTrue="1">
       <formula>OR($K41="CLOSED",$K41="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:M42">
-    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="61" stopIfTrue="1">
       <formula>$K42="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="62" stopIfTrue="1">
       <formula>$K42="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="63" stopIfTrue="1">
       <formula>$K42="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="64" stopIfTrue="1">
       <formula>OR($K42="CLOSED",$K42="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:M44">
-    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="57" stopIfTrue="1">
       <formula>$K43="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="58" stopIfTrue="1">
       <formula>$K43="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="59" stopIfTrue="1">
       <formula>$K43="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="60" stopIfTrue="1">
       <formula>OR($K43="CLOSED",$K43="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45:M46">
-    <cfRule type="expression" dxfId="39" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="53" stopIfTrue="1">
       <formula>$K45="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="54" stopIfTrue="1">
       <formula>$K45="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="55" stopIfTrue="1">
       <formula>$K45="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="56" stopIfTrue="1">
       <formula>OR($K45="CLOSED",$K45="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:M47">
-    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="49" stopIfTrue="1">
       <formula>$K47="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="50" stopIfTrue="1">
       <formula>$K47="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="51" stopIfTrue="1">
       <formula>$K47="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="52" stopIfTrue="1">
       <formula>OR($K47="CLOSED",$K47="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:M48">
-    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="45" stopIfTrue="1">
       <formula>$K48="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="46" stopIfTrue="1">
       <formula>$K48="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="47" stopIfTrue="1">
       <formula>$K48="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="48" stopIfTrue="1">
       <formula>OR($K48="CLOSED",$K48="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:M49">
-    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="41" stopIfTrue="1">
       <formula>$K49="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="42" stopIfTrue="1">
       <formula>$K49="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="43" stopIfTrue="1">
       <formula>$K49="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="44" stopIfTrue="1">
       <formula>OR($K49="CLOSED",$K49="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:M50">
-    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="37" stopIfTrue="1">
       <formula>$K50="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="38" stopIfTrue="1">
       <formula>$K50="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="39" stopIfTrue="1">
       <formula>$K50="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="40" stopIfTrue="1">
       <formula>OR($K50="CLOSED",$K50="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:M51">
-    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="33" stopIfTrue="1">
       <formula>$K51="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="34" stopIfTrue="1">
       <formula>$K51="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="35" stopIfTrue="1">
       <formula>$K51="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="36" stopIfTrue="1">
       <formula>OR($K51="CLOSED",$K51="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:M52">
-    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="29" stopIfTrue="1">
       <formula>$K52="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="30" stopIfTrue="1">
       <formula>$K52="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="31" stopIfTrue="1">
       <formula>$K52="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="32" stopIfTrue="1">
       <formula>OR($K52="CLOSED",$K52="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:M53">
-    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="25" stopIfTrue="1">
       <formula>$K53="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="26" stopIfTrue="1">
       <formula>$K53="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="27" stopIfTrue="1">
       <formula>$K53="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="28" stopIfTrue="1">
       <formula>OR($K53="CLOSED",$K53="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:M54">
-    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="21" stopIfTrue="1">
       <formula>$K54="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="22" stopIfTrue="1">
       <formula>$K54="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="23" stopIfTrue="1">
       <formula>$K54="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="24" stopIfTrue="1">
       <formula>OR($K54="CLOSED",$K54="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:M55">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="17" stopIfTrue="1">
       <formula>$K55="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="18" stopIfTrue="1">
       <formula>$K55="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="19" stopIfTrue="1">
       <formula>$K55="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="20" stopIfTrue="1">
       <formula>OR($K55="CLOSED",$K55="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56:M56">
+    <cfRule type="expression" dxfId="31" priority="13" stopIfTrue="1">
+      <formula>$K56="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="14" stopIfTrue="1">
+      <formula>$K56="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="15" stopIfTrue="1">
+      <formula>$K56="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="16" stopIfTrue="1">
+      <formula>OR($K56="CLOSED",$K56="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A57:M57">
+    <cfRule type="expression" dxfId="27" priority="9" stopIfTrue="1">
+      <formula>$K57="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="10" stopIfTrue="1">
+      <formula>$K57="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="11" stopIfTrue="1">
+      <formula>$K57="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="12" stopIfTrue="1">
+      <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A57:M57">
+    <cfRule type="expression" dxfId="23" priority="5" stopIfTrue="1">
+      <formula>$K57="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="6" stopIfTrue="1">
+      <formula>$K57="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="7" stopIfTrue="1">
+      <formula>$K57="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="8" stopIfTrue="1">
+      <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E57">
+    <cfRule type="expression" dxfId="19" priority="1" stopIfTrue="1">
+      <formula>$K57="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="2" stopIfTrue="1">
+      <formula>$K57="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3" stopIfTrue="1">
+      <formula>$K57="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="4" stopIfTrue="1">
+      <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -10435,8 +10600,9 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D55" r:id="rId1"/>
+    <hyperlink ref="D56" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId3"/>
 </worksheet>
 </file>
--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$M$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2015年'!$A$1:$M$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2015年'!$A$1:$M$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$M$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="292">
   <si>
     <r>
       <t>描述</t>
@@ -1462,6 +1462,14 @@
   </si>
   <si>
     <t>李伟超</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-850 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1833,63 +1841,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="212">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="204">
     <dxf>
       <fill>
         <patternFill>
@@ -4762,16 +4714,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M169">
-    <cfRule type="expression" dxfId="211" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="203" priority="1" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="210" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="202" priority="2" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="209" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="201" priority="3" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="208" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="200" priority="4" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5946,16 +5898,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L185">
-    <cfRule type="expression" dxfId="207" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="199" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="206" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="198" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="205" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="197" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="204" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="196" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5980,7 +5932,7 @@
   <sheetPr filterMode="1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -6859,22 +6811,18 @@
       <c r="L32" s="8"/>
       <c r="M32" s="14"/>
     </row>
-    <row r="33" spans="1:13" ht="54">
+    <row r="33" spans="1:13" ht="54" hidden="1">
       <c r="A33" s="13">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>278</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="C33" s="8"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="8" t="s">
-        <v>279</v>
-      </c>
+      <c r="E33" s="8"/>
       <c r="F33" s="8" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>12</v>
@@ -6883,19 +6831,19 @@
         <v>224</v>
       </c>
       <c r="I33" s="8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
       <c r="M33" s="14"/>
     </row>
-    <row r="34" spans="1:13" ht="54" hidden="1">
+    <row r="34" spans="1:13" ht="27" hidden="1">
       <c r="A34" s="13">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -6907,10 +6855,10 @@
         <v>12</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="I34" s="8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
@@ -6919,10 +6867,10 @@
     </row>
     <row r="35" spans="1:13" ht="27" hidden="1">
       <c r="A35" s="13">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -6937,19 +6885,19 @@
         <v>203</v>
       </c>
       <c r="I35" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
       <c r="M35" s="14"/>
     </row>
-    <row r="36" spans="1:13" ht="27" hidden="1">
+    <row r="36" spans="1:13" ht="40.5" hidden="1">
       <c r="A36" s="13">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -6958,106 +6906,114 @@
         <v>64</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="I36" s="8">
-        <v>4</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
       <c r="M36" s="14"/>
     </row>
-    <row r="37" spans="1:13" ht="40.5" hidden="1">
-      <c r="A37" s="13">
-        <v>54</v>
+    <row r="37" spans="1:13" ht="121.5">
+      <c r="A37" s="1">
+        <v>56</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G37" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D37" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="14"/>
-    </row>
-    <row r="38" spans="1:13" ht="121.5">
-      <c r="A38" s="1">
-        <v>56</v>
+      <c r="H37" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I37" s="2">
+        <v>18</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" s="3"/>
+    </row>
+    <row r="38" spans="1:13" ht="94.5">
+      <c r="A38" s="13">
+        <v>58</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>83</v>
+        <v>265</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="D38" s="35" t="s">
-        <v>259</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="D38" s="8"/>
       <c r="E38" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38" s="2" t="s">
+      <c r="F38" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G38" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" s="2">
-        <v>18</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="K38" s="2" t="s">
+      <c r="H38" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="I38" s="8">
+        <v>120</v>
+      </c>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="L38" s="2"/>
-      <c r="M38" s="3"/>
-    </row>
-    <row r="39" spans="1:13" ht="94.5">
+      <c r="L38" s="8"/>
+      <c r="M38" s="14"/>
+    </row>
+    <row r="39" spans="1:13" ht="27">
       <c r="A39" s="13">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8" t="s">
         <v>279</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I39" s="8">
-        <v>120</v>
-      </c>
-      <c r="J39" s="8"/>
+        <v>90</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>286</v>
+      </c>
       <c r="K39" s="8" t="s">
         <v>58</v>
       </c>
@@ -7066,14 +7022,12 @@
     </row>
     <row r="40" spans="1:13" ht="27">
       <c r="A40" s="13">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>283</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="C40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8" t="s">
         <v>279</v>
@@ -7085,13 +7039,13 @@
         <v>22</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I40" s="8">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="K40" s="8" t="s">
         <v>58</v>
@@ -7099,12 +7053,12 @@
       <c r="L40" s="8"/>
       <c r="M40" s="14"/>
     </row>
-    <row r="41" spans="1:13" ht="27">
+    <row r="41" spans="1:13" ht="54">
       <c r="A41" s="13">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
@@ -7118,13 +7072,13 @@
         <v>22</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I41" s="8">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>58</v>
@@ -7132,12 +7086,12 @@
       <c r="L41" s="8"/>
       <c r="M41" s="14"/>
     </row>
-    <row r="42" spans="1:13" ht="54">
+    <row r="42" spans="1:13" ht="27">
       <c r="A42" s="13">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
@@ -7151,13 +7105,13 @@
         <v>22</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I42" s="8">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K42" s="8" t="s">
         <v>58</v>
@@ -7167,10 +7121,10 @@
     </row>
     <row r="43" spans="1:13" ht="27">
       <c r="A43" s="13">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -7178,85 +7132,67 @@
         <v>279</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="I43" s="8">
-        <v>140</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="K43" s="8" t="s">
-        <v>58</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
       <c r="L43" s="8"/>
       <c r="M43" s="14"/>
     </row>
     <row r="44" spans="1:13" ht="27">
-      <c r="A44" s="13">
-        <v>63</v>
+      <c r="A44" s="1">
+        <v>64</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="C44" s="8"/>
+        <v>39</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>277</v>
+      </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="F44" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="I44" s="8">
-        <v>20</v>
-      </c>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
-      <c r="L44" s="8"/>
-      <c r="M44" s="14"/>
-    </row>
-    <row r="45" spans="1:13" ht="27">
-      <c r="A45" s="1">
-        <v>64</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>277</v>
-      </c>
+      <c r="F44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I44" s="2">
+        <v>4</v>
+      </c>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="13"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
       <c r="D45" s="8"/>
-      <c r="E45" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I45" s="2">
-        <v>4</v>
-      </c>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="3"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="14"/>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="13"/>
@@ -7708,38 +7644,23 @@
       <c r="L75" s="8"/>
       <c r="M75" s="14"/>
     </row>
-    <row r="76" spans="1:13">
-      <c r="A76" s="13"/>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="14"/>
-    </row>
-    <row r="77" spans="1:13" ht="14.25" thickBot="1">
-      <c r="A77" s="15"/>
-      <c r="B77" s="16"/>
-      <c r="C77" s="16"/>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16"/>
-      <c r="H77" s="16"/>
-      <c r="I77" s="16"/>
-      <c r="J77" s="16"/>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="17"/>
+    <row r="76" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A76" s="15"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="16"/>
+      <c r="H76" s="16"/>
+      <c r="I76" s="16"/>
+      <c r="J76" s="16"/>
+      <c r="K76" s="16"/>
+      <c r="L76" s="16"/>
+      <c r="M76" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M45">
+  <autoFilter ref="A1:M44">
     <filterColumn colId="4">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7751,7 +7672,7 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:M188">
+  <conditionalFormatting sqref="A2:M187">
     <cfRule type="expression" dxfId="15" priority="21" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
@@ -7779,47 +7700,47 @@
       <formula>OR($K7="CLOSED",$K7="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A38:M38">
+  <conditionalFormatting sqref="A37:M37">
     <cfRule type="expression" dxfId="7" priority="13" stopIfTrue="1">
-      <formula>$K38="HANG-UP"</formula>
+      <formula>$K37="HANG-UP"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="6" priority="14" stopIfTrue="1">
-      <formula>$K38="PLAN"</formula>
+      <formula>$K37="PLAN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="5" priority="15" stopIfTrue="1">
-      <formula>$K38="OPEN"</formula>
+      <formula>$K37="OPEN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="16" stopIfTrue="1">
-      <formula>OR($K38="CLOSED",$K38="CANCEL")</formula>
+      <formula>OR($K37="CLOSED",$K37="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A45:M45">
+  <conditionalFormatting sqref="A44:M44">
     <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
-      <formula>$K45="HANG-UP"</formula>
+      <formula>$K44="HANG-UP"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
-      <formula>$K45="PLAN"</formula>
+      <formula>$K44="PLAN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
-      <formula>$K45="OPEN"</formula>
+      <formula>$K44="OPEN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
-      <formula>OR($K45="CLOSED",$K45="CANCEL")</formula>
+      <formula>OR($K44="CLOSED",$K44="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F77">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F76">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G77">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G76">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K77">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K76">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D38" r:id="rId1"/>
+    <hyperlink ref="D37" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -9723,20 +9644,46 @@
       <c r="L57" s="30"/>
       <c r="M57" s="31"/>
     </row>
-    <row r="58" spans="1:13">
-      <c r="A58" s="1"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
-      <c r="L58" s="2"/>
-      <c r="M58" s="3"/>
+    <row r="58" spans="1:13" ht="54">
+      <c r="A58" s="13">
+        <v>45</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D58" s="35" t="s">
+        <v>291</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="I58" s="8">
+        <v>3</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L58" s="32">
+        <v>42131</v>
+      </c>
+      <c r="M58" s="34">
+        <v>42132</v>
+      </c>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="1"/>
@@ -9986,188 +9933,202 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:M9 A32:M37">
-    <cfRule type="expression" dxfId="187" priority="193" stopIfTrue="1">
+    <cfRule type="expression" dxfId="191" priority="197" stopIfTrue="1">
       <formula>$K9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="186" priority="194" stopIfTrue="1">
+    <cfRule type="expression" dxfId="190" priority="198" stopIfTrue="1">
       <formula>$K9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="185" priority="195" stopIfTrue="1">
+    <cfRule type="expression" dxfId="189" priority="199" stopIfTrue="1">
       <formula>$K9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="184" priority="196" stopIfTrue="1">
+    <cfRule type="expression" dxfId="188" priority="200" stopIfTrue="1">
       <formula>OR($K9="CLOSED",$K9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:M10">
-    <cfRule type="expression" dxfId="183" priority="189" stopIfTrue="1">
+    <cfRule type="expression" dxfId="187" priority="193" stopIfTrue="1">
       <formula>$K10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="182" priority="190" stopIfTrue="1">
+    <cfRule type="expression" dxfId="186" priority="194" stopIfTrue="1">
       <formula>$K10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="181" priority="191" stopIfTrue="1">
+    <cfRule type="expression" dxfId="185" priority="195" stopIfTrue="1">
       <formula>$K10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="180" priority="192" stopIfTrue="1">
+    <cfRule type="expression" dxfId="184" priority="196" stopIfTrue="1">
       <formula>OR($K10="CLOSED",$K10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:M11">
-    <cfRule type="expression" dxfId="179" priority="185" stopIfTrue="1">
+    <cfRule type="expression" dxfId="183" priority="189" stopIfTrue="1">
       <formula>$K11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="178" priority="186" stopIfTrue="1">
+    <cfRule type="expression" dxfId="182" priority="190" stopIfTrue="1">
       <formula>$K11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="177" priority="187" stopIfTrue="1">
+    <cfRule type="expression" dxfId="181" priority="191" stopIfTrue="1">
       <formula>$K11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="176" priority="188" stopIfTrue="1">
+    <cfRule type="expression" dxfId="180" priority="192" stopIfTrue="1">
       <formula>OR($K11="CLOSED",$K11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:M12">
-    <cfRule type="expression" dxfId="175" priority="181" stopIfTrue="1">
+    <cfRule type="expression" dxfId="179" priority="185" stopIfTrue="1">
       <formula>$K12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="174" priority="182" stopIfTrue="1">
+    <cfRule type="expression" dxfId="178" priority="186" stopIfTrue="1">
       <formula>$K12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="183" stopIfTrue="1">
+    <cfRule type="expression" dxfId="177" priority="187" stopIfTrue="1">
       <formula>$K12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="172" priority="184" stopIfTrue="1">
+    <cfRule type="expression" dxfId="176" priority="188" stopIfTrue="1">
       <formula>OR($K12="CLOSED",$K12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:M13">
-    <cfRule type="expression" dxfId="171" priority="177" stopIfTrue="1">
+    <cfRule type="expression" dxfId="175" priority="181" stopIfTrue="1">
       <formula>$K13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="170" priority="178" stopIfTrue="1">
+    <cfRule type="expression" dxfId="174" priority="182" stopIfTrue="1">
       <formula>$K13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="169" priority="179" stopIfTrue="1">
+    <cfRule type="expression" dxfId="173" priority="183" stopIfTrue="1">
       <formula>$K13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="168" priority="180" stopIfTrue="1">
+    <cfRule type="expression" dxfId="172" priority="184" stopIfTrue="1">
       <formula>OR($K13="CLOSED",$K13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:M14">
-    <cfRule type="expression" dxfId="167" priority="173" stopIfTrue="1">
+    <cfRule type="expression" dxfId="171" priority="177" stopIfTrue="1">
       <formula>$K14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="166" priority="174" stopIfTrue="1">
+    <cfRule type="expression" dxfId="170" priority="178" stopIfTrue="1">
       <formula>$K14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="165" priority="175" stopIfTrue="1">
+    <cfRule type="expression" dxfId="169" priority="179" stopIfTrue="1">
       <formula>$K14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="164" priority="176" stopIfTrue="1">
+    <cfRule type="expression" dxfId="168" priority="180" stopIfTrue="1">
       <formula>OR($K14="CLOSED",$K14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:M15">
-    <cfRule type="expression" dxfId="163" priority="169" stopIfTrue="1">
+    <cfRule type="expression" dxfId="167" priority="173" stopIfTrue="1">
       <formula>$K15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="162" priority="170" stopIfTrue="1">
+    <cfRule type="expression" dxfId="166" priority="174" stopIfTrue="1">
       <formula>$K15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="161" priority="171" stopIfTrue="1">
+    <cfRule type="expression" dxfId="165" priority="175" stopIfTrue="1">
       <formula>$K15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="160" priority="172" stopIfTrue="1">
+    <cfRule type="expression" dxfId="164" priority="176" stopIfTrue="1">
       <formula>OR($K15="CLOSED",$K15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:M16">
-    <cfRule type="expression" dxfId="159" priority="165" stopIfTrue="1">
+    <cfRule type="expression" dxfId="163" priority="169" stopIfTrue="1">
       <formula>$K16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="158" priority="166" stopIfTrue="1">
+    <cfRule type="expression" dxfId="162" priority="170" stopIfTrue="1">
       <formula>$K16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="157" priority="167" stopIfTrue="1">
+    <cfRule type="expression" dxfId="161" priority="171" stopIfTrue="1">
       <formula>$K16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="156" priority="168" stopIfTrue="1">
+    <cfRule type="expression" dxfId="160" priority="172" stopIfTrue="1">
       <formula>OR($K16="CLOSED",$K16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:M17">
-    <cfRule type="expression" dxfId="155" priority="161" stopIfTrue="1">
+    <cfRule type="expression" dxfId="159" priority="165" stopIfTrue="1">
       <formula>$K17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="154" priority="162" stopIfTrue="1">
+    <cfRule type="expression" dxfId="158" priority="166" stopIfTrue="1">
       <formula>$K17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="153" priority="163" stopIfTrue="1">
+    <cfRule type="expression" dxfId="157" priority="167" stopIfTrue="1">
       <formula>$K17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="152" priority="164" stopIfTrue="1">
+    <cfRule type="expression" dxfId="156" priority="168" stopIfTrue="1">
       <formula>OR($K17="CLOSED",$K17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:M18">
-    <cfRule type="expression" dxfId="151" priority="157" stopIfTrue="1">
+    <cfRule type="expression" dxfId="155" priority="161" stopIfTrue="1">
       <formula>$K18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="150" priority="158" stopIfTrue="1">
+    <cfRule type="expression" dxfId="154" priority="162" stopIfTrue="1">
       <formula>$K18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="149" priority="159" stopIfTrue="1">
+    <cfRule type="expression" dxfId="153" priority="163" stopIfTrue="1">
       <formula>$K18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="148" priority="160" stopIfTrue="1">
+    <cfRule type="expression" dxfId="152" priority="164" stopIfTrue="1">
       <formula>OR($K18="CLOSED",$K18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:M19">
-    <cfRule type="expression" dxfId="147" priority="153" stopIfTrue="1">
+    <cfRule type="expression" dxfId="151" priority="157" stopIfTrue="1">
       <formula>$K19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="146" priority="154" stopIfTrue="1">
+    <cfRule type="expression" dxfId="150" priority="158" stopIfTrue="1">
       <formula>$K19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="145" priority="155" stopIfTrue="1">
+    <cfRule type="expression" dxfId="149" priority="159" stopIfTrue="1">
       <formula>$K19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="144" priority="156" stopIfTrue="1">
+    <cfRule type="expression" dxfId="148" priority="160" stopIfTrue="1">
       <formula>OR($K19="CLOSED",$K19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:M20">
-    <cfRule type="expression" dxfId="143" priority="149" stopIfTrue="1">
+    <cfRule type="expression" dxfId="147" priority="153" stopIfTrue="1">
       <formula>$K20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="142" priority="150" stopIfTrue="1">
+    <cfRule type="expression" dxfId="146" priority="154" stopIfTrue="1">
       <formula>$K20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="141" priority="151" stopIfTrue="1">
+    <cfRule type="expression" dxfId="145" priority="155" stopIfTrue="1">
       <formula>$K20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="140" priority="152" stopIfTrue="1">
+    <cfRule type="expression" dxfId="144" priority="156" stopIfTrue="1">
       <formula>OR($K20="CLOSED",$K20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:M21">
-    <cfRule type="expression" dxfId="139" priority="145" stopIfTrue="1">
+    <cfRule type="expression" dxfId="143" priority="149" stopIfTrue="1">
       <formula>$K21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="146" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="150" stopIfTrue="1">
       <formula>$K21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="137" priority="147" stopIfTrue="1">
+    <cfRule type="expression" dxfId="141" priority="151" stopIfTrue="1">
       <formula>$K21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="148" stopIfTrue="1">
+    <cfRule type="expression" dxfId="140" priority="152" stopIfTrue="1">
       <formula>OR($K21="CLOSED",$K21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:M23">
+    <cfRule type="expression" dxfId="139" priority="145" stopIfTrue="1">
+      <formula>$K22="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="138" priority="146" stopIfTrue="1">
+      <formula>$K22="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="137" priority="147" stopIfTrue="1">
+      <formula>$K22="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="136" priority="148" stopIfTrue="1">
+      <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22:I22">
     <cfRule type="expression" dxfId="135" priority="141" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
@@ -10181,91 +10142,91 @@
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B22:I22">
+  <conditionalFormatting sqref="B23">
     <cfRule type="expression" dxfId="131" priority="137" stopIfTrue="1">
-      <formula>$K22="HANG-UP"</formula>
+      <formula>$K23="HANG-UP"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="130" priority="138" stopIfTrue="1">
-      <formula>$K22="PLAN"</formula>
+      <formula>$K23="PLAN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="129" priority="139" stopIfTrue="1">
-      <formula>$K22="OPEN"</formula>
+      <formula>$K23="OPEN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="128" priority="140" stopIfTrue="1">
-      <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="127" priority="133" stopIfTrue="1">
-      <formula>$K23="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="126" priority="134" stopIfTrue="1">
-      <formula>$K23="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="125" priority="135" stopIfTrue="1">
-      <formula>$K23="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="124" priority="136" stopIfTrue="1">
       <formula>OR($K23="CLOSED",$K23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:M25">
-    <cfRule type="expression" dxfId="123" priority="129" stopIfTrue="1">
+    <cfRule type="expression" dxfId="127" priority="133" stopIfTrue="1">
       <formula>$K24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="130" stopIfTrue="1">
+    <cfRule type="expression" dxfId="126" priority="134" stopIfTrue="1">
       <formula>$K24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="131" stopIfTrue="1">
+    <cfRule type="expression" dxfId="125" priority="135" stopIfTrue="1">
       <formula>$K24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="132" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="136" stopIfTrue="1">
       <formula>OR($K24="CLOSED",$K24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="119" priority="125" stopIfTrue="1">
+    <cfRule type="expression" dxfId="123" priority="129" stopIfTrue="1">
       <formula>$K25="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="126" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="130" stopIfTrue="1">
       <formula>$K25="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="127" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="131" stopIfTrue="1">
       <formula>$K25="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="128" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="132" stopIfTrue="1">
       <formula>OR($K25="CLOSED",$K25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:M26">
-    <cfRule type="expression" dxfId="115" priority="121" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="125" stopIfTrue="1">
       <formula>$K26="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="122" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="126" stopIfTrue="1">
       <formula>$K26="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="123" stopIfTrue="1">
+    <cfRule type="expression" dxfId="117" priority="127" stopIfTrue="1">
       <formula>$K26="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="124" stopIfTrue="1">
+    <cfRule type="expression" dxfId="116" priority="128" stopIfTrue="1">
       <formula>OR($K26="CLOSED",$K26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:M28">
-    <cfRule type="expression" dxfId="111" priority="117" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="121" stopIfTrue="1">
       <formula>$K27="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="118" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="122" stopIfTrue="1">
       <formula>$K27="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="119" stopIfTrue="1">
+    <cfRule type="expression" dxfId="113" priority="123" stopIfTrue="1">
       <formula>$K27="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="120" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="124" stopIfTrue="1">
       <formula>OR($K27="CLOSED",$K27="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M30">
+    <cfRule type="expression" dxfId="111" priority="117" stopIfTrue="1">
+      <formula>$K29="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="110" priority="118" stopIfTrue="1">
+      <formula>$K29="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="109" priority="119" stopIfTrue="1">
+      <formula>$K29="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="120" stopIfTrue="1">
+      <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29:M29">
     <cfRule type="expression" dxfId="107" priority="113" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
@@ -10279,270 +10240,270 @@
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A29:M29">
+  <conditionalFormatting sqref="A31:M31">
     <cfRule type="expression" dxfId="103" priority="109" stopIfTrue="1">
-      <formula>$K29="HANG-UP"</formula>
+      <formula>$K31="HANG-UP"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="102" priority="110" stopIfTrue="1">
-      <formula>$K29="PLAN"</formula>
+      <formula>$K31="PLAN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="101" priority="111" stopIfTrue="1">
-      <formula>$K29="OPEN"</formula>
+      <formula>$K31="OPEN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="100" priority="112" stopIfTrue="1">
-      <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31:M31">
-    <cfRule type="expression" dxfId="99" priority="105" stopIfTrue="1">
-      <formula>$K31="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="98" priority="106" stopIfTrue="1">
-      <formula>$K31="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="97" priority="107" stopIfTrue="1">
-      <formula>$K31="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="96" priority="108" stopIfTrue="1">
       <formula>OR($K31="CLOSED",$K31="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:M38">
-    <cfRule type="expression" dxfId="95" priority="77" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="81" stopIfTrue="1">
       <formula>$K38="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="78" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="82" stopIfTrue="1">
       <formula>$K38="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="79" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="83" stopIfTrue="1">
       <formula>$K38="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="80" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="84" stopIfTrue="1">
       <formula>OR($K38="CLOSED",$K38="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:M39">
-    <cfRule type="expression" dxfId="91" priority="73" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="77" stopIfTrue="1">
       <formula>$K39="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="78" stopIfTrue="1">
       <formula>$K39="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="75" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="79" stopIfTrue="1">
       <formula>$K39="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="80" stopIfTrue="1">
       <formula>OR($K39="CLOSED",$K39="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:M40">
-    <cfRule type="expression" dxfId="87" priority="69" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="73" stopIfTrue="1">
       <formula>$K40="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="74" stopIfTrue="1">
       <formula>$K40="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="71" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="75" stopIfTrue="1">
       <formula>$K40="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="76" stopIfTrue="1">
       <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:M41">
-    <cfRule type="expression" dxfId="83" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="69" stopIfTrue="1">
       <formula>$K41="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="70" stopIfTrue="1">
       <formula>$K41="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="71" stopIfTrue="1">
       <formula>$K41="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="72" stopIfTrue="1">
       <formula>OR($K41="CLOSED",$K41="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:M42">
-    <cfRule type="expression" dxfId="79" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="65" stopIfTrue="1">
       <formula>$K42="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="66" stopIfTrue="1">
       <formula>$K42="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="67" stopIfTrue="1">
       <formula>$K42="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="68" stopIfTrue="1">
       <formula>OR($K42="CLOSED",$K42="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:M44">
-    <cfRule type="expression" dxfId="75" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="61" stopIfTrue="1">
       <formula>$K43="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="62" stopIfTrue="1">
       <formula>$K43="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="63" stopIfTrue="1">
       <formula>$K43="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="64" stopIfTrue="1">
       <formula>OR($K43="CLOSED",$K43="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45:M46">
-    <cfRule type="expression" dxfId="71" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="57" stopIfTrue="1">
       <formula>$K45="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="58" stopIfTrue="1">
       <formula>$K45="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="59" stopIfTrue="1">
       <formula>$K45="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="60" stopIfTrue="1">
       <formula>OR($K45="CLOSED",$K45="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:M47">
-    <cfRule type="expression" dxfId="67" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="53" stopIfTrue="1">
       <formula>$K47="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="54" stopIfTrue="1">
       <formula>$K47="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="55" stopIfTrue="1">
       <formula>$K47="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="56" stopIfTrue="1">
       <formula>OR($K47="CLOSED",$K47="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:M48">
-    <cfRule type="expression" dxfId="63" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="49" stopIfTrue="1">
       <formula>$K48="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="50" stopIfTrue="1">
       <formula>$K48="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="51" stopIfTrue="1">
       <formula>$K48="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="52" stopIfTrue="1">
       <formula>OR($K48="CLOSED",$K48="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:M49">
-    <cfRule type="expression" dxfId="59" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="45" stopIfTrue="1">
       <formula>$K49="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="46" stopIfTrue="1">
       <formula>$K49="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="47" stopIfTrue="1">
       <formula>$K49="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="48" stopIfTrue="1">
       <formula>OR($K49="CLOSED",$K49="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:M50">
-    <cfRule type="expression" dxfId="55" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="41" stopIfTrue="1">
       <formula>$K50="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="42" stopIfTrue="1">
       <formula>$K50="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="43" stopIfTrue="1">
       <formula>$K50="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="44" stopIfTrue="1">
       <formula>OR($K50="CLOSED",$K50="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:M51">
-    <cfRule type="expression" dxfId="51" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="37" stopIfTrue="1">
       <formula>$K51="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="38" stopIfTrue="1">
       <formula>$K51="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="39" stopIfTrue="1">
       <formula>$K51="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="40" stopIfTrue="1">
       <formula>OR($K51="CLOSED",$K51="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:M52">
-    <cfRule type="expression" dxfId="47" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="33" stopIfTrue="1">
       <formula>$K52="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="34" stopIfTrue="1">
       <formula>$K52="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="35" stopIfTrue="1">
       <formula>$K52="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="36" stopIfTrue="1">
       <formula>OR($K52="CLOSED",$K52="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:M53">
-    <cfRule type="expression" dxfId="43" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="29" stopIfTrue="1">
       <formula>$K53="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="30" stopIfTrue="1">
       <formula>$K53="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="31" stopIfTrue="1">
       <formula>$K53="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="32" stopIfTrue="1">
       <formula>OR($K53="CLOSED",$K53="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:M54">
-    <cfRule type="expression" dxfId="39" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="25" stopIfTrue="1">
       <formula>$K54="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="26" stopIfTrue="1">
       <formula>$K54="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="27" stopIfTrue="1">
       <formula>$K54="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="28" stopIfTrue="1">
       <formula>OR($K54="CLOSED",$K54="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:M55">
-    <cfRule type="expression" dxfId="35" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="21" stopIfTrue="1">
       <formula>$K55="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="22" stopIfTrue="1">
       <formula>$K55="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="23" stopIfTrue="1">
       <formula>$K55="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="24" stopIfTrue="1">
       <formula>OR($K55="CLOSED",$K55="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56:M56">
+    <cfRule type="expression" dxfId="35" priority="17" stopIfTrue="1">
+      <formula>$K56="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="18" stopIfTrue="1">
+      <formula>$K56="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="19" stopIfTrue="1">
+      <formula>$K56="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="20" stopIfTrue="1">
+      <formula>OR($K56="CLOSED",$K56="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A57:M57">
     <cfRule type="expression" dxfId="31" priority="13" stopIfTrue="1">
-      <formula>$K56="HANG-UP"</formula>
+      <formula>$K57="HANG-UP"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="30" priority="14" stopIfTrue="1">
-      <formula>$K56="PLAN"</formula>
+      <formula>$K57="PLAN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="29" priority="15" stopIfTrue="1">
-      <formula>$K56="OPEN"</formula>
+      <formula>$K57="OPEN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="28" priority="16" stopIfTrue="1">
-      <formula>OR($K56="CLOSED",$K56="CANCEL")</formula>
+      <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:M57">
@@ -10559,7 +10520,7 @@
       <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A57:M57">
+  <conditionalFormatting sqref="E57">
     <cfRule type="expression" dxfId="23" priority="5" stopIfTrue="1">
       <formula>$K57="HANG-UP"</formula>
     </cfRule>
@@ -10573,18 +10534,18 @@
       <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E57">
+  <conditionalFormatting sqref="A58:M58">
     <cfRule type="expression" dxfId="19" priority="1" stopIfTrue="1">
-      <formula>$K57="HANG-UP"</formula>
+      <formula>$K58="HANG-UP"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="18" priority="2" stopIfTrue="1">
-      <formula>$K57="PLAN"</formula>
+      <formula>$K58="PLAN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3" stopIfTrue="1">
-      <formula>$K57="OPEN"</formula>
+      <formula>$K58="OPEN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="4" stopIfTrue="1">
-      <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
+      <formula>OR($K58="CLOSED",$K58="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -10601,8 +10562,9 @@
   <hyperlinks>
     <hyperlink ref="D55" r:id="rId1"/>
     <hyperlink ref="D56" r:id="rId2"/>
+    <hyperlink ref="D58" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId4"/>
 </worksheet>
 </file>
--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -852,11 +852,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Coord加入到系统管理，实现Coord自动负载均衡和监控（catalogaddr参数自动保存）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">提供sequence、time、count等field自动取值功能
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1470,6 +1465,11 @@
   </si>
   <si>
     <t xml:space="preserve">SEQUOIADBMAINSTREAM-850 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Coord加入到系统管理，实现Coord自动负载均衡和监控（所有coord节点的catalogaddr参数自动保存）
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1841,35 +1841,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="204">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="200">
     <dxf>
       <fill>
         <patternFill>
@@ -3776,7 +3748,7 @@
         <v>8</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>58</v>
@@ -3980,7 +3952,7 @@
         <v>28</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -4714,16 +4686,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M169">
-    <cfRule type="expression" dxfId="203" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="199" priority="1" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="202" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="198" priority="2" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="201" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="197" priority="3" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="200" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="196" priority="4" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5028,7 +5000,7 @@
         <v>30</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -5898,16 +5870,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L185">
-    <cfRule type="expression" dxfId="199" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="195" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="198" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="194" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="197" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="193" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="196" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="192" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5990,17 +5962,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="40.5">
+    <row r="2" spans="1:13" ht="54">
       <c r="A2" s="1">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>167</v>
+        <v>291</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>64</v>
@@ -6024,7 +5996,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -6049,7 +6021,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
@@ -6061,7 +6033,7 @@
         <v>22</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I4" s="29">
         <v>8</v>
@@ -6076,7 +6048,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -6103,12 +6075,12 @@
         <v>7</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>49</v>
@@ -6132,7 +6104,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -6144,7 +6116,7 @@
         <v>16</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -6157,7 +6129,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -6169,7 +6141,7 @@
         <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -6182,7 +6154,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -6194,7 +6166,7 @@
         <v>16</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -6207,12 +6179,12 @@
         <v>16</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="28"/>
       <c r="E10" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F10" s="29" t="s">
         <v>41</v>
@@ -6236,7 +6208,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="28"/>
@@ -6248,7 +6220,7 @@
         <v>16</v>
       </c>
       <c r="H11" s="29" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I11" s="29"/>
       <c r="J11" s="29"/>
@@ -6261,7 +6233,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -6286,7 +6258,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -6311,7 +6283,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -6323,7 +6295,7 @@
         <v>16</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -6336,12 +6308,12 @@
         <v>21</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>49</v>
@@ -6390,7 +6362,7 @@
         <v>23</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -6415,7 +6387,7 @@
         <v>24</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
@@ -6427,7 +6399,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -6440,7 +6412,7 @@
         <v>26</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
@@ -6452,7 +6424,7 @@
         <v>16</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -6465,12 +6437,12 @@
         <v>28</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>49</v>
@@ -6494,7 +6466,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -6506,7 +6478,7 @@
         <v>16</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -6519,7 +6491,7 @@
         <v>30</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -6544,7 +6516,7 @@
         <v>31</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -6556,7 +6528,7 @@
         <v>16</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -6569,12 +6541,12 @@
         <v>34</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>75</v>
@@ -6583,7 +6555,7 @@
         <v>22</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I24" s="2">
         <v>2</v>
@@ -6598,12 +6570,12 @@
         <v>35</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>75</v>
@@ -6612,7 +6584,7 @@
         <v>22</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I25" s="2">
         <v>3</v>
@@ -6627,7 +6599,7 @@
         <v>36</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -6639,7 +6611,7 @@
         <v>22</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I26" s="2">
         <v>18</v>
@@ -6654,7 +6626,7 @@
         <v>38</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -6666,7 +6638,7 @@
         <v>12</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I27" s="2">
         <v>33</v>
@@ -6681,7 +6653,7 @@
         <v>39</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -6693,7 +6665,7 @@
         <v>12</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I28" s="2">
         <v>10</v>
@@ -6708,7 +6680,7 @@
         <v>40</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -6720,7 +6692,7 @@
         <v>12</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I29" s="8">
         <v>10</v>
@@ -6735,7 +6707,7 @@
         <v>42</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -6747,7 +6719,7 @@
         <v>22</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I30" s="8">
         <v>8</v>
@@ -6762,7 +6734,7 @@
         <v>43</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -6774,7 +6746,7 @@
         <v>12</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I31" s="8">
         <v>12</v>
@@ -6789,7 +6761,7 @@
         <v>44</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -6801,7 +6773,7 @@
         <v>22</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I32" s="8">
         <v>4</v>
@@ -6816,7 +6788,7 @@
         <v>47</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -6828,7 +6800,7 @@
         <v>12</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I33" s="8">
         <v>7</v>
@@ -6843,7 +6815,7 @@
         <v>48</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -6855,7 +6827,7 @@
         <v>12</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I34" s="8">
         <v>3</v>
@@ -6870,7 +6842,7 @@
         <v>49</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -6882,7 +6854,7 @@
         <v>12</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I35" s="8">
         <v>4</v>
@@ -6897,7 +6869,7 @@
         <v>54</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -6923,13 +6895,13 @@
         <v>83</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D37" s="35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>14</v>
@@ -6944,7 +6916,7 @@
         <v>18</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>58</v>
@@ -6957,14 +6929,14 @@
         <v>58</v>
       </c>
       <c r="B38" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>265</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>266</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>41</v>
@@ -6973,7 +6945,7 @@
         <v>22</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I38" s="8">
         <v>120</v>
@@ -6990,14 +6962,14 @@
         <v>59</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>64</v>
@@ -7006,13 +6978,13 @@
         <v>22</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I39" s="8">
         <v>90</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K39" s="8" t="s">
         <v>58</v>
@@ -7025,12 +6997,12 @@
         <v>60</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>64</v>
@@ -7039,13 +7011,13 @@
         <v>22</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I40" s="8">
         <v>20</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K40" s="8" t="s">
         <v>58</v>
@@ -7058,12 +7030,12 @@
         <v>61</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
       <c r="E41" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>64</v>
@@ -7072,13 +7044,13 @@
         <v>22</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I41" s="8">
         <v>100</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>58</v>
@@ -7091,12 +7063,12 @@
         <v>62</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
       <c r="E42" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>64</v>
@@ -7105,13 +7077,13 @@
         <v>22</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I42" s="8">
         <v>140</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K42" s="8" t="s">
         <v>58</v>
@@ -7124,12 +7096,12 @@
         <v>63</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
       <c r="E43" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>14</v>
@@ -7138,7 +7110,7 @@
         <v>12</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I43" s="8">
         <v>20</v>
@@ -7156,11 +7128,11 @@
         <v>39</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>32</v>
@@ -7673,58 +7645,58 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M187">
-    <cfRule type="expression" dxfId="15" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="191" priority="21" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="190" priority="22" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="189" priority="23" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="188" priority="24" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:M7">
-    <cfRule type="expression" dxfId="11" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="187" priority="17" stopIfTrue="1">
       <formula>$K7="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="186" priority="18" stopIfTrue="1">
       <formula>$K7="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="185" priority="19" stopIfTrue="1">
       <formula>$K7="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="184" priority="20" stopIfTrue="1">
       <formula>OR($K7="CLOSED",$K7="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:M37">
-    <cfRule type="expression" dxfId="7" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="183" priority="13" stopIfTrue="1">
       <formula>$K37="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="182" priority="14" stopIfTrue="1">
       <formula>$K37="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="181" priority="15" stopIfTrue="1">
       <formula>$K37="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="180" priority="16" stopIfTrue="1">
       <formula>OR($K37="CLOSED",$K37="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:M44">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="179" priority="1" stopIfTrue="1">
       <formula>$K44="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="178" priority="2" stopIfTrue="1">
       <formula>$K44="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="177" priority="3" stopIfTrue="1">
       <formula>$K44="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="176" priority="4" stopIfTrue="1">
       <formula>OR($K44="CLOSED",$K44="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8813,7 +8785,7 @@
         <v>28</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>79</v>
@@ -8826,7 +8798,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -8846,7 +8818,7 @@
         <v>8</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>79</v>
@@ -8859,7 +8831,7 @@
         <v>9</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -8873,7 +8845,7 @@
         <v>22</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I34" s="2">
         <v>8</v>
@@ -8892,7 +8864,7 @@
         <v>15</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -8912,7 +8884,7 @@
         <v>80</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>79</v>
@@ -8925,7 +8897,7 @@
         <v>25</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -8945,7 +8917,7 @@
         <v>4</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>79</v>
@@ -8958,14 +8930,14 @@
         <v>11</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>32</v>
@@ -8980,7 +8952,7 @@
         <v>3</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>79</v>
@@ -8993,14 +8965,14 @@
         <v>27</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>32</v>
@@ -9015,7 +8987,7 @@
         <v>3</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>79</v>
@@ -9030,14 +9002,14 @@
         <v>46</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>64</v>
@@ -9046,13 +9018,13 @@
         <v>22</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I39" s="8">
         <v>5</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K39" s="8" t="s">
         <v>79</v>
@@ -9069,7 +9041,7 @@
         <v>55</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -9083,7 +9055,7 @@
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
       <c r="J40" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K40" s="8" t="s">
         <v>79</v>
@@ -9096,7 +9068,7 @@
         <v>53</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
@@ -9110,7 +9082,7 @@
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
       <c r="J41" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>79</v>
@@ -9123,12 +9095,12 @@
         <v>37</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
       <c r="E42" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>64</v>
@@ -9137,7 +9109,7 @@
         <v>22</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I42" s="2">
         <v>15</v>
@@ -9154,14 +9126,14 @@
         <v>32</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>64</v>
@@ -9176,7 +9148,7 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>79</v>
@@ -9191,12 +9163,12 @@
         <v>33</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
       <c r="E44" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>64</v>
@@ -9205,13 +9177,13 @@
         <v>12</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I44" s="2">
         <v>5</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>79</v>
@@ -9306,7 +9278,7 @@
         <v>2</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>79</v>
@@ -9337,7 +9309,7 @@
         <v>15</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>79</v>
@@ -9350,14 +9322,14 @@
         <v>41</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>64</v>
@@ -9366,7 +9338,7 @@
         <v>22</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I49" s="8">
         <v>5</v>
@@ -9383,14 +9355,14 @@
         <v>52</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>11</v>
@@ -9399,13 +9371,13 @@
         <v>22</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I50" s="8">
         <v>5</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K50" s="8" t="s">
         <v>79</v>
@@ -9418,11 +9390,11 @@
         <v>36</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E51" s="8"/>
       <c r="F51" s="2" t="s">
@@ -9438,7 +9410,7 @@
         <v>2</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>79</v>
@@ -9518,7 +9490,7 @@
         <v>28</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
@@ -9544,14 +9516,14 @@
         <v>55</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="35" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>64</v>
@@ -9560,13 +9532,13 @@
         <v>22</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I55" s="8">
         <v>7</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K55" s="8" t="s">
         <v>79</v>
@@ -9579,14 +9551,14 @@
         <v>50</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="35" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>64</v>
@@ -9595,13 +9567,13 @@
         <v>12</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I56" s="8">
         <v>3</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K56" s="8" t="s">
         <v>79</v>
@@ -9614,14 +9586,14 @@
         <v>57</v>
       </c>
       <c r="B57" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="C57" s="28" t="s">
         <v>263</v>
-      </c>
-      <c r="C57" s="28" t="s">
-        <v>264</v>
       </c>
       <c r="D57" s="28"/>
       <c r="E57" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F57" s="29" t="s">
         <v>75</v>
@@ -9649,16 +9621,16 @@
         <v>45</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C58" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="D58" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="E58" s="8" t="s">
         <v>278</v>
-      </c>
-      <c r="D58" s="35" t="s">
-        <v>291</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>279</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>75</v>
@@ -9667,13 +9639,13 @@
         <v>12</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I58" s="8">
         <v>3</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K58" s="8" t="s">
         <v>79</v>
@@ -9933,618 +9905,618 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:M9 A32:M37">
-    <cfRule type="expression" dxfId="191" priority="197" stopIfTrue="1">
+    <cfRule type="expression" dxfId="175" priority="197" stopIfTrue="1">
       <formula>$K9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="190" priority="198" stopIfTrue="1">
+    <cfRule type="expression" dxfId="174" priority="198" stopIfTrue="1">
       <formula>$K9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="189" priority="199" stopIfTrue="1">
+    <cfRule type="expression" dxfId="173" priority="199" stopIfTrue="1">
       <formula>$K9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="188" priority="200" stopIfTrue="1">
+    <cfRule type="expression" dxfId="172" priority="200" stopIfTrue="1">
       <formula>OR($K9="CLOSED",$K9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:M10">
-    <cfRule type="expression" dxfId="187" priority="193" stopIfTrue="1">
+    <cfRule type="expression" dxfId="171" priority="193" stopIfTrue="1">
       <formula>$K10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="186" priority="194" stopIfTrue="1">
+    <cfRule type="expression" dxfId="170" priority="194" stopIfTrue="1">
       <formula>$K10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="185" priority="195" stopIfTrue="1">
+    <cfRule type="expression" dxfId="169" priority="195" stopIfTrue="1">
       <formula>$K10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="184" priority="196" stopIfTrue="1">
+    <cfRule type="expression" dxfId="168" priority="196" stopIfTrue="1">
       <formula>OR($K10="CLOSED",$K10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:M11">
-    <cfRule type="expression" dxfId="183" priority="189" stopIfTrue="1">
+    <cfRule type="expression" dxfId="167" priority="189" stopIfTrue="1">
       <formula>$K11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="182" priority="190" stopIfTrue="1">
+    <cfRule type="expression" dxfId="166" priority="190" stopIfTrue="1">
       <formula>$K11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="181" priority="191" stopIfTrue="1">
+    <cfRule type="expression" dxfId="165" priority="191" stopIfTrue="1">
       <formula>$K11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="180" priority="192" stopIfTrue="1">
+    <cfRule type="expression" dxfId="164" priority="192" stopIfTrue="1">
       <formula>OR($K11="CLOSED",$K11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:M12">
-    <cfRule type="expression" dxfId="179" priority="185" stopIfTrue="1">
+    <cfRule type="expression" dxfId="163" priority="185" stopIfTrue="1">
       <formula>$K12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="178" priority="186" stopIfTrue="1">
+    <cfRule type="expression" dxfId="162" priority="186" stopIfTrue="1">
       <formula>$K12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="177" priority="187" stopIfTrue="1">
+    <cfRule type="expression" dxfId="161" priority="187" stopIfTrue="1">
       <formula>$K12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="176" priority="188" stopIfTrue="1">
+    <cfRule type="expression" dxfId="160" priority="188" stopIfTrue="1">
       <formula>OR($K12="CLOSED",$K12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:M13">
-    <cfRule type="expression" dxfId="175" priority="181" stopIfTrue="1">
+    <cfRule type="expression" dxfId="159" priority="181" stopIfTrue="1">
       <formula>$K13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="174" priority="182" stopIfTrue="1">
+    <cfRule type="expression" dxfId="158" priority="182" stopIfTrue="1">
       <formula>$K13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="183" stopIfTrue="1">
+    <cfRule type="expression" dxfId="157" priority="183" stopIfTrue="1">
       <formula>$K13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="172" priority="184" stopIfTrue="1">
+    <cfRule type="expression" dxfId="156" priority="184" stopIfTrue="1">
       <formula>OR($K13="CLOSED",$K13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:M14">
-    <cfRule type="expression" dxfId="171" priority="177" stopIfTrue="1">
+    <cfRule type="expression" dxfId="155" priority="177" stopIfTrue="1">
       <formula>$K14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="170" priority="178" stopIfTrue="1">
+    <cfRule type="expression" dxfId="154" priority="178" stopIfTrue="1">
       <formula>$K14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="169" priority="179" stopIfTrue="1">
+    <cfRule type="expression" dxfId="153" priority="179" stopIfTrue="1">
       <formula>$K14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="168" priority="180" stopIfTrue="1">
+    <cfRule type="expression" dxfId="152" priority="180" stopIfTrue="1">
       <formula>OR($K14="CLOSED",$K14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:M15">
-    <cfRule type="expression" dxfId="167" priority="173" stopIfTrue="1">
+    <cfRule type="expression" dxfId="151" priority="173" stopIfTrue="1">
       <formula>$K15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="166" priority="174" stopIfTrue="1">
+    <cfRule type="expression" dxfId="150" priority="174" stopIfTrue="1">
       <formula>$K15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="165" priority="175" stopIfTrue="1">
+    <cfRule type="expression" dxfId="149" priority="175" stopIfTrue="1">
       <formula>$K15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="164" priority="176" stopIfTrue="1">
+    <cfRule type="expression" dxfId="148" priority="176" stopIfTrue="1">
       <formula>OR($K15="CLOSED",$K15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:M16">
-    <cfRule type="expression" dxfId="163" priority="169" stopIfTrue="1">
+    <cfRule type="expression" dxfId="147" priority="169" stopIfTrue="1">
       <formula>$K16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="162" priority="170" stopIfTrue="1">
+    <cfRule type="expression" dxfId="146" priority="170" stopIfTrue="1">
       <formula>$K16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="161" priority="171" stopIfTrue="1">
+    <cfRule type="expression" dxfId="145" priority="171" stopIfTrue="1">
       <formula>$K16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="160" priority="172" stopIfTrue="1">
+    <cfRule type="expression" dxfId="144" priority="172" stopIfTrue="1">
       <formula>OR($K16="CLOSED",$K16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:M17">
-    <cfRule type="expression" dxfId="159" priority="165" stopIfTrue="1">
+    <cfRule type="expression" dxfId="143" priority="165" stopIfTrue="1">
       <formula>$K17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="158" priority="166" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="166" stopIfTrue="1">
       <formula>$K17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="157" priority="167" stopIfTrue="1">
+    <cfRule type="expression" dxfId="141" priority="167" stopIfTrue="1">
       <formula>$K17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="156" priority="168" stopIfTrue="1">
+    <cfRule type="expression" dxfId="140" priority="168" stopIfTrue="1">
       <formula>OR($K17="CLOSED",$K17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:M18">
-    <cfRule type="expression" dxfId="155" priority="161" stopIfTrue="1">
+    <cfRule type="expression" dxfId="139" priority="161" stopIfTrue="1">
       <formula>$K18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="154" priority="162" stopIfTrue="1">
+    <cfRule type="expression" dxfId="138" priority="162" stopIfTrue="1">
       <formula>$K18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="153" priority="163" stopIfTrue="1">
+    <cfRule type="expression" dxfId="137" priority="163" stopIfTrue="1">
       <formula>$K18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="152" priority="164" stopIfTrue="1">
+    <cfRule type="expression" dxfId="136" priority="164" stopIfTrue="1">
       <formula>OR($K18="CLOSED",$K18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:M19">
-    <cfRule type="expression" dxfId="151" priority="157" stopIfTrue="1">
+    <cfRule type="expression" dxfId="135" priority="157" stopIfTrue="1">
       <formula>$K19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="150" priority="158" stopIfTrue="1">
+    <cfRule type="expression" dxfId="134" priority="158" stopIfTrue="1">
       <formula>$K19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="149" priority="159" stopIfTrue="1">
+    <cfRule type="expression" dxfId="133" priority="159" stopIfTrue="1">
       <formula>$K19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="148" priority="160" stopIfTrue="1">
+    <cfRule type="expression" dxfId="132" priority="160" stopIfTrue="1">
       <formula>OR($K19="CLOSED",$K19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:M20">
-    <cfRule type="expression" dxfId="147" priority="153" stopIfTrue="1">
+    <cfRule type="expression" dxfId="131" priority="153" stopIfTrue="1">
       <formula>$K20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="146" priority="154" stopIfTrue="1">
+    <cfRule type="expression" dxfId="130" priority="154" stopIfTrue="1">
       <formula>$K20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="145" priority="155" stopIfTrue="1">
+    <cfRule type="expression" dxfId="129" priority="155" stopIfTrue="1">
       <formula>$K20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="144" priority="156" stopIfTrue="1">
+    <cfRule type="expression" dxfId="128" priority="156" stopIfTrue="1">
       <formula>OR($K20="CLOSED",$K20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:M21">
-    <cfRule type="expression" dxfId="143" priority="149" stopIfTrue="1">
+    <cfRule type="expression" dxfId="127" priority="149" stopIfTrue="1">
       <formula>$K21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="142" priority="150" stopIfTrue="1">
+    <cfRule type="expression" dxfId="126" priority="150" stopIfTrue="1">
       <formula>$K21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="141" priority="151" stopIfTrue="1">
+    <cfRule type="expression" dxfId="125" priority="151" stopIfTrue="1">
       <formula>$K21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="140" priority="152" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="152" stopIfTrue="1">
       <formula>OR($K21="CLOSED",$K21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:M23">
-    <cfRule type="expression" dxfId="139" priority="145" stopIfTrue="1">
+    <cfRule type="expression" dxfId="123" priority="145" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="146" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="146" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="137" priority="147" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="147" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="148" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="148" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:I22">
-    <cfRule type="expression" dxfId="135" priority="141" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="141" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="142" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="142" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="133" priority="143" stopIfTrue="1">
+    <cfRule type="expression" dxfId="117" priority="143" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="144" stopIfTrue="1">
+    <cfRule type="expression" dxfId="116" priority="144" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="131" priority="137" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="137" stopIfTrue="1">
       <formula>$K23="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="138" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="138" stopIfTrue="1">
       <formula>$K23="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="139" stopIfTrue="1">
+    <cfRule type="expression" dxfId="113" priority="139" stopIfTrue="1">
       <formula>$K23="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="128" priority="140" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="140" stopIfTrue="1">
       <formula>OR($K23="CLOSED",$K23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:M25">
-    <cfRule type="expression" dxfId="127" priority="133" stopIfTrue="1">
+    <cfRule type="expression" dxfId="111" priority="133" stopIfTrue="1">
       <formula>$K24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="134" stopIfTrue="1">
+    <cfRule type="expression" dxfId="110" priority="134" stopIfTrue="1">
       <formula>$K24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="135" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="135" stopIfTrue="1">
       <formula>$K24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="136" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="136" stopIfTrue="1">
       <formula>OR($K24="CLOSED",$K24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="123" priority="129" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="129" stopIfTrue="1">
       <formula>$K25="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="130" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="130" stopIfTrue="1">
       <formula>$K25="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="131" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="131" stopIfTrue="1">
       <formula>$K25="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="132" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="132" stopIfTrue="1">
       <formula>OR($K25="CLOSED",$K25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:M26">
-    <cfRule type="expression" dxfId="119" priority="125" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="125" stopIfTrue="1">
       <formula>$K26="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="126" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="126" stopIfTrue="1">
       <formula>$K26="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="127" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="127" stopIfTrue="1">
       <formula>$K26="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="128" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="128" stopIfTrue="1">
       <formula>OR($K26="CLOSED",$K26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:M28">
-    <cfRule type="expression" dxfId="115" priority="121" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="121" stopIfTrue="1">
       <formula>$K27="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="122" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="122" stopIfTrue="1">
       <formula>$K27="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="123" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="123" stopIfTrue="1">
       <formula>$K27="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="124" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="124" stopIfTrue="1">
       <formula>OR($K27="CLOSED",$K27="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M30">
-    <cfRule type="expression" dxfId="111" priority="117" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="117" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="118" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="118" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="119" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="119" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="120" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="120" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M29">
-    <cfRule type="expression" dxfId="107" priority="113" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="113" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="114" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="114" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="115" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="115" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="116" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="116" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:M31">
-    <cfRule type="expression" dxfId="103" priority="109" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="109" stopIfTrue="1">
       <formula>$K31="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="110" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="110" stopIfTrue="1">
       <formula>$K31="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="111" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="111" stopIfTrue="1">
       <formula>$K31="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="112" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="112" stopIfTrue="1">
       <formula>OR($K31="CLOSED",$K31="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:M38">
-    <cfRule type="expression" dxfId="99" priority="81" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="81" stopIfTrue="1">
       <formula>$K38="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="82" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="82" stopIfTrue="1">
       <formula>$K38="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="83" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="83" stopIfTrue="1">
       <formula>$K38="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="84" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="84" stopIfTrue="1">
       <formula>OR($K38="CLOSED",$K38="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:M39">
-    <cfRule type="expression" dxfId="95" priority="77" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="77" stopIfTrue="1">
       <formula>$K39="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="78" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="78" stopIfTrue="1">
       <formula>$K39="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="79" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="79" stopIfTrue="1">
       <formula>$K39="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="80" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="80" stopIfTrue="1">
       <formula>OR($K39="CLOSED",$K39="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:M40">
-    <cfRule type="expression" dxfId="91" priority="73" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="73" stopIfTrue="1">
       <formula>$K40="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="74" stopIfTrue="1">
       <formula>$K40="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="75" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="75" stopIfTrue="1">
       <formula>$K40="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="76" stopIfTrue="1">
       <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:M41">
-    <cfRule type="expression" dxfId="87" priority="69" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="69" stopIfTrue="1">
       <formula>$K41="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="70" stopIfTrue="1">
       <formula>$K41="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="71" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="71" stopIfTrue="1">
       <formula>$K41="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="72" stopIfTrue="1">
       <formula>OR($K41="CLOSED",$K41="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:M42">
-    <cfRule type="expression" dxfId="83" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="65" stopIfTrue="1">
       <formula>$K42="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="66" stopIfTrue="1">
       <formula>$K42="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="67" stopIfTrue="1">
       <formula>$K42="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="68" stopIfTrue="1">
       <formula>OR($K42="CLOSED",$K42="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:M44">
-    <cfRule type="expression" dxfId="79" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="61" stopIfTrue="1">
       <formula>$K43="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="62" stopIfTrue="1">
       <formula>$K43="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="63" stopIfTrue="1">
       <formula>$K43="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="64" stopIfTrue="1">
       <formula>OR($K43="CLOSED",$K43="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45:M46">
-    <cfRule type="expression" dxfId="75" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="57" stopIfTrue="1">
       <formula>$K45="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="58" stopIfTrue="1">
       <formula>$K45="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="59" stopIfTrue="1">
       <formula>$K45="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="60" stopIfTrue="1">
       <formula>OR($K45="CLOSED",$K45="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:M47">
-    <cfRule type="expression" dxfId="71" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="53" stopIfTrue="1">
       <formula>$K47="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="54" stopIfTrue="1">
       <formula>$K47="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="55" stopIfTrue="1">
       <formula>$K47="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="56" stopIfTrue="1">
       <formula>OR($K47="CLOSED",$K47="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:M48">
-    <cfRule type="expression" dxfId="67" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="49" stopIfTrue="1">
       <formula>$K48="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="50" stopIfTrue="1">
       <formula>$K48="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="51" stopIfTrue="1">
       <formula>$K48="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="52" stopIfTrue="1">
       <formula>OR($K48="CLOSED",$K48="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:M49">
-    <cfRule type="expression" dxfId="63" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
       <formula>$K49="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
       <formula>$K49="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
       <formula>$K49="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
       <formula>OR($K49="CLOSED",$K49="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:M50">
-    <cfRule type="expression" dxfId="59" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
       <formula>$K50="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
       <formula>$K50="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="43" stopIfTrue="1">
       <formula>$K50="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="44" stopIfTrue="1">
       <formula>OR($K50="CLOSED",$K50="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:M51">
-    <cfRule type="expression" dxfId="55" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="37" stopIfTrue="1">
       <formula>$K51="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="38" stopIfTrue="1">
       <formula>$K51="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="39" stopIfTrue="1">
       <formula>$K51="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="40" stopIfTrue="1">
       <formula>OR($K51="CLOSED",$K51="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:M52">
-    <cfRule type="expression" dxfId="51" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
       <formula>$K52="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
       <formula>$K52="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
       <formula>$K52="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
       <formula>OR($K52="CLOSED",$K52="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:M53">
-    <cfRule type="expression" dxfId="47" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
       <formula>$K53="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
       <formula>$K53="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="31" stopIfTrue="1">
       <formula>$K53="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
       <formula>OR($K53="CLOSED",$K53="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:M54">
-    <cfRule type="expression" dxfId="43" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
       <formula>$K54="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
       <formula>$K54="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="27" stopIfTrue="1">
       <formula>$K54="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="28" stopIfTrue="1">
       <formula>OR($K54="CLOSED",$K54="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:M55">
-    <cfRule type="expression" dxfId="39" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
       <formula>$K55="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
       <formula>$K55="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
       <formula>$K55="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
       <formula>OR($K55="CLOSED",$K55="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56:M56">
-    <cfRule type="expression" dxfId="35" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
       <formula>$K56="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
       <formula>$K56="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
       <formula>$K56="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
       <formula>OR($K56="CLOSED",$K56="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:M57">
-    <cfRule type="expression" dxfId="31" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
       <formula>$K57="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="14" stopIfTrue="1">
       <formula>$K57="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="15" stopIfTrue="1">
       <formula>$K57="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
       <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:M57">
-    <cfRule type="expression" dxfId="27" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
       <formula>$K57="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
       <formula>$K57="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
       <formula>$K57="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
       <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E57">
-    <cfRule type="expression" dxfId="23" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
       <formula>$K57="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
       <formula>$K57="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
       <formula>$K57="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
       <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:M58">
-    <cfRule type="expression" dxfId="19" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>$K58="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
       <formula>$K58="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>$K58="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
       <formula>OR($K58="CLOSED",$K58="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$M$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2015年'!$A$1:$M$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2015年'!$A$1:$M$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$M$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="355">
   <si>
     <r>
       <t>描述</t>
@@ -839,10 +839,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>归属</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">支持存储大对象（LOB、文件系统、分布式KV）
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -918,11 +914,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">索引压缩优化（相同Key保存引用）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Query性能优化（端对端全程序优化，减少内存拷贝，io和锁延时）
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -938,11 +929,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">主子表操作优化（1、主表下直接创建分区；2、只能attach被detach的分区；3、保持分区有效性）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">自动更改节点运行的用户（对于正式安装的版本，检测是否存在sdbadmin，如果存在则用该用户启动）
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1123,16 +1109,6 @@
   </si>
   <si>
     <t xml:space="preserve">读取LOB的完整性保证（如何保证在多幅本中的LOB是同一LOB对象，尤其是在LOB支持随机写时）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Domain中增加add group, del group操作
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">完善collection alter功能
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1349,106 +1325,427 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">数据中心灾备
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RTN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">第二代存储引擎开发
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalog元数据操作在并发时保证一致性要求
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在数据节点创建CS时会加Bucket锁， 通过Bucket锁解决并发创建的冲突问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过truncate来优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">通过post event到游标的线程，并能激活该线程立即处理
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2015Q2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM HA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注册成OM业务，能访问自身监控页面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-769 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武赟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林友滨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴易达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李伟超</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-850 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BSON</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SequoiaDB的BSON对象模型中支持Decimal类型数据，保持PG Decimal类型的兼容性
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SequoiaDB支持like匹配符，兼容PG的like语法
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MTH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SequoiaDB提供对长整型的json特殊语法{field:{$numberLong:x}}的支持
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PMD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供数据审计功能（基于现有的审计功能上进行增强，提供二进制的存储和转换工具）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">数据压缩算法的优化（字典大小，压缩解压性能，总体内存占用，非压缩集合开启压缩，压缩重构）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供SequoiaDB的版本升级功能（1、安装包升级，2、通过OM升级）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>OM</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">第二代存储引擎开发
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DMS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalog元数据操作在并发时保证一致性要求
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在数据节点创建CS时会加Bucket锁， 通过Bucket锁解决并发创建的冲突问题</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>通过truncate来优化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">通过post event到游标的线程，并能激活该线程立即处理
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2015Q2</t>
+    <t xml:space="preserve">DMS读写并发（块锁+记录锁+索引页锁）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SequoiaDB持久化能力优化
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Truncate/Drop Collection的性能优化
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RTN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">match支持函数和流式处理，支持对数组的精确匹配
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Coord加入到系统管理，向Catalog注册获取节点ID，实现Coord自动负载均衡和监控（所有coord节点的catalogaddr参数自动保存）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain功能和接口重构，增加add group, remove group, add cs/remove cs, rebalance操作，都通过alter接口实现
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">JS对象增强和重构：
+1、system对象增加进程操作killProcess, enumProcess等；
+2、所有对象提供远程new的能力
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">modify支持流式处理和嵌套能力，提供对数组的精确修改，支持modify记录数量限制
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">垂直切分功能重构（1、主表下直接创建分区；2、只能attach被detach的分区；3、保持分区有效性）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供视图功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">完善collection alter功能（支持sharding key, sharding type, enable sharding key的更改）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供集群的数据Load功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、规范snapshot和list的输出格式和内容；
+2、查看当前具体执行的SQL语句及时间和资源占用；
+3、记录慢查询操作信息，以便分析；
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">测试及健康检查工具（用例脚本）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOOL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">用户角色和数据权限管理
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AUTH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供归档日志（压缩存储）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供日志回滚保存和重新回放功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供数据中心按域进行灾备
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SequoiaDB支持按会话/操作优先级进行资源调度和限制（CPU，MEM等）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Build Tree调整优化，以及模块化调整去除模块依赖
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供通过OM进行SequoiaSQL的安装和部署
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">驱动接口规范化和性能优化（减少对象获取时的交互）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供策略定制功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SequoiaSQL的性能优化
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SequoiaSQL的定位和诊断能力
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SequoaSQL的元数据管理和HA
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SequoiaSQL的性能定位能力
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SequoiSQL和SequoiaDB业务拉通
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>归属</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">索引压缩优化（前缀压缩）
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">OM提供“主机监控管理”（主机状态，内存，CPU利用率，磁盘等）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OM HA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>SequoiaDB</t>
-    </r>
+OM提供“业务监控管理”（读写更新的IOPS，业务进程资源使用率等，CollectionSpace, Collection, Group, Domain, Record等，性能监控，扩容减容）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.12.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.12.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">同步数据压缩和索引压缩至1.12分支
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Driver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SQL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SequoiaSQL的业务操作管理
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杨上德</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林友滨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Java连接池的优化重构
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谭钊波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李伟超</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成总体部署的流程，接口和模块设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何嘉文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何嘉文/黄伟纲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成主机监控和业务监控的网页设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">PHP驱动重构
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘圳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>业务操作</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="宋体"/>
         <family val="2"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">管理（CollectionSpace, Collection, Group, Domain, Record等，性能监控，扩容减容）
-</t>
+      <t>备注</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>注册成OM业务，能访问自身监控页面</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">SEQUOIADBMAINSTREAM-769 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武赟</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>林友滨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>何嘉文</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>迭代</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迭代一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迭代二</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成各驱动getCL/getCS等的性能优化；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1456,28 +1753,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>李伟超</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>许建辉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">SEQUOIADBMAINSTREAM-850 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Coord加入到系统管理，实现Coord自动负载均衡和监控（所有coord节点的catalogaddr参数自动保存）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>PLAN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1538,15 +1821,6 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1574,7 +1848,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1717,6 +1991,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1727,7 +2010,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1836,12 +2119,64 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="200">
+  <dxfs count="204">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3748,7 +4083,7 @@
         <v>8</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>58</v>
@@ -3952,7 +4287,7 @@
         <v>28</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -4686,16 +5021,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M169">
-    <cfRule type="expression" dxfId="199" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="203" priority="1" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="198" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="202" priority="2" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="197" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="201" priority="3" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="196" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="200" priority="4" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5000,7 +5335,7 @@
         <v>30</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -5870,16 +6205,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L185">
-    <cfRule type="expression" dxfId="195" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="199" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="194" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="198" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="193" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="197" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="192" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="196" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5904,7 +6239,7 @@
   <sheetPr filterMode="1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:O90"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -5919,9 +6254,10 @@
     <col min="11" max="11" width="11" customWidth="1"/>
     <col min="12" max="12" width="15.875" customWidth="1"/>
     <col min="13" max="13" width="17.375" customWidth="1"/>
+    <col min="14" max="14" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="29.45" customHeight="1">
+    <row r="1" spans="1:15" ht="29.45" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
@@ -5935,7 +6271,7 @@
         <v>86</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>1</v>
@@ -5961,18 +6297,24 @@
       <c r="M1" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="54">
+      <c r="N1" s="40" t="s">
+        <v>348</v>
+      </c>
+      <c r="O1" s="41" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="54">
       <c r="A2" s="1">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
-      <c r="E2" s="8" t="s">
-        <v>278</v>
+      <c r="E2" s="8">
+        <v>2.2000000000000002</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>64</v>
@@ -5981,22 +6323,33 @@
         <v>12</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>13</v>
+        <v>168</v>
       </c>
       <c r="I2" s="2">
-        <v>10</v>
-      </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="3"/>
-    </row>
-    <row r="3" spans="1:13" ht="40.5" hidden="1">
+        <v>15</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L2" s="42">
+        <v>42454</v>
+      </c>
+      <c r="M2" s="43">
+        <v>42474</v>
+      </c>
+      <c r="O2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="40.5" hidden="1">
       <c r="A3" s="1">
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -6016,12 +6369,12 @@
       <c r="L3" s="2"/>
       <c r="M3" s="3"/>
     </row>
-    <row r="4" spans="1:13" ht="40.5" hidden="1">
+    <row r="4" spans="1:15" ht="40.5" hidden="1">
       <c r="A4" s="27">
         <v>4</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
@@ -6033,22 +6386,20 @@
         <v>22</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>169</v>
-      </c>
-      <c r="I4" s="29">
-        <v>8</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="I4" s="29"/>
       <c r="J4" s="29"/>
       <c r="K4" s="29"/>
       <c r="L4" s="30"/>
       <c r="M4" s="31"/>
     </row>
-    <row r="5" spans="1:13" ht="40.5" hidden="1">
+    <row r="5" spans="1:15" ht="40.5" hidden="1">
       <c r="A5" s="1">
         <v>5</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -6062,25 +6413,23 @@
       <c r="H5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="2">
-        <v>16</v>
-      </c>
+      <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:13" ht="54">
+    <row r="6" spans="1:15" ht="54" hidden="1">
       <c r="A6" s="1">
         <v>7</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
-      <c r="E6" s="8" t="s">
-        <v>278</v>
+      <c r="E6" s="8">
+        <v>2.4</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>49</v>
@@ -6092,19 +6441,19 @@
         <v>74</v>
       </c>
       <c r="I6" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:13" ht="40.5" hidden="1">
+    <row r="7" spans="1:15" ht="40.5" hidden="1">
       <c r="A7" s="1">
         <v>10</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -6116,7 +6465,7 @@
         <v>16</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -6124,12 +6473,12 @@
       <c r="L7" s="2"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="27" hidden="1">
+    <row r="8" spans="1:15" ht="27" hidden="1">
       <c r="A8" s="1">
         <v>13</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -6141,7 +6490,7 @@
         <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -6149,66 +6498,84 @@
       <c r="L8" s="2"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:13" ht="54" hidden="1">
+    <row r="9" spans="1:15" ht="54" hidden="1">
       <c r="A9" s="1">
         <v>14</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="E9" s="8">
+        <v>2.4</v>
+      </c>
       <c r="F9" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I9" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="I9" s="2">
+        <v>30</v>
+      </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="1:13" ht="40.5">
+    <row r="10" spans="1:15" ht="94.5">
       <c r="A10" s="27">
         <v>16</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>279</v>
+        <v>328</v>
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="28"/>
-      <c r="E10" s="8" t="s">
-        <v>278</v>
+      <c r="E10" s="8">
+        <v>2.2000000000000002</v>
       </c>
       <c r="F10" s="29" t="s">
         <v>41</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H10" s="29" t="s">
         <v>45</v>
       </c>
       <c r="I10" s="29">
-        <v>25</v>
-      </c>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="31"/>
-    </row>
-    <row r="11" spans="1:13" ht="27" hidden="1">
+        <v>90</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>344</v>
+      </c>
+      <c r="K10" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="38">
+        <v>42443</v>
+      </c>
+      <c r="M10" s="39">
+        <v>42457</v>
+      </c>
+      <c r="N10" t="s">
+        <v>345</v>
+      </c>
+      <c r="O10" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="27" hidden="1">
       <c r="A11" s="27">
         <v>17</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="28"/>
@@ -6220,7 +6587,7 @@
         <v>16</v>
       </c>
       <c r="H11" s="29" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I11" s="29"/>
       <c r="J11" s="29"/>
@@ -6228,37 +6595,52 @@
       <c r="L11" s="29"/>
       <c r="M11" s="31"/>
     </row>
-    <row r="12" spans="1:13" ht="27" hidden="1">
+    <row r="12" spans="1:15" ht="27">
       <c r="A12" s="1">
         <v>18</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>181</v>
+        <v>327</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
+      <c r="E12" s="8">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="F12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" ht="40.5" hidden="1">
+      <c r="I12" s="2">
+        <v>30</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="42">
+        <v>42473</v>
+      </c>
+      <c r="M12" s="43">
+        <v>42503</v>
+      </c>
+      <c r="O12" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="40.5" hidden="1">
       <c r="A13" s="1">
         <v>19</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -6278,12 +6660,12 @@
       <c r="L13" s="2"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" ht="27" hidden="1">
+    <row r="14" spans="1:15" ht="27" hidden="1">
       <c r="A14" s="1">
         <v>20</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -6295,7 +6677,7 @@
         <v>16</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -6303,36 +6685,36 @@
       <c r="L14" s="2"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:13" ht="40.5">
+    <row r="15" spans="1:15" ht="40.5" hidden="1">
       <c r="A15" s="1">
         <v>21</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="8" t="s">
-        <v>278</v>
+      <c r="E15" s="8">
+        <v>2.4</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>49</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I15" s="2">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:13" ht="40.5" hidden="1">
+    <row r="16" spans="1:15" ht="40.5" hidden="1">
       <c r="A16" s="1">
         <v>22</v>
       </c>
@@ -6362,7 +6744,7 @@
         <v>23</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -6382,26 +6764,30 @@
       <c r="L17" s="2"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" ht="54" hidden="1">
+    <row r="18" spans="1:13" ht="54">
       <c r="A18" s="1">
         <v>24</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>185</v>
+        <v>303</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+      <c r="E18" s="8">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="F18" s="2" t="s">
         <v>75</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I18" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="I18" s="2">
+        <v>25</v>
+      </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
@@ -6412,11 +6798,13 @@
         <v>26</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
+      <c r="E19" s="8">
+        <v>2.4</v>
+      </c>
       <c r="F19" s="2" t="s">
         <v>64</v>
       </c>
@@ -6424,9 +6812,11 @@
         <v>16</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I19" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="I19" s="2">
+        <v>20</v>
+      </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -6437,12 +6827,12 @@
         <v>28</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="8" t="s">
-        <v>278</v>
+      <c r="E20" s="8">
+        <v>2.2000000000000002</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>49</v>
@@ -6454,7 +6844,7 @@
         <v>51</v>
       </c>
       <c r="I20" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -6466,7 +6856,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -6478,7 +6868,7 @@
         <v>16</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -6491,21 +6881,25 @@
         <v>30</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
+      <c r="E22" s="8">
+        <v>2.4</v>
+      </c>
       <c r="F22" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I22" s="2"/>
+      <c r="I22" s="2">
+        <v>40</v>
+      </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -6516,7 +6910,7 @@
         <v>31</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -6528,7 +6922,7 @@
         <v>16</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -6541,12 +6935,12 @@
         <v>34</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
-      <c r="E24" s="8" t="s">
-        <v>278</v>
+      <c r="E24" s="8">
+        <v>2.2000000000000002</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>75</v>
@@ -6555,10 +6949,10 @@
         <v>22</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I24" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -6570,12 +6964,12 @@
         <v>35</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
-      <c r="E25" s="8" t="s">
-        <v>278</v>
+      <c r="E25" s="8">
+        <v>2.2000000000000002</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>75</v>
@@ -6584,10 +6978,10 @@
         <v>22</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I25" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -6599,11 +6993,13 @@
         <v>36</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
+      <c r="E26" s="8">
+        <v>2.4</v>
+      </c>
       <c r="F26" s="2" t="s">
         <v>32</v>
       </c>
@@ -6611,10 +7007,10 @@
         <v>22</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I26" s="2">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -6626,11 +7022,13 @@
         <v>38</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
+      <c r="E27" s="8">
+        <v>2.4</v>
+      </c>
       <c r="F27" s="2" t="s">
         <v>41</v>
       </c>
@@ -6638,10 +7036,10 @@
         <v>12</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I27" s="2">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -6653,22 +7051,24 @@
         <v>39</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
+      <c r="E28" s="8">
+        <v>2.4</v>
+      </c>
       <c r="F28" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I28" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -6680,7 +7080,7 @@
         <v>40</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -6692,7 +7092,7 @@
         <v>12</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I29" s="8">
         <v>10</v>
@@ -6707,7 +7107,7 @@
         <v>42</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -6719,7 +7119,7 @@
         <v>22</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I30" s="8">
         <v>8</v>
@@ -6734,7 +7134,7 @@
         <v>43</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -6746,7 +7146,7 @@
         <v>12</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I31" s="8">
         <v>12</v>
@@ -6761,7 +7161,7 @@
         <v>44</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -6773,7 +7173,7 @@
         <v>22</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I32" s="8">
         <v>4</v>
@@ -6783,12 +7183,12 @@
       <c r="L32" s="8"/>
       <c r="M32" s="14"/>
     </row>
-    <row r="33" spans="1:13" ht="54" hidden="1">
+    <row r="33" spans="1:15" ht="54" hidden="1">
       <c r="A33" s="13">
         <v>47</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -6800,7 +7200,7 @@
         <v>12</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I33" s="8">
         <v>7</v>
@@ -6810,200 +7210,196 @@
       <c r="L33" s="8"/>
       <c r="M33" s="14"/>
     </row>
-    <row r="34" spans="1:13" ht="27" hidden="1">
+    <row r="34" spans="1:15" ht="54" hidden="1">
       <c r="A34" s="13">
         <v>48</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>226</v>
+        <v>299</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
+      <c r="E34" s="8">
+        <v>2.4</v>
+      </c>
       <c r="F34" s="8" t="s">
         <v>64</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I34" s="8">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
       <c r="M34" s="14"/>
     </row>
-    <row r="35" spans="1:13" ht="27" hidden="1">
+    <row r="35" spans="1:15" ht="54" hidden="1">
       <c r="A35" s="13">
         <v>49</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>227</v>
+        <v>305</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
+      <c r="E35" s="8">
+        <v>2.4</v>
+      </c>
       <c r="F35" s="8" t="s">
         <v>64</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I35" s="8">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
       <c r="M35" s="14"/>
     </row>
-    <row r="36" spans="1:13" ht="40.5" hidden="1">
+    <row r="36" spans="1:15" ht="40.5" hidden="1">
       <c r="A36" s="13">
         <v>54</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
+      <c r="E36" s="8">
+        <v>2.4</v>
+      </c>
       <c r="F36" s="8" t="s">
         <v>64</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
+      <c r="H36" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="I36" s="8">
+        <v>20</v>
+      </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
       <c r="M36" s="14"/>
     </row>
-    <row r="37" spans="1:13" ht="121.5">
-      <c r="A37" s="1">
-        <v>56</v>
+    <row r="37" spans="1:15" ht="94.5" hidden="1">
+      <c r="A37" s="13">
+        <v>58</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>83</v>
+        <v>259</v>
       </c>
       <c r="C37" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="D37" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I37" s="2">
-        <v>18</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="K37" s="2" t="s">
+      <c r="I37" s="8">
+        <v>120</v>
+      </c>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="L37" s="2"/>
-      <c r="M37" s="3"/>
-    </row>
-    <row r="38" spans="1:13" ht="94.5">
+      <c r="L37" s="8"/>
+      <c r="M37" s="14"/>
+    </row>
+    <row r="38" spans="1:15" ht="27" hidden="1">
       <c r="A38" s="13">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D38" s="8"/>
-      <c r="E38" s="8" t="s">
-        <v>278</v>
-      </c>
+      <c r="E38" s="8"/>
       <c r="F38" s="8" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I38" s="8">
-        <v>120</v>
-      </c>
-      <c r="J38" s="8"/>
+        <v>90</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>276</v>
+      </c>
       <c r="K38" s="8" t="s">
         <v>58</v>
       </c>
       <c r="L38" s="8"/>
       <c r="M38" s="14"/>
     </row>
-    <row r="39" spans="1:13" ht="27">
+    <row r="39" spans="1:15" ht="27">
       <c r="A39" s="13">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>282</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="C39" s="8"/>
       <c r="D39" s="8"/>
-      <c r="E39" s="8" t="s">
-        <v>278</v>
+      <c r="E39" s="8">
+        <v>2.2000000000000002</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>64</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I39" s="8">
-        <v>90</v>
-      </c>
-      <c r="J39" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>58</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
       <c r="L39" s="8"/>
       <c r="M39" s="14"/>
     </row>
-    <row r="40" spans="1:13" ht="27">
+    <row r="40" spans="1:15" ht="27" hidden="1">
       <c r="A40" s="13">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
-      <c r="E40" s="8" t="s">
-        <v>278</v>
-      </c>
+      <c r="E40" s="8"/>
       <c r="F40" s="8" t="s">
         <v>64</v>
       </c>
@@ -7011,13 +7407,13 @@
         <v>22</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="I40" s="8">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="K40" s="8" t="s">
         <v>58</v>
@@ -7025,618 +7421,1377 @@
       <c r="L40" s="8"/>
       <c r="M40" s="14"/>
     </row>
-    <row r="41" spans="1:13" ht="54">
+    <row r="41" spans="1:15" ht="27" hidden="1">
       <c r="A41" s="13">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
-      <c r="E41" s="8" t="s">
-        <v>278</v>
+      <c r="E41" s="8">
+        <v>2.4</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="I41" s="8">
-        <v>100</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="K41" s="8" t="s">
-        <v>58</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
       <c r="L41" s="8"/>
       <c r="M41" s="14"/>
     </row>
-    <row r="42" spans="1:13" ht="27">
-      <c r="A42" s="13">
-        <v>62</v>
+    <row r="42" spans="1:15" ht="27" hidden="1">
+      <c r="A42" s="1">
+        <v>64</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="C42" s="8"/>
+        <v>39</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>269</v>
+      </c>
       <c r="D42" s="8"/>
-      <c r="E42" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G42" s="8" t="s">
+      <c r="E42" s="8"/>
+      <c r="F42" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="I42" s="8">
-        <v>140</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="L42" s="8"/>
-      <c r="M42" s="14"/>
-    </row>
-    <row r="43" spans="1:13" ht="27">
+      <c r="H42" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="1:15" ht="40.5">
       <c r="A43" s="13">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
-      <c r="E43" s="8" t="s">
-        <v>278</v>
+      <c r="E43" s="8">
+        <v>2.2000000000000002</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="I43" s="8">
-        <v>20</v>
-      </c>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="14"/>
-    </row>
-    <row r="44" spans="1:13" ht="27">
-      <c r="A44" s="1">
+        <v>30</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L43" s="36">
+        <v>42446</v>
+      </c>
+      <c r="M43" s="37">
+        <v>42474</v>
+      </c>
+      <c r="O43" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="40.5">
+      <c r="A44" s="13">
+        <v>66</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F44" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I44" s="2">
-        <v>4</v>
-      </c>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="1:13">
-      <c r="A45" s="13"/>
-      <c r="B45" s="8"/>
+      <c r="G44" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="I44" s="8">
+        <v>18</v>
+      </c>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="14"/>
+    </row>
+    <row r="45" spans="1:15" ht="40.5">
+      <c r="A45" s="13">
+        <v>67</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>285</v>
+      </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="14"/>
-    </row>
-    <row r="46" spans="1:13">
-      <c r="A46" s="13"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
+      <c r="E45" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="I45" s="8">
+        <v>15</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L45" s="36">
+        <v>42446</v>
+      </c>
+      <c r="M45" s="37">
+        <v>42460</v>
+      </c>
+      <c r="O45" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="40.5">
+      <c r="A46" s="13">
+        <v>68</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>330</v>
+      </c>
       <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
+      <c r="E46" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I46" s="8">
+        <v>30</v>
+      </c>
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
       <c r="M46" s="14"/>
     </row>
-    <row r="47" spans="1:13">
-      <c r="A47" s="13"/>
-      <c r="B47" s="8"/>
+    <row r="47" spans="1:15" ht="40.5" hidden="1">
+      <c r="A47" s="13">
+        <v>70</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>287</v>
+      </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
+      <c r="E47" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="I47" s="8">
+        <v>24</v>
+      </c>
       <c r="J47" s="8"/>
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
       <c r="M47" s="14"/>
     </row>
-    <row r="48" spans="1:13">
-      <c r="A48" s="13"/>
-      <c r="B48" s="8"/>
+    <row r="48" spans="1:15" ht="54">
+      <c r="A48" s="13">
+        <v>71</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>288</v>
+      </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8"/>
-      <c r="L48" s="8"/>
-      <c r="M48" s="14"/>
-    </row>
-    <row r="49" spans="1:13">
-      <c r="A49" s="13"/>
-      <c r="B49" s="8"/>
+      <c r="E48" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="I48" s="8">
+        <v>22</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L48" s="36">
+        <v>42443</v>
+      </c>
+      <c r="M48" s="37">
+        <v>42468</v>
+      </c>
+      <c r="O48" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="40.5">
+      <c r="A49" s="13">
+        <v>72</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>290</v>
+      </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="14"/>
-    </row>
-    <row r="50" spans="1:13">
-      <c r="A50" s="13"/>
-      <c r="B50" s="8"/>
+      <c r="E49" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="I49" s="8">
+        <v>10</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L49" s="36">
+        <v>42451</v>
+      </c>
+      <c r="M49" s="37">
+        <v>42461</v>
+      </c>
+      <c r="O49" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="27" hidden="1">
+      <c r="A50" s="13">
+        <v>73</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>292</v>
+      </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8"/>
+      <c r="E50" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="I50" s="8">
+        <v>45</v>
+      </c>
       <c r="J50" s="8"/>
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
       <c r="M50" s="14"/>
     </row>
-    <row r="51" spans="1:13">
-      <c r="A51" s="13"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
+    <row r="51" spans="1:15" ht="27">
+      <c r="A51" s="13">
+        <v>74</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>329</v>
+      </c>
       <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
-      <c r="M51" s="14"/>
-    </row>
-    <row r="52" spans="1:13">
-      <c r="A52" s="13"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
+      <c r="E51" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="I51" s="8">
+        <v>33</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L51" s="36">
+        <v>42447</v>
+      </c>
+      <c r="M51" s="37">
+        <v>42474</v>
+      </c>
+      <c r="O51" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="27">
+      <c r="A52" s="13">
+        <v>75</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>329</v>
+      </c>
       <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="8"/>
+      <c r="E52" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="I52" s="8">
+        <v>15</v>
+      </c>
       <c r="J52" s="8"/>
       <c r="K52" s="8"/>
       <c r="L52" s="8"/>
       <c r="M52" s="14"/>
     </row>
-    <row r="53" spans="1:13">
-      <c r="A53" s="13"/>
-      <c r="B53" s="8"/>
+    <row r="53" spans="1:15" ht="40.5">
+      <c r="A53" s="13">
+        <v>76</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>296</v>
+      </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
-      <c r="M53" s="14"/>
-    </row>
-    <row r="54" spans="1:13">
-      <c r="A54" s="13"/>
-      <c r="B54" s="8"/>
+      <c r="E53" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="I53" s="8">
+        <v>22</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="L53" s="36">
+        <v>42476</v>
+      </c>
+      <c r="M53" s="37">
+        <v>42500</v>
+      </c>
+      <c r="O53" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="40.5">
+      <c r="A54" s="13">
+        <v>77</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>302</v>
+      </c>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8"/>
+      <c r="E54" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="I54" s="8">
+        <v>22</v>
+      </c>
       <c r="J54" s="8"/>
       <c r="K54" s="8"/>
       <c r="L54" s="8"/>
       <c r="M54" s="14"/>
     </row>
-    <row r="55" spans="1:13">
-      <c r="A55" s="13"/>
-      <c r="B55" s="8"/>
+    <row r="55" spans="1:15" ht="67.5">
+      <c r="A55" s="13">
+        <v>78</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>300</v>
+      </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-      <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="8"/>
-      <c r="M55" s="14"/>
-    </row>
-    <row r="56" spans="1:13">
-      <c r="A56" s="13"/>
-      <c r="B56" s="8"/>
+      <c r="E55" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="I55" s="8">
+        <v>14</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L55" s="36">
+        <v>42467</v>
+      </c>
+      <c r="M55" s="37">
+        <v>42486</v>
+      </c>
+      <c r="O55" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="27" hidden="1">
+      <c r="A56" s="13">
+        <v>79</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>304</v>
+      </c>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="I56" s="8"/>
+      <c r="E56" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="I56" s="8">
+        <v>30</v>
+      </c>
       <c r="J56" s="8"/>
       <c r="K56" s="8"/>
       <c r="L56" s="8"/>
       <c r="M56" s="14"/>
     </row>
-    <row r="57" spans="1:13">
-      <c r="A57" s="13"/>
-      <c r="B57" s="8"/>
+    <row r="57" spans="1:15" ht="27">
+      <c r="A57" s="13">
+        <v>80</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>306</v>
+      </c>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
-      <c r="I57" s="8"/>
+      <c r="E57" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="I57" s="8">
+        <v>40</v>
+      </c>
       <c r="J57" s="8"/>
       <c r="K57" s="8"/>
       <c r="L57" s="8"/>
       <c r="M57" s="14"/>
     </row>
-    <row r="58" spans="1:13">
-      <c r="A58" s="13"/>
-      <c r="B58" s="8"/>
+    <row r="58" spans="1:15" ht="67.5">
+      <c r="A58" s="13">
+        <v>81</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>307</v>
+      </c>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
+      <c r="E58" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="I58" s="8">
+        <v>30</v>
+      </c>
       <c r="J58" s="8"/>
       <c r="K58" s="8"/>
       <c r="L58" s="8"/>
       <c r="M58" s="14"/>
     </row>
-    <row r="59" spans="1:13">
-      <c r="A59" s="13"/>
-      <c r="B59" s="8"/>
+    <row r="59" spans="1:15" ht="27" hidden="1">
+      <c r="A59" s="13">
+        <v>82</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>308</v>
+      </c>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="8"/>
+      <c r="E59" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H59" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="I59" s="8">
+        <v>14</v>
+      </c>
       <c r="J59" s="8"/>
       <c r="K59" s="8"/>
       <c r="L59" s="8"/>
       <c r="M59" s="14"/>
     </row>
-    <row r="60" spans="1:13">
-      <c r="A60" s="13"/>
-      <c r="B60" s="8"/>
+    <row r="60" spans="1:15" ht="27" hidden="1">
+      <c r="A60" s="13">
+        <v>83</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>310</v>
+      </c>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
+      <c r="F60" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>311</v>
+      </c>
       <c r="I60" s="8"/>
       <c r="J60" s="8"/>
       <c r="K60" s="8"/>
       <c r="L60" s="8"/>
       <c r="M60" s="14"/>
     </row>
-    <row r="61" spans="1:13">
-      <c r="A61" s="13"/>
-      <c r="B61" s="8"/>
+    <row r="61" spans="1:15" ht="27" hidden="1">
+      <c r="A61" s="13">
+        <v>84</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>312</v>
+      </c>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="8"/>
+      <c r="E61" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="I61" s="8">
+        <v>20</v>
+      </c>
       <c r="J61" s="8"/>
       <c r="K61" s="8"/>
       <c r="L61" s="8"/>
       <c r="M61" s="14"/>
     </row>
-    <row r="62" spans="1:13">
-      <c r="A62" s="13"/>
-      <c r="B62" s="8"/>
+    <row r="62" spans="1:15" ht="27" hidden="1">
+      <c r="A62" s="13">
+        <v>85</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>313</v>
+      </c>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="8"/>
+      <c r="E62" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="I62" s="8">
+        <v>20</v>
+      </c>
       <c r="J62" s="8"/>
       <c r="K62" s="8"/>
       <c r="L62" s="8"/>
       <c r="M62" s="14"/>
     </row>
-    <row r="63" spans="1:13">
-      <c r="A63" s="13"/>
-      <c r="B63" s="8"/>
+    <row r="63" spans="1:15" ht="40.5">
+      <c r="A63" s="13">
+        <v>86</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>317</v>
+      </c>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-      <c r="I63" s="8"/>
+      <c r="E63" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I63" s="8">
+        <v>21</v>
+      </c>
       <c r="J63" s="8"/>
       <c r="K63" s="8"/>
       <c r="L63" s="8"/>
       <c r="M63" s="14"/>
     </row>
-    <row r="64" spans="1:13">
-      <c r="A64" s="13"/>
-      <c r="B64" s="8"/>
+    <row r="64" spans="1:15" ht="27">
+      <c r="A64" s="13">
+        <v>87</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>318</v>
+      </c>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
-      <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="14"/>
-    </row>
-    <row r="65" spans="1:13">
-      <c r="A65" s="13"/>
-      <c r="B65" s="8"/>
+      <c r="E64" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="I64" s="8">
+        <v>60</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L64" s="36">
+        <v>42445</v>
+      </c>
+      <c r="M64" s="37">
+        <v>42458</v>
+      </c>
+      <c r="N64" t="s">
+        <v>342</v>
+      </c>
+      <c r="O64" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="40.5">
+      <c r="A65" s="13">
+        <v>88</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>319</v>
+      </c>
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="8"/>
-      <c r="K65" s="8"/>
-      <c r="L65" s="8"/>
-      <c r="M65" s="14"/>
-    </row>
-    <row r="66" spans="1:13">
-      <c r="A66" s="13"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
+      <c r="E65" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="I65" s="8">
+        <v>45</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L65" s="36">
+        <v>42447</v>
+      </c>
+      <c r="M65" s="37">
+        <v>42465</v>
+      </c>
+      <c r="N65" t="s">
+        <v>352</v>
+      </c>
+      <c r="O65" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="27" hidden="1">
+      <c r="A66" s="13">
+        <v>89</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>330</v>
+      </c>
       <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
-      <c r="I66" s="8"/>
+      <c r="E66" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="I66" s="8">
+        <v>60</v>
+      </c>
       <c r="J66" s="8"/>
       <c r="K66" s="8"/>
       <c r="L66" s="8"/>
       <c r="M66" s="14"/>
     </row>
-    <row r="67" spans="1:13">
-      <c r="A67" s="13"/>
-      <c r="B67" s="8"/>
+    <row r="67" spans="1:15" ht="27">
+      <c r="A67" s="13">
+        <v>91</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>321</v>
+      </c>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="8"/>
+      <c r="E67" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="I67" s="8">
+        <v>30</v>
+      </c>
       <c r="J67" s="8"/>
       <c r="K67" s="8"/>
       <c r="L67" s="8"/>
       <c r="M67" s="14"/>
     </row>
-    <row r="68" spans="1:13">
-      <c r="A68" s="13"/>
-      <c r="B68" s="8"/>
+    <row r="68" spans="1:15" ht="27">
+      <c r="A68" s="13">
+        <v>92</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>322</v>
+      </c>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
+      <c r="E68" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="I68" s="8">
+        <v>30</v>
+      </c>
       <c r="J68" s="8"/>
       <c r="K68" s="8"/>
       <c r="L68" s="8"/>
       <c r="M68" s="14"/>
     </row>
-    <row r="69" spans="1:13">
-      <c r="A69" s="13"/>
-      <c r="B69" s="8"/>
+    <row r="69" spans="1:15" ht="27" hidden="1">
+      <c r="A69" s="13">
+        <v>93</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>323</v>
+      </c>
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8"/>
+      <c r="E69" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="I69" s="8">
+        <v>60</v>
+      </c>
       <c r="J69" s="8"/>
       <c r="K69" s="8"/>
       <c r="L69" s="8"/>
       <c r="M69" s="14"/>
     </row>
-    <row r="70" spans="1:13">
-      <c r="A70" s="13"/>
-      <c r="B70" s="8"/>
+    <row r="70" spans="1:15" ht="27" hidden="1">
+      <c r="A70" s="13">
+        <v>94</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>324</v>
+      </c>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
+      <c r="E70" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="I70" s="8">
+        <v>30</v>
+      </c>
       <c r="J70" s="8"/>
       <c r="K70" s="8"/>
       <c r="L70" s="8"/>
       <c r="M70" s="14"/>
     </row>
-    <row r="71" spans="1:13">
-      <c r="A71" s="13"/>
-      <c r="B71" s="8"/>
+    <row r="71" spans="1:15" ht="27" hidden="1">
+      <c r="A71" s="13">
+        <v>95</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>325</v>
+      </c>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
+      <c r="E71" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>12</v>
+      </c>
       <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
+      <c r="I71" s="8">
+        <v>40</v>
+      </c>
       <c r="J71" s="8"/>
       <c r="K71" s="8"/>
       <c r="L71" s="8"/>
       <c r="M71" s="14"/>
     </row>
-    <row r="72" spans="1:13">
-      <c r="A72" s="13"/>
-      <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
+    <row r="72" spans="1:15" ht="27" hidden="1">
+      <c r="A72" s="13">
+        <v>96</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>330</v>
+      </c>
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
+      <c r="F72" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="H72" s="8"/>
-      <c r="I72" s="8"/>
+      <c r="I72" s="8">
+        <v>15</v>
+      </c>
       <c r="J72" s="8"/>
       <c r="K72" s="8"/>
       <c r="L72" s="8"/>
       <c r="M72" s="14"/>
     </row>
-    <row r="73" spans="1:13">
-      <c r="A73" s="13"/>
-      <c r="B73" s="8"/>
+    <row r="73" spans="1:15" ht="27" hidden="1">
+      <c r="A73" s="13">
+        <v>97</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>334</v>
+      </c>
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="8"/>
+      <c r="E73" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="I73" s="8">
+        <v>90</v>
+      </c>
       <c r="J73" s="8"/>
       <c r="K73" s="8"/>
       <c r="L73" s="8"/>
       <c r="M73" s="14"/>
     </row>
-    <row r="74" spans="1:13">
-      <c r="A74" s="13"/>
-      <c r="B74" s="8"/>
+    <row r="74" spans="1:15" ht="27">
+      <c r="A74" s="13">
+        <v>98</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>339</v>
+      </c>
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="14"/>
-    </row>
-    <row r="75" spans="1:13">
-      <c r="A75" s="13"/>
-      <c r="B75" s="8"/>
+      <c r="E74" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="I74" s="8">
+        <v>18</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="K74" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L74" s="36">
+        <v>42443</v>
+      </c>
+      <c r="M74" s="37">
+        <v>42461</v>
+      </c>
+      <c r="O74" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" ht="27">
+      <c r="A75" s="13">
+        <v>99</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>346</v>
+      </c>
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="8"/>
-      <c r="I75" s="8"/>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8"/>
-      <c r="L75" s="8"/>
-      <c r="M75" s="14"/>
-    </row>
-    <row r="76" spans="1:13" ht="14.25" thickBot="1">
-      <c r="A76" s="15"/>
-      <c r="B76" s="16"/>
-      <c r="C76" s="16"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="16"/>
-      <c r="H76" s="16"/>
-      <c r="I76" s="16"/>
-      <c r="J76" s="16"/>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="17"/>
+      <c r="E75" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="I75" s="8">
+        <v>20</v>
+      </c>
+      <c r="J75" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="K75" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L75" s="36">
+        <v>42445</v>
+      </c>
+      <c r="M75" s="37">
+        <v>42471</v>
+      </c>
+      <c r="O75" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" s="13"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="8"/>
+      <c r="M76" s="14"/>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" s="13"/>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="8"/>
+      <c r="M77" s="14"/>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" s="13"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+      <c r="M78" s="14"/>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" s="13"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="8"/>
+      <c r="M79" s="14"/>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" s="13"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="8"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="8"/>
+      <c r="I80" s="8"/>
+      <c r="J80" s="8"/>
+      <c r="K80" s="8"/>
+      <c r="L80" s="8"/>
+      <c r="M80" s="14"/>
+    </row>
+    <row r="81" spans="1:13">
+      <c r="A81" s="13"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="8"/>
+      <c r="J81" s="8"/>
+      <c r="K81" s="8"/>
+      <c r="L81" s="8"/>
+      <c r="M81" s="14"/>
+    </row>
+    <row r="82" spans="1:13">
+      <c r="A82" s="13"/>
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8"/>
+      <c r="I82" s="8"/>
+      <c r="J82" s="8"/>
+      <c r="K82" s="8"/>
+      <c r="L82" s="8"/>
+      <c r="M82" s="14"/>
+    </row>
+    <row r="83" spans="1:13">
+      <c r="A83" s="13"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="8"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="8"/>
+      <c r="M83" s="14"/>
+    </row>
+    <row r="84" spans="1:13">
+      <c r="A84" s="13"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="8"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="8"/>
+      <c r="M84" s="14"/>
+    </row>
+    <row r="85" spans="1:13">
+      <c r="A85" s="13"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="8"/>
+      <c r="K85" s="8"/>
+      <c r="L85" s="8"/>
+      <c r="M85" s="14"/>
+    </row>
+    <row r="86" spans="1:13">
+      <c r="A86" s="13"/>
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="8"/>
+      <c r="J86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="8"/>
+      <c r="M86" s="14"/>
+    </row>
+    <row r="87" spans="1:13">
+      <c r="A87" s="13"/>
+      <c r="B87" s="8"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="8"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="8"/>
+      <c r="M87" s="14"/>
+    </row>
+    <row r="88" spans="1:13">
+      <c r="A88" s="13"/>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="8"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="8"/>
+      <c r="J88" s="8"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="8"/>
+      <c r="M88" s="14"/>
+    </row>
+    <row r="89" spans="1:13">
+      <c r="A89" s="13"/>
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="8"/>
+      <c r="F89" s="8"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="8"/>
+      <c r="J89" s="8"/>
+      <c r="K89" s="8"/>
+      <c r="L89" s="8"/>
+      <c r="M89" s="14"/>
+    </row>
+    <row r="90" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A90" s="15"/>
+      <c r="B90" s="16"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="16"/>
+      <c r="F90" s="16"/>
+      <c r="G90" s="16"/>
+      <c r="H90" s="16"/>
+      <c r="I90" s="16"/>
+      <c r="J90" s="16"/>
+      <c r="K90" s="16"/>
+      <c r="L90" s="16"/>
+      <c r="M90" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M44">
+  <autoFilter ref="A1:M75">
     <filterColumn colId="4">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
+      <filters>
+        <filter val="2.2"/>
+      </filters>
     </filterColumn>
     <filterColumn colId="6"/>
     <sortState ref="A2:M48">
@@ -7644,78 +8799,61 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:M187">
-    <cfRule type="expression" dxfId="191" priority="21" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:M201">
+    <cfRule type="expression" dxfId="195" priority="21" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="190" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="194" priority="22" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="189" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="193" priority="23" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="188" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="192" priority="24" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:M7">
-    <cfRule type="expression" dxfId="187" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="191" priority="17" stopIfTrue="1">
       <formula>$K7="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="186" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="190" priority="18" stopIfTrue="1">
       <formula>$K7="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="185" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="189" priority="19" stopIfTrue="1">
       <formula>$K7="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="184" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="188" priority="20" stopIfTrue="1">
       <formula>OR($K7="CLOSED",$K7="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A37:M37">
-    <cfRule type="expression" dxfId="183" priority="13" stopIfTrue="1">
-      <formula>$K37="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="182" priority="14" stopIfTrue="1">
-      <formula>$K37="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="181" priority="15" stopIfTrue="1">
-      <formula>$K37="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="180" priority="16" stopIfTrue="1">
-      <formula>OR($K37="CLOSED",$K37="CANCEL")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A44:M44">
-    <cfRule type="expression" dxfId="179" priority="1" stopIfTrue="1">
-      <formula>$K44="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="178" priority="2" stopIfTrue="1">
-      <formula>$K44="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="177" priority="3" stopIfTrue="1">
-      <formula>$K44="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="176" priority="4" stopIfTrue="1">
-      <formula>OR($K44="CLOSED",$K44="CANCEL")</formula>
+  <conditionalFormatting sqref="A42:M42">
+    <cfRule type="expression" dxfId="187" priority="1" stopIfTrue="1">
+      <formula>$K42="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="186" priority="2" stopIfTrue="1">
+      <formula>$K42="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="185" priority="3" stopIfTrue="1">
+      <formula>$K42="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="184" priority="4" stopIfTrue="1">
+      <formula>OR($K42="CLOSED",$K42="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F76">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F90">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G76">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G90">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K76">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K90">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="D37" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8765,12 +9903,12 @@
         <v>1</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>64</v>
@@ -8785,7 +9923,7 @@
         <v>28</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>79</v>
@@ -8798,12 +9936,12 @@
         <v>6</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>14</v>
@@ -8818,7 +9956,7 @@
         <v>8</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>79</v>
@@ -8831,12 +9969,12 @@
         <v>9</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>11</v>
@@ -8845,7 +9983,7 @@
         <v>22</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I34" s="2">
         <v>8</v>
@@ -8864,12 +10002,12 @@
         <v>15</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
       <c r="E35" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>41</v>
@@ -8884,7 +10022,7 @@
         <v>80</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>79</v>
@@ -8897,12 +10035,12 @@
         <v>25</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>75</v>
@@ -8917,7 +10055,7 @@
         <v>4</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>79</v>
@@ -8930,14 +10068,14 @@
         <v>11</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>32</v>
@@ -8952,7 +10090,7 @@
         <v>3</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>79</v>
@@ -8965,14 +10103,14 @@
         <v>27</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>32</v>
@@ -8987,7 +10125,7 @@
         <v>3</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>79</v>
@@ -9002,14 +10140,14 @@
         <v>46</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>64</v>
@@ -9018,13 +10156,13 @@
         <v>22</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I39" s="8">
         <v>5</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="K39" s="8" t="s">
         <v>79</v>
@@ -9041,7 +10179,7 @@
         <v>55</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -9055,7 +10193,7 @@
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
       <c r="J40" s="8" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="K40" s="8" t="s">
         <v>79</v>
@@ -9068,7 +10206,7 @@
         <v>53</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
@@ -9082,7 +10220,7 @@
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
       <c r="J41" s="8" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>79</v>
@@ -9095,12 +10233,12 @@
         <v>37</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
       <c r="E42" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>64</v>
@@ -9109,7 +10247,7 @@
         <v>22</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I42" s="2">
         <v>15</v>
@@ -9126,14 +10264,14 @@
         <v>32</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>64</v>
@@ -9148,7 +10286,7 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>79</v>
@@ -9163,12 +10301,12 @@
         <v>33</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
       <c r="E44" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>64</v>
@@ -9177,13 +10315,13 @@
         <v>12</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I44" s="2">
         <v>5</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>79</v>
@@ -9278,7 +10416,7 @@
         <v>2</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>79</v>
@@ -9309,7 +10447,7 @@
         <v>15</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>79</v>
@@ -9322,14 +10460,14 @@
         <v>41</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>64</v>
@@ -9338,7 +10476,7 @@
         <v>22</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I49" s="8">
         <v>5</v>
@@ -9355,14 +10493,14 @@
         <v>52</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>11</v>
@@ -9371,13 +10509,13 @@
         <v>22</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="I50" s="8">
         <v>5</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="K50" s="8" t="s">
         <v>79</v>
@@ -9390,11 +10528,11 @@
         <v>36</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E51" s="8"/>
       <c r="F51" s="2" t="s">
@@ -9410,7 +10548,7 @@
         <v>2</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>79</v>
@@ -9490,7 +10628,7 @@
         <v>28</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
@@ -9516,14 +10654,14 @@
         <v>55</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="35" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>64</v>
@@ -9532,13 +10670,13 @@
         <v>22</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I55" s="8">
         <v>7</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="K55" s="8" t="s">
         <v>79</v>
@@ -9551,14 +10689,14 @@
         <v>50</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="35" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>64</v>
@@ -9567,13 +10705,13 @@
         <v>12</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I56" s="8">
         <v>3</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="K56" s="8" t="s">
         <v>79</v>
@@ -9586,14 +10724,14 @@
         <v>57</v>
       </c>
       <c r="B57" s="28" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C57" s="28" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D57" s="28"/>
       <c r="E57" s="8" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="F57" s="29" t="s">
         <v>75</v>
@@ -9621,16 +10759,16 @@
         <v>45</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="D58" s="35" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>75</v>
@@ -9639,13 +10777,13 @@
         <v>12</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I58" s="8">
         <v>3</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="K58" s="8" t="s">
         <v>79</v>
@@ -9657,20 +10795,42 @@
         <v>42132</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
-      <c r="A59" s="1"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-      <c r="L59" s="21"/>
-      <c r="M59" s="22"/>
+    <row r="59" spans="1:13" ht="135">
+      <c r="A59" s="1">
+        <v>56</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D59" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I59" s="2">
+        <v>18</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L59" s="2"/>
+      <c r="M59" s="3"/>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="1"/>
@@ -9905,566 +11065,594 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:M9 A32:M37">
-    <cfRule type="expression" dxfId="175" priority="197" stopIfTrue="1">
+    <cfRule type="expression" dxfId="183" priority="205" stopIfTrue="1">
       <formula>$K9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="174" priority="198" stopIfTrue="1">
+    <cfRule type="expression" dxfId="182" priority="206" stopIfTrue="1">
       <formula>$K9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="199" stopIfTrue="1">
+    <cfRule type="expression" dxfId="181" priority="207" stopIfTrue="1">
       <formula>$K9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="172" priority="200" stopIfTrue="1">
+    <cfRule type="expression" dxfId="180" priority="208" stopIfTrue="1">
       <formula>OR($K9="CLOSED",$K9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:M10">
-    <cfRule type="expression" dxfId="171" priority="193" stopIfTrue="1">
+    <cfRule type="expression" dxfId="179" priority="201" stopIfTrue="1">
       <formula>$K10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="170" priority="194" stopIfTrue="1">
+    <cfRule type="expression" dxfId="178" priority="202" stopIfTrue="1">
       <formula>$K10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="169" priority="195" stopIfTrue="1">
+    <cfRule type="expression" dxfId="177" priority="203" stopIfTrue="1">
       <formula>$K10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="168" priority="196" stopIfTrue="1">
+    <cfRule type="expression" dxfId="176" priority="204" stopIfTrue="1">
       <formula>OR($K10="CLOSED",$K10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:M11">
-    <cfRule type="expression" dxfId="167" priority="189" stopIfTrue="1">
+    <cfRule type="expression" dxfId="175" priority="197" stopIfTrue="1">
       <formula>$K11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="166" priority="190" stopIfTrue="1">
+    <cfRule type="expression" dxfId="174" priority="198" stopIfTrue="1">
       <formula>$K11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="165" priority="191" stopIfTrue="1">
+    <cfRule type="expression" dxfId="173" priority="199" stopIfTrue="1">
       <formula>$K11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="164" priority="192" stopIfTrue="1">
+    <cfRule type="expression" dxfId="172" priority="200" stopIfTrue="1">
       <formula>OR($K11="CLOSED",$K11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:M12">
-    <cfRule type="expression" dxfId="163" priority="185" stopIfTrue="1">
+    <cfRule type="expression" dxfId="171" priority="193" stopIfTrue="1">
       <formula>$K12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="162" priority="186" stopIfTrue="1">
+    <cfRule type="expression" dxfId="170" priority="194" stopIfTrue="1">
       <formula>$K12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="161" priority="187" stopIfTrue="1">
+    <cfRule type="expression" dxfId="169" priority="195" stopIfTrue="1">
       <formula>$K12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="160" priority="188" stopIfTrue="1">
+    <cfRule type="expression" dxfId="168" priority="196" stopIfTrue="1">
       <formula>OR($K12="CLOSED",$K12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:M13">
-    <cfRule type="expression" dxfId="159" priority="181" stopIfTrue="1">
+    <cfRule type="expression" dxfId="167" priority="189" stopIfTrue="1">
       <formula>$K13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="158" priority="182" stopIfTrue="1">
+    <cfRule type="expression" dxfId="166" priority="190" stopIfTrue="1">
       <formula>$K13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="157" priority="183" stopIfTrue="1">
+    <cfRule type="expression" dxfId="165" priority="191" stopIfTrue="1">
       <formula>$K13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="156" priority="184" stopIfTrue="1">
+    <cfRule type="expression" dxfId="164" priority="192" stopIfTrue="1">
       <formula>OR($K13="CLOSED",$K13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:M14">
-    <cfRule type="expression" dxfId="155" priority="177" stopIfTrue="1">
+    <cfRule type="expression" dxfId="163" priority="185" stopIfTrue="1">
       <formula>$K14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="154" priority="178" stopIfTrue="1">
+    <cfRule type="expression" dxfId="162" priority="186" stopIfTrue="1">
       <formula>$K14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="153" priority="179" stopIfTrue="1">
+    <cfRule type="expression" dxfId="161" priority="187" stopIfTrue="1">
       <formula>$K14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="152" priority="180" stopIfTrue="1">
+    <cfRule type="expression" dxfId="160" priority="188" stopIfTrue="1">
       <formula>OR($K14="CLOSED",$K14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:M15">
-    <cfRule type="expression" dxfId="151" priority="173" stopIfTrue="1">
+    <cfRule type="expression" dxfId="159" priority="181" stopIfTrue="1">
       <formula>$K15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="150" priority="174" stopIfTrue="1">
+    <cfRule type="expression" dxfId="158" priority="182" stopIfTrue="1">
       <formula>$K15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="149" priority="175" stopIfTrue="1">
+    <cfRule type="expression" dxfId="157" priority="183" stopIfTrue="1">
       <formula>$K15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="148" priority="176" stopIfTrue="1">
+    <cfRule type="expression" dxfId="156" priority="184" stopIfTrue="1">
       <formula>OR($K15="CLOSED",$K15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:M16">
-    <cfRule type="expression" dxfId="147" priority="169" stopIfTrue="1">
+    <cfRule type="expression" dxfId="155" priority="177" stopIfTrue="1">
       <formula>$K16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="146" priority="170" stopIfTrue="1">
+    <cfRule type="expression" dxfId="154" priority="178" stopIfTrue="1">
       <formula>$K16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="145" priority="171" stopIfTrue="1">
+    <cfRule type="expression" dxfId="153" priority="179" stopIfTrue="1">
       <formula>$K16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="144" priority="172" stopIfTrue="1">
+    <cfRule type="expression" dxfId="152" priority="180" stopIfTrue="1">
       <formula>OR($K16="CLOSED",$K16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:M17">
-    <cfRule type="expression" dxfId="143" priority="165" stopIfTrue="1">
+    <cfRule type="expression" dxfId="151" priority="173" stopIfTrue="1">
       <formula>$K17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="142" priority="166" stopIfTrue="1">
+    <cfRule type="expression" dxfId="150" priority="174" stopIfTrue="1">
       <formula>$K17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="141" priority="167" stopIfTrue="1">
+    <cfRule type="expression" dxfId="149" priority="175" stopIfTrue="1">
       <formula>$K17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="140" priority="168" stopIfTrue="1">
+    <cfRule type="expression" dxfId="148" priority="176" stopIfTrue="1">
       <formula>OR($K17="CLOSED",$K17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:M18">
-    <cfRule type="expression" dxfId="139" priority="161" stopIfTrue="1">
+    <cfRule type="expression" dxfId="147" priority="169" stopIfTrue="1">
       <formula>$K18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="162" stopIfTrue="1">
+    <cfRule type="expression" dxfId="146" priority="170" stopIfTrue="1">
       <formula>$K18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="137" priority="163" stopIfTrue="1">
+    <cfRule type="expression" dxfId="145" priority="171" stopIfTrue="1">
       <formula>$K18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="164" stopIfTrue="1">
+    <cfRule type="expression" dxfId="144" priority="172" stopIfTrue="1">
       <formula>OR($K18="CLOSED",$K18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:M19">
-    <cfRule type="expression" dxfId="135" priority="157" stopIfTrue="1">
+    <cfRule type="expression" dxfId="143" priority="165" stopIfTrue="1">
       <formula>$K19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="158" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="166" stopIfTrue="1">
       <formula>$K19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="133" priority="159" stopIfTrue="1">
+    <cfRule type="expression" dxfId="141" priority="167" stopIfTrue="1">
       <formula>$K19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="160" stopIfTrue="1">
+    <cfRule type="expression" dxfId="140" priority="168" stopIfTrue="1">
       <formula>OR($K19="CLOSED",$K19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:M20">
-    <cfRule type="expression" dxfId="131" priority="153" stopIfTrue="1">
+    <cfRule type="expression" dxfId="139" priority="161" stopIfTrue="1">
       <formula>$K20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="154" stopIfTrue="1">
+    <cfRule type="expression" dxfId="138" priority="162" stopIfTrue="1">
       <formula>$K20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="155" stopIfTrue="1">
+    <cfRule type="expression" dxfId="137" priority="163" stopIfTrue="1">
       <formula>$K20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="128" priority="156" stopIfTrue="1">
+    <cfRule type="expression" dxfId="136" priority="164" stopIfTrue="1">
       <formula>OR($K20="CLOSED",$K20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:M21">
-    <cfRule type="expression" dxfId="127" priority="149" stopIfTrue="1">
+    <cfRule type="expression" dxfId="135" priority="157" stopIfTrue="1">
       <formula>$K21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="150" stopIfTrue="1">
+    <cfRule type="expression" dxfId="134" priority="158" stopIfTrue="1">
       <formula>$K21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="151" stopIfTrue="1">
+    <cfRule type="expression" dxfId="133" priority="159" stopIfTrue="1">
       <formula>$K21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="152" stopIfTrue="1">
+    <cfRule type="expression" dxfId="132" priority="160" stopIfTrue="1">
       <formula>OR($K21="CLOSED",$K21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:M23">
-    <cfRule type="expression" dxfId="123" priority="145" stopIfTrue="1">
+    <cfRule type="expression" dxfId="131" priority="153" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="146" stopIfTrue="1">
+    <cfRule type="expression" dxfId="130" priority="154" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="147" stopIfTrue="1">
+    <cfRule type="expression" dxfId="129" priority="155" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="148" stopIfTrue="1">
+    <cfRule type="expression" dxfId="128" priority="156" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:I22">
-    <cfRule type="expression" dxfId="119" priority="141" stopIfTrue="1">
+    <cfRule type="expression" dxfId="127" priority="149" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="142" stopIfTrue="1">
+    <cfRule type="expression" dxfId="126" priority="150" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="143" stopIfTrue="1">
+    <cfRule type="expression" dxfId="125" priority="151" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="144" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="152" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="115" priority="137" stopIfTrue="1">
+    <cfRule type="expression" dxfId="123" priority="145" stopIfTrue="1">
       <formula>$K23="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="138" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="146" stopIfTrue="1">
       <formula>$K23="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="139" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="147" stopIfTrue="1">
       <formula>$K23="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="140" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="148" stopIfTrue="1">
       <formula>OR($K23="CLOSED",$K23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:M25">
-    <cfRule type="expression" dxfId="111" priority="133" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="141" stopIfTrue="1">
       <formula>$K24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="134" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="142" stopIfTrue="1">
       <formula>$K24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="135" stopIfTrue="1">
+    <cfRule type="expression" dxfId="117" priority="143" stopIfTrue="1">
       <formula>$K24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="136" stopIfTrue="1">
+    <cfRule type="expression" dxfId="116" priority="144" stopIfTrue="1">
       <formula>OR($K24="CLOSED",$K24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="107" priority="129" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="137" stopIfTrue="1">
       <formula>$K25="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="130" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="138" stopIfTrue="1">
       <formula>$K25="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="131" stopIfTrue="1">
+    <cfRule type="expression" dxfId="113" priority="139" stopIfTrue="1">
       <formula>$K25="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="132" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="140" stopIfTrue="1">
       <formula>OR($K25="CLOSED",$K25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:M26">
-    <cfRule type="expression" dxfId="103" priority="125" stopIfTrue="1">
+    <cfRule type="expression" dxfId="111" priority="133" stopIfTrue="1">
       <formula>$K26="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="126" stopIfTrue="1">
+    <cfRule type="expression" dxfId="110" priority="134" stopIfTrue="1">
       <formula>$K26="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="127" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="135" stopIfTrue="1">
       <formula>$K26="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="128" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="136" stopIfTrue="1">
       <formula>OR($K26="CLOSED",$K26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:M28">
-    <cfRule type="expression" dxfId="99" priority="121" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="129" stopIfTrue="1">
       <formula>$K27="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="122" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="130" stopIfTrue="1">
       <formula>$K27="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="123" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="131" stopIfTrue="1">
       <formula>$K27="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="124" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="132" stopIfTrue="1">
       <formula>OR($K27="CLOSED",$K27="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M30">
-    <cfRule type="expression" dxfId="95" priority="117" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="125" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="118" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="126" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="119" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="127" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="120" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="128" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M29">
-    <cfRule type="expression" dxfId="91" priority="113" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="121" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="114" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="122" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="115" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="123" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="116" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="124" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:M31">
-    <cfRule type="expression" dxfId="87" priority="109" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="117" stopIfTrue="1">
       <formula>$K31="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="110" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="118" stopIfTrue="1">
       <formula>$K31="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="111" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="119" stopIfTrue="1">
       <formula>$K31="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="112" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="120" stopIfTrue="1">
       <formula>OR($K31="CLOSED",$K31="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:M38">
-    <cfRule type="expression" dxfId="83" priority="81" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="89" stopIfTrue="1">
       <formula>$K38="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="82" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="90" stopIfTrue="1">
       <formula>$K38="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="83" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="91" stopIfTrue="1">
       <formula>$K38="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="84" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="92" stopIfTrue="1">
       <formula>OR($K38="CLOSED",$K38="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:M39">
-    <cfRule type="expression" dxfId="79" priority="77" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="85" stopIfTrue="1">
       <formula>$K39="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="78" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="86" stopIfTrue="1">
       <formula>$K39="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="79" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="87" stopIfTrue="1">
       <formula>$K39="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="80" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="88" stopIfTrue="1">
       <formula>OR($K39="CLOSED",$K39="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:M40">
-    <cfRule type="expression" dxfId="75" priority="73" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="81" stopIfTrue="1">
       <formula>$K40="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="82" stopIfTrue="1">
       <formula>$K40="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="75" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="83" stopIfTrue="1">
       <formula>$K40="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="84" stopIfTrue="1">
       <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:M41">
-    <cfRule type="expression" dxfId="71" priority="69" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="77" stopIfTrue="1">
       <formula>$K41="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="78" stopIfTrue="1">
       <formula>$K41="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="71" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="79" stopIfTrue="1">
       <formula>$K41="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="80" stopIfTrue="1">
       <formula>OR($K41="CLOSED",$K41="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:M42">
-    <cfRule type="expression" dxfId="67" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="73" stopIfTrue="1">
       <formula>$K42="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="74" stopIfTrue="1">
       <formula>$K42="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="75" stopIfTrue="1">
       <formula>$K42="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="76" stopIfTrue="1">
       <formula>OR($K42="CLOSED",$K42="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:M44">
-    <cfRule type="expression" dxfId="63" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="69" stopIfTrue="1">
       <formula>$K43="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="70" stopIfTrue="1">
       <formula>$K43="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="71" stopIfTrue="1">
       <formula>$K43="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="72" stopIfTrue="1">
       <formula>OR($K43="CLOSED",$K43="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45:M46">
-    <cfRule type="expression" dxfId="59" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="65" stopIfTrue="1">
       <formula>$K45="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="66" stopIfTrue="1">
       <formula>$K45="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="67" stopIfTrue="1">
       <formula>$K45="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="68" stopIfTrue="1">
       <formula>OR($K45="CLOSED",$K45="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:M47">
-    <cfRule type="expression" dxfId="55" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="61" stopIfTrue="1">
       <formula>$K47="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="62" stopIfTrue="1">
       <formula>$K47="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="63" stopIfTrue="1">
       <formula>$K47="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="64" stopIfTrue="1">
       <formula>OR($K47="CLOSED",$K47="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:M48">
-    <cfRule type="expression" dxfId="51" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="57" stopIfTrue="1">
       <formula>$K48="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="58" stopIfTrue="1">
       <formula>$K48="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="59" stopIfTrue="1">
       <formula>$K48="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="60" stopIfTrue="1">
       <formula>OR($K48="CLOSED",$K48="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:M49">
-    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="53" stopIfTrue="1">
       <formula>$K49="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="54" stopIfTrue="1">
       <formula>$K49="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="55" stopIfTrue="1">
       <formula>$K49="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="56" stopIfTrue="1">
       <formula>OR($K49="CLOSED",$K49="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:M50">
-    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="49" stopIfTrue="1">
       <formula>$K50="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="50" stopIfTrue="1">
       <formula>$K50="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="51" stopIfTrue="1">
       <formula>$K50="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="52" stopIfTrue="1">
       <formula>OR($K50="CLOSED",$K50="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:M51">
-    <cfRule type="expression" dxfId="39" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
       <formula>$K51="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
       <formula>$K51="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
       <formula>$K51="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
       <formula>OR($K51="CLOSED",$K51="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:M52">
-    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
       <formula>$K52="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
       <formula>$K52="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="43" stopIfTrue="1">
       <formula>$K52="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="44" stopIfTrue="1">
       <formula>OR($K52="CLOSED",$K52="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:M53">
-    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="37" stopIfTrue="1">
       <formula>$K53="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="38" stopIfTrue="1">
       <formula>$K53="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="39" stopIfTrue="1">
       <formula>$K53="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="40" stopIfTrue="1">
       <formula>OR($K53="CLOSED",$K53="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:M54">
-    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
       <formula>$K54="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
       <formula>$K54="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
       <formula>$K54="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
       <formula>OR($K54="CLOSED",$K54="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:M55">
-    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
       <formula>$K55="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
       <formula>$K55="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="31" stopIfTrue="1">
       <formula>$K55="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
       <formula>OR($K55="CLOSED",$K55="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56:M56">
-    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
       <formula>$K56="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
       <formula>$K56="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="27" stopIfTrue="1">
       <formula>$K56="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="28" stopIfTrue="1">
       <formula>OR($K56="CLOSED",$K56="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:M57">
+    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
+      <formula>$K57="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
+      <formula>$K57="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
+      <formula>$K57="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
+      <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A57:M57">
+    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
+      <formula>$K57="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
+      <formula>$K57="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
+      <formula>$K57="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
+      <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E57">
     <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
       <formula>$K57="HANG-UP"</formula>
     </cfRule>
@@ -10478,46 +11666,46 @@
       <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A57:M57">
+  <conditionalFormatting sqref="A58:M58">
     <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
-      <formula>$K57="HANG-UP"</formula>
+      <formula>$K58="HANG-UP"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
-      <formula>$K57="PLAN"</formula>
+      <formula>$K58="PLAN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
-      <formula>$K57="OPEN"</formula>
+      <formula>$K58="OPEN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
-      <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
+      <formula>OR($K58="CLOSED",$K58="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E57">
+  <conditionalFormatting sqref="A59:M59">
     <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
-      <formula>$K57="HANG-UP"</formula>
+      <formula>$K59="HANG-UP"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
-      <formula>$K57="PLAN"</formula>
+      <formula>$K59="PLAN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
-      <formula>$K57="OPEN"</formula>
+      <formula>$K59="OPEN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
-      <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
+      <formula>OR($K59="CLOSED",$K59="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A58:M58">
+  <conditionalFormatting sqref="A59:M59">
     <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
-      <formula>$K58="HANG-UP"</formula>
+      <formula>$K59="HANG-UP"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
-      <formula>$K58="PLAN"</formula>
+      <formula>$K59="PLAN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
-      <formula>$K58="OPEN"</formula>
+      <formula>$K59="OPEN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
-      <formula>OR($K58="CLOSED",$K58="CANCEL")</formula>
+      <formula>OR($K59="CLOSED",$K59="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -10535,8 +11723,9 @@
     <hyperlink ref="D55" r:id="rId1"/>
     <hyperlink ref="D56" r:id="rId2"/>
     <hyperlink ref="D58" r:id="rId3"/>
+    <hyperlink ref="D59" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId5"/>
 </worksheet>
 </file>
--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$M$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2015年'!$A$1:$M$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2015年'!$A$1:$O$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$M$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="357">
   <si>
     <r>
       <t>描述</t>
@@ -1754,6 +1754,14 @@
   </si>
   <si>
     <t>PLAN</t>
+  </si>
+  <si>
+    <t>???</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成run包升级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6244,11 +6252,12 @@
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
     <col min="2" max="2" width="39.75" customWidth="1"/>
-    <col min="3" max="3" width="20.125" customWidth="1"/>
-    <col min="4" max="4" width="24.75" customWidth="1"/>
-    <col min="5" max="6" width="9.375" customWidth="1"/>
-    <col min="7" max="7" width="9.75" customWidth="1"/>
-    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="3" max="3" width="20.125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="24.75" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="9.375" customWidth="1"/>
+    <col min="6" max="6" width="9.375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.75" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="14.125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
@@ -6595,7 +6604,7 @@
       <c r="L11" s="29"/>
       <c r="M11" s="31"/>
     </row>
-    <row r="12" spans="1:15" ht="27">
+    <row r="12" spans="1:15" ht="27" hidden="1">
       <c r="A12" s="1">
         <v>18</v>
       </c>
@@ -6764,7 +6773,7 @@
       <c r="L17" s="2"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" ht="54">
+    <row r="18" spans="1:13" ht="54" hidden="1">
       <c r="A18" s="1">
         <v>24</v>
       </c>
@@ -6822,7 +6831,7 @@
       <c r="L19" s="2"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:13" ht="40.5">
+    <row r="20" spans="1:13" ht="40.5" hidden="1">
       <c r="A20" s="1">
         <v>28</v>
       </c>
@@ -6930,7 +6939,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:13" ht="27">
+    <row r="24" spans="1:13" ht="27" hidden="1">
       <c r="A24" s="1">
         <v>34</v>
       </c>
@@ -6959,7 +6968,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" spans="1:13" ht="40.5">
+    <row r="25" spans="1:13" ht="40.5" hidden="1">
       <c r="A25" s="1">
         <v>35</v>
       </c>
@@ -7361,7 +7370,7 @@
       <c r="L38" s="8"/>
       <c r="M38" s="14"/>
     </row>
-    <row r="39" spans="1:15" ht="27">
+    <row r="39" spans="1:15" ht="27" hidden="1">
       <c r="A39" s="13">
         <v>60</v>
       </c>
@@ -7513,11 +7522,14 @@
       <c r="M43" s="37">
         <v>42474</v>
       </c>
+      <c r="N43" t="s">
+        <v>355</v>
+      </c>
       <c r="O43" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="40.5">
+    <row r="44" spans="1:15" ht="40.5" hidden="1">
       <c r="A44" s="13">
         <v>66</v>
       </c>
@@ -7586,7 +7598,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="40.5">
+    <row r="46" spans="1:15" ht="40.5" hidden="1">
       <c r="A46" s="13">
         <v>68</v>
       </c>
@@ -7708,7 +7720,7 @@
         <v>291</v>
       </c>
       <c r="I49" s="8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J49" s="8" t="s">
         <v>336</v>
@@ -7720,7 +7732,10 @@
         <v>42451</v>
       </c>
       <c r="M49" s="37">
-        <v>42461</v>
+        <v>42467</v>
+      </c>
+      <c r="N49" t="s">
+        <v>356</v>
       </c>
       <c r="O49" t="s">
         <v>350</v>
@@ -7797,7 +7812,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="27">
+    <row r="52" spans="1:15" ht="27" hidden="1">
       <c r="A52" s="13">
         <v>75</v>
       </c>
@@ -7828,7 +7843,7 @@
       <c r="L52" s="8"/>
       <c r="M52" s="14"/>
     </row>
-    <row r="53" spans="1:15" ht="40.5">
+    <row r="53" spans="1:15" ht="40.5" hidden="1">
       <c r="A53" s="13">
         <v>76</v>
       </c>
@@ -7868,7 +7883,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="40.5">
+    <row r="54" spans="1:15" ht="40.5" hidden="1">
       <c r="A54" s="13">
         <v>77</v>
       </c>
@@ -7897,7 +7912,7 @@
       <c r="L54" s="8"/>
       <c r="M54" s="14"/>
     </row>
-    <row r="55" spans="1:15" ht="67.5">
+    <row r="55" spans="1:15" ht="67.5" hidden="1">
       <c r="A55" s="13">
         <v>78</v>
       </c>
@@ -7925,7 +7940,7 @@
         <v>347</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>58</v>
+        <v>354</v>
       </c>
       <c r="L55" s="36">
         <v>42467</v>
@@ -7966,7 +7981,7 @@
       <c r="L56" s="8"/>
       <c r="M56" s="14"/>
     </row>
-    <row r="57" spans="1:15" ht="27">
+    <row r="57" spans="1:15" ht="27" hidden="1">
       <c r="A57" s="13">
         <v>80</v>
       </c>
@@ -7995,7 +8010,7 @@
       <c r="L57" s="8"/>
       <c r="M57" s="14"/>
     </row>
-    <row r="58" spans="1:15" ht="67.5">
+    <row r="58" spans="1:15" ht="67.5" hidden="1">
       <c r="A58" s="13">
         <v>81</v>
       </c>
@@ -8136,7 +8151,7 @@
       <c r="L62" s="8"/>
       <c r="M62" s="14"/>
     </row>
-    <row r="63" spans="1:15" ht="40.5">
+    <row r="63" spans="1:15" ht="40.5" hidden="1">
       <c r="A63" s="13">
         <v>86</v>
       </c>
@@ -8282,7 +8297,7 @@
       <c r="L66" s="8"/>
       <c r="M66" s="14"/>
     </row>
-    <row r="67" spans="1:15" ht="27">
+    <row r="67" spans="1:15" ht="27" hidden="1">
       <c r="A67" s="13">
         <v>91</v>
       </c>
@@ -8311,7 +8326,7 @@
       <c r="L67" s="8"/>
       <c r="M67" s="14"/>
     </row>
-    <row r="68" spans="1:15" ht="27">
+    <row r="68" spans="1:15" ht="27" hidden="1">
       <c r="A68" s="13">
         <v>92</v>
       </c>
@@ -8787,16 +8802,12 @@
       <c r="M90" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M75">
-    <filterColumn colId="4">
+  <autoFilter ref="A1:O75">
+    <filterColumn colId="14">
       <filters>
-        <filter val="2.2"/>
+        <filter val="迭代一"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="6"/>
-    <sortState ref="A2:M48">
-      <sortCondition ref="A1:A48"/>
-    </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M201">

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -6252,8 +6252,8 @@
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
     <col min="2" max="2" width="39.75" customWidth="1"/>
-    <col min="3" max="3" width="20.125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="24.75" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="20.125" customWidth="1"/>
+    <col min="4" max="4" width="24.75" customWidth="1"/>
     <col min="5" max="5" width="9.375" customWidth="1"/>
     <col min="6" max="6" width="9.375" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="9.75" hidden="1" customWidth="1"/>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="2014年1季度" sheetId="1" r:id="rId1"/>
     <sheet name="2014年2季度" sheetId="3" r:id="rId2"/>
-    <sheet name="2015年" sheetId="4" r:id="rId3"/>
+    <sheet name="2016年" sheetId="4" r:id="rId3"/>
     <sheet name="已完成任务" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$M$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2015年'!$A$1:$O$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2016年'!$A$1:$O$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$M$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="368">
   <si>
     <r>
       <t>描述</t>
@@ -1761,6 +1761,50 @@
   </si>
   <si>
     <t>完成run包升级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-1608</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-1609</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-1610</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-1611</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-1612</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-1613</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-1614</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-1615</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-1616</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-1617</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EQUOIADBMAINSTREAM-1618</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2018,7 +2062,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2149,6 +2193,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6321,7 +6368,9 @@
         <v>297</v>
       </c>
       <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="D2" s="35" t="s">
+        <v>364</v>
+      </c>
       <c r="E2" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -6544,7 +6593,9 @@
         <v>328</v>
       </c>
       <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
+      <c r="D10" s="44" t="s">
+        <v>365</v>
+      </c>
       <c r="E10" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -7494,7 +7545,9 @@
         <v>282</v>
       </c>
       <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
+      <c r="D43" s="35" t="s">
+        <v>359</v>
+      </c>
       <c r="E43" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -7566,7 +7619,9 @@
         <v>285</v>
       </c>
       <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
+      <c r="D45" s="44" t="s">
+        <v>358</v>
+      </c>
       <c r="E45" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -7666,7 +7721,9 @@
         <v>288</v>
       </c>
       <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
+      <c r="D48" s="35" t="s">
+        <v>357</v>
+      </c>
       <c r="E48" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -7706,7 +7763,9 @@
         <v>290</v>
       </c>
       <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
+      <c r="D49" s="35" t="s">
+        <v>360</v>
+      </c>
       <c r="E49" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -7780,7 +7839,9 @@
       <c r="C51" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="D51" s="8"/>
+      <c r="D51" s="35" t="s">
+        <v>362</v>
+      </c>
       <c r="E51" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -8188,7 +8249,9 @@
         <v>318</v>
       </c>
       <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
+      <c r="D64" s="35" t="s">
+        <v>367</v>
+      </c>
       <c r="E64" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -8231,7 +8294,9 @@
         <v>319</v>
       </c>
       <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
+      <c r="D65" s="35" t="s">
+        <v>363</v>
+      </c>
       <c r="E65" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -8504,7 +8569,9 @@
         <v>339</v>
       </c>
       <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
+      <c r="D74" s="35" t="s">
+        <v>361</v>
+      </c>
       <c r="E74" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -8544,7 +8611,9 @@
         <v>346</v>
       </c>
       <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
+      <c r="D75" s="35" t="s">
+        <v>366</v>
+      </c>
       <c r="E75" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -8863,8 +8932,21 @@
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="D48" r:id="rId1"/>
+    <hyperlink ref="D45" r:id="rId2"/>
+    <hyperlink ref="D43" r:id="rId3"/>
+    <hyperlink ref="D49" r:id="rId4"/>
+    <hyperlink ref="D74" r:id="rId5"/>
+    <hyperlink ref="D51" r:id="rId6"/>
+    <hyperlink ref="D65" r:id="rId7"/>
+    <hyperlink ref="D2" r:id="rId8"/>
+    <hyperlink ref="D10" r:id="rId9"/>
+    <hyperlink ref="D75" r:id="rId10"/>
+    <hyperlink ref="D64" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>
 </worksheet>
 </file>
 

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="369">
   <si>
     <r>
       <t>描述</t>
@@ -1805,6 +1805,10 @@
   </si>
   <si>
     <t>EQUOIADBMAINSTREAM-1618</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开始时间延期1周</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6398,6 +6402,9 @@
       <c r="M2" s="43">
         <v>42474</v>
       </c>
+      <c r="N2" t="s">
+        <v>368</v>
+      </c>
       <c r="O2" t="s">
         <v>350</v>
       </c>
@@ -7864,10 +7871,13 @@
         <v>58</v>
       </c>
       <c r="L51" s="36">
-        <v>42447</v>
+        <v>42459</v>
       </c>
       <c r="M51" s="37">
         <v>42474</v>
+      </c>
+      <c r="N51" t="s">
+        <v>368</v>
       </c>
       <c r="O51" t="s">
         <v>350</v>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$M$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2016年'!$A$1:$O$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2016年'!$A$1:$O$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$M$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="373">
   <si>
     <r>
       <t>描述</t>
@@ -1809,6 +1809,23 @@
   </si>
   <si>
     <t>开始时间延期1周</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LOB提供缓存能力与性能优化
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-1739</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迭代一</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7574,7 +7591,7 @@
         <v>338</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="L43" s="36">
         <v>42446</v>
@@ -7648,7 +7665,7 @@
         <v>353</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="L45" s="36">
         <v>42446</v>
@@ -7750,7 +7767,7 @@
         <v>337</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="L48" s="36">
         <v>42443</v>
@@ -7792,7 +7809,7 @@
         <v>336</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="L49" s="36">
         <v>42451</v>
@@ -8326,7 +8343,7 @@
         <v>347</v>
       </c>
       <c r="K65" s="8" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="L65" s="36">
         <v>42447</v>
@@ -8601,7 +8618,7 @@
         <v>340</v>
       </c>
       <c r="K74" s="8" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="L74" s="36">
         <v>42443</v>
@@ -8643,7 +8660,7 @@
         <v>343</v>
       </c>
       <c r="K75" s="8" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="L75" s="36">
         <v>42445</v>
@@ -8655,20 +8672,41 @@
         <v>350</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
-      <c r="A76" s="13"/>
-      <c r="B76" s="8"/>
+    <row r="76" spans="1:15" ht="27">
+      <c r="A76" s="13">
+        <v>100</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>369</v>
+      </c>
       <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
+      <c r="D76" s="35" t="s">
+        <v>370</v>
+      </c>
+      <c r="E76" s="8">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="F76" s="8"/>
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="14"/>
+      <c r="I76" s="8">
+        <v>30</v>
+      </c>
+      <c r="J76" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="K76" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L76" s="36">
+        <v>42507</v>
+      </c>
+      <c r="M76" s="37">
+        <v>42538</v>
+      </c>
+      <c r="O76" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="77" spans="1:15">
       <c r="A77" s="13"/>
@@ -8881,7 +8919,7 @@
       <c r="M90" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O75">
+  <autoFilter ref="A1:O76">
     <filterColumn colId="14">
       <filters>
         <filter val="迭代一"/>
@@ -8954,9 +8992,10 @@
     <hyperlink ref="D10" r:id="rId9"/>
     <hyperlink ref="D75" r:id="rId10"/>
     <hyperlink ref="D64" r:id="rId11"/>
+    <hyperlink ref="D76" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>
 

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$M$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2016年'!$A$1:$O$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2016年'!$A$1:$O$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$M$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="384">
   <si>
     <r>
       <t>描述</t>
@@ -1545,11 +1545,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">提供归档日志（压缩存储）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">提供日志回滚保存和重新回放功能
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1689,14 +1684,6 @@
   </si>
   <si>
     <t>何嘉文</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>何嘉文/黄伟纲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>完成主机监控和业务监控的网页设计</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1808,10 +1795,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>开始时间延期1周</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">LOB提供缓存能力与性能优化
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1826,6 +1809,72 @@
   </si>
   <si>
     <t>迭代一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-1754</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何嘉文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迭代二</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">cJSON解析重构（增加错误处理能力，支持流解析，支持单引号）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成主机监控和业务监控的网页与后台对接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整到迭代二</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李建华</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>延迟到迭代二</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供归档日志
+-提供过期清除方式
+-压缩存储
+-支持指定日志回放，带过滤条件
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整至迭代二</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李伟超</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">C++提供连接池功能
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴嘉明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何嘉文/黄伟钢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李霄剑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6322,10 +6371,9 @@
     <col min="2" max="2" width="39.75" customWidth="1"/>
     <col min="3" max="3" width="20.125" customWidth="1"/>
     <col min="4" max="4" width="24.75" customWidth="1"/>
-    <col min="5" max="5" width="9.375" customWidth="1"/>
-    <col min="6" max="6" width="9.375" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.75" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="9.875" hidden="1" customWidth="1"/>
+    <col min="5" max="6" width="9.375" customWidth="1"/>
+    <col min="7" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
     <col min="9" max="9" width="14.125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
@@ -6348,7 +6396,7 @@
         <v>86</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>1</v>
@@ -6375,10 +6423,10 @@
         <v>7</v>
       </c>
       <c r="N1" s="40" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="O1" s="41" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="54">
@@ -6390,7 +6438,7 @@
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="35" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E2" s="8">
         <v>2.2000000000000002</v>
@@ -6408,22 +6456,20 @@
         <v>15</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>58</v>
       </c>
       <c r="L2" s="42">
-        <v>42454</v>
-      </c>
-      <c r="M2" s="43">
-        <v>42474</v>
-      </c>
+        <v>42561</v>
+      </c>
+      <c r="M2" s="43"/>
       <c r="N2" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="O2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="40.5" hidden="1">
@@ -6614,11 +6660,11 @@
         <v>16</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="44" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E10" s="8">
         <v>2.2000000000000002</v>
@@ -6636,22 +6682,20 @@
         <v>90</v>
       </c>
       <c r="J10" s="29" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="K10" s="29" t="s">
         <v>58</v>
       </c>
       <c r="L10" s="38">
-        <v>42443</v>
-      </c>
-      <c r="M10" s="39">
-        <v>42457</v>
-      </c>
+        <v>42551</v>
+      </c>
+      <c r="M10" s="39"/>
       <c r="N10" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="O10" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="27" hidden="1">
@@ -6679,12 +6723,12 @@
       <c r="L11" s="29"/>
       <c r="M11" s="31"/>
     </row>
-    <row r="12" spans="1:15" ht="27" hidden="1">
+    <row r="12" spans="1:15" ht="27">
       <c r="A12" s="1">
         <v>18</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -6704,19 +6748,17 @@
         <v>30</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>58</v>
+        <v>351</v>
       </c>
       <c r="L12" s="42">
-        <v>42473</v>
-      </c>
-      <c r="M12" s="43">
-        <v>42503</v>
-      </c>
+        <v>42559</v>
+      </c>
+      <c r="M12" s="43"/>
       <c r="O12" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="40.5" hidden="1">
@@ -6823,7 +6865,7 @@
       <c r="L16" s="2"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="1:13" ht="40.5" hidden="1">
+    <row r="17" spans="1:15" ht="40.5" hidden="1">
       <c r="A17" s="1">
         <v>23</v>
       </c>
@@ -6848,7 +6890,7 @@
       <c r="L17" s="2"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" ht="54" hidden="1">
+    <row r="18" spans="1:15" ht="54" hidden="1">
       <c r="A18" s="1">
         <v>24</v>
       </c>
@@ -6877,7 +6919,7 @@
       <c r="L18" s="2"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="1:13" ht="40.5" hidden="1">
+    <row r="19" spans="1:15" ht="40.5" hidden="1">
       <c r="A19" s="1">
         <v>26</v>
       </c>
@@ -6906,7 +6948,7 @@
       <c r="L19" s="2"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:13" ht="40.5" hidden="1">
+    <row r="20" spans="1:15" ht="40.5" hidden="1">
       <c r="A20" s="1">
         <v>28</v>
       </c>
@@ -6935,7 +6977,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="1:13" ht="40.5" hidden="1">
+    <row r="21" spans="1:15" ht="40.5" hidden="1">
       <c r="A21" s="1">
         <v>29</v>
       </c>
@@ -6944,7 +6986,9 @@
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
+      <c r="E21" s="8">
+        <v>2.4</v>
+      </c>
       <c r="F21" s="2" t="s">
         <v>32</v>
       </c>
@@ -6960,7 +7004,7 @@
       <c r="L21" s="2"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:13" ht="27" hidden="1">
+    <row r="22" spans="1:15" ht="27" hidden="1">
       <c r="A22" s="1">
         <v>30</v>
       </c>
@@ -6989,7 +7033,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:13" ht="27" hidden="1">
+    <row r="23" spans="1:15" ht="27" hidden="1">
       <c r="A23" s="1">
         <v>31</v>
       </c>
@@ -6998,7 +7042,9 @@
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
+      <c r="E23" s="8">
+        <v>2.4</v>
+      </c>
       <c r="F23" s="2" t="s">
         <v>64</v>
       </c>
@@ -7014,7 +7060,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:13" ht="27" hidden="1">
+    <row r="24" spans="1:15" ht="27" hidden="1">
       <c r="A24" s="1">
         <v>34</v>
       </c>
@@ -7043,7 +7089,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" spans="1:13" ht="40.5" hidden="1">
+    <row r="25" spans="1:15" ht="40.5" hidden="1">
       <c r="A25" s="1">
         <v>35</v>
       </c>
@@ -7072,7 +7118,7 @@
       <c r="L25" s="2"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="1:13" ht="54" hidden="1">
+    <row r="26" spans="1:15" ht="54" hidden="1">
       <c r="A26" s="1">
         <v>36</v>
       </c>
@@ -7101,7 +7147,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:13" ht="27" hidden="1">
+    <row r="27" spans="1:15" ht="27" hidden="1">
       <c r="A27" s="1">
         <v>38</v>
       </c>
@@ -7130,7 +7176,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:13" ht="27" hidden="1">
+    <row r="28" spans="1:15" ht="27" hidden="1">
       <c r="A28" s="1">
         <v>39</v>
       </c>
@@ -7159,7 +7205,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:13" ht="27" hidden="1">
+    <row r="29" spans="1:15" ht="27" hidden="1">
       <c r="A29" s="13">
         <v>40</v>
       </c>
@@ -7186,7 +7232,7 @@
       <c r="L29" s="8"/>
       <c r="M29" s="14"/>
     </row>
-    <row r="30" spans="1:13" ht="27" hidden="1">
+    <row r="30" spans="1:15" ht="27" hidden="1">
       <c r="A30" s="13">
         <v>42</v>
       </c>
@@ -7213,7 +7259,7 @@
       <c r="L30" s="8"/>
       <c r="M30" s="14"/>
     </row>
-    <row r="31" spans="1:13" ht="27" hidden="1">
+    <row r="31" spans="1:15" ht="27" hidden="1">
       <c r="A31" s="13">
         <v>43</v>
       </c>
@@ -7240,7 +7286,7 @@
       <c r="L31" s="8"/>
       <c r="M31" s="14"/>
     </row>
-    <row r="32" spans="1:13" ht="54" hidden="1">
+    <row r="32" spans="1:15" ht="54">
       <c r="A32" s="13">
         <v>44</v>
       </c>
@@ -7249,7 +7295,9 @@
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
+      <c r="E32" s="8">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="F32" s="8" t="s">
         <v>64</v>
       </c>
@@ -7266,6 +7314,9 @@
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
       <c r="M32" s="14"/>
+      <c r="O32" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="33" spans="1:15" ht="54" hidden="1">
       <c r="A33" s="13">
@@ -7450,7 +7501,7 @@
         <v>60</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -7561,7 +7612,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" spans="1:15" ht="40.5">
+    <row r="43" spans="1:15" ht="40.5" hidden="1">
       <c r="A43" s="13">
         <v>65</v>
       </c>
@@ -7570,7 +7621,7 @@
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="35" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E43" s="8">
         <v>2.2000000000000002</v>
@@ -7588,7 +7639,7 @@
         <v>30</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K43" s="8" t="s">
         <v>79</v>
@@ -7600,13 +7651,13 @@
         <v>42474</v>
       </c>
       <c r="N43" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="O43" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" ht="40.5" hidden="1">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="40.5">
       <c r="A44" s="13">
         <v>66</v>
       </c>
@@ -7631,11 +7682,16 @@
         <v>18</v>
       </c>
       <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
+      <c r="K44" s="8" t="s">
+        <v>351</v>
+      </c>
       <c r="L44" s="8"/>
       <c r="M44" s="14"/>
-    </row>
-    <row r="45" spans="1:15" ht="40.5">
+      <c r="O44" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="40.5" hidden="1">
       <c r="A45" s="13">
         <v>67</v>
       </c>
@@ -7644,7 +7700,7 @@
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="44" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E45" s="8">
         <v>2.2000000000000002</v>
@@ -7662,7 +7718,7 @@
         <v>15</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="K45" s="8" t="s">
         <v>79</v>
@@ -7674,7 +7730,7 @@
         <v>42460</v>
       </c>
       <c r="O45" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="40.5" hidden="1">
@@ -7682,10 +7738,10 @@
         <v>68</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="8">
@@ -7703,8 +7759,12 @@
       <c r="I46" s="8">
         <v>30</v>
       </c>
-      <c r="J46" s="8"/>
-      <c r="K46" s="8"/>
+      <c r="J46" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="L46" s="8"/>
       <c r="M46" s="14"/>
     </row>
@@ -7737,7 +7797,7 @@
       <c r="L47" s="8"/>
       <c r="M47" s="14"/>
     </row>
-    <row r="48" spans="1:15" ht="54">
+    <row r="48" spans="1:15" ht="54" hidden="1">
       <c r="A48" s="13">
         <v>71</v>
       </c>
@@ -7746,7 +7806,7 @@
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="35" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E48" s="8">
         <v>2.2000000000000002</v>
@@ -7764,7 +7824,7 @@
         <v>22</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="K48" s="8" t="s">
         <v>79</v>
@@ -7776,10 +7836,10 @@
         <v>42468</v>
       </c>
       <c r="O48" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="40.5">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="40.5" hidden="1">
       <c r="A49" s="13">
         <v>72</v>
       </c>
@@ -7788,7 +7848,7 @@
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="35" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E49" s="8">
         <v>2.2000000000000002</v>
@@ -7806,7 +7866,7 @@
         <v>12</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="K49" s="8" t="s">
         <v>79</v>
@@ -7818,10 +7878,10 @@
         <v>42467</v>
       </c>
       <c r="N49" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="O49" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="27" hidden="1">
@@ -7861,10 +7921,10 @@
         <v>293</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D51" s="35" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E51" s="8">
         <v>2.2000000000000002</v>
@@ -7882,22 +7942,20 @@
         <v>33</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K51" s="8" t="s">
         <v>58</v>
       </c>
       <c r="L51" s="36">
-        <v>42459</v>
-      </c>
-      <c r="M51" s="37">
-        <v>42474</v>
-      </c>
+        <v>42552</v>
+      </c>
+      <c r="M51" s="37"/>
       <c r="N51" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="O51" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="27" hidden="1">
@@ -7908,7 +7966,7 @@
         <v>294</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D52" s="8"/>
       <c r="E52" s="8">
@@ -7931,7 +7989,7 @@
       <c r="L52" s="8"/>
       <c r="M52" s="14"/>
     </row>
-    <row r="53" spans="1:15" ht="40.5" hidden="1">
+    <row r="53" spans="1:15" ht="40.5">
       <c r="A53" s="13">
         <v>76</v>
       </c>
@@ -7956,22 +8014,20 @@
         <v>22</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="L53" s="36">
-        <v>42476</v>
-      </c>
-      <c r="M53" s="37">
-        <v>42500</v>
-      </c>
+        <v>42552</v>
+      </c>
+      <c r="M53" s="37"/>
       <c r="O53" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" ht="40.5" hidden="1">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="40.5">
       <c r="A54" s="13">
         <v>77</v>
       </c>
@@ -7999,8 +8055,11 @@
       <c r="K54" s="8"/>
       <c r="L54" s="8"/>
       <c r="M54" s="14"/>
-    </row>
-    <row r="55" spans="1:15" ht="67.5" hidden="1">
+      <c r="O54" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="67.5">
       <c r="A55" s="13">
         <v>78</v>
       </c>
@@ -8025,19 +8084,17 @@
         <v>14</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>347</v>
+        <v>381</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="L55" s="36">
-        <v>42467</v>
-      </c>
-      <c r="M55" s="37">
-        <v>42486</v>
-      </c>
+        <v>42551</v>
+      </c>
+      <c r="M55" s="37"/>
       <c r="O55" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="27" hidden="1">
@@ -8098,7 +8155,7 @@
       <c r="L57" s="8"/>
       <c r="M57" s="14"/>
     </row>
-    <row r="58" spans="1:15" ht="67.5" hidden="1">
+    <row r="58" spans="1:15" ht="67.5">
       <c r="A58" s="13">
         <v>81</v>
       </c>
@@ -8123,9 +8180,14 @@
         <v>30</v>
       </c>
       <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
+      <c r="K58" s="8" t="s">
+        <v>351</v>
+      </c>
       <c r="L58" s="8"/>
       <c r="M58" s="14"/>
+      <c r="O58" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="59" spans="1:15" ht="27" hidden="1">
       <c r="A59" s="13">
@@ -8181,17 +8243,17 @@
       <c r="L60" s="8"/>
       <c r="M60" s="14"/>
     </row>
-    <row r="61" spans="1:15" ht="27" hidden="1">
+    <row r="61" spans="1:15" ht="67.5">
       <c r="A61" s="13">
         <v>84</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>312</v>
+        <v>377</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
       <c r="E61" s="8">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>64</v>
@@ -8200,22 +8262,32 @@
         <v>12</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I61" s="8">
         <v>20</v>
       </c>
-      <c r="J61" s="8"/>
-      <c r="K61" s="8"/>
+      <c r="J61" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="K61" s="8" t="s">
+        <v>351</v>
+      </c>
       <c r="L61" s="8"/>
       <c r="M61" s="14"/>
+      <c r="N61" t="s">
+        <v>378</v>
+      </c>
+      <c r="O61" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="62" spans="1:15" ht="27" hidden="1">
       <c r="A62" s="13">
         <v>85</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
@@ -8244,7 +8316,7 @@
         <v>86</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
@@ -8268,16 +8340,16 @@
       <c r="L63" s="8"/>
       <c r="M63" s="14"/>
     </row>
-    <row r="64" spans="1:15" ht="27">
+    <row r="64" spans="1:15" ht="27" hidden="1">
       <c r="A64" s="13">
         <v>87</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="35" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E64" s="8">
         <v>2.2000000000000002</v>
@@ -8289,16 +8361,16 @@
         <v>12</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I64" s="8">
         <v>60</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K64" s="8" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="L64" s="36">
         <v>42445</v>
@@ -8307,22 +8379,22 @@
         <v>42458</v>
       </c>
       <c r="N64" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O64" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" ht="40.5">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="40.5" hidden="1">
       <c r="A65" s="13">
         <v>88</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C65" s="8"/>
       <c r="D65" s="35" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E65" s="8">
         <v>2.2000000000000002</v>
@@ -8334,13 +8406,13 @@
         <v>22</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I65" s="8">
         <v>45</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="K65" s="8" t="s">
         <v>79</v>
@@ -8352,10 +8424,10 @@
         <v>42465</v>
       </c>
       <c r="N65" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="O65" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="27" hidden="1">
@@ -8363,10 +8435,10 @@
         <v>89</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="8">
@@ -8394,7 +8466,7 @@
         <v>91</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
@@ -8408,7 +8480,7 @@
         <v>16</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I67" s="8">
         <v>30</v>
@@ -8423,7 +8495,7 @@
         <v>92</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
@@ -8437,7 +8509,7 @@
         <v>16</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I68" s="8">
         <v>30</v>
@@ -8452,7 +8524,7 @@
         <v>93</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
@@ -8466,7 +8538,7 @@
         <v>12</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I69" s="8">
         <v>60</v>
@@ -8481,7 +8553,7 @@
         <v>94</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
@@ -8495,7 +8567,7 @@
         <v>16</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I70" s="8">
         <v>30</v>
@@ -8510,7 +8582,7 @@
         <v>95</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
@@ -8537,10 +8609,10 @@
         <v>96</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
@@ -8564,7 +8636,7 @@
         <v>97</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
@@ -8578,7 +8650,7 @@
         <v>22</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I73" s="8">
         <v>90</v>
@@ -8588,16 +8660,16 @@
       <c r="L73" s="8"/>
       <c r="M73" s="14"/>
     </row>
-    <row r="74" spans="1:15" ht="27">
+    <row r="74" spans="1:15" ht="27" hidden="1">
       <c r="A74" s="13">
         <v>98</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C74" s="8"/>
       <c r="D74" s="35" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E74" s="8">
         <v>2.2000000000000002</v>
@@ -8609,13 +8681,13 @@
         <v>12</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I74" s="8">
         <v>18</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K74" s="8" t="s">
         <v>79</v>
@@ -8627,19 +8699,19 @@
         <v>42461</v>
       </c>
       <c r="O74" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" ht="27">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" ht="27" hidden="1">
       <c r="A75" s="13">
         <v>99</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C75" s="8"/>
       <c r="D75" s="35" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E75" s="8">
         <v>2.2000000000000002</v>
@@ -8651,13 +8723,13 @@
         <v>12</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I75" s="8">
         <v>20</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K75" s="8" t="s">
         <v>79</v>
@@ -8669,19 +8741,19 @@
         <v>42471</v>
       </c>
       <c r="O75" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" ht="27">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" ht="27" hidden="1">
       <c r="A76" s="13">
         <v>100</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C76" s="8"/>
       <c r="D76" s="35" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E76" s="8">
         <v>2.2000000000000002</v>
@@ -8693,7 +8765,7 @@
         <v>30</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="K76" s="8" t="s">
         <v>79</v>
@@ -8705,38 +8777,72 @@
         <v>42538</v>
       </c>
       <c r="O76" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" ht="40.5">
+      <c r="A77" s="13">
+        <v>101</v>
+      </c>
+      <c r="B77" s="8" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="77" spans="1:15">
-      <c r="A77" s="13"/>
-      <c r="B77" s="8"/>
       <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
+      <c r="D77" s="35" t="s">
+        <v>369</v>
+      </c>
+      <c r="E77" s="8">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="F77" s="8"/>
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="8"/>
-      <c r="M77" s="14"/>
-    </row>
-    <row r="78" spans="1:15">
-      <c r="A78" s="13"/>
-      <c r="B78" s="8"/>
+      <c r="I77" s="8">
+        <v>20</v>
+      </c>
+      <c r="J77" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="K77" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L77" s="36">
+        <v>42521</v>
+      </c>
+      <c r="M77" s="37">
+        <v>42546</v>
+      </c>
+      <c r="O77" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" ht="27">
+      <c r="A78" s="13">
+        <v>102</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>380</v>
+      </c>
       <c r="C78" s="8"/>
       <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
+      <c r="E78" s="8">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
       <c r="H78" s="8"/>
       <c r="I78" s="8"/>
-      <c r="J78" s="8"/>
-      <c r="K78" s="8"/>
+      <c r="J78" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="K78" s="8" t="s">
+        <v>351</v>
+      </c>
       <c r="L78" s="8"/>
       <c r="M78" s="14"/>
+      <c r="O78" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="79" spans="1:15">
       <c r="A79" s="13"/>
@@ -8919,10 +9025,10 @@
       <c r="M90" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O76">
+  <autoFilter ref="A1:O78">
     <filterColumn colId="14">
       <filters>
-        <filter val="迭代一"/>
+        <filter val="迭代二"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -8993,9 +9099,10 @@
     <hyperlink ref="D75" r:id="rId10"/>
     <hyperlink ref="D64" r:id="rId11"/>
     <hyperlink ref="D76" r:id="rId12"/>
+    <hyperlink ref="D77" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
 </worksheet>
 </file>
 

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="386">
   <si>
     <r>
       <t>描述</t>
@@ -1875,6 +1875,16 @@
   </si>
   <si>
     <t>李霄剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">sdb shell中的date和time支持$format
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供编码转换工具
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6361,7 +6371,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:O90"/>
@@ -6472,7 +6482,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="40.5" hidden="1">
+    <row r="3" spans="1:15" ht="40.5">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -6497,7 +6507,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="3"/>
     </row>
-    <row r="4" spans="1:15" ht="40.5" hidden="1">
+    <row r="4" spans="1:15" ht="40.5">
       <c r="A4" s="27">
         <v>4</v>
       </c>
@@ -6522,7 +6532,7 @@
       <c r="L4" s="30"/>
       <c r="M4" s="31"/>
     </row>
-    <row r="5" spans="1:15" ht="40.5" hidden="1">
+    <row r="5" spans="1:15" ht="40.5">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -6547,7 +6557,7 @@
       <c r="L5" s="2"/>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:15" ht="54" hidden="1">
+    <row r="6" spans="1:15" ht="54">
       <c r="A6" s="1">
         <v>7</v>
       </c>
@@ -6576,7 +6586,7 @@
       <c r="L6" s="2"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:15" ht="40.5" hidden="1">
+    <row r="7" spans="1:15" ht="40.5">
       <c r="A7" s="1">
         <v>10</v>
       </c>
@@ -6601,7 +6611,7 @@
       <c r="L7" s="2"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:15" ht="27" hidden="1">
+    <row r="8" spans="1:15" ht="27">
       <c r="A8" s="1">
         <v>13</v>
       </c>
@@ -6626,7 +6636,7 @@
       <c r="L8" s="2"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:15" ht="54" hidden="1">
+    <row r="9" spans="1:15" ht="54">
       <c r="A9" s="1">
         <v>14</v>
       </c>
@@ -6698,7 +6708,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="27" hidden="1">
+    <row r="11" spans="1:15" ht="27">
       <c r="A11" s="27">
         <v>17</v>
       </c>
@@ -6761,7 +6771,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="40.5" hidden="1">
+    <row r="13" spans="1:15" ht="40.5">
       <c r="A13" s="1">
         <v>19</v>
       </c>
@@ -6786,7 +6796,7 @@
       <c r="L13" s="2"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:15" ht="27" hidden="1">
+    <row r="14" spans="1:15" ht="27">
       <c r="A14" s="1">
         <v>20</v>
       </c>
@@ -6811,7 +6821,7 @@
       <c r="L14" s="2"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:15" ht="40.5" hidden="1">
+    <row r="15" spans="1:15" ht="40.5">
       <c r="A15" s="1">
         <v>21</v>
       </c>
@@ -6840,7 +6850,7 @@
       <c r="L15" s="2"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:15" ht="40.5" hidden="1">
+    <row r="16" spans="1:15" ht="40.5">
       <c r="A16" s="1">
         <v>22</v>
       </c>
@@ -6865,7 +6875,7 @@
       <c r="L16" s="2"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="1:15" ht="40.5" hidden="1">
+    <row r="17" spans="1:15" ht="40.5">
       <c r="A17" s="1">
         <v>23</v>
       </c>
@@ -6890,7 +6900,7 @@
       <c r="L17" s="2"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:15" ht="54" hidden="1">
+    <row r="18" spans="1:15" ht="54">
       <c r="A18" s="1">
         <v>24</v>
       </c>
@@ -6919,7 +6929,7 @@
       <c r="L18" s="2"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="1:15" ht="40.5" hidden="1">
+    <row r="19" spans="1:15" ht="40.5">
       <c r="A19" s="1">
         <v>26</v>
       </c>
@@ -6948,7 +6958,7 @@
       <c r="L19" s="2"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:15" ht="40.5" hidden="1">
+    <row r="20" spans="1:15" ht="40.5">
       <c r="A20" s="1">
         <v>28</v>
       </c>
@@ -6977,7 +6987,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="1:15" ht="40.5" hidden="1">
+    <row r="21" spans="1:15" ht="40.5">
       <c r="A21" s="1">
         <v>29</v>
       </c>
@@ -7004,7 +7014,7 @@
       <c r="L21" s="2"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:15" ht="27" hidden="1">
+    <row r="22" spans="1:15" ht="27">
       <c r="A22" s="1">
         <v>30</v>
       </c>
@@ -7033,7 +7043,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:15" ht="27" hidden="1">
+    <row r="23" spans="1:15" ht="27">
       <c r="A23" s="1">
         <v>31</v>
       </c>
@@ -7060,7 +7070,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:15" ht="27" hidden="1">
+    <row r="24" spans="1:15" ht="27">
       <c r="A24" s="1">
         <v>34</v>
       </c>
@@ -7089,7 +7099,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" spans="1:15" ht="40.5" hidden="1">
+    <row r="25" spans="1:15" ht="40.5">
       <c r="A25" s="1">
         <v>35</v>
       </c>
@@ -7118,7 +7128,7 @@
       <c r="L25" s="2"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="1:15" ht="54" hidden="1">
+    <row r="26" spans="1:15" ht="54">
       <c r="A26" s="1">
         <v>36</v>
       </c>
@@ -7147,7 +7157,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:15" ht="27" hidden="1">
+    <row r="27" spans="1:15" ht="27">
       <c r="A27" s="1">
         <v>38</v>
       </c>
@@ -7176,7 +7186,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:15" ht="27" hidden="1">
+    <row r="28" spans="1:15" ht="27">
       <c r="A28" s="1">
         <v>39</v>
       </c>
@@ -7205,7 +7215,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:15" ht="27" hidden="1">
+    <row r="29" spans="1:15" ht="27">
       <c r="A29" s="13">
         <v>40</v>
       </c>
@@ -7232,7 +7242,7 @@
       <c r="L29" s="8"/>
       <c r="M29" s="14"/>
     </row>
-    <row r="30" spans="1:15" ht="27" hidden="1">
+    <row r="30" spans="1:15" ht="27">
       <c r="A30" s="13">
         <v>42</v>
       </c>
@@ -7259,7 +7269,7 @@
       <c r="L30" s="8"/>
       <c r="M30" s="14"/>
     </row>
-    <row r="31" spans="1:15" ht="27" hidden="1">
+    <row r="31" spans="1:15" ht="27">
       <c r="A31" s="13">
         <v>43</v>
       </c>
@@ -7318,7 +7328,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="54" hidden="1">
+    <row r="33" spans="1:15" ht="54">
       <c r="A33" s="13">
         <v>47</v>
       </c>
@@ -7345,7 +7355,7 @@
       <c r="L33" s="8"/>
       <c r="M33" s="14"/>
     </row>
-    <row r="34" spans="1:15" ht="54" hidden="1">
+    <row r="34" spans="1:15" ht="54">
       <c r="A34" s="13">
         <v>48</v>
       </c>
@@ -7374,7 +7384,7 @@
       <c r="L34" s="8"/>
       <c r="M34" s="14"/>
     </row>
-    <row r="35" spans="1:15" ht="54" hidden="1">
+    <row r="35" spans="1:15" ht="54">
       <c r="A35" s="13">
         <v>49</v>
       </c>
@@ -7403,7 +7413,7 @@
       <c r="L35" s="8"/>
       <c r="M35" s="14"/>
     </row>
-    <row r="36" spans="1:15" ht="40.5" hidden="1">
+    <row r="36" spans="1:15" ht="40.5">
       <c r="A36" s="13">
         <v>54</v>
       </c>
@@ -7432,7 +7442,7 @@
       <c r="L36" s="8"/>
       <c r="M36" s="14"/>
     </row>
-    <row r="37" spans="1:15" ht="94.5" hidden="1">
+    <row r="37" spans="1:15" ht="94.5">
       <c r="A37" s="13">
         <v>58</v>
       </c>
@@ -7463,7 +7473,7 @@
       <c r="L37" s="8"/>
       <c r="M37" s="14"/>
     </row>
-    <row r="38" spans="1:15" ht="27" hidden="1">
+    <row r="38" spans="1:15" ht="27">
       <c r="A38" s="13">
         <v>59</v>
       </c>
@@ -7496,7 +7506,7 @@
       <c r="L38" s="8"/>
       <c r="M38" s="14"/>
     </row>
-    <row r="39" spans="1:15" ht="27" hidden="1">
+    <row r="39" spans="1:15" ht="27">
       <c r="A39" s="13">
         <v>60</v>
       </c>
@@ -7525,7 +7535,7 @@
       <c r="L39" s="8"/>
       <c r="M39" s="14"/>
     </row>
-    <row r="40" spans="1:15" ht="27" hidden="1">
+    <row r="40" spans="1:15" ht="27">
       <c r="A40" s="13">
         <v>62</v>
       </c>
@@ -7556,7 +7566,7 @@
       <c r="L40" s="8"/>
       <c r="M40" s="14"/>
     </row>
-    <row r="41" spans="1:15" ht="27" hidden="1">
+    <row r="41" spans="1:15" ht="27">
       <c r="A41" s="13">
         <v>63</v>
       </c>
@@ -7585,7 +7595,7 @@
       <c r="L41" s="8"/>
       <c r="M41" s="14"/>
     </row>
-    <row r="42" spans="1:15" ht="27" hidden="1">
+    <row r="42" spans="1:15" ht="27">
       <c r="A42" s="1">
         <v>64</v>
       </c>
@@ -7612,7 +7622,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" spans="1:15" ht="40.5" hidden="1">
+    <row r="43" spans="1:15" ht="40.5">
       <c r="A43" s="13">
         <v>65</v>
       </c>
@@ -7691,7 +7701,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="40.5" hidden="1">
+    <row r="45" spans="1:15" ht="40.5">
       <c r="A45" s="13">
         <v>67</v>
       </c>
@@ -7733,7 +7743,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="40.5" hidden="1">
+    <row r="46" spans="1:15" ht="40.5">
       <c r="A46" s="13">
         <v>68</v>
       </c>
@@ -7768,7 +7778,7 @@
       <c r="L46" s="8"/>
       <c r="M46" s="14"/>
     </row>
-    <row r="47" spans="1:15" ht="40.5" hidden="1">
+    <row r="47" spans="1:15" ht="40.5">
       <c r="A47" s="13">
         <v>70</v>
       </c>
@@ -7797,7 +7807,7 @@
       <c r="L47" s="8"/>
       <c r="M47" s="14"/>
     </row>
-    <row r="48" spans="1:15" ht="54" hidden="1">
+    <row r="48" spans="1:15" ht="54">
       <c r="A48" s="13">
         <v>71</v>
       </c>
@@ -7839,7 +7849,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="40.5" hidden="1">
+    <row r="49" spans="1:15" ht="40.5">
       <c r="A49" s="13">
         <v>72</v>
       </c>
@@ -7884,7 +7894,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="27" hidden="1">
+    <row r="50" spans="1:15" ht="27">
       <c r="A50" s="13">
         <v>73</v>
       </c>
@@ -7958,7 +7968,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="27" hidden="1">
+    <row r="52" spans="1:15" ht="27">
       <c r="A52" s="13">
         <v>75</v>
       </c>
@@ -8097,7 +8107,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="27" hidden="1">
+    <row r="56" spans="1:15" ht="27">
       <c r="A56" s="13">
         <v>79</v>
       </c>
@@ -8126,7 +8136,7 @@
       <c r="L56" s="8"/>
       <c r="M56" s="14"/>
     </row>
-    <row r="57" spans="1:15" ht="27" hidden="1">
+    <row r="57" spans="1:15" ht="27">
       <c r="A57" s="13">
         <v>80</v>
       </c>
@@ -8189,7 +8199,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="27" hidden="1">
+    <row r="59" spans="1:15" ht="27">
       <c r="A59" s="13">
         <v>82</v>
       </c>
@@ -8218,7 +8228,7 @@
       <c r="L59" s="8"/>
       <c r="M59" s="14"/>
     </row>
-    <row r="60" spans="1:15" ht="27" hidden="1">
+    <row r="60" spans="1:15" ht="27">
       <c r="A60" s="13">
         <v>83</v>
       </c>
@@ -8282,7 +8292,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="27" hidden="1">
+    <row r="62" spans="1:15" ht="27">
       <c r="A62" s="13">
         <v>85</v>
       </c>
@@ -8311,7 +8321,7 @@
       <c r="L62" s="8"/>
       <c r="M62" s="14"/>
     </row>
-    <row r="63" spans="1:15" ht="40.5" hidden="1">
+    <row r="63" spans="1:15" ht="40.5">
       <c r="A63" s="13">
         <v>86</v>
       </c>
@@ -8340,7 +8350,7 @@
       <c r="L63" s="8"/>
       <c r="M63" s="14"/>
     </row>
-    <row r="64" spans="1:15" ht="27" hidden="1">
+    <row r="64" spans="1:15" ht="27">
       <c r="A64" s="13">
         <v>87</v>
       </c>
@@ -8385,7 +8395,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="40.5" hidden="1">
+    <row r="65" spans="1:15" ht="40.5">
       <c r="A65" s="13">
         <v>88</v>
       </c>
@@ -8430,7 +8440,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="27" hidden="1">
+    <row r="66" spans="1:15" ht="27">
       <c r="A66" s="13">
         <v>89</v>
       </c>
@@ -8461,7 +8471,7 @@
       <c r="L66" s="8"/>
       <c r="M66" s="14"/>
     </row>
-    <row r="67" spans="1:15" ht="27" hidden="1">
+    <row r="67" spans="1:15" ht="27">
       <c r="A67" s="13">
         <v>91</v>
       </c>
@@ -8490,7 +8500,7 @@
       <c r="L67" s="8"/>
       <c r="M67" s="14"/>
     </row>
-    <row r="68" spans="1:15" ht="27" hidden="1">
+    <row r="68" spans="1:15" ht="27">
       <c r="A68" s="13">
         <v>92</v>
       </c>
@@ -8519,7 +8529,7 @@
       <c r="L68" s="8"/>
       <c r="M68" s="14"/>
     </row>
-    <row r="69" spans="1:15" ht="27" hidden="1">
+    <row r="69" spans="1:15" ht="27">
       <c r="A69" s="13">
         <v>93</v>
       </c>
@@ -8548,7 +8558,7 @@
       <c r="L69" s="8"/>
       <c r="M69" s="14"/>
     </row>
-    <row r="70" spans="1:15" ht="27" hidden="1">
+    <row r="70" spans="1:15" ht="27">
       <c r="A70" s="13">
         <v>94</v>
       </c>
@@ -8577,7 +8587,7 @@
       <c r="L70" s="8"/>
       <c r="M70" s="14"/>
     </row>
-    <row r="71" spans="1:15" ht="27" hidden="1">
+    <row r="71" spans="1:15" ht="27">
       <c r="A71" s="13">
         <v>95</v>
       </c>
@@ -8604,7 +8614,7 @@
       <c r="L71" s="8"/>
       <c r="M71" s="14"/>
     </row>
-    <row r="72" spans="1:15" ht="27" hidden="1">
+    <row r="72" spans="1:15" ht="27">
       <c r="A72" s="13">
         <v>96</v>
       </c>
@@ -8631,7 +8641,7 @@
       <c r="L72" s="8"/>
       <c r="M72" s="14"/>
     </row>
-    <row r="73" spans="1:15" ht="27" hidden="1">
+    <row r="73" spans="1:15" ht="27">
       <c r="A73" s="13">
         <v>97</v>
       </c>
@@ -8660,7 +8670,7 @@
       <c r="L73" s="8"/>
       <c r="M73" s="14"/>
     </row>
-    <row r="74" spans="1:15" ht="27" hidden="1">
+    <row r="74" spans="1:15" ht="27">
       <c r="A74" s="13">
         <v>98</v>
       </c>
@@ -8702,7 +8712,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="27" hidden="1">
+    <row r="75" spans="1:15" ht="27">
       <c r="A75" s="13">
         <v>99</v>
       </c>
@@ -8744,7 +8754,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="27" hidden="1">
+    <row r="76" spans="1:15" ht="27">
       <c r="A76" s="13">
         <v>100</v>
       </c>
@@ -8844,9 +8854,13 @@
         <v>371</v>
       </c>
     </row>
-    <row r="79" spans="1:15">
-      <c r="A79" s="13"/>
-      <c r="B79" s="8"/>
+    <row r="79" spans="1:15" ht="27">
+      <c r="A79" s="13">
+        <v>103</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>385</v>
+      </c>
       <c r="C79" s="8"/>
       <c r="D79" s="8"/>
       <c r="E79" s="8"/>
@@ -8859,9 +8873,13 @@
       <c r="L79" s="8"/>
       <c r="M79" s="14"/>
     </row>
-    <row r="80" spans="1:15">
-      <c r="A80" s="13"/>
-      <c r="B80" s="8"/>
+    <row r="80" spans="1:15" ht="27">
+      <c r="A80" s="13">
+        <v>104</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>384</v>
+      </c>
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
       <c r="E80" s="8"/>
@@ -9026,11 +9044,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O78">
-    <filterColumn colId="14">
-      <filters>
-        <filter val="迭代二"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="14"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M201">

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="387">
   <si>
     <r>
       <t>描述</t>
@@ -1884,6 +1884,11 @@
   </si>
   <si>
     <t xml:space="preserve">提供编码转换工具
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">selector中增加trunc、type（取字段类型值）、size、splitby（push...)等操作
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8892,9 +8897,13 @@
       <c r="L80" s="8"/>
       <c r="M80" s="14"/>
     </row>
-    <row r="81" spans="1:13">
-      <c r="A81" s="13"/>
-      <c r="B81" s="8"/>
+    <row r="81" spans="1:13" ht="40.5">
+      <c r="A81" s="13">
+        <v>105</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>386</v>
+      </c>
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -1888,7 +1888,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">selector中增加trunc、type（取字段类型值）、size、splitby（push...)等操作
+    <t xml:space="preserve">selector中增加trunc、type（取字段类型值）、size、splitby、buildobj等操作
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$M$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2016年'!$A$1:$O$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2016年'!$A$1:$O$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$M$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="389">
   <si>
     <r>
       <t>描述</t>
@@ -1833,15 +1833,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>调整到迭代二</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>李建华</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>延迟到迭代二</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1853,10 +1845,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>调整至迭代二</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>李伟超</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1890,6 +1878,26 @@
   <si>
     <t xml:space="preserve">selector中增加trunc、type（取字段类型值）、size、splitby、buildobj等操作
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5K + 1.2K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.2K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4K</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6376,7 +6384,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:O90"/>
@@ -6474,20 +6482,15 @@
         <v>334</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L2" s="42">
-        <v>42561</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="L2" s="42"/>
       <c r="M2" s="43"/>
-      <c r="N2" t="s">
-        <v>374</v>
-      </c>
       <c r="O2" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="40.5">
+    <row r="3" spans="1:15" ht="40.5" hidden="1">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -6512,7 +6515,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="3"/>
     </row>
-    <row r="4" spans="1:15" ht="40.5">
+    <row r="4" spans="1:15" ht="40.5" hidden="1">
       <c r="A4" s="27">
         <v>4</v>
       </c>
@@ -6537,7 +6540,7 @@
       <c r="L4" s="30"/>
       <c r="M4" s="31"/>
     </row>
-    <row r="5" spans="1:15" ht="40.5">
+    <row r="5" spans="1:15" ht="40.5" hidden="1">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -6562,7 +6565,7 @@
       <c r="L5" s="2"/>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:15" ht="54">
+    <row r="6" spans="1:15" ht="54" hidden="1">
       <c r="A6" s="1">
         <v>7</v>
       </c>
@@ -6591,7 +6594,7 @@
       <c r="L6" s="2"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:15" ht="40.5">
+    <row r="7" spans="1:15" ht="40.5" hidden="1">
       <c r="A7" s="1">
         <v>10</v>
       </c>
@@ -6616,7 +6619,7 @@
       <c r="L7" s="2"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:15" ht="27">
+    <row r="8" spans="1:15" ht="27" hidden="1">
       <c r="A8" s="1">
         <v>13</v>
       </c>
@@ -6641,7 +6644,7 @@
       <c r="L8" s="2"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:15" ht="54">
+    <row r="9" spans="1:15" ht="54" hidden="1">
       <c r="A9" s="1">
         <v>14</v>
       </c>
@@ -6694,10 +6697,10 @@
         <v>45</v>
       </c>
       <c r="I10" s="29">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="J10" s="29" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="K10" s="29" t="s">
         <v>58</v>
@@ -6705,7 +6708,9 @@
       <c r="L10" s="38">
         <v>42551</v>
       </c>
-      <c r="M10" s="39"/>
+      <c r="M10" s="39">
+        <v>42592</v>
+      </c>
       <c r="N10" t="s">
         <v>373</v>
       </c>
@@ -6713,7 +6718,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="27">
+    <row r="11" spans="1:15" ht="27" hidden="1">
       <c r="A11" s="27">
         <v>17</v>
       </c>
@@ -6769,14 +6774,19 @@
         <v>351</v>
       </c>
       <c r="L12" s="42">
-        <v>42559</v>
-      </c>
-      <c r="M12" s="43"/>
+        <v>42566</v>
+      </c>
+      <c r="M12" s="43">
+        <v>42607</v>
+      </c>
+      <c r="N12" t="s">
+        <v>388</v>
+      </c>
       <c r="O12" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="40.5">
+    <row r="13" spans="1:15" ht="40.5" hidden="1">
       <c r="A13" s="1">
         <v>19</v>
       </c>
@@ -6801,7 +6811,7 @@
       <c r="L13" s="2"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:15" ht="27">
+    <row r="14" spans="1:15" ht="27" hidden="1">
       <c r="A14" s="1">
         <v>20</v>
       </c>
@@ -6826,7 +6836,7 @@
       <c r="L14" s="2"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:15" ht="40.5">
+    <row r="15" spans="1:15" ht="40.5" hidden="1">
       <c r="A15" s="1">
         <v>21</v>
       </c>
@@ -6855,7 +6865,7 @@
       <c r="L15" s="2"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:15" ht="40.5">
+    <row r="16" spans="1:15" ht="40.5" hidden="1">
       <c r="A16" s="1">
         <v>22</v>
       </c>
@@ -6880,7 +6890,7 @@
       <c r="L16" s="2"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="1:15" ht="40.5">
+    <row r="17" spans="1:15" ht="40.5" hidden="1">
       <c r="A17" s="1">
         <v>23</v>
       </c>
@@ -6905,7 +6915,7 @@
       <c r="L17" s="2"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:15" ht="54">
+    <row r="18" spans="1:15" ht="54" hidden="1">
       <c r="A18" s="1">
         <v>24</v>
       </c>
@@ -6934,7 +6944,7 @@
       <c r="L18" s="2"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="1:15" ht="40.5">
+    <row r="19" spans="1:15" ht="40.5" hidden="1">
       <c r="A19" s="1">
         <v>26</v>
       </c>
@@ -6963,7 +6973,7 @@
       <c r="L19" s="2"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:15" ht="40.5">
+    <row r="20" spans="1:15" ht="40.5" hidden="1">
       <c r="A20" s="1">
         <v>28</v>
       </c>
@@ -6992,7 +7002,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="1:15" ht="40.5">
+    <row r="21" spans="1:15" ht="40.5" hidden="1">
       <c r="A21" s="1">
         <v>29</v>
       </c>
@@ -7019,7 +7029,7 @@
       <c r="L21" s="2"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:15" ht="27">
+    <row r="22" spans="1:15" ht="27" hidden="1">
       <c r="A22" s="1">
         <v>30</v>
       </c>
@@ -7048,7 +7058,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:15" ht="27">
+    <row r="23" spans="1:15" ht="27" hidden="1">
       <c r="A23" s="1">
         <v>31</v>
       </c>
@@ -7075,7 +7085,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:15" ht="27">
+    <row r="24" spans="1:15" ht="27" hidden="1">
       <c r="A24" s="1">
         <v>34</v>
       </c>
@@ -7104,7 +7114,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" spans="1:15" ht="40.5">
+    <row r="25" spans="1:15" ht="40.5" hidden="1">
       <c r="A25" s="1">
         <v>35</v>
       </c>
@@ -7133,7 +7143,7 @@
       <c r="L25" s="2"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="1:15" ht="54">
+    <row r="26" spans="1:15" ht="54" hidden="1">
       <c r="A26" s="1">
         <v>36</v>
       </c>
@@ -7162,7 +7172,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:15" ht="27">
+    <row r="27" spans="1:15" ht="27" hidden="1">
       <c r="A27" s="1">
         <v>38</v>
       </c>
@@ -7191,7 +7201,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:15" ht="27">
+    <row r="28" spans="1:15" ht="27" hidden="1">
       <c r="A28" s="1">
         <v>39</v>
       </c>
@@ -7220,7 +7230,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:15" ht="27">
+    <row r="29" spans="1:15" ht="27" hidden="1">
       <c r="A29" s="13">
         <v>40</v>
       </c>
@@ -7247,7 +7257,7 @@
       <c r="L29" s="8"/>
       <c r="M29" s="14"/>
     </row>
-    <row r="30" spans="1:15" ht="27">
+    <row r="30" spans="1:15" ht="27" hidden="1">
       <c r="A30" s="13">
         <v>42</v>
       </c>
@@ -7274,7 +7284,7 @@
       <c r="L30" s="8"/>
       <c r="M30" s="14"/>
     </row>
-    <row r="31" spans="1:15" ht="27">
+    <row r="31" spans="1:15" ht="27" hidden="1">
       <c r="A31" s="13">
         <v>43</v>
       </c>
@@ -7333,7 +7343,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="54">
+    <row r="33" spans="1:15" ht="54" hidden="1">
       <c r="A33" s="13">
         <v>47</v>
       </c>
@@ -7360,7 +7370,7 @@
       <c r="L33" s="8"/>
       <c r="M33" s="14"/>
     </row>
-    <row r="34" spans="1:15" ht="54">
+    <row r="34" spans="1:15" ht="54" hidden="1">
       <c r="A34" s="13">
         <v>48</v>
       </c>
@@ -7389,7 +7399,7 @@
       <c r="L34" s="8"/>
       <c r="M34" s="14"/>
     </row>
-    <row r="35" spans="1:15" ht="54">
+    <row r="35" spans="1:15" ht="54" hidden="1">
       <c r="A35" s="13">
         <v>49</v>
       </c>
@@ -7418,7 +7428,7 @@
       <c r="L35" s="8"/>
       <c r="M35" s="14"/>
     </row>
-    <row r="36" spans="1:15" ht="40.5">
+    <row r="36" spans="1:15" ht="40.5" hidden="1">
       <c r="A36" s="13">
         <v>54</v>
       </c>
@@ -7447,7 +7457,7 @@
       <c r="L36" s="8"/>
       <c r="M36" s="14"/>
     </row>
-    <row r="37" spans="1:15" ht="94.5">
+    <row r="37" spans="1:15" ht="94.5" hidden="1">
       <c r="A37" s="13">
         <v>58</v>
       </c>
@@ -7478,7 +7488,7 @@
       <c r="L37" s="8"/>
       <c r="M37" s="14"/>
     </row>
-    <row r="38" spans="1:15" ht="27">
+    <row r="38" spans="1:15" ht="27" hidden="1">
       <c r="A38" s="13">
         <v>59</v>
       </c>
@@ -7511,7 +7521,7 @@
       <c r="L38" s="8"/>
       <c r="M38" s="14"/>
     </row>
-    <row r="39" spans="1:15" ht="27">
+    <row r="39" spans="1:15" ht="27" hidden="1">
       <c r="A39" s="13">
         <v>60</v>
       </c>
@@ -7540,7 +7550,7 @@
       <c r="L39" s="8"/>
       <c r="M39" s="14"/>
     </row>
-    <row r="40" spans="1:15" ht="27">
+    <row r="40" spans="1:15" ht="27" hidden="1">
       <c r="A40" s="13">
         <v>62</v>
       </c>
@@ -7571,7 +7581,7 @@
       <c r="L40" s="8"/>
       <c r="M40" s="14"/>
     </row>
-    <row r="41" spans="1:15" ht="27">
+    <row r="41" spans="1:15" ht="27" hidden="1">
       <c r="A41" s="13">
         <v>63</v>
       </c>
@@ -7600,7 +7610,7 @@
       <c r="L41" s="8"/>
       <c r="M41" s="14"/>
     </row>
-    <row r="42" spans="1:15" ht="27">
+    <row r="42" spans="1:15" ht="27" hidden="1">
       <c r="A42" s="1">
         <v>64</v>
       </c>
@@ -7627,7 +7637,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" spans="1:15" ht="40.5">
+    <row r="43" spans="1:15" ht="40.5" hidden="1">
       <c r="A43" s="13">
         <v>65</v>
       </c>
@@ -7706,7 +7716,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="40.5">
+    <row r="45" spans="1:15" ht="40.5" hidden="1">
       <c r="A45" s="13">
         <v>67</v>
       </c>
@@ -7748,7 +7758,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="40.5">
+    <row r="46" spans="1:15" ht="40.5" hidden="1">
       <c r="A46" s="13">
         <v>68</v>
       </c>
@@ -7775,7 +7785,7 @@
         <v>30</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K46" s="8" t="s">
         <v>58</v>
@@ -7783,7 +7793,7 @@
       <c r="L46" s="8"/>
       <c r="M46" s="14"/>
     </row>
-    <row r="47" spans="1:15" ht="40.5">
+    <row r="47" spans="1:15" ht="40.5" hidden="1">
       <c r="A47" s="13">
         <v>70</v>
       </c>
@@ -7812,7 +7822,7 @@
       <c r="L47" s="8"/>
       <c r="M47" s="14"/>
     </row>
-    <row r="48" spans="1:15" ht="54">
+    <row r="48" spans="1:15" ht="54" hidden="1">
       <c r="A48" s="13">
         <v>71</v>
       </c>
@@ -7854,7 +7864,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="40.5">
+    <row r="49" spans="1:15" ht="40.5" hidden="1">
       <c r="A49" s="13">
         <v>72</v>
       </c>
@@ -7899,7 +7909,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="27">
+    <row r="50" spans="1:15" ht="27" hidden="1">
       <c r="A50" s="13">
         <v>73</v>
       </c>
@@ -7954,7 +7964,7 @@
         <v>289</v>
       </c>
       <c r="I51" s="8">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J51" s="8" t="s">
         <v>334</v>
@@ -7963,17 +7973,19 @@
         <v>58</v>
       </c>
       <c r="L51" s="36">
-        <v>42552</v>
-      </c>
-      <c r="M51" s="37"/>
+        <v>42557</v>
+      </c>
+      <c r="M51" s="37">
+        <v>42583</v>
+      </c>
       <c r="N51" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="O51" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="27">
+    <row r="52" spans="1:15" ht="27" hidden="1">
       <c r="A52" s="13">
         <v>75</v>
       </c>
@@ -8037,7 +8049,12 @@
       <c r="L53" s="36">
         <v>42552</v>
       </c>
-      <c r="M53" s="37"/>
+      <c r="M53" s="37">
+        <v>42586</v>
+      </c>
+      <c r="N53" t="s">
+        <v>385</v>
+      </c>
       <c r="O53" t="s">
         <v>348</v>
       </c>
@@ -8096,23 +8113,28 @@
         <v>301</v>
       </c>
       <c r="I55" s="8">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="K55" s="8" t="s">
         <v>351</v>
       </c>
       <c r="L55" s="36">
-        <v>42551</v>
-      </c>
-      <c r="M55" s="37"/>
+        <v>42555</v>
+      </c>
+      <c r="M55" s="37">
+        <v>42579</v>
+      </c>
+      <c r="N55" t="s">
+        <v>386</v>
+      </c>
       <c r="O55" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="27">
+    <row r="56" spans="1:15" ht="27" hidden="1">
       <c r="A56" s="13">
         <v>79</v>
       </c>
@@ -8141,7 +8163,7 @@
       <c r="L56" s="8"/>
       <c r="M56" s="14"/>
     </row>
-    <row r="57" spans="1:15" ht="27">
+    <row r="57" spans="1:15" ht="27" hidden="1">
       <c r="A57" s="13">
         <v>80</v>
       </c>
@@ -8204,7 +8226,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="27">
+    <row r="59" spans="1:15" ht="27" hidden="1">
       <c r="A59" s="13">
         <v>82</v>
       </c>
@@ -8233,7 +8255,7 @@
       <c r="L59" s="8"/>
       <c r="M59" s="14"/>
     </row>
-    <row r="60" spans="1:15" ht="27">
+    <row r="60" spans="1:15" ht="27" hidden="1">
       <c r="A60" s="13">
         <v>83</v>
       </c>
@@ -8263,7 +8285,7 @@
         <v>84</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
@@ -8280,24 +8302,28 @@
         <v>313</v>
       </c>
       <c r="I61" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="K61" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="L61" s="8"/>
-      <c r="M61" s="14"/>
+      <c r="L61" s="36">
+        <v>42552</v>
+      </c>
+      <c r="M61" s="37">
+        <v>42583</v>
+      </c>
       <c r="N61" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="O61" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="27">
+    <row r="62" spans="1:15" ht="27" hidden="1">
       <c r="A62" s="13">
         <v>85</v>
       </c>
@@ -8326,7 +8352,7 @@
       <c r="L62" s="8"/>
       <c r="M62" s="14"/>
     </row>
-    <row r="63" spans="1:15" ht="40.5">
+    <row r="63" spans="1:15" ht="40.5" hidden="1">
       <c r="A63" s="13">
         <v>86</v>
       </c>
@@ -8355,7 +8381,7 @@
       <c r="L63" s="8"/>
       <c r="M63" s="14"/>
     </row>
-    <row r="64" spans="1:15" ht="27">
+    <row r="64" spans="1:15" ht="27" hidden="1">
       <c r="A64" s="13">
         <v>87</v>
       </c>
@@ -8400,7 +8426,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="40.5">
+    <row r="65" spans="1:15" ht="40.5" hidden="1">
       <c r="A65" s="13">
         <v>88</v>
       </c>
@@ -8445,7 +8471,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="27">
+    <row r="66" spans="1:15" ht="27" hidden="1">
       <c r="A66" s="13">
         <v>89</v>
       </c>
@@ -8476,7 +8502,7 @@
       <c r="L66" s="8"/>
       <c r="M66" s="14"/>
     </row>
-    <row r="67" spans="1:15" ht="27">
+    <row r="67" spans="1:15" ht="27" hidden="1">
       <c r="A67" s="13">
         <v>91</v>
       </c>
@@ -8505,7 +8531,7 @@
       <c r="L67" s="8"/>
       <c r="M67" s="14"/>
     </row>
-    <row r="68" spans="1:15" ht="27">
+    <row r="68" spans="1:15" ht="27" hidden="1">
       <c r="A68" s="13">
         <v>92</v>
       </c>
@@ -8534,7 +8560,7 @@
       <c r="L68" s="8"/>
       <c r="M68" s="14"/>
     </row>
-    <row r="69" spans="1:15" ht="27">
+    <row r="69" spans="1:15" ht="27" hidden="1">
       <c r="A69" s="13">
         <v>93</v>
       </c>
@@ -8563,7 +8589,7 @@
       <c r="L69" s="8"/>
       <c r="M69" s="14"/>
     </row>
-    <row r="70" spans="1:15" ht="27">
+    <row r="70" spans="1:15" ht="27" hidden="1">
       <c r="A70" s="13">
         <v>94</v>
       </c>
@@ -8592,7 +8618,7 @@
       <c r="L70" s="8"/>
       <c r="M70" s="14"/>
     </row>
-    <row r="71" spans="1:15" ht="27">
+    <row r="71" spans="1:15" ht="27" hidden="1">
       <c r="A71" s="13">
         <v>95</v>
       </c>
@@ -8619,7 +8645,7 @@
       <c r="L71" s="8"/>
       <c r="M71" s="14"/>
     </row>
-    <row r="72" spans="1:15" ht="27">
+    <row r="72" spans="1:15" ht="27" hidden="1">
       <c r="A72" s="13">
         <v>96</v>
       </c>
@@ -8646,7 +8672,7 @@
       <c r="L72" s="8"/>
       <c r="M72" s="14"/>
     </row>
-    <row r="73" spans="1:15" ht="27">
+    <row r="73" spans="1:15" ht="27" hidden="1">
       <c r="A73" s="13">
         <v>97</v>
       </c>
@@ -8675,7 +8701,7 @@
       <c r="L73" s="8"/>
       <c r="M73" s="14"/>
     </row>
-    <row r="74" spans="1:15" ht="27">
+    <row r="74" spans="1:15" ht="27" hidden="1">
       <c r="A74" s="13">
         <v>98</v>
       </c>
@@ -8717,7 +8743,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="27">
+    <row r="75" spans="1:15" ht="27" hidden="1">
       <c r="A75" s="13">
         <v>99</v>
       </c>
@@ -8759,7 +8785,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="27">
+    <row r="76" spans="1:15" ht="27" hidden="1">
       <c r="A76" s="13">
         <v>100</v>
       </c>
@@ -8836,7 +8862,7 @@
         <v>102</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="8"/>
@@ -8846,25 +8872,34 @@
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
       <c r="H78" s="8"/>
-      <c r="I78" s="8"/>
+      <c r="I78" s="8">
+        <v>20</v>
+      </c>
       <c r="J78" s="8" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="K78" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="L78" s="8"/>
-      <c r="M78" s="14"/>
+      <c r="L78" s="36">
+        <v>42551</v>
+      </c>
+      <c r="M78" s="37">
+        <v>42579</v>
+      </c>
+      <c r="N78" t="s">
+        <v>387</v>
+      </c>
       <c r="O78" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="27">
+    <row r="79" spans="1:15" ht="27" hidden="1">
       <c r="A79" s="13">
         <v>103</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C79" s="8"/>
       <c r="D79" s="8"/>
@@ -8878,12 +8913,12 @@
       <c r="L79" s="8"/>
       <c r="M79" s="14"/>
     </row>
-    <row r="80" spans="1:15" ht="27">
+    <row r="80" spans="1:15" ht="27" hidden="1">
       <c r="A80" s="13">
         <v>104</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
@@ -8897,12 +8932,12 @@
       <c r="L80" s="8"/>
       <c r="M80" s="14"/>
     </row>
-    <row r="81" spans="1:13" ht="40.5">
+    <row r="81" spans="1:13" ht="40.5" hidden="1">
       <c r="A81" s="13">
         <v>105</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
@@ -9052,8 +9087,12 @@
       <c r="M90" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O78">
-    <filterColumn colId="14"/>
+  <autoFilter ref="A1:O81">
+    <filterColumn colId="14">
+      <filters>
+        <filter val="迭代二"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M201">

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="390">
   <si>
     <r>
       <t>描述</t>
@@ -1675,10 +1675,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>李伟超</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>完成总体部署的流程，接口和模块设计</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1804,19 +1800,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>许建辉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>迭代一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SEQUOIADBMAINSTREAM-1754</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>何嘉文</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1845,27 +1829,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>李伟超</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">C++提供连接池功能
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>吴嘉明</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>何嘉文/黄伟钢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李霄剑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">sdb shell中的date和time支持$format
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1898,6 +1866,42 @@
   </si>
   <si>
     <t>4K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何嘉文/黄伟钢/梁雪望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杨上德/黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李伟超/吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉/王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何嘉文/吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李霄剑/王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林友滨/赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李伟超/余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴嘉明/余婷</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6446,10 +6450,10 @@
         <v>7</v>
       </c>
       <c r="N1" s="40" t="s">
+        <v>344</v>
+      </c>
+      <c r="O1" s="41" t="s">
         <v>345</v>
-      </c>
-      <c r="O1" s="41" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="54">
@@ -6461,7 +6465,7 @@
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="35" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E2" s="8">
         <v>2.2000000000000002</v>
@@ -6482,12 +6486,12 @@
         <v>334</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L2" s="42"/>
       <c r="M2" s="43"/>
       <c r="O2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="40.5" hidden="1">
@@ -6682,7 +6686,7 @@
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="44" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E10" s="8">
         <v>2.2000000000000002</v>
@@ -6700,7 +6704,7 @@
         <v>61</v>
       </c>
       <c r="J10" s="29" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K10" s="29" t="s">
         <v>58</v>
@@ -6712,10 +6716,10 @@
         <v>42592</v>
       </c>
       <c r="N10" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="O10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="27" hidden="1">
@@ -6768,10 +6772,10 @@
         <v>30</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L12" s="42">
         <v>42566</v>
@@ -6780,10 +6784,10 @@
         <v>42607</v>
       </c>
       <c r="N12" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="O12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="40.5" hidden="1">
@@ -7340,7 +7344,7 @@
       <c r="L32" s="8"/>
       <c r="M32" s="14"/>
       <c r="O32" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="54" hidden="1">
@@ -7646,7 +7650,7 @@
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="35" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E43" s="8">
         <v>2.2000000000000002</v>
@@ -7676,10 +7680,10 @@
         <v>42474</v>
       </c>
       <c r="N43" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O43" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="40.5">
@@ -7708,12 +7712,12 @@
       </c>
       <c r="J44" s="8"/>
       <c r="K44" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L44" s="8"/>
       <c r="M44" s="14"/>
       <c r="O44" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="40.5" hidden="1">
@@ -7725,7 +7729,7 @@
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="44" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E45" s="8">
         <v>2.2000000000000002</v>
@@ -7743,7 +7747,7 @@
         <v>15</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K45" s="8" t="s">
         <v>79</v>
@@ -7755,7 +7759,7 @@
         <v>42460</v>
       </c>
       <c r="O45" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="40.5" hidden="1">
@@ -7785,7 +7789,7 @@
         <v>30</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="K46" s="8" t="s">
         <v>58</v>
@@ -7831,7 +7835,7 @@
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="35" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E48" s="8">
         <v>2.2000000000000002</v>
@@ -7861,7 +7865,7 @@
         <v>42468</v>
       </c>
       <c r="O48" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="40.5" hidden="1">
@@ -7873,7 +7877,7 @@
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="35" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E49" s="8">
         <v>2.2000000000000002</v>
@@ -7903,10 +7907,10 @@
         <v>42467</v>
       </c>
       <c r="N49" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O49" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="27" hidden="1">
@@ -7949,7 +7953,7 @@
         <v>328</v>
       </c>
       <c r="D51" s="35" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E51" s="8">
         <v>2.2000000000000002</v>
@@ -7967,7 +7971,7 @@
         <v>20</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>334</v>
+        <v>384</v>
       </c>
       <c r="K51" s="8" t="s">
         <v>58</v>
@@ -7979,10 +7983,10 @@
         <v>42583</v>
       </c>
       <c r="N51" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="O51" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="27" hidden="1">
@@ -8041,10 +8045,10 @@
         <v>22</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>337</v>
+        <v>387</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L53" s="36">
         <v>42552</v>
@@ -8053,10 +8057,10 @@
         <v>42586</v>
       </c>
       <c r="N53" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="O53" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="40.5">
@@ -8088,7 +8092,7 @@
       <c r="L54" s="8"/>
       <c r="M54" s="14"/>
       <c r="O54" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="67.5">
@@ -8116,10 +8120,10 @@
         <v>17</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L55" s="36">
         <v>42555</v>
@@ -8128,10 +8132,10 @@
         <v>42579</v>
       </c>
       <c r="N55" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="O55" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="27" hidden="1">
@@ -8218,12 +8222,12 @@
       </c>
       <c r="J58" s="8"/>
       <c r="K58" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L58" s="8"/>
       <c r="M58" s="14"/>
       <c r="O58" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="27" hidden="1">
@@ -8285,7 +8289,7 @@
         <v>84</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
@@ -8305,10 +8309,10 @@
         <v>21</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="K61" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L61" s="36">
         <v>42552</v>
@@ -8317,10 +8321,10 @@
         <v>42583</v>
       </c>
       <c r="N61" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="O61" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="27" hidden="1">
@@ -8381,7 +8385,7 @@
       <c r="L63" s="8"/>
       <c r="M63" s="14"/>
     </row>
-    <row r="64" spans="1:15" ht="27" hidden="1">
+    <row r="64" spans="1:15" ht="27">
       <c r="A64" s="13">
         <v>87</v>
       </c>
@@ -8390,7 +8394,7 @@
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="35" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E64" s="8">
         <v>2.2000000000000002</v>
@@ -8408,7 +8412,7 @@
         <v>60</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>340</v>
+        <v>383</v>
       </c>
       <c r="K64" s="8" t="s">
         <v>79</v>
@@ -8420,7 +8424,7 @@
         <v>42458</v>
       </c>
       <c r="N64" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O64" t="s">
         <v>347</v>
@@ -8435,7 +8439,7 @@
       </c>
       <c r="C65" s="8"/>
       <c r="D65" s="35" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E65" s="8">
         <v>2.2000000000000002</v>
@@ -8453,7 +8457,7 @@
         <v>45</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K65" s="8" t="s">
         <v>79</v>
@@ -8465,10 +8469,10 @@
         <v>42465</v>
       </c>
       <c r="N65" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O65" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="27" hidden="1">
@@ -8710,7 +8714,7 @@
       </c>
       <c r="C74" s="8"/>
       <c r="D74" s="35" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E74" s="8">
         <v>2.2000000000000002</v>
@@ -8740,7 +8744,7 @@
         <v>42461</v>
       </c>
       <c r="O74" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="27" hidden="1">
@@ -8748,11 +8752,11 @@
         <v>99</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C75" s="8"/>
       <c r="D75" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E75" s="8">
         <v>2.2000000000000002</v>
@@ -8770,7 +8774,7 @@
         <v>20</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K75" s="8" t="s">
         <v>79</v>
@@ -8782,19 +8786,19 @@
         <v>42471</v>
       </c>
       <c r="O75" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" ht="27" hidden="1">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" ht="27">
       <c r="A76" s="13">
         <v>100</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C76" s="8"/>
       <c r="D76" s="35" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E76" s="8">
         <v>2.2000000000000002</v>
@@ -8806,7 +8810,7 @@
         <v>30</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="K76" s="8" t="s">
         <v>79</v>
@@ -8818,7 +8822,7 @@
         <v>42538</v>
       </c>
       <c r="O76" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="40.5">
@@ -8826,11 +8830,11 @@
         <v>101</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="35" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E77" s="8">
         <v>2.2000000000000002</v>
@@ -8842,7 +8846,7 @@
         <v>20</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="K77" s="8" t="s">
         <v>79</v>
@@ -8854,7 +8858,7 @@
         <v>42546</v>
       </c>
       <c r="O77" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="27">
@@ -8862,7 +8866,7 @@
         <v>102</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="8"/>
@@ -8876,10 +8880,10 @@
         <v>20</v>
       </c>
       <c r="J78" s="8" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="K78" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L78" s="36">
         <v>42551</v>
@@ -8888,10 +8892,10 @@
         <v>42579</v>
       </c>
       <c r="N78" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="O78" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="27" hidden="1">
@@ -8899,7 +8903,7 @@
         <v>103</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C79" s="8"/>
       <c r="D79" s="8"/>
@@ -8918,7 +8922,7 @@
         <v>104</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
@@ -8937,7 +8941,7 @@
         <v>105</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="391">
   <si>
     <r>
       <t>描述</t>
@@ -1902,6 +1902,12 @@
   </si>
   <si>
     <t>吴嘉明/余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">sdb shell支持 "&gt;&gt;"将结果写入文件，支持"&lt;&lt;"从文件读取内容；
+sdb js语法中支持 import( fileName )，导入新的js文件
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6388,7 +6394,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:O90"/>
@@ -6494,7 +6500,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="40.5" hidden="1">
+    <row r="3" spans="1:15" ht="40.5">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -6519,7 +6525,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="3"/>
     </row>
-    <row r="4" spans="1:15" ht="40.5" hidden="1">
+    <row r="4" spans="1:15" ht="40.5">
       <c r="A4" s="27">
         <v>4</v>
       </c>
@@ -6544,7 +6550,7 @@
       <c r="L4" s="30"/>
       <c r="M4" s="31"/>
     </row>
-    <row r="5" spans="1:15" ht="40.5" hidden="1">
+    <row r="5" spans="1:15" ht="40.5">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -6569,7 +6575,7 @@
       <c r="L5" s="2"/>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:15" ht="54" hidden="1">
+    <row r="6" spans="1:15" ht="54">
       <c r="A6" s="1">
         <v>7</v>
       </c>
@@ -6598,7 +6604,7 @@
       <c r="L6" s="2"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:15" ht="40.5" hidden="1">
+    <row r="7" spans="1:15" ht="40.5">
       <c r="A7" s="1">
         <v>10</v>
       </c>
@@ -6623,7 +6629,7 @@
       <c r="L7" s="2"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:15" ht="27" hidden="1">
+    <row r="8" spans="1:15" ht="27">
       <c r="A8" s="1">
         <v>13</v>
       </c>
@@ -6648,7 +6654,7 @@
       <c r="L8" s="2"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:15" ht="54" hidden="1">
+    <row r="9" spans="1:15" ht="54">
       <c r="A9" s="1">
         <v>14</v>
       </c>
@@ -6722,7 +6728,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="27" hidden="1">
+    <row r="11" spans="1:15" ht="27">
       <c r="A11" s="27">
         <v>17</v>
       </c>
@@ -6790,7 +6796,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="40.5" hidden="1">
+    <row r="13" spans="1:15" ht="40.5">
       <c r="A13" s="1">
         <v>19</v>
       </c>
@@ -6815,7 +6821,7 @@
       <c r="L13" s="2"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:15" ht="27" hidden="1">
+    <row r="14" spans="1:15" ht="27">
       <c r="A14" s="1">
         <v>20</v>
       </c>
@@ -6840,7 +6846,7 @@
       <c r="L14" s="2"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:15" ht="40.5" hidden="1">
+    <row r="15" spans="1:15" ht="40.5">
       <c r="A15" s="1">
         <v>21</v>
       </c>
@@ -6869,7 +6875,7 @@
       <c r="L15" s="2"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:15" ht="40.5" hidden="1">
+    <row r="16" spans="1:15" ht="40.5">
       <c r="A16" s="1">
         <v>22</v>
       </c>
@@ -6894,7 +6900,7 @@
       <c r="L16" s="2"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="1:15" ht="40.5" hidden="1">
+    <row r="17" spans="1:15" ht="40.5">
       <c r="A17" s="1">
         <v>23</v>
       </c>
@@ -6919,7 +6925,7 @@
       <c r="L17" s="2"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:15" ht="54" hidden="1">
+    <row r="18" spans="1:15" ht="54">
       <c r="A18" s="1">
         <v>24</v>
       </c>
@@ -6948,7 +6954,7 @@
       <c r="L18" s="2"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="1:15" ht="40.5" hidden="1">
+    <row r="19" spans="1:15" ht="40.5">
       <c r="A19" s="1">
         <v>26</v>
       </c>
@@ -6977,7 +6983,7 @@
       <c r="L19" s="2"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:15" ht="40.5" hidden="1">
+    <row r="20" spans="1:15" ht="40.5">
       <c r="A20" s="1">
         <v>28</v>
       </c>
@@ -7006,7 +7012,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="1:15" ht="40.5" hidden="1">
+    <row r="21" spans="1:15" ht="40.5">
       <c r="A21" s="1">
         <v>29</v>
       </c>
@@ -7033,7 +7039,7 @@
       <c r="L21" s="2"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:15" ht="27" hidden="1">
+    <row r="22" spans="1:15" ht="27">
       <c r="A22" s="1">
         <v>30</v>
       </c>
@@ -7062,7 +7068,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:15" ht="27" hidden="1">
+    <row r="23" spans="1:15" ht="27">
       <c r="A23" s="1">
         <v>31</v>
       </c>
@@ -7089,7 +7095,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:15" ht="27" hidden="1">
+    <row r="24" spans="1:15" ht="27">
       <c r="A24" s="1">
         <v>34</v>
       </c>
@@ -7118,7 +7124,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" spans="1:15" ht="40.5" hidden="1">
+    <row r="25" spans="1:15" ht="40.5">
       <c r="A25" s="1">
         <v>35</v>
       </c>
@@ -7147,7 +7153,7 @@
       <c r="L25" s="2"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="1:15" ht="54" hidden="1">
+    <row r="26" spans="1:15" ht="54">
       <c r="A26" s="1">
         <v>36</v>
       </c>
@@ -7176,7 +7182,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:15" ht="27" hidden="1">
+    <row r="27" spans="1:15" ht="27">
       <c r="A27" s="1">
         <v>38</v>
       </c>
@@ -7205,7 +7211,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:15" ht="27" hidden="1">
+    <row r="28" spans="1:15" ht="27">
       <c r="A28" s="1">
         <v>39</v>
       </c>
@@ -7234,7 +7240,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:15" ht="27" hidden="1">
+    <row r="29" spans="1:15" ht="27">
       <c r="A29" s="13">
         <v>40</v>
       </c>
@@ -7261,7 +7267,7 @@
       <c r="L29" s="8"/>
       <c r="M29" s="14"/>
     </row>
-    <row r="30" spans="1:15" ht="27" hidden="1">
+    <row r="30" spans="1:15" ht="27">
       <c r="A30" s="13">
         <v>42</v>
       </c>
@@ -7288,7 +7294,7 @@
       <c r="L30" s="8"/>
       <c r="M30" s="14"/>
     </row>
-    <row r="31" spans="1:15" ht="27" hidden="1">
+    <row r="31" spans="1:15" ht="27">
       <c r="A31" s="13">
         <v>43</v>
       </c>
@@ -7347,7 +7353,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="54" hidden="1">
+    <row r="33" spans="1:15" ht="54">
       <c r="A33" s="13">
         <v>47</v>
       </c>
@@ -7374,7 +7380,7 @@
       <c r="L33" s="8"/>
       <c r="M33" s="14"/>
     </row>
-    <row r="34" spans="1:15" ht="54" hidden="1">
+    <row r="34" spans="1:15" ht="54">
       <c r="A34" s="13">
         <v>48</v>
       </c>
@@ -7403,7 +7409,7 @@
       <c r="L34" s="8"/>
       <c r="M34" s="14"/>
     </row>
-    <row r="35" spans="1:15" ht="54" hidden="1">
+    <row r="35" spans="1:15" ht="54">
       <c r="A35" s="13">
         <v>49</v>
       </c>
@@ -7432,7 +7438,7 @@
       <c r="L35" s="8"/>
       <c r="M35" s="14"/>
     </row>
-    <row r="36" spans="1:15" ht="40.5" hidden="1">
+    <row r="36" spans="1:15" ht="40.5">
       <c r="A36" s="13">
         <v>54</v>
       </c>
@@ -7461,7 +7467,7 @@
       <c r="L36" s="8"/>
       <c r="M36" s="14"/>
     </row>
-    <row r="37" spans="1:15" ht="94.5" hidden="1">
+    <row r="37" spans="1:15" ht="94.5">
       <c r="A37" s="13">
         <v>58</v>
       </c>
@@ -7492,7 +7498,7 @@
       <c r="L37" s="8"/>
       <c r="M37" s="14"/>
     </row>
-    <row r="38" spans="1:15" ht="27" hidden="1">
+    <row r="38" spans="1:15" ht="27">
       <c r="A38" s="13">
         <v>59</v>
       </c>
@@ -7525,7 +7531,7 @@
       <c r="L38" s="8"/>
       <c r="M38" s="14"/>
     </row>
-    <row r="39" spans="1:15" ht="27" hidden="1">
+    <row r="39" spans="1:15" ht="27">
       <c r="A39" s="13">
         <v>60</v>
       </c>
@@ -7554,7 +7560,7 @@
       <c r="L39" s="8"/>
       <c r="M39" s="14"/>
     </row>
-    <row r="40" spans="1:15" ht="27" hidden="1">
+    <row r="40" spans="1:15" ht="27">
       <c r="A40" s="13">
         <v>62</v>
       </c>
@@ -7585,7 +7591,7 @@
       <c r="L40" s="8"/>
       <c r="M40" s="14"/>
     </row>
-    <row r="41" spans="1:15" ht="27" hidden="1">
+    <row r="41" spans="1:15" ht="27">
       <c r="A41" s="13">
         <v>63</v>
       </c>
@@ -7614,7 +7620,7 @@
       <c r="L41" s="8"/>
       <c r="M41" s="14"/>
     </row>
-    <row r="42" spans="1:15" ht="27" hidden="1">
+    <row r="42" spans="1:15" ht="27">
       <c r="A42" s="1">
         <v>64</v>
       </c>
@@ -7641,7 +7647,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" spans="1:15" ht="40.5" hidden="1">
+    <row r="43" spans="1:15" ht="40.5">
       <c r="A43" s="13">
         <v>65</v>
       </c>
@@ -7720,7 +7726,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="40.5" hidden="1">
+    <row r="45" spans="1:15" ht="40.5">
       <c r="A45" s="13">
         <v>67</v>
       </c>
@@ -7762,7 +7768,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="40.5" hidden="1">
+    <row r="46" spans="1:15" ht="40.5">
       <c r="A46" s="13">
         <v>68</v>
       </c>
@@ -7797,7 +7803,7 @@
       <c r="L46" s="8"/>
       <c r="M46" s="14"/>
     </row>
-    <row r="47" spans="1:15" ht="40.5" hidden="1">
+    <row r="47" spans="1:15" ht="40.5">
       <c r="A47" s="13">
         <v>70</v>
       </c>
@@ -7826,7 +7832,7 @@
       <c r="L47" s="8"/>
       <c r="M47" s="14"/>
     </row>
-    <row r="48" spans="1:15" ht="54" hidden="1">
+    <row r="48" spans="1:15" ht="54">
       <c r="A48" s="13">
         <v>71</v>
       </c>
@@ -7868,7 +7874,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="40.5" hidden="1">
+    <row r="49" spans="1:15" ht="40.5">
       <c r="A49" s="13">
         <v>72</v>
       </c>
@@ -7913,7 +7919,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="27" hidden="1">
+    <row r="50" spans="1:15" ht="27">
       <c r="A50" s="13">
         <v>73</v>
       </c>
@@ -7989,7 +7995,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="27" hidden="1">
+    <row r="52" spans="1:15" ht="27">
       <c r="A52" s="13">
         <v>75</v>
       </c>
@@ -8138,7 +8144,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="27" hidden="1">
+    <row r="56" spans="1:15" ht="27">
       <c r="A56" s="13">
         <v>79</v>
       </c>
@@ -8167,7 +8173,7 @@
       <c r="L56" s="8"/>
       <c r="M56" s="14"/>
     </row>
-    <row r="57" spans="1:15" ht="27" hidden="1">
+    <row r="57" spans="1:15" ht="27">
       <c r="A57" s="13">
         <v>80</v>
       </c>
@@ -8230,7 +8236,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="27" hidden="1">
+    <row r="59" spans="1:15" ht="27">
       <c r="A59" s="13">
         <v>82</v>
       </c>
@@ -8259,7 +8265,7 @@
       <c r="L59" s="8"/>
       <c r="M59" s="14"/>
     </row>
-    <row r="60" spans="1:15" ht="27" hidden="1">
+    <row r="60" spans="1:15" ht="27">
       <c r="A60" s="13">
         <v>83</v>
       </c>
@@ -8327,7 +8333,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="27" hidden="1">
+    <row r="62" spans="1:15" ht="27">
       <c r="A62" s="13">
         <v>85</v>
       </c>
@@ -8356,7 +8362,7 @@
       <c r="L62" s="8"/>
       <c r="M62" s="14"/>
     </row>
-    <row r="63" spans="1:15" ht="40.5" hidden="1">
+    <row r="63" spans="1:15" ht="40.5">
       <c r="A63" s="13">
         <v>86</v>
       </c>
@@ -8430,7 +8436,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="40.5" hidden="1">
+    <row r="65" spans="1:15" ht="40.5">
       <c r="A65" s="13">
         <v>88</v>
       </c>
@@ -8475,7 +8481,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="27" hidden="1">
+    <row r="66" spans="1:15" ht="27">
       <c r="A66" s="13">
         <v>89</v>
       </c>
@@ -8506,7 +8512,7 @@
       <c r="L66" s="8"/>
       <c r="M66" s="14"/>
     </row>
-    <row r="67" spans="1:15" ht="27" hidden="1">
+    <row r="67" spans="1:15" ht="27">
       <c r="A67" s="13">
         <v>91</v>
       </c>
@@ -8535,7 +8541,7 @@
       <c r="L67" s="8"/>
       <c r="M67" s="14"/>
     </row>
-    <row r="68" spans="1:15" ht="27" hidden="1">
+    <row r="68" spans="1:15" ht="27">
       <c r="A68" s="13">
         <v>92</v>
       </c>
@@ -8564,7 +8570,7 @@
       <c r="L68" s="8"/>
       <c r="M68" s="14"/>
     </row>
-    <row r="69" spans="1:15" ht="27" hidden="1">
+    <row r="69" spans="1:15" ht="27">
       <c r="A69" s="13">
         <v>93</v>
       </c>
@@ -8593,7 +8599,7 @@
       <c r="L69" s="8"/>
       <c r="M69" s="14"/>
     </row>
-    <row r="70" spans="1:15" ht="27" hidden="1">
+    <row r="70" spans="1:15" ht="27">
       <c r="A70" s="13">
         <v>94</v>
       </c>
@@ -8622,7 +8628,7 @@
       <c r="L70" s="8"/>
       <c r="M70" s="14"/>
     </row>
-    <row r="71" spans="1:15" ht="27" hidden="1">
+    <row r="71" spans="1:15" ht="27">
       <c r="A71" s="13">
         <v>95</v>
       </c>
@@ -8649,7 +8655,7 @@
       <c r="L71" s="8"/>
       <c r="M71" s="14"/>
     </row>
-    <row r="72" spans="1:15" ht="27" hidden="1">
+    <row r="72" spans="1:15" ht="27">
       <c r="A72" s="13">
         <v>96</v>
       </c>
@@ -8676,7 +8682,7 @@
       <c r="L72" s="8"/>
       <c r="M72" s="14"/>
     </row>
-    <row r="73" spans="1:15" ht="27" hidden="1">
+    <row r="73" spans="1:15" ht="27">
       <c r="A73" s="13">
         <v>97</v>
       </c>
@@ -8705,7 +8711,7 @@
       <c r="L73" s="8"/>
       <c r="M73" s="14"/>
     </row>
-    <row r="74" spans="1:15" ht="27" hidden="1">
+    <row r="74" spans="1:15" ht="27">
       <c r="A74" s="13">
         <v>98</v>
       </c>
@@ -8747,7 +8753,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="27" hidden="1">
+    <row r="75" spans="1:15" ht="27">
       <c r="A75" s="13">
         <v>99</v>
       </c>
@@ -8898,7 +8904,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="27" hidden="1">
+    <row r="79" spans="1:15" ht="27">
       <c r="A79" s="13">
         <v>103</v>
       </c>
@@ -8917,7 +8923,7 @@
       <c r="L79" s="8"/>
       <c r="M79" s="14"/>
     </row>
-    <row r="80" spans="1:15" ht="27" hidden="1">
+    <row r="80" spans="1:15" ht="27">
       <c r="A80" s="13">
         <v>104</v>
       </c>
@@ -8936,7 +8942,7 @@
       <c r="L80" s="8"/>
       <c r="M80" s="14"/>
     </row>
-    <row r="81" spans="1:13" ht="40.5" hidden="1">
+    <row r="81" spans="1:13" ht="40.5">
       <c r="A81" s="13">
         <v>105</v>
       </c>
@@ -8955,9 +8961,13 @@
       <c r="L81" s="8"/>
       <c r="M81" s="14"/>
     </row>
-    <row r="82" spans="1:13">
-      <c r="A82" s="13"/>
-      <c r="B82" s="8"/>
+    <row r="82" spans="1:13" ht="67.5">
+      <c r="A82" s="13">
+        <v>106</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>390</v>
+      </c>
       <c r="C82" s="8"/>
       <c r="D82" s="8"/>
       <c r="E82" s="8"/>
@@ -9092,11 +9102,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O81">
-    <filterColumn colId="14">
-      <filters>
-        <filter val="迭代二"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="14"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M201">

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2014年1季度'!$A$1:$M$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2016年'!$A$1:$O$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2016年'!$A$1:$O$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">已完成任务!$A$1:$M$64</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="395">
   <si>
     <r>
       <t>描述</t>
@@ -1465,11 +1465,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">match支持函数和流式处理，支持对数组的精确匹配
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Coord加入到系统管理，向Catalog注册获取节点ID，实现Coord自动负载均衡和监控（所有coord节点的catalogaddr参数自动保存）
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1907,6 +1902,31 @@
   <si>
     <t xml:space="preserve">sdb shell支持 "&gt;&gt;"将结果写入文件，支持"&lt;&lt;"从文件读取内容；
 sdb js语法中支持 import( fileName )，导入新的js文件
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">match支持函数和递规处理，支持对数组的精确匹配
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多数据中心提供实时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>？？？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提供全文检索能力
+1、松耦合：插件；接口, 需求：日志查寻
+2、紧耦合：lucen+合入数据节点
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">在线重组数据页（后台任务在闲时，该集合无查询，页空洞达到预设条件时自动重组页）
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2306,7 +2326,399 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="204">
+  <dxfs count="260">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5179,16 +5591,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M169">
-    <cfRule type="expression" dxfId="203" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="259" priority="1" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="202" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="258" priority="2" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="201" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="257" priority="3" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="200" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="256" priority="4" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6363,16 +6775,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L185">
-    <cfRule type="expression" dxfId="199" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="255" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="198" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="254" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="197" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="253" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="196" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="252" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6397,7 +6809,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:O90"/>
+  <dimension ref="A1:P100"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
@@ -6429,7 +6841,7 @@
         <v>86</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>1</v>
@@ -6456,10 +6868,10 @@
         <v>7</v>
       </c>
       <c r="N1" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="O1" s="41" t="s">
         <v>344</v>
-      </c>
-      <c r="O1" s="41" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="54">
@@ -6467,11 +6879,11 @@
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="35" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E2" s="8">
         <v>2.2000000000000002</v>
@@ -6489,15 +6901,15 @@
         <v>15</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L2" s="42"/>
       <c r="M2" s="43"/>
       <c r="O2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="40.5">
@@ -6688,11 +7100,11 @@
         <v>16</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="44" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E10" s="8">
         <v>2.2000000000000002</v>
@@ -6710,7 +7122,7 @@
         <v>61</v>
       </c>
       <c r="J10" s="29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K10" s="29" t="s">
         <v>58</v>
@@ -6722,10 +7134,10 @@
         <v>42592</v>
       </c>
       <c r="N10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="27">
@@ -6758,7 +7170,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -6778,10 +7190,10 @@
         <v>30</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L12" s="42">
         <v>42566</v>
@@ -6790,10 +7202,10 @@
         <v>42607</v>
       </c>
       <c r="N12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="O12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="40.5">
@@ -6930,7 +7342,7 @@
         <v>24</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
@@ -7038,6 +7450,9 @@
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="3"/>
+      <c r="N21" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="22" spans="1:15" ht="27">
       <c r="A22" s="1">
@@ -7350,7 +7765,7 @@
       <c r="L32" s="8"/>
       <c r="M32" s="14"/>
       <c r="O32" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="54">
@@ -7385,7 +7800,7 @@
         <v>48</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -7414,7 +7829,7 @@
         <v>49</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -7536,7 +7951,7 @@
         <v>60</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -7649,15 +8064,13 @@
     </row>
     <row r="43" spans="1:15" ht="40.5">
       <c r="A43" s="13">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C43" s="8"/>
-      <c r="D43" s="35" t="s">
-        <v>355</v>
-      </c>
+      <c r="D43" s="8"/>
       <c r="E43" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -7665,41 +8078,34 @@
         <v>64</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I43" s="8">
-        <v>30</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>337</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="J43" s="8"/>
       <c r="K43" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="L43" s="36">
-        <v>42446</v>
-      </c>
-      <c r="M43" s="37">
-        <v>42474</v>
-      </c>
-      <c r="N43" t="s">
-        <v>351</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="L43" s="8"/>
+      <c r="M43" s="14"/>
       <c r="O43" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="40.5">
       <c r="A44" s="13">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="C44" s="8"/>
+        <v>314</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>328</v>
+      </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8">
         <v>2.2000000000000002</v>
@@ -7708,183 +8114,168 @@
         <v>64</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I44" s="8">
-        <v>18</v>
-      </c>
-      <c r="J44" s="8"/>
+        <v>30</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>369</v>
+      </c>
       <c r="K44" s="8" t="s">
-        <v>350</v>
+        <v>58</v>
       </c>
       <c r="L44" s="8"/>
       <c r="M44" s="14"/>
-      <c r="O44" t="s">
-        <v>367</v>
-      </c>
     </row>
     <row r="45" spans="1:15" ht="40.5">
       <c r="A45" s="13">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C45" s="8"/>
-      <c r="D45" s="44" t="s">
-        <v>354</v>
-      </c>
+      <c r="D45" s="8"/>
       <c r="E45" s="8">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>64</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>281</v>
+        <v>176</v>
       </c>
       <c r="I45" s="8">
-        <v>15</v>
-      </c>
-      <c r="J45" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="L45" s="36">
-        <v>42446</v>
-      </c>
-      <c r="M45" s="37">
-        <v>42460</v>
-      </c>
-      <c r="O45" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" ht="40.5">
+        <v>24</v>
+      </c>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="14"/>
+    </row>
+    <row r="46" spans="1:15" ht="27">
       <c r="A46" s="13">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>329</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="C46" s="8"/>
       <c r="D46" s="8"/>
       <c r="E46" s="8">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="G46" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="I46" s="8">
-        <v>30</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="K46" s="8" t="s">
-        <v>58</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
       <c r="L46" s="8"/>
       <c r="M46" s="14"/>
     </row>
-    <row r="47" spans="1:15" ht="40.5">
+    <row r="47" spans="1:15" ht="27">
       <c r="A47" s="13">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
+        <v>293</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="D47" s="35" t="s">
+        <v>357</v>
+      </c>
       <c r="E47" s="8">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>176</v>
+        <v>289</v>
       </c>
       <c r="I47" s="8">
-        <v>24</v>
-      </c>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="14"/>
-    </row>
-    <row r="48" spans="1:15" ht="54">
+        <v>20</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L47" s="36">
+        <v>42557</v>
+      </c>
+      <c r="M47" s="37">
+        <v>42583</v>
+      </c>
+      <c r="N47" t="s">
+        <v>376</v>
+      </c>
+      <c r="O47" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="27">
       <c r="A48" s="13">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="35" t="s">
-        <v>353</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="D48" s="8"/>
       <c r="E48" s="8">
         <v>2.2000000000000002</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="I48" s="8">
-        <v>22</v>
-      </c>
-      <c r="J48" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="L48" s="36">
-        <v>42443</v>
-      </c>
-      <c r="M48" s="37">
-        <v>42468</v>
-      </c>
-      <c r="O48" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="40.5">
+        <v>15</v>
+      </c>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="14"/>
+    </row>
+    <row r="49" spans="1:16" ht="40.5">
       <c r="A49" s="13">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>290</v>
+        <v>390</v>
       </c>
       <c r="C49" s="8"/>
-      <c r="D49" s="35" t="s">
-        <v>356</v>
-      </c>
+      <c r="D49" s="8"/>
       <c r="E49" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -7895,143 +8286,140 @@
         <v>12</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="I49" s="8">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>335</v>
+        <v>386</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>79</v>
+        <v>349</v>
       </c>
       <c r="L49" s="36">
-        <v>42451</v>
+        <v>42552</v>
       </c>
       <c r="M49" s="37">
-        <v>42467</v>
+        <v>42586</v>
       </c>
       <c r="N49" t="s">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="O49" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="27">
+    <row r="50" spans="1:16" ht="40.5">
       <c r="A50" s="13">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
       <c r="E50" s="8">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="G50" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="I50" s="8">
         <v>22</v>
-      </c>
-      <c r="H50" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="I50" s="8">
-        <v>45</v>
       </c>
       <c r="J50" s="8"/>
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
       <c r="M50" s="14"/>
-    </row>
-    <row r="51" spans="1:15" ht="27">
+      <c r="O50" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="67.5">
       <c r="A51" s="13">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="D51" s="35" t="s">
-        <v>358</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
       <c r="E51" s="8">
         <v>2.2000000000000002</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="I51" s="8">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>58</v>
+        <v>349</v>
       </c>
       <c r="L51" s="36">
-        <v>42557</v>
+        <v>42555</v>
       </c>
       <c r="M51" s="37">
-        <v>42583</v>
+        <v>42579</v>
       </c>
       <c r="N51" t="s">
         <v>377</v>
       </c>
       <c r="O51" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" ht="27">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="27">
       <c r="A52" s="13">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>328</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="C52" s="8"/>
       <c r="D52" s="8"/>
       <c r="E52" s="8">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="G52" s="8" t="s">
         <v>16</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I52" s="8">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J52" s="8"/>
       <c r="K52" s="8"/>
       <c r="L52" s="8"/>
       <c r="M52" s="14"/>
     </row>
-    <row r="53" spans="1:15" ht="40.5">
+    <row r="53" spans="1:16" ht="27">
       <c r="A53" s="13">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
@@ -8042,39 +8430,25 @@
         <v>64</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="I53" s="8">
-        <v>22</v>
-      </c>
-      <c r="J53" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="K53" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="L53" s="36">
-        <v>42552</v>
-      </c>
-      <c r="M53" s="37">
-        <v>42586</v>
-      </c>
-      <c r="N53" t="s">
-        <v>377</v>
-      </c>
-      <c r="O53" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" ht="40.5">
+        <v>40</v>
+      </c>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="14"/>
+    </row>
+    <row r="54" spans="1:16" ht="67.5">
       <c r="A54" s="13">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
@@ -8082,103 +8456,87 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="G54" s="8" t="s">
         <v>12</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="I54" s="8">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J54" s="8"/>
-      <c r="K54" s="8"/>
+      <c r="K54" s="8" t="s">
+        <v>349</v>
+      </c>
       <c r="L54" s="8"/>
       <c r="M54" s="14"/>
       <c r="O54" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" ht="67.5">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="27">
       <c r="A55" s="13">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
       <c r="E55" s="8">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="I55" s="8">
-        <v>17</v>
-      </c>
-      <c r="J55" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="K55" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="L55" s="36">
-        <v>42555</v>
-      </c>
-      <c r="M55" s="37">
-        <v>42579</v>
-      </c>
-      <c r="N55" t="s">
-        <v>378</v>
-      </c>
-      <c r="O55" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" ht="27">
+        <v>14</v>
+      </c>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+      <c r="M55" s="14"/>
+    </row>
+    <row r="56" spans="1:16" ht="27">
       <c r="A56" s="13">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
-      <c r="E56" s="8">
-        <v>2.4</v>
-      </c>
+      <c r="E56" s="8"/>
       <c r="F56" s="8" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="I56" s="8">
-        <v>30</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="I56" s="8"/>
       <c r="J56" s="8"/>
       <c r="K56" s="8"/>
       <c r="L56" s="8"/>
       <c r="M56" s="14"/>
     </row>
-    <row r="57" spans="1:15" ht="27">
+    <row r="57" spans="1:16" ht="67.5">
       <c r="A57" s="13">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>306</v>
+        <v>370</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
@@ -8189,113 +8547,131 @@
         <v>64</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="I57" s="8">
-        <v>40</v>
-      </c>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
-      <c r="M57" s="14"/>
-    </row>
-    <row r="58" spans="1:15" ht="67.5">
+        <v>21</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="L57" s="36">
+        <v>42552</v>
+      </c>
+      <c r="M57" s="37">
+        <v>42583</v>
+      </c>
+      <c r="N57" t="s">
+        <v>375</v>
+      </c>
+      <c r="O57" t="s">
+        <v>366</v>
+      </c>
+      <c r="P57" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="27">
       <c r="A58" s="13">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
       <c r="E58" s="8">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="G58" s="8" t="s">
         <v>12</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>295</v>
+        <v>191</v>
       </c>
       <c r="I58" s="8">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J58" s="8"/>
-      <c r="K58" s="8" t="s">
-        <v>350</v>
-      </c>
+      <c r="K58" s="8"/>
       <c r="L58" s="8"/>
       <c r="M58" s="14"/>
-      <c r="O58" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" ht="27">
+    </row>
+    <row r="59" spans="1:16" ht="40.5">
       <c r="A59" s="13">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
       <c r="E59" s="8">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="I59" s="8">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J59" s="8"/>
       <c r="K59" s="8"/>
       <c r="L59" s="8"/>
       <c r="M59" s="14"/>
     </row>
-    <row r="60" spans="1:15" ht="27">
+    <row r="60" spans="1:16" ht="27">
       <c r="A60" s="13">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C60" s="8"/>
+        <v>318</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>328</v>
+      </c>
       <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
+      <c r="E60" s="8">
+        <v>2.4</v>
+      </c>
       <c r="F60" s="8" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="G60" s="8" t="s">
         <v>12</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="I60" s="8"/>
+        <v>291</v>
+      </c>
+      <c r="I60" s="8">
+        <v>60</v>
+      </c>
       <c r="J60" s="8"/>
       <c r="K60" s="8"/>
       <c r="L60" s="8"/>
       <c r="M60" s="14"/>
     </row>
-    <row r="61" spans="1:15" ht="67.5">
+    <row r="61" spans="1:16" ht="27">
       <c r="A61" s="13">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
@@ -8303,209 +8679,157 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="I61" s="8">
-        <v>21</v>
-      </c>
-      <c r="J61" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="K61" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="L61" s="36">
-        <v>42552</v>
-      </c>
-      <c r="M61" s="37">
-        <v>42583</v>
-      </c>
-      <c r="N61" t="s">
-        <v>376</v>
-      </c>
-      <c r="O61" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" ht="27">
+        <v>30</v>
+      </c>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="8"/>
+      <c r="M61" s="14"/>
+    </row>
+    <row r="62" spans="1:16" ht="27">
       <c r="A62" s="13">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
       <c r="E62" s="8">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>191</v>
+        <v>331</v>
       </c>
       <c r="I62" s="8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J62" s="8"/>
       <c r="K62" s="8"/>
       <c r="L62" s="8"/>
       <c r="M62" s="14"/>
     </row>
-    <row r="63" spans="1:15" ht="40.5">
+    <row r="63" spans="1:16" ht="27">
       <c r="A63" s="13">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
       <c r="E63" s="8">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="G63" s="8" t="s">
         <v>12</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>286</v>
+        <v>331</v>
       </c>
       <c r="I63" s="8">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="J63" s="8"/>
       <c r="K63" s="8"/>
       <c r="L63" s="8"/>
       <c r="M63" s="14"/>
     </row>
-    <row r="64" spans="1:15" ht="27">
+    <row r="64" spans="1:16" ht="27">
       <c r="A64" s="13">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C64" s="8"/>
-      <c r="D64" s="35" t="s">
-        <v>363</v>
-      </c>
+      <c r="D64" s="8"/>
       <c r="E64" s="8">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="F64" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="I64" s="8">
+        <v>30</v>
+      </c>
+      <c r="J64" s="8"/>
+      <c r="K64" s="8"/>
+      <c r="L64" s="8"/>
+      <c r="M64" s="14"/>
+    </row>
+    <row r="65" spans="1:15" ht="27">
+      <c r="A65" s="13">
+        <v>95</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="F65" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="G64" s="8" t="s">
+      <c r="G65" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H64" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="I64" s="8">
-        <v>60</v>
-      </c>
-      <c r="J64" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="K64" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="L64" s="36">
-        <v>42445</v>
-      </c>
-      <c r="M64" s="37">
-        <v>42458</v>
-      </c>
-      <c r="N64" t="s">
-        <v>340</v>
-      </c>
-      <c r="O64" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" ht="40.5">
-      <c r="A65" s="13">
-        <v>88</v>
-      </c>
-      <c r="B65" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="C65" s="8"/>
-      <c r="D65" s="35" t="s">
-        <v>359</v>
-      </c>
-      <c r="E65" s="8">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G65" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H65" s="8" t="s">
-        <v>331</v>
-      </c>
+      <c r="H65" s="8"/>
       <c r="I65" s="8">
-        <v>45</v>
-      </c>
-      <c r="J65" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="K65" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="L65" s="36">
-        <v>42447</v>
-      </c>
-      <c r="M65" s="37">
-        <v>42465</v>
-      </c>
-      <c r="N65" t="s">
-        <v>348</v>
-      </c>
-      <c r="O65" t="s">
-        <v>346</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="14"/>
     </row>
     <row r="66" spans="1:15" ht="27">
       <c r="A66" s="13">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D66" s="8"/>
-      <c r="E66" s="8">
-        <v>2.4</v>
-      </c>
+      <c r="E66" s="8"/>
       <c r="F66" s="8" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H66" s="8" t="s">
-        <v>291</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H66" s="8"/>
       <c r="I66" s="8">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="J66" s="8"/>
       <c r="K66" s="8"/>
@@ -8514,27 +8838,27 @@
     </row>
     <row r="67" spans="1:15" ht="27">
       <c r="A67" s="13">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
       <c r="E67" s="8">
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I67" s="8">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="J67" s="8"/>
       <c r="K67" s="8"/>
@@ -8543,57 +8867,55 @@
     </row>
     <row r="68" spans="1:15" ht="27">
       <c r="A68" s="13">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>321</v>
+        <v>371</v>
       </c>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
       <c r="E68" s="8">
         <v>2.2000000000000002</v>
       </c>
-      <c r="F68" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H68" s="8" t="s">
-        <v>332</v>
-      </c>
+      <c r="F68" s="8"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
       <c r="I68" s="8">
-        <v>30</v>
-      </c>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="14"/>
+        <v>20</v>
+      </c>
+      <c r="J68" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="K68" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="L68" s="36">
+        <v>42551</v>
+      </c>
+      <c r="M68" s="37">
+        <v>42579</v>
+      </c>
+      <c r="N68" t="s">
+        <v>378</v>
+      </c>
+      <c r="O68" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="69" spans="1:15" ht="27">
       <c r="A69" s="13">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
-      <c r="E69" s="8">
-        <v>2.4</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G69" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H69" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="I69" s="8">
-        <v>60</v>
-      </c>
+      <c r="E69" s="8"/>
+      <c r="F69" s="8"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="8"/>
       <c r="J69" s="8"/>
       <c r="K69" s="8"/>
       <c r="L69" s="8"/>
@@ -8601,316 +8923,164 @@
     </row>
     <row r="70" spans="1:15" ht="27">
       <c r="A70" s="13">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>323</v>
+        <v>372</v>
       </c>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
-      <c r="E70" s="8">
-        <v>2.4</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G70" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H70" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="I70" s="8">
-        <v>30</v>
-      </c>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
       <c r="J70" s="8"/>
       <c r="K70" s="8"/>
       <c r="L70" s="8"/>
       <c r="M70" s="14"/>
     </row>
-    <row r="71" spans="1:15" ht="27">
+    <row r="71" spans="1:15" ht="40.5">
       <c r="A71" s="13">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>324</v>
+        <v>374</v>
       </c>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
-      <c r="E71" s="8">
-        <v>2.6</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>12</v>
-      </c>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8"/>
       <c r="H71" s="8"/>
-      <c r="I71" s="8">
-        <v>40</v>
-      </c>
+      <c r="I71" s="8"/>
       <c r="J71" s="8"/>
       <c r="K71" s="8"/>
       <c r="L71" s="8"/>
       <c r="M71" s="14"/>
     </row>
-    <row r="72" spans="1:15" ht="27">
+    <row r="72" spans="1:15" ht="67.5">
       <c r="A72" s="13">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>329</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="C72" s="8"/>
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
-      <c r="F72" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>22</v>
-      </c>
+      <c r="F72" s="8"/>
+      <c r="G72" s="8"/>
       <c r="H72" s="8"/>
-      <c r="I72" s="8">
-        <v>15</v>
-      </c>
+      <c r="I72" s="8"/>
       <c r="J72" s="8"/>
       <c r="K72" s="8"/>
       <c r="L72" s="8"/>
       <c r="M72" s="14"/>
     </row>
-    <row r="73" spans="1:15" ht="27">
+    <row r="73" spans="1:15" ht="54">
       <c r="A73" s="13">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>333</v>
+        <v>393</v>
       </c>
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
-      <c r="E73" s="8">
-        <v>2.4</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H73" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="I73" s="8">
-        <v>90</v>
-      </c>
+      <c r="E73" s="8"/>
+      <c r="F73" s="8"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
+      <c r="I73" s="8"/>
       <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
+      <c r="K73" s="8" t="s">
+        <v>349</v>
+      </c>
       <c r="L73" s="8"/>
       <c r="M73" s="14"/>
     </row>
-    <row r="74" spans="1:15" ht="27">
+    <row r="74" spans="1:15" ht="40.5">
       <c r="A74" s="13">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>338</v>
+        <v>394</v>
       </c>
       <c r="C74" s="8"/>
-      <c r="D74" s="35" t="s">
-        <v>357</v>
-      </c>
-      <c r="E74" s="8">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H74" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="I74" s="8">
-        <v>18</v>
-      </c>
-      <c r="J74" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="K74" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="L74" s="36">
-        <v>42443</v>
-      </c>
-      <c r="M74" s="37">
-        <v>42461</v>
-      </c>
-      <c r="O74" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" ht="27">
-      <c r="A75" s="13">
-        <v>99</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>342</v>
-      </c>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+      <c r="M74" s="14"/>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" s="13"/>
+      <c r="B75" s="8"/>
       <c r="C75" s="8"/>
-      <c r="D75" s="35" t="s">
-        <v>362</v>
-      </c>
-      <c r="E75" s="8">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G75" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H75" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="I75" s="8">
-        <v>20</v>
-      </c>
-      <c r="J75" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="K75" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="L75" s="36">
-        <v>42445</v>
-      </c>
-      <c r="M75" s="37">
-        <v>42471</v>
-      </c>
-      <c r="O75" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" ht="27">
-      <c r="A76" s="13">
-        <v>100</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>364</v>
-      </c>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="8"/>
+      <c r="M75" s="14"/>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" s="13"/>
+      <c r="B76" s="8"/>
       <c r="C76" s="8"/>
-      <c r="D76" s="35" t="s">
-        <v>365</v>
-      </c>
-      <c r="E76" s="8">
-        <v>2.2000000000000002</v>
-      </c>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
       <c r="F76" s="8"/>
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
-      <c r="I76" s="8">
-        <v>30</v>
-      </c>
-      <c r="J76" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="K76" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="L76" s="36">
-        <v>42507</v>
-      </c>
-      <c r="M76" s="37">
-        <v>42538</v>
-      </c>
-      <c r="O76" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" ht="40.5">
-      <c r="A77" s="13">
-        <v>101</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>368</v>
-      </c>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="8"/>
+      <c r="M76" s="14"/>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" s="13"/>
+      <c r="B77" s="8"/>
       <c r="C77" s="8"/>
-      <c r="D77" s="35" t="s">
-        <v>366</v>
-      </c>
-      <c r="E77" s="8">
-        <v>2.2000000000000002</v>
-      </c>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
       <c r="F77" s="8"/>
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
-      <c r="I77" s="8">
-        <v>20</v>
-      </c>
-      <c r="J77" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="K77" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="L77" s="36">
-        <v>42521</v>
-      </c>
-      <c r="M77" s="37">
-        <v>42546</v>
-      </c>
-      <c r="O77" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" ht="27">
-      <c r="A78" s="13">
-        <v>102</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>372</v>
-      </c>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="8"/>
+      <c r="M77" s="14"/>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" s="13"/>
+      <c r="B78" s="8"/>
       <c r="C78" s="8"/>
       <c r="D78" s="8"/>
-      <c r="E78" s="8">
-        <v>2.2000000000000002</v>
-      </c>
+      <c r="E78" s="8"/>
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
       <c r="H78" s="8"/>
-      <c r="I78" s="8">
-        <v>20</v>
-      </c>
-      <c r="J78" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="K78" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="L78" s="36">
-        <v>42551</v>
-      </c>
-      <c r="M78" s="37">
-        <v>42579</v>
-      </c>
-      <c r="N78" t="s">
-        <v>379</v>
-      </c>
-      <c r="O78" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" ht="27">
-      <c r="A79" s="13">
-        <v>103</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>374</v>
-      </c>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+      <c r="M78" s="14"/>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" s="13"/>
+      <c r="B79" s="8"/>
       <c r="C79" s="8"/>
       <c r="D79" s="8"/>
       <c r="E79" s="8"/>
@@ -8923,13 +9093,9 @@
       <c r="L79" s="8"/>
       <c r="M79" s="14"/>
     </row>
-    <row r="80" spans="1:15" ht="27">
-      <c r="A80" s="13">
-        <v>104</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>373</v>
-      </c>
+    <row r="80" spans="1:15">
+      <c r="A80" s="13"/>
+      <c r="B80" s="8"/>
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
       <c r="E80" s="8"/>
@@ -8942,13 +9108,9 @@
       <c r="L80" s="8"/>
       <c r="M80" s="14"/>
     </row>
-    <row r="81" spans="1:13" ht="40.5">
-      <c r="A81" s="13">
-        <v>105</v>
-      </c>
-      <c r="B81" s="8" t="s">
-        <v>375</v>
-      </c>
+    <row r="81" spans="1:13">
+      <c r="A81" s="13"/>
+      <c r="B81" s="8"/>
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
@@ -8961,13 +9123,9 @@
       <c r="L81" s="8"/>
       <c r="M81" s="14"/>
     </row>
-    <row r="82" spans="1:13" ht="67.5">
-      <c r="A82" s="13">
-        <v>106</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>390</v>
-      </c>
+    <row r="82" spans="1:13">
+      <c r="A82" s="13"/>
+      <c r="B82" s="8"/>
       <c r="C82" s="8"/>
       <c r="D82" s="8"/>
       <c r="E82" s="8"/>
@@ -9085,102 +9243,242 @@
       <c r="L89" s="8"/>
       <c r="M89" s="14"/>
     </row>
-    <row r="90" spans="1:13" ht="14.25" thickBot="1">
-      <c r="A90" s="15"/>
-      <c r="B90" s="16"/>
-      <c r="C90" s="16"/>
-      <c r="D90" s="16"/>
-      <c r="E90" s="16"/>
-      <c r="F90" s="16"/>
-      <c r="G90" s="16"/>
-      <c r="H90" s="16"/>
-      <c r="I90" s="16"/>
-      <c r="J90" s="16"/>
-      <c r="K90" s="16"/>
-      <c r="L90" s="16"/>
-      <c r="M90" s="17"/>
+    <row r="90" spans="1:13">
+      <c r="A90" s="13"/>
+      <c r="B90" s="8"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="8"/>
+      <c r="E90" s="8"/>
+      <c r="F90" s="8"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="8"/>
+      <c r="J90" s="8"/>
+      <c r="K90" s="8"/>
+      <c r="L90" s="8"/>
+      <c r="M90" s="14"/>
+    </row>
+    <row r="91" spans="1:13">
+      <c r="A91" s="13"/>
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="8"/>
+      <c r="I91" s="8"/>
+      <c r="J91" s="8"/>
+      <c r="K91" s="8"/>
+      <c r="L91" s="8"/>
+      <c r="M91" s="14"/>
+    </row>
+    <row r="92" spans="1:13">
+      <c r="A92" s="13"/>
+      <c r="B92" s="8"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="8"/>
+      <c r="I92" s="8"/>
+      <c r="J92" s="8"/>
+      <c r="K92" s="8"/>
+      <c r="L92" s="8"/>
+      <c r="M92" s="14"/>
+    </row>
+    <row r="93" spans="1:13">
+      <c r="A93" s="13"/>
+      <c r="B93" s="8"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="8"/>
+      <c r="J93" s="8"/>
+      <c r="K93" s="8"/>
+      <c r="L93" s="8"/>
+      <c r="M93" s="14"/>
+    </row>
+    <row r="94" spans="1:13">
+      <c r="A94" s="13"/>
+      <c r="B94" s="8"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="8"/>
+      <c r="E94" s="8"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="8"/>
+      <c r="J94" s="8"/>
+      <c r="K94" s="8"/>
+      <c r="L94" s="8"/>
+      <c r="M94" s="14"/>
+    </row>
+    <row r="95" spans="1:13">
+      <c r="A95" s="13"/>
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="8"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="8"/>
+      <c r="J95" s="8"/>
+      <c r="K95" s="8"/>
+      <c r="L95" s="8"/>
+      <c r="M95" s="14"/>
+    </row>
+    <row r="96" spans="1:13">
+      <c r="A96" s="13"/>
+      <c r="B96" s="8"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="8"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="8"/>
+      <c r="J96" s="8"/>
+      <c r="K96" s="8"/>
+      <c r="L96" s="8"/>
+      <c r="M96" s="14"/>
+    </row>
+    <row r="97" spans="1:13">
+      <c r="A97" s="13"/>
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="8"/>
+      <c r="J97" s="8"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="8"/>
+      <c r="M97" s="14"/>
+    </row>
+    <row r="98" spans="1:13">
+      <c r="A98" s="13"/>
+      <c r="B98" s="8"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="8"/>
+      <c r="E98" s="8"/>
+      <c r="F98" s="8"/>
+      <c r="G98" s="8"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="8"/>
+      <c r="J98" s="8"/>
+      <c r="K98" s="8"/>
+      <c r="L98" s="8"/>
+      <c r="M98" s="14"/>
+    </row>
+    <row r="99" spans="1:13">
+      <c r="A99" s="13"/>
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="8"/>
+      <c r="J99" s="8"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="8"/>
+      <c r="M99" s="14"/>
+    </row>
+    <row r="100" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A100" s="15"/>
+      <c r="B100" s="16"/>
+      <c r="C100" s="16"/>
+      <c r="D100" s="16"/>
+      <c r="E100" s="16"/>
+      <c r="F100" s="16"/>
+      <c r="G100" s="16"/>
+      <c r="H100" s="16"/>
+      <c r="I100" s="16"/>
+      <c r="J100" s="16"/>
+      <c r="K100" s="16"/>
+      <c r="L100" s="16"/>
+      <c r="M100" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O81">
+  <autoFilter ref="A1:O72">
     <filterColumn colId="14"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:M201">
-    <cfRule type="expression" dxfId="195" priority="21" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:M211">
+    <cfRule type="expression" dxfId="223" priority="21" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="194" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="222" priority="22" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="193" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="221" priority="23" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="192" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="220" priority="24" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:M7">
-    <cfRule type="expression" dxfId="191" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="219" priority="17" stopIfTrue="1">
       <formula>$K7="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="190" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="218" priority="18" stopIfTrue="1">
       <formula>$K7="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="189" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="217" priority="19" stopIfTrue="1">
       <formula>$K7="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="188" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="216" priority="20" stopIfTrue="1">
       <formula>OR($K7="CLOSED",$K7="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:M42">
-    <cfRule type="expression" dxfId="187" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="215" priority="1" stopIfTrue="1">
       <formula>$K42="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="186" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="214" priority="2" stopIfTrue="1">
       <formula>$K42="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="185" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="213" priority="3" stopIfTrue="1">
       <formula>$K42="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="184" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="212" priority="4" stopIfTrue="1">
       <formula>OR($K42="CLOSED",$K42="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F90">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F100">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G90">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G100">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K90">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K100">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D48" r:id="rId1"/>
-    <hyperlink ref="D45" r:id="rId2"/>
-    <hyperlink ref="D43" r:id="rId3"/>
-    <hyperlink ref="D49" r:id="rId4"/>
-    <hyperlink ref="D74" r:id="rId5"/>
-    <hyperlink ref="D51" r:id="rId6"/>
-    <hyperlink ref="D65" r:id="rId7"/>
-    <hyperlink ref="D2" r:id="rId8"/>
-    <hyperlink ref="D10" r:id="rId9"/>
-    <hyperlink ref="D75" r:id="rId10"/>
-    <hyperlink ref="D64" r:id="rId11"/>
-    <hyperlink ref="D76" r:id="rId12"/>
-    <hyperlink ref="D77" r:id="rId13"/>
+    <hyperlink ref="D47" r:id="rId1"/>
+    <hyperlink ref="D2" r:id="rId2"/>
+    <hyperlink ref="D10" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.5" customWidth="1"/>
@@ -10776,7 +11074,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="3"/>
     </row>
-    <row r="49" spans="1:13" ht="27">
+    <row r="49" spans="1:15" ht="27">
       <c r="A49" s="13">
         <v>41</v>
       </c>
@@ -10809,7 +11107,7 @@
       <c r="L49" s="8"/>
       <c r="M49" s="14"/>
     </row>
-    <row r="50" spans="1:13" ht="54">
+    <row r="50" spans="1:15" ht="54">
       <c r="A50" s="13">
         <v>52</v>
       </c>
@@ -10844,7 +11142,7 @@
       <c r="L50" s="8"/>
       <c r="M50" s="14"/>
     </row>
-    <row r="51" spans="1:13" ht="40.5">
+    <row r="51" spans="1:15" ht="40.5">
       <c r="A51" s="1">
         <v>36</v>
       </c>
@@ -10877,7 +11175,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="3"/>
     </row>
-    <row r="52" spans="1:13" ht="40.5">
+    <row r="52" spans="1:15" ht="40.5">
       <c r="A52" s="1">
         <v>46</v>
       </c>
@@ -10914,7 +11212,7 @@
         <v>41679</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="54">
+    <row r="53" spans="1:15" ht="54">
       <c r="A53" s="1">
         <v>1</v>
       </c>
@@ -10941,7 +11239,7 @@
       <c r="L53" s="2"/>
       <c r="M53" s="3"/>
     </row>
-    <row r="54" spans="1:13" ht="67.5">
+    <row r="54" spans="1:15" ht="67.5">
       <c r="A54" s="1">
         <v>12</v>
       </c>
@@ -10970,7 +11268,7 @@
       <c r="L54" s="2"/>
       <c r="M54" s="3"/>
     </row>
-    <row r="55" spans="1:13" ht="40.5">
+    <row r="55" spans="1:15" ht="40.5">
       <c r="A55" s="13">
         <v>55</v>
       </c>
@@ -11005,7 +11303,7 @@
       <c r="L55" s="8"/>
       <c r="M55" s="14"/>
     </row>
-    <row r="56" spans="1:13" ht="27">
+    <row r="56" spans="1:15" ht="27">
       <c r="A56" s="13">
         <v>50</v>
       </c>
@@ -11040,7 +11338,7 @@
       <c r="L56" s="8"/>
       <c r="M56" s="14"/>
     </row>
-    <row r="57" spans="1:13" ht="67.5">
+    <row r="57" spans="1:15" ht="67.5">
       <c r="A57" s="27">
         <v>57</v>
       </c>
@@ -11075,7 +11373,7 @@
       <c r="L57" s="30"/>
       <c r="M57" s="31"/>
     </row>
-    <row r="58" spans="1:13" ht="54">
+    <row r="58" spans="1:15" ht="54">
       <c r="A58" s="13">
         <v>45</v>
       </c>
@@ -11116,7 +11414,7 @@
         <v>42132</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="135">
+    <row r="59" spans="1:15" ht="135">
       <c r="A59" s="1">
         <v>56</v>
       </c>
@@ -11153,161 +11451,431 @@
       <c r="L59" s="2"/>
       <c r="M59" s="3"/>
     </row>
-    <row r="60" spans="1:13">
-      <c r="A60" s="1"/>
-      <c r="B60" s="8"/>
+    <row r="60" spans="1:15" ht="40.5">
+      <c r="A60" s="13">
+        <v>67</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>285</v>
+      </c>
       <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
-      <c r="L60" s="2"/>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="1:13">
-      <c r="A61" s="13"/>
-      <c r="B61" s="8"/>
+      <c r="D60" s="44" t="s">
+        <v>353</v>
+      </c>
+      <c r="E60" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="I60" s="8">
+        <v>15</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="K60" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L60" s="36">
+        <v>42446</v>
+      </c>
+      <c r="M60" s="37">
+        <v>42460</v>
+      </c>
+      <c r="O60" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="40.5">
+      <c r="A61" s="13">
+        <v>65</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>282</v>
+      </c>
       <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="8"/>
-      <c r="J61" s="8"/>
-      <c r="K61" s="8"/>
-      <c r="L61" s="8"/>
-      <c r="M61" s="14"/>
-    </row>
-    <row r="62" spans="1:13">
-      <c r="A62" s="13"/>
-      <c r="B62" s="8"/>
+      <c r="D61" s="35" t="s">
+        <v>354</v>
+      </c>
+      <c r="E61" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="I61" s="8">
+        <v>30</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="K61" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L61" s="36">
+        <v>42446</v>
+      </c>
+      <c r="M61" s="37">
+        <v>42474</v>
+      </c>
+      <c r="N61" t="s">
+        <v>350</v>
+      </c>
+      <c r="O61" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="54">
+      <c r="A62" s="13">
+        <v>71</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>288</v>
+      </c>
       <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
-      <c r="M62" s="14"/>
-    </row>
-    <row r="63" spans="1:13">
-      <c r="A63" s="13"/>
-      <c r="B63" s="8"/>
+      <c r="D62" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="E62" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="I62" s="8">
+        <v>22</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="K62" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L62" s="36">
+        <v>42443</v>
+      </c>
+      <c r="M62" s="37">
+        <v>42468</v>
+      </c>
+      <c r="O62" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="40.5">
+      <c r="A63" s="13">
+        <v>72</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>290</v>
+      </c>
       <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-      <c r="I63" s="8"/>
-      <c r="J63" s="8"/>
-      <c r="K63" s="8"/>
-      <c r="L63" s="8"/>
-      <c r="M63" s="14"/>
-    </row>
-    <row r="64" spans="1:13">
-      <c r="A64" s="13"/>
-      <c r="B64" s="8"/>
+      <c r="D63" s="35" t="s">
+        <v>355</v>
+      </c>
+      <c r="E63" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="I63" s="8">
+        <v>12</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L63" s="36">
+        <v>42451</v>
+      </c>
+      <c r="M63" s="37">
+        <v>42467</v>
+      </c>
+      <c r="N63" t="s">
+        <v>351</v>
+      </c>
+      <c r="O63" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="27">
+      <c r="A64" s="13">
+        <v>87</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>316</v>
+      </c>
       <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
-      <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="14"/>
-    </row>
-    <row r="65" spans="1:13">
-      <c r="A65" s="13"/>
-      <c r="B65" s="8"/>
+      <c r="D64" s="35" t="s">
+        <v>362</v>
+      </c>
+      <c r="E64" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="I64" s="8">
+        <v>60</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L64" s="36">
+        <v>42445</v>
+      </c>
+      <c r="M64" s="37">
+        <v>42458</v>
+      </c>
+      <c r="N64" t="s">
+        <v>339</v>
+      </c>
+      <c r="O64" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="40.5">
+      <c r="A65" s="13">
+        <v>88</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>317</v>
+      </c>
       <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="8"/>
-      <c r="K65" s="8"/>
-      <c r="L65" s="8"/>
-      <c r="M65" s="14"/>
-    </row>
-    <row r="66" spans="1:13">
-      <c r="A66" s="13"/>
-      <c r="B66" s="8"/>
+      <c r="D65" s="35" t="s">
+        <v>358</v>
+      </c>
+      <c r="E65" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="I65" s="8">
+        <v>45</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L65" s="36">
+        <v>42447</v>
+      </c>
+      <c r="M65" s="37">
+        <v>42465</v>
+      </c>
+      <c r="N65" t="s">
+        <v>347</v>
+      </c>
+      <c r="O65" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="27">
+      <c r="A66" s="13">
+        <v>98</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>337</v>
+      </c>
       <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
-      <c r="I66" s="8"/>
-      <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="8"/>
-      <c r="M66" s="14"/>
-    </row>
-    <row r="67" spans="1:13">
-      <c r="A67" s="13"/>
-      <c r="B67" s="8"/>
+      <c r="D66" s="35" t="s">
+        <v>356</v>
+      </c>
+      <c r="E66" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="I66" s="8">
+        <v>18</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="K66" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L66" s="36">
+        <v>42443</v>
+      </c>
+      <c r="M66" s="37">
+        <v>42461</v>
+      </c>
+      <c r="O66" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" ht="27">
+      <c r="A67" s="13">
+        <v>99</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>341</v>
+      </c>
       <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="8"/>
-      <c r="J67" s="8"/>
-      <c r="K67" s="8"/>
-      <c r="L67" s="8"/>
-      <c r="M67" s="14"/>
-    </row>
-    <row r="68" spans="1:13">
-      <c r="A68" s="13"/>
-      <c r="B68" s="8"/>
+      <c r="D67" s="35" t="s">
+        <v>361</v>
+      </c>
+      <c r="E67" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="I67" s="8">
+        <v>20</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="K67" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L67" s="36">
+        <v>42445</v>
+      </c>
+      <c r="M67" s="37">
+        <v>42471</v>
+      </c>
+      <c r="O67" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" ht="27">
+      <c r="A68" s="13">
+        <v>100</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>363</v>
+      </c>
       <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
+      <c r="D68" s="35" t="s">
+        <v>364</v>
+      </c>
+      <c r="E68" s="8">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="14"/>
-    </row>
-    <row r="69" spans="1:13">
-      <c r="A69" s="13"/>
-      <c r="B69" s="8"/>
+      <c r="I68" s="8">
+        <v>30</v>
+      </c>
+      <c r="J68" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="K68" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L68" s="36">
+        <v>42507</v>
+      </c>
+      <c r="M68" s="37">
+        <v>42538</v>
+      </c>
+      <c r="O68" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="40.5">
+      <c r="A69" s="13">
+        <v>101</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>367</v>
+      </c>
       <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
+      <c r="D69" s="35" t="s">
+        <v>365</v>
+      </c>
+      <c r="E69" s="8">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="F69" s="8"/>
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
-      <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="8"/>
-      <c r="M69" s="14"/>
-    </row>
-    <row r="70" spans="1:13">
+      <c r="I69" s="8">
+        <v>20</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="K69" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L69" s="36">
+        <v>42521</v>
+      </c>
+      <c r="M69" s="37">
+        <v>42546</v>
+      </c>
+      <c r="O69" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
       <c r="A70" s="13"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
+      <c r="D70" s="35"/>
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
       <c r="G70" s="8"/>
@@ -11315,14 +11883,14 @@
       <c r="I70" s="8"/>
       <c r="J70" s="8"/>
       <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="14"/>
-    </row>
-    <row r="71" spans="1:13">
+      <c r="L70" s="36"/>
+      <c r="M70" s="37"/>
+    </row>
+    <row r="71" spans="1:15">
       <c r="A71" s="13"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
+      <c r="D71" s="35"/>
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
@@ -11330,14 +11898,14 @@
       <c r="I71" s="8"/>
       <c r="J71" s="8"/>
       <c r="K71" s="8"/>
-      <c r="L71" s="8"/>
-      <c r="M71" s="14"/>
-    </row>
-    <row r="72" spans="1:13">
+      <c r="L71" s="36"/>
+      <c r="M71" s="37"/>
+    </row>
+    <row r="72" spans="1:15">
       <c r="A72" s="13"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
+      <c r="D72" s="35"/>
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
@@ -11345,14 +11913,14 @@
       <c r="I72" s="8"/>
       <c r="J72" s="8"/>
       <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="14"/>
-    </row>
-    <row r="73" spans="1:13">
+      <c r="L72" s="36"/>
+      <c r="M72" s="37"/>
+    </row>
+    <row r="73" spans="1:15">
       <c r="A73" s="13"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
+      <c r="D73" s="35"/>
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
       <c r="G73" s="8"/>
@@ -11360,23 +11928,278 @@
       <c r="I73" s="8"/>
       <c r="J73" s="8"/>
       <c r="K73" s="8"/>
-      <c r="L73" s="8"/>
-      <c r="M73" s="14"/>
-    </row>
-    <row r="74" spans="1:13" ht="14.25" thickBot="1">
-      <c r="A74" s="15"/>
-      <c r="B74" s="16"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="16"/>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="16"/>
-      <c r="H74" s="16"/>
-      <c r="I74" s="16"/>
-      <c r="J74" s="16"/>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="17"/>
+      <c r="L73" s="36"/>
+      <c r="M73" s="37"/>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" s="13"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="35"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="36"/>
+      <c r="M74" s="37"/>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" s="13"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="35"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="36"/>
+      <c r="M75" s="37"/>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" s="13"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="35"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="36"/>
+      <c r="M76" s="37"/>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" s="13"/>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="35"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="36"/>
+      <c r="M77" s="37"/>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" s="13"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="35"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="36"/>
+      <c r="M78" s="37"/>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" s="13"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="35"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="36"/>
+      <c r="M79" s="37"/>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" s="13"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="35"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="8"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="8"/>
+      <c r="I80" s="8"/>
+      <c r="J80" s="8"/>
+      <c r="K80" s="8"/>
+      <c r="L80" s="36"/>
+      <c r="M80" s="37"/>
+    </row>
+    <row r="81" spans="1:13">
+      <c r="A81" s="13"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="35"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="8"/>
+      <c r="J81" s="8"/>
+      <c r="K81" s="8"/>
+      <c r="L81" s="36"/>
+      <c r="M81" s="37"/>
+    </row>
+    <row r="82" spans="1:13">
+      <c r="A82" s="13"/>
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="35"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8"/>
+      <c r="I82" s="8"/>
+      <c r="J82" s="8"/>
+      <c r="K82" s="8"/>
+      <c r="L82" s="36"/>
+      <c r="M82" s="37"/>
+    </row>
+    <row r="83" spans="1:13">
+      <c r="A83" s="13"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="35"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="8"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="36"/>
+      <c r="M83" s="37"/>
+    </row>
+    <row r="84" spans="1:13">
+      <c r="A84" s="13"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="35"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="8"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="36"/>
+      <c r="M84" s="37"/>
+    </row>
+    <row r="85" spans="1:13">
+      <c r="A85" s="13"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="35"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="8"/>
+      <c r="K85" s="8"/>
+      <c r="L85" s="36"/>
+      <c r="M85" s="37"/>
+    </row>
+    <row r="86" spans="1:13">
+      <c r="A86" s="13"/>
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="35"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="8"/>
+      <c r="J86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="36"/>
+      <c r="M86" s="37"/>
+    </row>
+    <row r="87" spans="1:13">
+      <c r="A87" s="13"/>
+      <c r="B87" s="8"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="8"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="8"/>
+      <c r="M87" s="14"/>
+    </row>
+    <row r="88" spans="1:13">
+      <c r="A88" s="13"/>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="8"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="8"/>
+      <c r="J88" s="8"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="8"/>
+      <c r="M88" s="14"/>
+    </row>
+    <row r="89" spans="1:13">
+      <c r="A89" s="13"/>
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="8"/>
+      <c r="F89" s="8"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="8"/>
+      <c r="J89" s="8"/>
+      <c r="K89" s="8"/>
+      <c r="L89" s="8"/>
+      <c r="M89" s="14"/>
+    </row>
+    <row r="90" spans="1:13">
+      <c r="A90" s="13"/>
+      <c r="B90" s="8"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="8"/>
+      <c r="E90" s="8"/>
+      <c r="F90" s="8"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="8"/>
+      <c r="J90" s="8"/>
+      <c r="K90" s="8"/>
+      <c r="L90" s="8"/>
+      <c r="M90" s="14"/>
+    </row>
+    <row r="91" spans="1:13" ht="14.25" thickBot="1">
+      <c r="A91" s="15"/>
+      <c r="B91" s="16"/>
+      <c r="C91" s="16"/>
+      <c r="D91" s="16"/>
+      <c r="E91" s="16"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="16"/>
+      <c r="H91" s="16"/>
+      <c r="I91" s="16"/>
+      <c r="J91" s="16"/>
+      <c r="K91" s="16"/>
+      <c r="L91" s="16"/>
+      <c r="M91" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M64">
@@ -11386,657 +12209,755 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:M9 A32:M37">
-    <cfRule type="expression" dxfId="183" priority="205" stopIfTrue="1">
+    <cfRule type="expression" dxfId="211" priority="233" stopIfTrue="1">
       <formula>$K9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="182" priority="206" stopIfTrue="1">
+    <cfRule type="expression" dxfId="210" priority="234" stopIfTrue="1">
       <formula>$K9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="181" priority="207" stopIfTrue="1">
+    <cfRule type="expression" dxfId="209" priority="235" stopIfTrue="1">
       <formula>$K9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="180" priority="208" stopIfTrue="1">
+    <cfRule type="expression" dxfId="208" priority="236" stopIfTrue="1">
       <formula>OR($K9="CLOSED",$K9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:M10">
-    <cfRule type="expression" dxfId="179" priority="201" stopIfTrue="1">
+    <cfRule type="expression" dxfId="207" priority="229" stopIfTrue="1">
       <formula>$K10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="178" priority="202" stopIfTrue="1">
+    <cfRule type="expression" dxfId="206" priority="230" stopIfTrue="1">
       <formula>$K10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="177" priority="203" stopIfTrue="1">
+    <cfRule type="expression" dxfId="205" priority="231" stopIfTrue="1">
       <formula>$K10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="176" priority="204" stopIfTrue="1">
+    <cfRule type="expression" dxfId="204" priority="232" stopIfTrue="1">
       <formula>OR($K10="CLOSED",$K10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:M11">
-    <cfRule type="expression" dxfId="175" priority="197" stopIfTrue="1">
+    <cfRule type="expression" dxfId="203" priority="225" stopIfTrue="1">
       <formula>$K11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="174" priority="198" stopIfTrue="1">
+    <cfRule type="expression" dxfId="202" priority="226" stopIfTrue="1">
       <formula>$K11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="199" stopIfTrue="1">
+    <cfRule type="expression" dxfId="201" priority="227" stopIfTrue="1">
       <formula>$K11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="172" priority="200" stopIfTrue="1">
+    <cfRule type="expression" dxfId="200" priority="228" stopIfTrue="1">
       <formula>OR($K11="CLOSED",$K11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:M12">
-    <cfRule type="expression" dxfId="171" priority="193" stopIfTrue="1">
+    <cfRule type="expression" dxfId="199" priority="221" stopIfTrue="1">
       <formula>$K12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="170" priority="194" stopIfTrue="1">
+    <cfRule type="expression" dxfId="198" priority="222" stopIfTrue="1">
       <formula>$K12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="169" priority="195" stopIfTrue="1">
+    <cfRule type="expression" dxfId="197" priority="223" stopIfTrue="1">
       <formula>$K12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="168" priority="196" stopIfTrue="1">
+    <cfRule type="expression" dxfId="196" priority="224" stopIfTrue="1">
       <formula>OR($K12="CLOSED",$K12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:M13">
-    <cfRule type="expression" dxfId="167" priority="189" stopIfTrue="1">
+    <cfRule type="expression" dxfId="195" priority="217" stopIfTrue="1">
       <formula>$K13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="166" priority="190" stopIfTrue="1">
+    <cfRule type="expression" dxfId="194" priority="218" stopIfTrue="1">
       <formula>$K13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="165" priority="191" stopIfTrue="1">
+    <cfRule type="expression" dxfId="193" priority="219" stopIfTrue="1">
       <formula>$K13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="164" priority="192" stopIfTrue="1">
+    <cfRule type="expression" dxfId="192" priority="220" stopIfTrue="1">
       <formula>OR($K13="CLOSED",$K13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:M14">
-    <cfRule type="expression" dxfId="163" priority="185" stopIfTrue="1">
+    <cfRule type="expression" dxfId="191" priority="213" stopIfTrue="1">
       <formula>$K14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="162" priority="186" stopIfTrue="1">
+    <cfRule type="expression" dxfId="190" priority="214" stopIfTrue="1">
       <formula>$K14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="161" priority="187" stopIfTrue="1">
+    <cfRule type="expression" dxfId="189" priority="215" stopIfTrue="1">
       <formula>$K14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="160" priority="188" stopIfTrue="1">
+    <cfRule type="expression" dxfId="188" priority="216" stopIfTrue="1">
       <formula>OR($K14="CLOSED",$K14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:M15">
-    <cfRule type="expression" dxfId="159" priority="181" stopIfTrue="1">
+    <cfRule type="expression" dxfId="187" priority="209" stopIfTrue="1">
       <formula>$K15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="158" priority="182" stopIfTrue="1">
+    <cfRule type="expression" dxfId="186" priority="210" stopIfTrue="1">
       <formula>$K15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="157" priority="183" stopIfTrue="1">
+    <cfRule type="expression" dxfId="185" priority="211" stopIfTrue="1">
       <formula>$K15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="156" priority="184" stopIfTrue="1">
+    <cfRule type="expression" dxfId="184" priority="212" stopIfTrue="1">
       <formula>OR($K15="CLOSED",$K15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:M16">
-    <cfRule type="expression" dxfId="155" priority="177" stopIfTrue="1">
+    <cfRule type="expression" dxfId="183" priority="205" stopIfTrue="1">
       <formula>$K16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="154" priority="178" stopIfTrue="1">
+    <cfRule type="expression" dxfId="182" priority="206" stopIfTrue="1">
       <formula>$K16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="153" priority="179" stopIfTrue="1">
+    <cfRule type="expression" dxfId="181" priority="207" stopIfTrue="1">
       <formula>$K16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="152" priority="180" stopIfTrue="1">
+    <cfRule type="expression" dxfId="180" priority="208" stopIfTrue="1">
       <formula>OR($K16="CLOSED",$K16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:M17">
-    <cfRule type="expression" dxfId="151" priority="173" stopIfTrue="1">
+    <cfRule type="expression" dxfId="179" priority="201" stopIfTrue="1">
       <formula>$K17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="150" priority="174" stopIfTrue="1">
+    <cfRule type="expression" dxfId="178" priority="202" stopIfTrue="1">
       <formula>$K17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="149" priority="175" stopIfTrue="1">
+    <cfRule type="expression" dxfId="177" priority="203" stopIfTrue="1">
       <formula>$K17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="148" priority="176" stopIfTrue="1">
+    <cfRule type="expression" dxfId="176" priority="204" stopIfTrue="1">
       <formula>OR($K17="CLOSED",$K17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:M18">
-    <cfRule type="expression" dxfId="147" priority="169" stopIfTrue="1">
+    <cfRule type="expression" dxfId="175" priority="197" stopIfTrue="1">
       <formula>$K18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="146" priority="170" stopIfTrue="1">
+    <cfRule type="expression" dxfId="174" priority="198" stopIfTrue="1">
       <formula>$K18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="145" priority="171" stopIfTrue="1">
+    <cfRule type="expression" dxfId="173" priority="199" stopIfTrue="1">
       <formula>$K18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="144" priority="172" stopIfTrue="1">
+    <cfRule type="expression" dxfId="172" priority="200" stopIfTrue="1">
       <formula>OR($K18="CLOSED",$K18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:M19">
-    <cfRule type="expression" dxfId="143" priority="165" stopIfTrue="1">
+    <cfRule type="expression" dxfId="171" priority="193" stopIfTrue="1">
       <formula>$K19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="142" priority="166" stopIfTrue="1">
+    <cfRule type="expression" dxfId="170" priority="194" stopIfTrue="1">
       <formula>$K19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="141" priority="167" stopIfTrue="1">
+    <cfRule type="expression" dxfId="169" priority="195" stopIfTrue="1">
       <formula>$K19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="140" priority="168" stopIfTrue="1">
+    <cfRule type="expression" dxfId="168" priority="196" stopIfTrue="1">
       <formula>OR($K19="CLOSED",$K19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:M20">
-    <cfRule type="expression" dxfId="139" priority="161" stopIfTrue="1">
+    <cfRule type="expression" dxfId="167" priority="189" stopIfTrue="1">
       <formula>$K20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="162" stopIfTrue="1">
+    <cfRule type="expression" dxfId="166" priority="190" stopIfTrue="1">
       <formula>$K20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="137" priority="163" stopIfTrue="1">
+    <cfRule type="expression" dxfId="165" priority="191" stopIfTrue="1">
       <formula>$K20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="164" stopIfTrue="1">
+    <cfRule type="expression" dxfId="164" priority="192" stopIfTrue="1">
       <formula>OR($K20="CLOSED",$K20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:M21">
-    <cfRule type="expression" dxfId="135" priority="157" stopIfTrue="1">
+    <cfRule type="expression" dxfId="163" priority="185" stopIfTrue="1">
       <formula>$K21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="158" stopIfTrue="1">
+    <cfRule type="expression" dxfId="162" priority="186" stopIfTrue="1">
       <formula>$K21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="133" priority="159" stopIfTrue="1">
+    <cfRule type="expression" dxfId="161" priority="187" stopIfTrue="1">
       <formula>$K21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="160" stopIfTrue="1">
+    <cfRule type="expression" dxfId="160" priority="188" stopIfTrue="1">
       <formula>OR($K21="CLOSED",$K21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:M23">
-    <cfRule type="expression" dxfId="131" priority="153" stopIfTrue="1">
+    <cfRule type="expression" dxfId="159" priority="181" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="154" stopIfTrue="1">
+    <cfRule type="expression" dxfId="158" priority="182" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="155" stopIfTrue="1">
+    <cfRule type="expression" dxfId="157" priority="183" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="128" priority="156" stopIfTrue="1">
+    <cfRule type="expression" dxfId="156" priority="184" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:I22">
-    <cfRule type="expression" dxfId="127" priority="149" stopIfTrue="1">
+    <cfRule type="expression" dxfId="155" priority="177" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="150" stopIfTrue="1">
+    <cfRule type="expression" dxfId="154" priority="178" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="151" stopIfTrue="1">
+    <cfRule type="expression" dxfId="153" priority="179" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="152" stopIfTrue="1">
+    <cfRule type="expression" dxfId="152" priority="180" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="123" priority="145" stopIfTrue="1">
+    <cfRule type="expression" dxfId="151" priority="173" stopIfTrue="1">
       <formula>$K23="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="146" stopIfTrue="1">
+    <cfRule type="expression" dxfId="150" priority="174" stopIfTrue="1">
       <formula>$K23="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="147" stopIfTrue="1">
+    <cfRule type="expression" dxfId="149" priority="175" stopIfTrue="1">
       <formula>$K23="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="148" stopIfTrue="1">
+    <cfRule type="expression" dxfId="148" priority="176" stopIfTrue="1">
       <formula>OR($K23="CLOSED",$K23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:M25">
-    <cfRule type="expression" dxfId="119" priority="141" stopIfTrue="1">
+    <cfRule type="expression" dxfId="147" priority="169" stopIfTrue="1">
       <formula>$K24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="142" stopIfTrue="1">
+    <cfRule type="expression" dxfId="146" priority="170" stopIfTrue="1">
       <formula>$K24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="143" stopIfTrue="1">
+    <cfRule type="expression" dxfId="145" priority="171" stopIfTrue="1">
       <formula>$K24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="144" stopIfTrue="1">
+    <cfRule type="expression" dxfId="144" priority="172" stopIfTrue="1">
       <formula>OR($K24="CLOSED",$K24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="115" priority="137" stopIfTrue="1">
+    <cfRule type="expression" dxfId="143" priority="165" stopIfTrue="1">
       <formula>$K25="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="138" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="166" stopIfTrue="1">
       <formula>$K25="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="139" stopIfTrue="1">
+    <cfRule type="expression" dxfId="141" priority="167" stopIfTrue="1">
       <formula>$K25="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="140" stopIfTrue="1">
+    <cfRule type="expression" dxfId="140" priority="168" stopIfTrue="1">
       <formula>OR($K25="CLOSED",$K25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:M26">
-    <cfRule type="expression" dxfId="111" priority="133" stopIfTrue="1">
+    <cfRule type="expression" dxfId="139" priority="161" stopIfTrue="1">
       <formula>$K26="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="134" stopIfTrue="1">
+    <cfRule type="expression" dxfId="138" priority="162" stopIfTrue="1">
       <formula>$K26="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="135" stopIfTrue="1">
+    <cfRule type="expression" dxfId="137" priority="163" stopIfTrue="1">
       <formula>$K26="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="136" stopIfTrue="1">
+    <cfRule type="expression" dxfId="136" priority="164" stopIfTrue="1">
       <formula>OR($K26="CLOSED",$K26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:M28">
-    <cfRule type="expression" dxfId="107" priority="129" stopIfTrue="1">
+    <cfRule type="expression" dxfId="135" priority="157" stopIfTrue="1">
       <formula>$K27="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="130" stopIfTrue="1">
+    <cfRule type="expression" dxfId="134" priority="158" stopIfTrue="1">
       <formula>$K27="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="131" stopIfTrue="1">
+    <cfRule type="expression" dxfId="133" priority="159" stopIfTrue="1">
       <formula>$K27="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="132" stopIfTrue="1">
+    <cfRule type="expression" dxfId="132" priority="160" stopIfTrue="1">
       <formula>OR($K27="CLOSED",$K27="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M30">
-    <cfRule type="expression" dxfId="103" priority="125" stopIfTrue="1">
+    <cfRule type="expression" dxfId="131" priority="153" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="126" stopIfTrue="1">
+    <cfRule type="expression" dxfId="130" priority="154" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="127" stopIfTrue="1">
+    <cfRule type="expression" dxfId="129" priority="155" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="128" stopIfTrue="1">
+    <cfRule type="expression" dxfId="128" priority="156" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M29">
-    <cfRule type="expression" dxfId="99" priority="121" stopIfTrue="1">
+    <cfRule type="expression" dxfId="127" priority="149" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="122" stopIfTrue="1">
+    <cfRule type="expression" dxfId="126" priority="150" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="123" stopIfTrue="1">
+    <cfRule type="expression" dxfId="125" priority="151" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="124" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="152" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:M31">
-    <cfRule type="expression" dxfId="95" priority="117" stopIfTrue="1">
+    <cfRule type="expression" dxfId="123" priority="145" stopIfTrue="1">
       <formula>$K31="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="118" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="146" stopIfTrue="1">
       <formula>$K31="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="119" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="147" stopIfTrue="1">
       <formula>$K31="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="120" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="148" stopIfTrue="1">
       <formula>OR($K31="CLOSED",$K31="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:M38">
-    <cfRule type="expression" dxfId="91" priority="89" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="117" stopIfTrue="1">
       <formula>$K38="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="118" stopIfTrue="1">
       <formula>$K38="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="91" stopIfTrue="1">
+    <cfRule type="expression" dxfId="117" priority="119" stopIfTrue="1">
       <formula>$K38="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="92" stopIfTrue="1">
+    <cfRule type="expression" dxfId="116" priority="120" stopIfTrue="1">
       <formula>OR($K38="CLOSED",$K38="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:M39">
-    <cfRule type="expression" dxfId="87" priority="85" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="113" stopIfTrue="1">
       <formula>$K39="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="86" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="114" stopIfTrue="1">
       <formula>$K39="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="87" stopIfTrue="1">
+    <cfRule type="expression" dxfId="113" priority="115" stopIfTrue="1">
       <formula>$K39="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="88" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="116" stopIfTrue="1">
       <formula>OR($K39="CLOSED",$K39="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:M40">
-    <cfRule type="expression" dxfId="83" priority="81" stopIfTrue="1">
+    <cfRule type="expression" dxfId="111" priority="109" stopIfTrue="1">
       <formula>$K40="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="82" stopIfTrue="1">
+    <cfRule type="expression" dxfId="110" priority="110" stopIfTrue="1">
       <formula>$K40="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="83" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="111" stopIfTrue="1">
       <formula>$K40="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="84" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="112" stopIfTrue="1">
       <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:M41">
-    <cfRule type="expression" dxfId="79" priority="77" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="105" stopIfTrue="1">
       <formula>$K41="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="78" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="106" stopIfTrue="1">
       <formula>$K41="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="79" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="107" stopIfTrue="1">
       <formula>$K41="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="80" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="108" stopIfTrue="1">
       <formula>OR($K41="CLOSED",$K41="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:M42">
-    <cfRule type="expression" dxfId="75" priority="73" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="101" stopIfTrue="1">
       <formula>$K42="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="102" stopIfTrue="1">
       <formula>$K42="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="75" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="103" stopIfTrue="1">
       <formula>$K42="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="104" stopIfTrue="1">
       <formula>OR($K42="CLOSED",$K42="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:M44">
-    <cfRule type="expression" dxfId="71" priority="69" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="97" stopIfTrue="1">
       <formula>$K43="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="98" stopIfTrue="1">
       <formula>$K43="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="71" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="99" stopIfTrue="1">
       <formula>$K43="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="100" stopIfTrue="1">
       <formula>OR($K43="CLOSED",$K43="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45:M46">
-    <cfRule type="expression" dxfId="67" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="93" stopIfTrue="1">
       <formula>$K45="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="94" stopIfTrue="1">
       <formula>$K45="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="95" stopIfTrue="1">
       <formula>$K45="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="96" stopIfTrue="1">
       <formula>OR($K45="CLOSED",$K45="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:M47">
-    <cfRule type="expression" dxfId="63" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="89" stopIfTrue="1">
       <formula>$K47="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="90" stopIfTrue="1">
       <formula>$K47="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="91" stopIfTrue="1">
       <formula>$K47="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="92" stopIfTrue="1">
       <formula>OR($K47="CLOSED",$K47="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:M48">
-    <cfRule type="expression" dxfId="59" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="85" stopIfTrue="1">
       <formula>$K48="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="86" stopIfTrue="1">
       <formula>$K48="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="87" stopIfTrue="1">
       <formula>$K48="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="88" stopIfTrue="1">
       <formula>OR($K48="CLOSED",$K48="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:M49">
-    <cfRule type="expression" dxfId="55" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="81" stopIfTrue="1">
       <formula>$K49="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="82" stopIfTrue="1">
       <formula>$K49="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="83" stopIfTrue="1">
       <formula>$K49="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="84" stopIfTrue="1">
       <formula>OR($K49="CLOSED",$K49="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:M50">
-    <cfRule type="expression" dxfId="51" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="77" stopIfTrue="1">
       <formula>$K50="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="78" stopIfTrue="1">
       <formula>$K50="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="79" stopIfTrue="1">
       <formula>$K50="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="80" stopIfTrue="1">
       <formula>OR($K50="CLOSED",$K50="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:M51">
-    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="73" stopIfTrue="1">
       <formula>$K51="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="74" stopIfTrue="1">
       <formula>$K51="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="75" stopIfTrue="1">
       <formula>$K51="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="76" stopIfTrue="1">
       <formula>OR($K51="CLOSED",$K51="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:M52">
-    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="69" stopIfTrue="1">
       <formula>$K52="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="70" stopIfTrue="1">
       <formula>$K52="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="71" stopIfTrue="1">
       <formula>$K52="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="72" stopIfTrue="1">
       <formula>OR($K52="CLOSED",$K52="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:M53">
-    <cfRule type="expression" dxfId="39" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="65" stopIfTrue="1">
       <formula>$K53="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="66" stopIfTrue="1">
       <formula>$K53="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="67" stopIfTrue="1">
       <formula>$K53="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="68" stopIfTrue="1">
       <formula>OR($K53="CLOSED",$K53="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:M54">
-    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="61" stopIfTrue="1">
       <formula>$K54="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="62" stopIfTrue="1">
       <formula>$K54="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="63" stopIfTrue="1">
       <formula>$K54="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="64" stopIfTrue="1">
       <formula>OR($K54="CLOSED",$K54="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:M55">
-    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="57" stopIfTrue="1">
       <formula>$K55="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="58" stopIfTrue="1">
       <formula>$K55="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="59" stopIfTrue="1">
       <formula>$K55="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="60" stopIfTrue="1">
       <formula>OR($K55="CLOSED",$K55="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56:M56">
-    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="53" stopIfTrue="1">
       <formula>$K56="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="54" stopIfTrue="1">
       <formula>$K56="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="55" stopIfTrue="1">
       <formula>$K56="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="56" stopIfTrue="1">
       <formula>OR($K56="CLOSED",$K56="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:M57">
-    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="49" stopIfTrue="1">
       <formula>$K57="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="50" stopIfTrue="1">
       <formula>$K57="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="51" stopIfTrue="1">
       <formula>$K57="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="52" stopIfTrue="1">
       <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:M57">
-    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
       <formula>$K57="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
       <formula>$K57="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
       <formula>$K57="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
       <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E57">
-    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
       <formula>$K57="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
       <formula>$K57="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="43" stopIfTrue="1">
       <formula>$K57="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="44" stopIfTrue="1">
       <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:M58">
-    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="37" stopIfTrue="1">
       <formula>$K58="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="38" stopIfTrue="1">
       <formula>$K58="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="39" stopIfTrue="1">
       <formula>$K58="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="40" stopIfTrue="1">
       <formula>OR($K58="CLOSED",$K58="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:M59">
-    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
       <formula>$K59="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
       <formula>$K59="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
       <formula>$K59="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
       <formula>OR($K59="CLOSED",$K59="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:M59">
+    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
+      <formula>$K59="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
+      <formula>$K59="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="31" stopIfTrue="1">
+      <formula>$K59="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
+      <formula>OR($K59="CLOSED",$K59="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A60:M60">
+    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
+      <formula>$K60="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
+      <formula>$K60="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="27" stopIfTrue="1">
+      <formula>$K60="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="28" stopIfTrue="1">
+      <formula>OR($K60="CLOSED",$K60="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A61:M61">
+    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
+      <formula>$K61="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
+      <formula>$K61="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
+      <formula>$K61="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
+      <formula>OR($K61="CLOSED",$K61="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62:M62">
+    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
+      <formula>$K62="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
+      <formula>$K62="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
+      <formula>$K62="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
+      <formula>OR($K62="CLOSED",$K62="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A63:M63">
+    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
+      <formula>$K63="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="14" stopIfTrue="1">
+      <formula>$K63="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="15" stopIfTrue="1">
+      <formula>$K63="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
+      <formula>OR($K63="CLOSED",$K63="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A64:M64">
+    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
+      <formula>$K64="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
+      <formula>$K64="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
+      <formula>$K64="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
+      <formula>OR($K64="CLOSED",$K64="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A65:M65">
+    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
+      <formula>$K65="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+      <formula>$K65="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+      <formula>$K65="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+      <formula>OR($K65="CLOSED",$K65="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A66:M86">
     <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
-      <formula>$K59="HANG-UP"</formula>
+      <formula>$K66="HANG-UP"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
-      <formula>$K59="PLAN"</formula>
+      <formula>$K66="PLAN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
-      <formula>$K59="OPEN"</formula>
+      <formula>$K66="OPEN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
-      <formula>OR($K59="CLOSED",$K59="CANCEL")</formula>
+      <formula>OR($K66="CLOSED",$K66="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K74">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K91">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G74">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G91">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F74">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F91">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12045,8 +12966,18 @@
     <hyperlink ref="D56" r:id="rId2"/>
     <hyperlink ref="D58" r:id="rId3"/>
     <hyperlink ref="D59" r:id="rId4"/>
+    <hyperlink ref="D60" r:id="rId5"/>
+    <hyperlink ref="D61" r:id="rId6"/>
+    <hyperlink ref="D62" r:id="rId7"/>
+    <hyperlink ref="D63" r:id="rId8"/>
+    <hyperlink ref="D64" r:id="rId9"/>
+    <hyperlink ref="D65" r:id="rId10"/>
+    <hyperlink ref="D66" r:id="rId11"/>
+    <hyperlink ref="D67" r:id="rId12"/>
+    <hyperlink ref="D68" r:id="rId13"/>
+    <hyperlink ref="D69" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId15"/>
 </worksheet>
 </file>
--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="397">
   <si>
     <r>
       <t>描述</t>
@@ -1927,6 +1927,16 @@
   </si>
   <si>
     <t xml:space="preserve">在线重组数据页（后台任务在闲时，该集合无查询，页空洞达到预设条件时自动重组页）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">备份支持压缩
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">创建Collection可以指定overflowratio的属性
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2326,203 +2336,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="260">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="232">
     <dxf>
       <fill>
         <patternFill>
@@ -5591,16 +5405,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M169">
-    <cfRule type="expression" dxfId="259" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="231" priority="1" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="258" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="230" priority="2" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="257" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="229" priority="3" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="256" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="228" priority="4" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6775,16 +6589,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L185">
-    <cfRule type="expression" dxfId="255" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="227" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="254" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="226" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="253" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="225" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="252" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="224" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9018,9 +8832,13 @@
       <c r="L74" s="8"/>
       <c r="M74" s="14"/>
     </row>
-    <row r="75" spans="1:15">
-      <c r="A75" s="13"/>
-      <c r="B75" s="8"/>
+    <row r="75" spans="1:15" ht="27">
+      <c r="A75" s="13">
+        <v>109</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>395</v>
+      </c>
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
@@ -9033,9 +8851,13 @@
       <c r="L75" s="8"/>
       <c r="M75" s="14"/>
     </row>
-    <row r="76" spans="1:15">
-      <c r="A76" s="13"/>
-      <c r="B76" s="8"/>
+    <row r="76" spans="1:15" ht="40.5">
+      <c r="A76" s="13">
+        <v>110</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>396</v>
+      </c>
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
       <c r="E76" s="8"/>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="398">
   <si>
     <r>
       <t>描述</t>
@@ -1937,6 +1937,11 @@
   </si>
   <si>
     <t xml:space="preserve">创建Collection可以指定overflowratio的属性
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">导入工具支持从HDFS中读取CSV文件
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8870,9 +8875,13 @@
       <c r="L76" s="8"/>
       <c r="M76" s="14"/>
     </row>
-    <row r="77" spans="1:15">
-      <c r="A77" s="13"/>
-      <c r="B77" s="8"/>
+    <row r="77" spans="1:15" ht="27">
+      <c r="A77" s="13">
+        <v>111</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>397</v>
+      </c>
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="9300" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="9240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="2014年1季度" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="400">
   <si>
     <r>
       <t>描述</t>
@@ -1945,12 +1945,18 @@
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-2034</t>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-2035</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2009,6 +2015,14 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2200,7 +2214,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2335,6 +2349,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7563,7 +7580,9 @@
         <v>217</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
+      <c r="D32" s="45" t="s">
+        <v>399</v>
+      </c>
       <c r="E32" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -8169,7 +8188,9 @@
         <v>299</v>
       </c>
       <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
+      <c r="D51" s="45" t="s">
+        <v>398</v>
+      </c>
       <c r="E51" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -9244,7 +9265,7 @@
     <filterColumn colId="14"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:M211">
+  <conditionalFormatting sqref="A2:C211 E2:M211 D52:D211 D2:D31 D33:D50">
     <cfRule type="expression" dxfId="223" priority="21" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
@@ -9301,9 +9322,11 @@
     <hyperlink ref="D47" r:id="rId1"/>
     <hyperlink ref="D2" r:id="rId2"/>
     <hyperlink ref="D10" r:id="rId3"/>
+    <hyperlink ref="D51" r:id="rId4" display="http://jira:8080/browse/SEQUOIADBMAINSTREAM-2034"/>
+    <hyperlink ref="D32" r:id="rId5" display="http://jira:8080/browse/SEQUOIADBMAINSTREAM-2035"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
 

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="401">
   <si>
     <r>
       <t>描述</t>
@@ -1950,6 +1950,10 @@
   </si>
   <si>
     <t>SEQUOIADBMAINSTREAM-2035</t>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-1957</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -8379,7 +8383,9 @@
         <v>370</v>
       </c>
       <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
+      <c r="D57" s="35" t="s">
+        <v>400</v>
+      </c>
       <c r="E57" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -8399,7 +8405,7 @@
         <v>387</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>349</v>
+        <v>58</v>
       </c>
       <c r="L57" s="36">
         <v>42552</v>
@@ -9324,9 +9330,10 @@
     <hyperlink ref="D10" r:id="rId3"/>
     <hyperlink ref="D51" r:id="rId4" display="http://jira:8080/browse/SEQUOIADBMAINSTREAM-2034"/>
     <hyperlink ref="D32" r:id="rId5" display="http://jira:8080/browse/SEQUOIADBMAINSTREAM-2035"/>
+    <hyperlink ref="D57" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="402">
   <si>
     <r>
       <t>描述</t>
@@ -1946,13 +1946,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>SEQUOIADBMAINSTREAM-1957</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>SEQUOIADBMAINSTREAM-2034</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>SEQUOIADBMAINSTREAM-2035</t>
-  </si>
-  <si>
-    <t>SEQUOIADBMAINSTREAM-1957</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何国民</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1960,7 +1966,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2019,14 +2025,6 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2218,7 +2216,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2354,15 +2352,208 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="232">
+  <dxfs count="260">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5431,16 +5622,16 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:M169">
-    <cfRule type="expression" dxfId="231" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="259" priority="1" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="230" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="258" priority="2" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="229" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="257" priority="3" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="228" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="256" priority="4" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6615,16 +6806,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L185">
-    <cfRule type="expression" dxfId="227" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="255" priority="21" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="226" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="254" priority="22" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="225" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="253" priority="23" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="224" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="252" priority="24" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7584,8 +7775,8 @@
         <v>217</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="45" t="s">
-        <v>399</v>
+      <c r="D32" s="35" t="s">
+        <v>400</v>
       </c>
       <c r="E32" s="8">
         <v>2.2000000000000002</v>
@@ -7603,7 +7794,9 @@
         <v>4</v>
       </c>
       <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
+      <c r="K32" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="L32" s="8"/>
       <c r="M32" s="14"/>
       <c r="O32" t="s">
@@ -7872,8 +8065,12 @@
       <c r="I41" s="8">
         <v>40</v>
       </c>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
+      <c r="J41" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="L41" s="8"/>
       <c r="M41" s="14"/>
     </row>
@@ -8192,8 +8389,8 @@
         <v>299</v>
       </c>
       <c r="C51" s="8"/>
-      <c r="D51" s="45" t="s">
-        <v>398</v>
+      <c r="D51" s="35" t="s">
+        <v>399</v>
       </c>
       <c r="E51" s="8">
         <v>2.2000000000000002</v>
@@ -8214,7 +8411,7 @@
         <v>388</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>349</v>
+        <v>79</v>
       </c>
       <c r="L51" s="36">
         <v>42555</v>
@@ -8384,7 +8581,7 @@
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="35" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E57" s="8">
         <v>2.2000000000000002</v>
@@ -9272,45 +9469,87 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:C211 E2:M211 D52:D211 D2:D31 D33:D50">
-    <cfRule type="expression" dxfId="223" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="251" priority="33" stopIfTrue="1">
       <formula>$K2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="222" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="250" priority="34" stopIfTrue="1">
       <formula>$K2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="221" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="249" priority="35" stopIfTrue="1">
       <formula>$K2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="220" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="248" priority="36" stopIfTrue="1">
       <formula>OR($K2="CLOSED",$K2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:M7">
-    <cfRule type="expression" dxfId="219" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="247" priority="29" stopIfTrue="1">
       <formula>$K7="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="218" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="246" priority="30" stopIfTrue="1">
       <formula>$K7="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="217" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="245" priority="31" stopIfTrue="1">
       <formula>$K7="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="216" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="244" priority="32" stopIfTrue="1">
       <formula>OR($K7="CLOSED",$K7="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:M42">
-    <cfRule type="expression" dxfId="215" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="243" priority="13" stopIfTrue="1">
       <formula>$K42="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="214" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="242" priority="14" stopIfTrue="1">
       <formula>$K42="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="213" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="241" priority="15" stopIfTrue="1">
       <formula>$K42="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="212" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="240" priority="16" stopIfTrue="1">
       <formula>OR($K42="CLOSED",$K42="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D51">
+    <cfRule type="expression" dxfId="23" priority="9" stopIfTrue="1">
+      <formula>$K51="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="10" stopIfTrue="1">
+      <formula>$K51="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="11" stopIfTrue="1">
+      <formula>$K51="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="12" stopIfTrue="1">
+      <formula>OR($K51="CLOSED",$K51="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D32">
+    <cfRule type="expression" dxfId="15" priority="5" stopIfTrue="1">
+      <formula>$K32="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="6" stopIfTrue="1">
+      <formula>$K32="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="7" stopIfTrue="1">
+      <formula>$K32="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="8" stopIfTrue="1">
+      <formula>OR($K32="CLOSED",$K32="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D32">
+    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
+      <formula>$K32="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
+      <formula>$K32="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
+      <formula>$K32="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="4" stopIfTrue="1">
+      <formula>OR($K32="CLOSED",$K32="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -12070,744 +12309,744 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A9:M9 A32:M37">
-    <cfRule type="expression" dxfId="211" priority="233" stopIfTrue="1">
+    <cfRule type="expression" dxfId="239" priority="233" stopIfTrue="1">
       <formula>$K9="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="210" priority="234" stopIfTrue="1">
+    <cfRule type="expression" dxfId="238" priority="234" stopIfTrue="1">
       <formula>$K9="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="209" priority="235" stopIfTrue="1">
+    <cfRule type="expression" dxfId="237" priority="235" stopIfTrue="1">
       <formula>$K9="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="208" priority="236" stopIfTrue="1">
+    <cfRule type="expression" dxfId="236" priority="236" stopIfTrue="1">
       <formula>OR($K9="CLOSED",$K9="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:M10">
-    <cfRule type="expression" dxfId="207" priority="229" stopIfTrue="1">
+    <cfRule type="expression" dxfId="235" priority="229" stopIfTrue="1">
       <formula>$K10="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="206" priority="230" stopIfTrue="1">
+    <cfRule type="expression" dxfId="234" priority="230" stopIfTrue="1">
       <formula>$K10="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="205" priority="231" stopIfTrue="1">
+    <cfRule type="expression" dxfId="233" priority="231" stopIfTrue="1">
       <formula>$K10="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="204" priority="232" stopIfTrue="1">
+    <cfRule type="expression" dxfId="232" priority="232" stopIfTrue="1">
       <formula>OR($K10="CLOSED",$K10="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:M11">
-    <cfRule type="expression" dxfId="203" priority="225" stopIfTrue="1">
+    <cfRule type="expression" dxfId="231" priority="225" stopIfTrue="1">
       <formula>$K11="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="202" priority="226" stopIfTrue="1">
+    <cfRule type="expression" dxfId="230" priority="226" stopIfTrue="1">
       <formula>$K11="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="201" priority="227" stopIfTrue="1">
+    <cfRule type="expression" dxfId="229" priority="227" stopIfTrue="1">
       <formula>$K11="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="200" priority="228" stopIfTrue="1">
+    <cfRule type="expression" dxfId="228" priority="228" stopIfTrue="1">
       <formula>OR($K11="CLOSED",$K11="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:M12">
-    <cfRule type="expression" dxfId="199" priority="221" stopIfTrue="1">
+    <cfRule type="expression" dxfId="227" priority="221" stopIfTrue="1">
       <formula>$K12="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="198" priority="222" stopIfTrue="1">
+    <cfRule type="expression" dxfId="226" priority="222" stopIfTrue="1">
       <formula>$K12="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="197" priority="223" stopIfTrue="1">
+    <cfRule type="expression" dxfId="225" priority="223" stopIfTrue="1">
       <formula>$K12="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="196" priority="224" stopIfTrue="1">
+    <cfRule type="expression" dxfId="224" priority="224" stopIfTrue="1">
       <formula>OR($K12="CLOSED",$K12="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:M13">
-    <cfRule type="expression" dxfId="195" priority="217" stopIfTrue="1">
+    <cfRule type="expression" dxfId="223" priority="217" stopIfTrue="1">
       <formula>$K13="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="194" priority="218" stopIfTrue="1">
+    <cfRule type="expression" dxfId="222" priority="218" stopIfTrue="1">
       <formula>$K13="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="193" priority="219" stopIfTrue="1">
+    <cfRule type="expression" dxfId="221" priority="219" stopIfTrue="1">
       <formula>$K13="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="192" priority="220" stopIfTrue="1">
+    <cfRule type="expression" dxfId="220" priority="220" stopIfTrue="1">
       <formula>OR($K13="CLOSED",$K13="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:M14">
-    <cfRule type="expression" dxfId="191" priority="213" stopIfTrue="1">
+    <cfRule type="expression" dxfId="219" priority="213" stopIfTrue="1">
       <formula>$K14="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="190" priority="214" stopIfTrue="1">
+    <cfRule type="expression" dxfId="218" priority="214" stopIfTrue="1">
       <formula>$K14="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="189" priority="215" stopIfTrue="1">
+    <cfRule type="expression" dxfId="217" priority="215" stopIfTrue="1">
       <formula>$K14="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="188" priority="216" stopIfTrue="1">
+    <cfRule type="expression" dxfId="216" priority="216" stopIfTrue="1">
       <formula>OR($K14="CLOSED",$K14="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:M15">
-    <cfRule type="expression" dxfId="187" priority="209" stopIfTrue="1">
+    <cfRule type="expression" dxfId="215" priority="209" stopIfTrue="1">
       <formula>$K15="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="186" priority="210" stopIfTrue="1">
+    <cfRule type="expression" dxfId="214" priority="210" stopIfTrue="1">
       <formula>$K15="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="185" priority="211" stopIfTrue="1">
+    <cfRule type="expression" dxfId="213" priority="211" stopIfTrue="1">
       <formula>$K15="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="184" priority="212" stopIfTrue="1">
+    <cfRule type="expression" dxfId="212" priority="212" stopIfTrue="1">
       <formula>OR($K15="CLOSED",$K15="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:M16">
-    <cfRule type="expression" dxfId="183" priority="205" stopIfTrue="1">
+    <cfRule type="expression" dxfId="211" priority="205" stopIfTrue="1">
       <formula>$K16="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="182" priority="206" stopIfTrue="1">
+    <cfRule type="expression" dxfId="210" priority="206" stopIfTrue="1">
       <formula>$K16="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="181" priority="207" stopIfTrue="1">
+    <cfRule type="expression" dxfId="209" priority="207" stopIfTrue="1">
       <formula>$K16="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="180" priority="208" stopIfTrue="1">
+    <cfRule type="expression" dxfId="208" priority="208" stopIfTrue="1">
       <formula>OR($K16="CLOSED",$K16="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:M17">
-    <cfRule type="expression" dxfId="179" priority="201" stopIfTrue="1">
+    <cfRule type="expression" dxfId="207" priority="201" stopIfTrue="1">
       <formula>$K17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="178" priority="202" stopIfTrue="1">
+    <cfRule type="expression" dxfId="206" priority="202" stopIfTrue="1">
       <formula>$K17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="177" priority="203" stopIfTrue="1">
+    <cfRule type="expression" dxfId="205" priority="203" stopIfTrue="1">
       <formula>$K17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="176" priority="204" stopIfTrue="1">
+    <cfRule type="expression" dxfId="204" priority="204" stopIfTrue="1">
       <formula>OR($K17="CLOSED",$K17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:M18">
-    <cfRule type="expression" dxfId="175" priority="197" stopIfTrue="1">
+    <cfRule type="expression" dxfId="203" priority="197" stopIfTrue="1">
       <formula>$K18="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="174" priority="198" stopIfTrue="1">
+    <cfRule type="expression" dxfId="202" priority="198" stopIfTrue="1">
       <formula>$K18="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="199" stopIfTrue="1">
+    <cfRule type="expression" dxfId="201" priority="199" stopIfTrue="1">
       <formula>$K18="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="172" priority="200" stopIfTrue="1">
+    <cfRule type="expression" dxfId="200" priority="200" stopIfTrue="1">
       <formula>OR($K18="CLOSED",$K18="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:M19">
-    <cfRule type="expression" dxfId="171" priority="193" stopIfTrue="1">
+    <cfRule type="expression" dxfId="199" priority="193" stopIfTrue="1">
       <formula>$K19="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="170" priority="194" stopIfTrue="1">
+    <cfRule type="expression" dxfId="198" priority="194" stopIfTrue="1">
       <formula>$K19="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="169" priority="195" stopIfTrue="1">
+    <cfRule type="expression" dxfId="197" priority="195" stopIfTrue="1">
       <formula>$K19="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="168" priority="196" stopIfTrue="1">
+    <cfRule type="expression" dxfId="196" priority="196" stopIfTrue="1">
       <formula>OR($K19="CLOSED",$K19="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:M20">
-    <cfRule type="expression" dxfId="167" priority="189" stopIfTrue="1">
+    <cfRule type="expression" dxfId="195" priority="189" stopIfTrue="1">
       <formula>$K20="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="166" priority="190" stopIfTrue="1">
+    <cfRule type="expression" dxfId="194" priority="190" stopIfTrue="1">
       <formula>$K20="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="165" priority="191" stopIfTrue="1">
+    <cfRule type="expression" dxfId="193" priority="191" stopIfTrue="1">
       <formula>$K20="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="164" priority="192" stopIfTrue="1">
+    <cfRule type="expression" dxfId="192" priority="192" stopIfTrue="1">
       <formula>OR($K20="CLOSED",$K20="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:M21">
-    <cfRule type="expression" dxfId="163" priority="185" stopIfTrue="1">
+    <cfRule type="expression" dxfId="191" priority="185" stopIfTrue="1">
       <formula>$K21="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="162" priority="186" stopIfTrue="1">
+    <cfRule type="expression" dxfId="190" priority="186" stopIfTrue="1">
       <formula>$K21="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="161" priority="187" stopIfTrue="1">
+    <cfRule type="expression" dxfId="189" priority="187" stopIfTrue="1">
       <formula>$K21="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="160" priority="188" stopIfTrue="1">
+    <cfRule type="expression" dxfId="188" priority="188" stopIfTrue="1">
       <formula>OR($K21="CLOSED",$K21="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:M23">
-    <cfRule type="expression" dxfId="159" priority="181" stopIfTrue="1">
+    <cfRule type="expression" dxfId="187" priority="181" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="158" priority="182" stopIfTrue="1">
+    <cfRule type="expression" dxfId="186" priority="182" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="157" priority="183" stopIfTrue="1">
+    <cfRule type="expression" dxfId="185" priority="183" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="156" priority="184" stopIfTrue="1">
+    <cfRule type="expression" dxfId="184" priority="184" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:I22">
-    <cfRule type="expression" dxfId="155" priority="177" stopIfTrue="1">
+    <cfRule type="expression" dxfId="183" priority="177" stopIfTrue="1">
       <formula>$K22="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="154" priority="178" stopIfTrue="1">
+    <cfRule type="expression" dxfId="182" priority="178" stopIfTrue="1">
       <formula>$K22="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="153" priority="179" stopIfTrue="1">
+    <cfRule type="expression" dxfId="181" priority="179" stopIfTrue="1">
       <formula>$K22="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="152" priority="180" stopIfTrue="1">
+    <cfRule type="expression" dxfId="180" priority="180" stopIfTrue="1">
       <formula>OR($K22="CLOSED",$K22="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="151" priority="173" stopIfTrue="1">
+    <cfRule type="expression" dxfId="179" priority="173" stopIfTrue="1">
       <formula>$K23="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="150" priority="174" stopIfTrue="1">
+    <cfRule type="expression" dxfId="178" priority="174" stopIfTrue="1">
       <formula>$K23="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="149" priority="175" stopIfTrue="1">
+    <cfRule type="expression" dxfId="177" priority="175" stopIfTrue="1">
       <formula>$K23="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="148" priority="176" stopIfTrue="1">
+    <cfRule type="expression" dxfId="176" priority="176" stopIfTrue="1">
       <formula>OR($K23="CLOSED",$K23="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:M25">
-    <cfRule type="expression" dxfId="147" priority="169" stopIfTrue="1">
+    <cfRule type="expression" dxfId="175" priority="169" stopIfTrue="1">
       <formula>$K24="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="146" priority="170" stopIfTrue="1">
+    <cfRule type="expression" dxfId="174" priority="170" stopIfTrue="1">
       <formula>$K24="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="145" priority="171" stopIfTrue="1">
+    <cfRule type="expression" dxfId="173" priority="171" stopIfTrue="1">
       <formula>$K24="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="144" priority="172" stopIfTrue="1">
+    <cfRule type="expression" dxfId="172" priority="172" stopIfTrue="1">
       <formula>OR($K24="CLOSED",$K24="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="143" priority="165" stopIfTrue="1">
+    <cfRule type="expression" dxfId="171" priority="165" stopIfTrue="1">
       <formula>$K25="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="142" priority="166" stopIfTrue="1">
+    <cfRule type="expression" dxfId="170" priority="166" stopIfTrue="1">
       <formula>$K25="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="141" priority="167" stopIfTrue="1">
+    <cfRule type="expression" dxfId="169" priority="167" stopIfTrue="1">
       <formula>$K25="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="140" priority="168" stopIfTrue="1">
+    <cfRule type="expression" dxfId="168" priority="168" stopIfTrue="1">
       <formula>OR($K25="CLOSED",$K25="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:M26">
-    <cfRule type="expression" dxfId="139" priority="161" stopIfTrue="1">
+    <cfRule type="expression" dxfId="167" priority="161" stopIfTrue="1">
       <formula>$K26="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="162" stopIfTrue="1">
+    <cfRule type="expression" dxfId="166" priority="162" stopIfTrue="1">
       <formula>$K26="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="137" priority="163" stopIfTrue="1">
+    <cfRule type="expression" dxfId="165" priority="163" stopIfTrue="1">
       <formula>$K26="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="164" stopIfTrue="1">
+    <cfRule type="expression" dxfId="164" priority="164" stopIfTrue="1">
       <formula>OR($K26="CLOSED",$K26="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:M28">
-    <cfRule type="expression" dxfId="135" priority="157" stopIfTrue="1">
+    <cfRule type="expression" dxfId="163" priority="157" stopIfTrue="1">
       <formula>$K27="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="158" stopIfTrue="1">
+    <cfRule type="expression" dxfId="162" priority="158" stopIfTrue="1">
       <formula>$K27="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="133" priority="159" stopIfTrue="1">
+    <cfRule type="expression" dxfId="161" priority="159" stopIfTrue="1">
       <formula>$K27="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="160" stopIfTrue="1">
+    <cfRule type="expression" dxfId="160" priority="160" stopIfTrue="1">
       <formula>OR($K27="CLOSED",$K27="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M30">
-    <cfRule type="expression" dxfId="131" priority="153" stopIfTrue="1">
+    <cfRule type="expression" dxfId="159" priority="153" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="154" stopIfTrue="1">
+    <cfRule type="expression" dxfId="158" priority="154" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="155" stopIfTrue="1">
+    <cfRule type="expression" dxfId="157" priority="155" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="128" priority="156" stopIfTrue="1">
+    <cfRule type="expression" dxfId="156" priority="156" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:M29">
-    <cfRule type="expression" dxfId="127" priority="149" stopIfTrue="1">
+    <cfRule type="expression" dxfId="155" priority="149" stopIfTrue="1">
       <formula>$K29="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="150" stopIfTrue="1">
+    <cfRule type="expression" dxfId="154" priority="150" stopIfTrue="1">
       <formula>$K29="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="151" stopIfTrue="1">
+    <cfRule type="expression" dxfId="153" priority="151" stopIfTrue="1">
       <formula>$K29="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="152" stopIfTrue="1">
+    <cfRule type="expression" dxfId="152" priority="152" stopIfTrue="1">
       <formula>OR($K29="CLOSED",$K29="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:M31">
-    <cfRule type="expression" dxfId="123" priority="145" stopIfTrue="1">
+    <cfRule type="expression" dxfId="151" priority="145" stopIfTrue="1">
       <formula>$K31="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="146" stopIfTrue="1">
+    <cfRule type="expression" dxfId="150" priority="146" stopIfTrue="1">
       <formula>$K31="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="147" stopIfTrue="1">
+    <cfRule type="expression" dxfId="149" priority="147" stopIfTrue="1">
       <formula>$K31="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="148" stopIfTrue="1">
+    <cfRule type="expression" dxfId="148" priority="148" stopIfTrue="1">
       <formula>OR($K31="CLOSED",$K31="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:M38">
-    <cfRule type="expression" dxfId="119" priority="117" stopIfTrue="1">
+    <cfRule type="expression" dxfId="147" priority="117" stopIfTrue="1">
       <formula>$K38="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="118" stopIfTrue="1">
+    <cfRule type="expression" dxfId="146" priority="118" stopIfTrue="1">
       <formula>$K38="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="119" stopIfTrue="1">
+    <cfRule type="expression" dxfId="145" priority="119" stopIfTrue="1">
       <formula>$K38="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="120" stopIfTrue="1">
+    <cfRule type="expression" dxfId="144" priority="120" stopIfTrue="1">
       <formula>OR($K38="CLOSED",$K38="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:M39">
-    <cfRule type="expression" dxfId="115" priority="113" stopIfTrue="1">
+    <cfRule type="expression" dxfId="143" priority="113" stopIfTrue="1">
       <formula>$K39="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="114" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="114" stopIfTrue="1">
       <formula>$K39="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="115" stopIfTrue="1">
+    <cfRule type="expression" dxfId="141" priority="115" stopIfTrue="1">
       <formula>$K39="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="116" stopIfTrue="1">
+    <cfRule type="expression" dxfId="140" priority="116" stopIfTrue="1">
       <formula>OR($K39="CLOSED",$K39="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:M40">
-    <cfRule type="expression" dxfId="111" priority="109" stopIfTrue="1">
+    <cfRule type="expression" dxfId="139" priority="109" stopIfTrue="1">
       <formula>$K40="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="110" stopIfTrue="1">
+    <cfRule type="expression" dxfId="138" priority="110" stopIfTrue="1">
       <formula>$K40="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="111" stopIfTrue="1">
+    <cfRule type="expression" dxfId="137" priority="111" stopIfTrue="1">
       <formula>$K40="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="112" stopIfTrue="1">
+    <cfRule type="expression" dxfId="136" priority="112" stopIfTrue="1">
       <formula>OR($K40="CLOSED",$K40="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:M41">
-    <cfRule type="expression" dxfId="107" priority="105" stopIfTrue="1">
+    <cfRule type="expression" dxfId="135" priority="105" stopIfTrue="1">
       <formula>$K41="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="106" stopIfTrue="1">
+    <cfRule type="expression" dxfId="134" priority="106" stopIfTrue="1">
       <formula>$K41="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="107" stopIfTrue="1">
+    <cfRule type="expression" dxfId="133" priority="107" stopIfTrue="1">
       <formula>$K41="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="108" stopIfTrue="1">
+    <cfRule type="expression" dxfId="132" priority="108" stopIfTrue="1">
       <formula>OR($K41="CLOSED",$K41="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:M42">
-    <cfRule type="expression" dxfId="103" priority="101" stopIfTrue="1">
+    <cfRule type="expression" dxfId="131" priority="101" stopIfTrue="1">
       <formula>$K42="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="102" stopIfTrue="1">
+    <cfRule type="expression" dxfId="130" priority="102" stopIfTrue="1">
       <formula>$K42="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="103" stopIfTrue="1">
+    <cfRule type="expression" dxfId="129" priority="103" stopIfTrue="1">
       <formula>$K42="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="104" stopIfTrue="1">
+    <cfRule type="expression" dxfId="128" priority="104" stopIfTrue="1">
       <formula>OR($K42="CLOSED",$K42="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:M44">
-    <cfRule type="expression" dxfId="99" priority="97" stopIfTrue="1">
+    <cfRule type="expression" dxfId="127" priority="97" stopIfTrue="1">
       <formula>$K43="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="98" stopIfTrue="1">
+    <cfRule type="expression" dxfId="126" priority="98" stopIfTrue="1">
       <formula>$K43="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="99" stopIfTrue="1">
+    <cfRule type="expression" dxfId="125" priority="99" stopIfTrue="1">
       <formula>$K43="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="100" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="100" stopIfTrue="1">
       <formula>OR($K43="CLOSED",$K43="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45:M46">
-    <cfRule type="expression" dxfId="95" priority="93" stopIfTrue="1">
+    <cfRule type="expression" dxfId="123" priority="93" stopIfTrue="1">
       <formula>$K45="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="94" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="94" stopIfTrue="1">
       <formula>$K45="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="95" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="95" stopIfTrue="1">
       <formula>$K45="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="96" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="96" stopIfTrue="1">
       <formula>OR($K45="CLOSED",$K45="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:M47">
-    <cfRule type="expression" dxfId="91" priority="89" stopIfTrue="1">
+    <cfRule type="expression" dxfId="119" priority="89" stopIfTrue="1">
       <formula>$K47="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="90" stopIfTrue="1">
       <formula>$K47="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="91" stopIfTrue="1">
+    <cfRule type="expression" dxfId="117" priority="91" stopIfTrue="1">
       <formula>$K47="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="92" stopIfTrue="1">
+    <cfRule type="expression" dxfId="116" priority="92" stopIfTrue="1">
       <formula>OR($K47="CLOSED",$K47="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:M48">
-    <cfRule type="expression" dxfId="87" priority="85" stopIfTrue="1">
+    <cfRule type="expression" dxfId="115" priority="85" stopIfTrue="1">
       <formula>$K48="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="86" stopIfTrue="1">
+    <cfRule type="expression" dxfId="114" priority="86" stopIfTrue="1">
       <formula>$K48="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="87" stopIfTrue="1">
+    <cfRule type="expression" dxfId="113" priority="87" stopIfTrue="1">
       <formula>$K48="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="88" stopIfTrue="1">
+    <cfRule type="expression" dxfId="112" priority="88" stopIfTrue="1">
       <formula>OR($K48="CLOSED",$K48="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:M49">
-    <cfRule type="expression" dxfId="83" priority="81" stopIfTrue="1">
+    <cfRule type="expression" dxfId="111" priority="81" stopIfTrue="1">
       <formula>$K49="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="82" stopIfTrue="1">
+    <cfRule type="expression" dxfId="110" priority="82" stopIfTrue="1">
       <formula>$K49="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="83" stopIfTrue="1">
+    <cfRule type="expression" dxfId="109" priority="83" stopIfTrue="1">
       <formula>$K49="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="84" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="84" stopIfTrue="1">
       <formula>OR($K49="CLOSED",$K49="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:M50">
-    <cfRule type="expression" dxfId="79" priority="77" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="77" stopIfTrue="1">
       <formula>$K50="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="78" stopIfTrue="1">
+    <cfRule type="expression" dxfId="106" priority="78" stopIfTrue="1">
       <formula>$K50="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="79" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="79" stopIfTrue="1">
       <formula>$K50="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="80" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="80" stopIfTrue="1">
       <formula>OR($K50="CLOSED",$K50="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:M51">
-    <cfRule type="expression" dxfId="75" priority="73" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="73" stopIfTrue="1">
       <formula>$K51="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="74" stopIfTrue="1">
       <formula>$K51="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="75" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="75" stopIfTrue="1">
       <formula>$K51="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="76" stopIfTrue="1">
       <formula>OR($K51="CLOSED",$K51="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:M52">
-    <cfRule type="expression" dxfId="71" priority="69" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="69" stopIfTrue="1">
       <formula>$K52="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="70" stopIfTrue="1">
       <formula>$K52="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="71" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="71" stopIfTrue="1">
       <formula>$K52="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="72" stopIfTrue="1">
       <formula>OR($K52="CLOSED",$K52="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:M53">
-    <cfRule type="expression" dxfId="67" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="65" stopIfTrue="1">
       <formula>$K53="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="66" stopIfTrue="1">
       <formula>$K53="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="67" stopIfTrue="1">
       <formula>$K53="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="68" stopIfTrue="1">
       <formula>OR($K53="CLOSED",$K53="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:M54">
-    <cfRule type="expression" dxfId="63" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="61" stopIfTrue="1">
       <formula>$K54="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="62" stopIfTrue="1">
       <formula>$K54="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="63" stopIfTrue="1">
       <formula>$K54="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="64" stopIfTrue="1">
       <formula>OR($K54="CLOSED",$K54="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:M55">
-    <cfRule type="expression" dxfId="59" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="57" stopIfTrue="1">
       <formula>$K55="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="58" stopIfTrue="1">
       <formula>$K55="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="59" stopIfTrue="1">
       <formula>$K55="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="60" stopIfTrue="1">
       <formula>OR($K55="CLOSED",$K55="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56:M56">
-    <cfRule type="expression" dxfId="55" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="53" stopIfTrue="1">
       <formula>$K56="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="54" stopIfTrue="1">
       <formula>$K56="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="55" stopIfTrue="1">
       <formula>$K56="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="56" stopIfTrue="1">
       <formula>OR($K56="CLOSED",$K56="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:M57">
-    <cfRule type="expression" dxfId="51" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="49" stopIfTrue="1">
       <formula>$K57="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="50" stopIfTrue="1">
       <formula>$K57="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="51" stopIfTrue="1">
       <formula>$K57="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="52" stopIfTrue="1">
       <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:M57">
-    <cfRule type="expression" dxfId="47" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="45" stopIfTrue="1">
       <formula>$K57="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="46" stopIfTrue="1">
       <formula>$K57="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="47" stopIfTrue="1">
       <formula>$K57="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="48" stopIfTrue="1">
       <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E57">
-    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="41" stopIfTrue="1">
       <formula>$K57="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="42" stopIfTrue="1">
       <formula>$K57="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="43" stopIfTrue="1">
       <formula>$K57="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="44" stopIfTrue="1">
       <formula>OR($K57="CLOSED",$K57="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:M58">
-    <cfRule type="expression" dxfId="39" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="37" stopIfTrue="1">
       <formula>$K58="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="38" stopIfTrue="1">
       <formula>$K58="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="39" stopIfTrue="1">
       <formula>$K58="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="40" stopIfTrue="1">
       <formula>OR($K58="CLOSED",$K58="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:M59">
-    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="33" stopIfTrue="1">
       <formula>$K59="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="34" stopIfTrue="1">
       <formula>$K59="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="35" stopIfTrue="1">
       <formula>$K59="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="36" stopIfTrue="1">
       <formula>OR($K59="CLOSED",$K59="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:M59">
-    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="29" stopIfTrue="1">
       <formula>$K59="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="30" stopIfTrue="1">
       <formula>$K59="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="31" stopIfTrue="1">
       <formula>$K59="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="32" stopIfTrue="1">
       <formula>OR($K59="CLOSED",$K59="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60:M60">
-    <cfRule type="expression" dxfId="27" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="25" stopIfTrue="1">
       <formula>$K60="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="26" stopIfTrue="1">
       <formula>$K60="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="27" stopIfTrue="1">
       <formula>$K60="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="28" stopIfTrue="1">
       <formula>OR($K60="CLOSED",$K60="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:M61">
-    <cfRule type="expression" dxfId="23" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="21" stopIfTrue="1">
       <formula>$K61="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="22" stopIfTrue="1">
       <formula>$K61="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="23" stopIfTrue="1">
       <formula>$K61="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="24" stopIfTrue="1">
       <formula>OR($K61="CLOSED",$K61="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A62:M62">
-    <cfRule type="expression" dxfId="19" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="17" stopIfTrue="1">
       <formula>$K62="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="18" stopIfTrue="1">
       <formula>$K62="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="19" stopIfTrue="1">
       <formula>$K62="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="20" stopIfTrue="1">
       <formula>OR($K62="CLOSED",$K62="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:M63">
-    <cfRule type="expression" dxfId="15" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="13" stopIfTrue="1">
       <formula>$K63="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="14" stopIfTrue="1">
       <formula>$K63="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="15" stopIfTrue="1">
       <formula>$K63="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="16" stopIfTrue="1">
       <formula>OR($K63="CLOSED",$K63="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:M64">
-    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="9" stopIfTrue="1">
       <formula>$K64="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="10" stopIfTrue="1">
       <formula>$K64="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="11" stopIfTrue="1">
       <formula>$K64="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="12" stopIfTrue="1">
       <formula>OR($K64="CLOSED",$K64="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A65:M65">
-    <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="5" stopIfTrue="1">
       <formula>$K65="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="6" stopIfTrue="1">
       <formula>$K65="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="7" stopIfTrue="1">
       <formula>$K65="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="8" stopIfTrue="1">
       <formula>OR($K65="CLOSED",$K65="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66:M86">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="1" stopIfTrue="1">
       <formula>$K66="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="2" stopIfTrue="1">
       <formula>$K66="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="3" stopIfTrue="1">
       <formula>$K66="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="4" stopIfTrue="1">
       <formula>OR($K66="CLOSED",$K66="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB任务表.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" co